--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0013.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0013.xlsx
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>"Chúng tôi tin rằng các ngươi đã hiểu được bản chất của Lament, và cư dân Solaris đã vượt xa Etheric Seaic, tiến vào những vùng đất xa xôi."</t>
+          <t>"Chúng tôi tin rằng các ngươi đã hiểu được bản chất của Lament, và cư dân Solaris đã vượt xa Biển Etheric, tiến vào những vùng đất xa xôi."</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Bên trong chỉ toàn là những Creatures Tàn Dư phân tán khắp toa như những vì sao. Like một vùng đất bị lãng quên, hay những vách đá xa xôi, khung cảnh này gợi nhớ đến những không gian mà thời gian dường như trôi chậm—cái cũ thì mục rữa, cái mới thì chưa thức tỉnh.</t>
+          <t>Bên trong chỉ toàn là những Sinh Vật Tàn Dư phân tán khắp toa như những vì sao. Giống như một vùng đất bị lãng quên, hay những vách đá xa xôi, khung cảnh này gợi nhớ đến những không gian mà thời gian dường như trôi chậm—cái cũ thì mục rữa, cái mới thì chưa thức tỉnh.</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Khi mọi thứ đã ổn định, cậu hãy nghỉ ngơi thật tốt ở khu rừng này. From now on, những "vầng trăng" này sẽ thay thế ánh trăng thật, tắm rừng cây trong ánh sáng dịu dàng. Cậu lặng lẽ ước một điều gì đó trong lòng.</t>
+          <t>Khi mọi thứ đã ổn định, cậu hãy nghỉ ngơi thật tốt ở khu rừng này. Từ giờ trở đi, những "vầng trăng" này sẽ thay thế ánh trăng thật, tắm rừng cây trong ánh sáng dịu dàng. Cậu lặng lẽ ước một điều gì đó trong lòng.</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Fallacy of Không Return sử dụng dữ liệu để triệu hồi các Tacet Discord cấp Overlord &lt;color=#b72924ff&gt;Lampylumen Myriad, Inferno Rider và Impermanence Heron&lt;/color&gt; chiến đấu cho nó.</t>
+          <t>Fallacy of No Return sử dụng dữ liệu để triệu hồi các Tacet Discord cấp Overlord &lt;color=#b72924ff&gt;Lampylumen Myriad, Inferno Rider và Impermanence Heron&lt;/color&gt; chiến đấu cho nó.</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy Sự Tiến Hóa làm khả năng cốt lõi. Khi đạt đủ điều kiện Tiến Hóa, sản lượng Daily Coupon của chúng sẽ tăng lên.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy Sự Tiến Hóa làm khả năng cốt lõi. Khi đạt đủ điều kiện Tiến Hóa, sản lượng Phiếu Hằng Ngày của chúng sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy Sự Nuốt Chửng làm khả năng cốt lõi. Một số Resonator sẽ trở nên mạnh mẽ hơn trong giấc mơ thông qua Sự Nuốt Chửng. Khi một Resonator mạnh hấp thụ kẻ yếu hơn, sản lượng Daily Coupon của nó sẽ tăng lên.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy Sự Nuốt Chửng làm khả năng cốt lõi. Một số Cộng Hưởng Giả sẽ trở nên mạnh mẽ hơn trong giấc mơ thông qua Sự Nuốt Chửng. Khi một Cộng Hưởng Giả mạnh hấp thụ kẻ yếu hơn, sản lượng Phiếu Hằng Ngày của nó sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Lịch sử Second Coming of Solaris có nhắc đến một nhóm nghiên cứu tuyệt mật, và các nhà thiết kế đã cố tái hiện căn cứ của họ trong game. Đáng tiếc là nó được giấu quá kỹ đến nỗi chẳng ai biết nó trông như thế nào.</t>
+          <t>Lịch sử Sự Trở Lại Của Solaris có nhắc đến một nhóm nghiên cứu tuyệt mật, và các nhà thiết kế đã cố tái hiện căn cứ của họ trong game. Đáng tiếc là nó được giấu quá kỹ đến nỗi chẳng ai biết nó trông như thế nào.</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Mỗi Namipon thất lạc đều phản ánh một khía cạnh khác của bản thể gốc. Ví dụ như con này, nó từng mơ trở thành nhân viên ngân hàng. Một cư dân tốt bụng kể rằng nó từng xuất hiện ở ngã ba đường trong &lt;color=#d08c0f&gt;Sakura Quarter&lt;/color&gt;. Bạn có thể đến đó tìm thử.</t>
+          <t>Mỗi Namipon thất lạc đều phản ánh một khía cạnh khác của bản thể gốc. Ví dụ như con này, nó từng mơ trở thành nhân viên ngân hàng. Một cư dân tốt bụng kể rằng nó từng xuất hiện ở ngã ba đường trong &lt;color=#d08c0f&gt;Khu Sakura&lt;/color&gt;. Bạn có thể đến đó tìm thử.</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Ta chẳng hiểu nổi cách nói chuyện của thằng Namipon này. Lần trước ta thấy nó lang thang &lt;color=#d08c0f&gt;ở công viên dân cư gần khu Sakura&lt;/color&gt;. À, còn mấy tấm biển quảng cáo trước cửa hàng kia... Sao lại không cùng phong cách nhỉ?</t>
+          <t>Tao chẳng hiểu nổi cách nói chuyện của thằng Namipon này. Lần trước tao thấy nó lang thang &lt;color=#d08c0f&gt;ở công viên dân cư gần khu Sakura&lt;/color&gt;. À, còn mấy tấm biển quảng cáo trước cửa hàng kia... Sao lại không cùng phong cách nhỉ?</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Thật lòng mà nói, thằng Namipon này có lẽ là đứa dũng cảm nhất trong đám... dù tất nhiên ta vẫn hơn. Lần cuối thấy nó ở &lt;color=#d08c0f&gt;Meishin Passageway&lt;/color&gt;, nơi mà hầu hết các truyền thuyết đô thị của Honami đều bắt nguồn.</t>
+          <t>Thật lòng mà nói, thằng Namipon này có lẽ là đứa dũng cảm nhất trong đám... dù tất nhiên tao vẫn hơn. Lần cuối thấy nó ở &lt;color=#d08c0f&gt;Hành Lang Meishin&lt;/color&gt;, nơi mà hầu hết các truyền thuyết đô thị của Honami đều bắt nguồn.</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Cái này làm việc ở &lt;color=#d08c0f&gt;Commercial District&lt;/color&gt; của Honami, nơi san sát những tòa nhà văn phòng và trung tâm mua sắm. Nhưng giữa rừng bê tông ấy, lại có một &lt;color=#d08c0f&gt;cây anh đào khổng lồ&lt;/color&gt; cao đến mức cành lá che kín cả bầu trời... Làm sao nó có thể lớn đến thế nhỉ?</t>
+          <t>Cái này làm việc ở &lt;color=#d08c0f&gt;Khu Thương mại&lt;/color&gt; của Honami, nơi san sát những tòa nhà văn phòng và trung tâm mua sắm. Nhưng giữa rừng bê tông ấy, lại có một &lt;color=#d08c0f&gt;cây anh đào khổng lồ&lt;/color&gt; cao đến mức cành lá che kín cả bầu trời... Làm sao nó có thể lớn đến thế nhỉ?</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Là một thám tử chuyên nghiệp, tôi có thể khẳng định chắc nịch rằng con Namipon này đang trốn trong &lt;color=#d08c0f&gt;Meishin Passageway&lt;/color&gt;—nơi gắn liền với vô số truyền thuyết đô thị. Nó còn thích để lại những câu đố mà chỉ có nó mới giải nổi. Nếu thấy &lt;color=#d08c0f&gt;vật gì kỳ lạ xung quanh&lt;/color&gt;, chắc chắn là do nó làm đấy.</t>
+          <t>Là một thám tử chuyên nghiệp, tôi có thể khẳng định chắc nịch rằng con Namipon này đang trốn trong &lt;color=#d08c0f&gt;Hành Lang Meishin&lt;/color&gt;—nơi gắn liền với vô số truyền thuyết đô thị. Nó còn thích để lại những câu đố mà chỉ có nó mới giải nổi. Nếu thấy &lt;color=#d08c0f&gt;vật gì kỳ lạ xung quanh&lt;/color&gt;, chắc chắn là do nó làm đấy.</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Một đứa bạn capybara của tớ thề là đã thấy nó ở &lt;color=#d08c0f&gt;phố dưới lòng đất&lt;/color&gt;, bị một con Discord đuổi theo. Nhưng tụi nó gọi nó là Học Sinh May Mắn Tột Đỉnh, nên chắc cũng chẳng sao... Tớ đoán vậy.</t>
+          <t>Một đứa bạn capybara của tớ thề là đã thấy nó ở &lt;color=#d08c0f&gt;phố dưới lòng đất&lt;/color&gt;, bị một con Tacet Discord đuổi theo. Nhưng tụi nó gọi nó là Học Sinh May Mắn Tột Đỉnh, nên chắc cũng chẳng sao... Tớ đoán vậy.</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Gia tộc Nami từng thống trị con phố ngầm. Người ta nói nếu thắp đèn trong bóng tối, sẽ có người đến giúp đỡ. Nếu cậu đang tìm kiếm tên yakuza Namipon, hãy thử vận may ở &lt;color=#d08c0f&gt;Garden Seisen&lt;/color&gt;. Nơi đó nằm sâu trong con phố ngầm.</t>
+          <t>Gia tộc Nami từng thống trị con phố ngầm. Người ta nói nếu thắp đèn trong bóng tối, sẽ có người đến giúp đỡ. Nếu cậu đang tìm kiếm tên yakuza Namipon, hãy thử vận may ở &lt;color=#d08c0f&gt;Vườn Seisen&lt;/color&gt;. Nơi đó nằm sâu trong con phố ngầm.</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Not long ago, nó để lại lời nhắn bảo đi công viên luyện tập ninja. Sau đó thì biệt tăm. Nhưng nghĩ lại, cậu có để ý mấy bức tượng Namipon mới dưới &lt;color=#d08c0f&gt;cây tử đằng ở Công viên Trung tâm&lt;/color&gt; không? Không biết có phải do nó làm không nhỉ?</t>
+          <t>Cách đây không lâu, nó để lại lời nhắn bảo đi công viên luyện tập ninja. Sau đó thì biệt tăm. Nhưng nghĩ lại, cậu có để ý mấy bức tượng Namipon mới dưới &lt;color=#d08c0f&gt;cây tử đằng ở Công viên Trung tâm&lt;/color&gt; không? Không biết có phải do nó làm không nhỉ?</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Ngay cả trước Lời Than Thở, Meishin Passageway đã là một phần trong truyền thuyết đô thị của Honami. Theo nghĩa chặt chẽ nhất, nó là một lối đi nối hai đường hầm song song ở Khu Thương Mại, chỉ mở vào một số thời điểm trong năm. Nhiều cư dân thề rằng họ nghe thấy những âm thanh kỳ lạ, thấy những chiếc nón giao thông tự tập hợp lại, hoặc cảm nhận được một cái vỗ vai, nhưng khi quay lại thì chẳng thấy ai.
+          <t>Ngay cả trước Lời Than Thở, Hành Lang Meishin đã là một phần trong truyền thuyết đô thị của Honami. Theo nghĩa chặt chẽ nhất, nó là một lối đi nối hai đường hầm song song ở Khu Thương Mại, chỉ mở vào một số thời điểm trong năm. Nhiều cư dân thề rằng họ nghe thấy những âm thanh kỳ lạ, thấy những chiếc nón giao thông tự tập hợp lại, hoặc cảm nhận được một cái vỗ vai, nhưng khi quay lại thì chẳng thấy ai.
 Dù chính quyền thành phố khẳng định đó chỉ là một lối đi phục vụ xây dựng cũ, điều này chẳng ngăn được những kẻ tìm kiếm cảm giác mạnh. Qua nhiều năm, những câu chuyện ngày càng nhiều. Có người nói rằng mười phút bên trong đồng nghĩa với một ngày bên ngoài. Câu chuyện nổi tiếng nhất đến từ một cuộc phỏng vấn trên đài phát thanh địa phương. Một người đàn ông kể rằng hành lang đã giúp ông thực hiện ước nguyện—được gặp lại gia đình đã mất từ lâu... Bằng chứng của ông là một con thú nhồi bông Namipon phiên bản giới hạn với số seri độc nhất, từng bị thiêu hủy trong một vụ hỏa hoạn, nhưng lại xuất hiện trong hành lang.</t>
         </is>
       </c>
@@ -6045,8 +6045,8 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Hanakage Underground Street vốn là một phần của hệ thống tàu điện ngầm Honami, sau này được cải tạo thành một lối đi văn hóa với chủ đề nghệ thuật đương đại. Trước Thảm Họa Than Thở, các liên hoan phim và triển lãm hàng quý đã biến con phố này thành nơi trưng bày các tác phẩm nghệ thuật từ khắp Ashinohara. Những cửa hàng lưu niệm ở đây bán những món đồ độc nhất vô nhị chỉ có thể tìm thấy ở Honami.
-Trong số các sự kiện, triển lãm "Huyền Thoại Đô Thị Honami" hàng năm luôn thu hút đông đảo người tham dự nhất. Các tác phẩm dự thi trải dài từ những bộ phim nghiệp dư của sinh viên đến những tác phẩm của các nhiếp ảnh gia nổi tiếng thuộc Pioneer Association. Một bộ phim ngắn ẩn danh từng bị bỏ qua khi ra mắt, nhưng nhiều năm sau, nó bất ngờ trở thành đề tài tranh luận sôi nổi. Vô số cách giải thích được đưa ra khi những câu chuyện trong phim dần trở thành hiện thực, từng cái một: "Lồng Đèn Cá Di Cư", "Lối Đi Ban Phước", và "Xe Buýt Ma Nửa Đêm".</t>
+          <t>Phố Ngầm Hanakage vốn là một phần của hệ thống tàu điện ngầm Honami, sau này được cải tạo thành một lối đi văn hóa với chủ đề nghệ thuật đương đại. Trước Thảm Họa Than Thở, các liên hoan phim và triển lãm hàng quý đã biến con phố này thành nơi trưng bày các tác phẩm nghệ thuật từ khắp Ashinohara. Những cửa hàng lưu niệm ở đây bán những món đồ độc nhất vô nhị chỉ có thể tìm thấy ở Honami.
+Trong số các sự kiện, triển lãm "Huyền Thoại Đô Thị Honami" hàng năm luôn thu hút đông đảo người tham dự nhất. Các tác phẩm dự thi trải dài từ những bộ phim nghiệp dư của sinh viên đến những tác phẩm của các nhiếp ảnh gia nổi tiếng thuộc Hiệp Hội Tiên Phong. Một bộ phim ngắn ẩn danh từng bị bỏ qua khi ra mắt, nhưng nhiều năm sau, nó bất ngờ trở thành đề tài tranh luận sôi nổi. Vô số cách giải thích được đưa ra khi những câu chuyện trong phim dần trở thành hiện thực, từng cái một: "Lồng Đèn Cá Di Cư", "Lối Đi Ban Phước", và "Xe Buýt Ma Nửa Đêm".</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Trái với những gì nhiều người nhớ, công viên quanh Neon Tower thực ra có trước cả tòa tháp. Thực tế, Neon Tower được xây ở đây chính vì khu đất trống của công viên giúp giảm thiểu nhiễu sóng vô tuyến. Sau khi tòa tháp hoàn thành, Công viên Honami gốc được mở rộng thành Công viên Trung tâm Honami – biểu tượng tự hào của trung tâm thành phố. Lúc bấy giờ, đây cũng là công viên lớn nhất toàn Ashinohara.</t>
+          <t>Trái với những gì nhiều người nhớ, công viên quanh Tháp Neon thực ra có trước cả tòa tháp. Thực tế, Tháp Neon được xây ở đây chính vì khu đất trống của công viên giúp giảm thiểu nhiễu sóng vô tuyến. Sau khi tòa tháp hoàn thành, Công viên Honami gốc được mở rộng thành Công viên Trung tâm Honami – biểu tượng tự hào của trung tâm thành phố. Lúc bấy giờ, đây cũng là công viên lớn nhất toàn Ashinohara.</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6180,7 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>Hyvatia là hệ thống dò tìm đầu tiên của Spacetrek Collective được xây dựng tại Sundermere để giám sát và ổn định trạng thái năng lượng của Reactor Drive theo thời gian thực.
-Viện Nghiên Cứu đã cấy mô-đun hiệu chỉnh lỗi không-thời gian của Exostrider vào lõi của Hyvatia, cho phép nó điều chỉnh quỹ đạo của Exostrider và phát hiện các mối đe dọa ẩn trong không gian với độ chính xác cao. Do đó, Hyvatia có đủ năng lực tính toán để dự đoán vòng quay của Reactor Drive.
+Viện Nghiên cứu đã cấy mô-đun hiệu chỉnh lỗi không-thời gian của Exostrider vào lõi của Hyvatia, cho phép nó điều chỉnh quỹ đạo của Exostrider và phát hiện các mối đe dọa ẩn trong không gian với độ chính xác cao. Do đó, Hyvatia có đủ năng lực tính toán để dự đoán vòng quay của Reactor Drive.
 Chức năng cốt lõi của Hyvatia là phát hiện các dao động năng lượng bất thường hoặc nguy hiểm, thực hiện hiệu chỉnh khẩn cấp ngay lập tức, và truyền dữ liệu này về Drive để đảm bảo hoạt động ổn định.</t>
         </is>
       </c>
@@ -6249,8 +6249,8 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>Sau khi Lò Phản Ứng được Exostrider đặt lên trên Lahai-Roi, nó luôn cảnh giác cao độ với các hoạt động của Aleph-1. 
-Khi phản ứng miễn dịch của Lò Phản Ứng bị kích hoạt, một "Reactor Husk" cơ khí sẽ trỗi dậy từ đáy giếng năng lượng, với mục đích duy nhất là tiêu diệt kẻ xâm nhập bằng mọi giá. 
-Nghiên cứu của Spacetrek Collective cho thấy Reactor Husk từng là một phần của Exostrider. Cả hai đều có chung sứ mệnh chống lại mối đe dọa Threnodian và bảo vệ nền văn minh.</t>
+Khi phản ứng miễn dịch của Lò Phản Ứng bị kích hoạt, một "Vỏ Lò Phản Ứng" cơ khí sẽ trỗi dậy từ đáy giếng năng lượng, với mục đích duy nhất là tiêu diệt kẻ xâm nhập bằng mọi giá. 
+Nghiên cứu của Spacetrek Collective cho thấy Vỏ Lò Phản Ứng từng là một phần của Exostrider. Cả hai đều có chung sứ mệnh chống lại mối đe dọa Threnodian và bảo vệ nền văn minh.</t>
         </is>
       </c>
     </row>
@@ -6316,8 +6316,8 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Để đến được Lahai-Roi giữa cơn Void Storm, cậu lao vào đường hầm không gian, bị cuốn vào một chiều không gian kỳ lạ...
-Khi đến Lahai-Roi, cậu tình cờ gặp Lynae, một học sinh dẫn cậu đến Startorch Academy. Khi bắt đầu nhập học, mọi thứ về "đô thị học thuật" này dần hiện ra trước mắt. Đồng thời, những bóng tối khuấy động bên dưới Void Storm...</t>
+          <t>Để đến được Lahai-Roi giữa cơn Bão Hư Không, cậu lao vào đường hầm không gian, bị cuốn vào một chiều không gian kỳ lạ...
+Khi đến Lahai-Roi, cậu tình cờ gặp Lynae, một học sinh dẫn cậu đến Học viện Startorch. Khi bắt đầu nhập học, mọi thứ về "đô thị học thuật" này dần hiện ra trước mắt. Đồng thời, những bóng tối khuấy động bên dưới Bão Hư Không...</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Một thiên đường ấm áp và ẩm ướt dưới lòng đất vùng Roya Frostlands. Sau một sự dịch chuyển cực cổ xưa, khu vực này trở thành cực mới của Solaris, buộc tộc Roya phải di cư xuống lòng đất. Tại đây, Spacetrek Collective đã thành lập Startorch Academy. Ngày nay, thành phố học thuật không biên giới này đã trở thành cái nôi của vô số học giả trẻ tài năng.</t>
+          <t>Một thiên đường ấm áp và ẩm ướt dưới lòng đất vùng Roya Frostlands. Sau một sự dịch chuyển cực cổ xưa, khu vực này trở thành cực mới của Solaris, buộc tộc Roya phải di cư xuống lòng đất. Tại đây, Spacetrek Collective đã thành lập Học viện Startorch. Ngày nay, thành phố học thuật không biên giới này đã trở thành cái nôi của vô số học giả trẻ tài năng.</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Startorch Academy thuộc Tập đoàn Spacetrek: một cộng đồng khoa học không biên giới, cống hiến cho việc theo đuổi tri thức thuần túy. Cái tên của nó thể hiện tinh thần: "giữ ngọn lửa tìm tòi và thắp sáng ngọn đuốc văn minh". Trong thành phố học thuật rộng lớn này, tri thức được trao đổi tự do, các nền văn hóa giao thoa hòa quyện.</t>
+          <t>Học viện Startorch thuộc Tập đoàn Spacetrek: một cộng đồng khoa học không biên giới, cống hiến cho việc theo đuổi tri thức thuần túy. Cái tên của nó thể hiện tinh thần: "giữ ngọn lửa tìm tòi và thắp sáng ngọn đuốc văn minh". Trong thành phố học thuật rộng lớn này, tri thức được trao đổi tự do, các nền văn hóa giao thoa hòa quyện.</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       <c r="M99" t="inlineStr">
         <is>
           <t>Hãy Đến Học Viện Startorch
-Sau khi Bản Cập Nhật 3.0 ra mắt, đăng nhập vào game để nhận Radiant Tide x10 và Crystal Solvent x10 từ Hòm Mail trong game.
+Sau khi Bản Cập Nhật 3.0 ra mắt, đăng nhập vào game để nhận Radiant Tide x10 và Crystal Solvent x10 từ Hòm Thư trong game.
 Quà Tuần Lễ Tân Sinh Viên
 Khi sự kiện bắt đầu, đăng nhập vào game mỗi ngày để nhận quà điểm danh hàng ngày.</t>
         </is>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Câu lạc bộ fan "Peaks of Prestige" của Startorch Academy đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh.
+          <t>Câu lạc bộ fan "Đỉnh Cao Danh Vọng" của Học viện Startorch đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh.
 Giờ đây, số phận của câu lạc bộ hoàn toàn nằm trong tay cậu. Hãy giành lấy chiến thắng và đập tan bóng tối đang phủ xuống!</t>
         </is>
       </c>
@@ -7114,7 +7114,7 @@
         <is>
           <t>Khi khám phá Lahai-Roi, một tiện ích mới cho Xe Thám Hiểm sẽ xuất hiện
 Xe Thám Hiểm giúp cậu di chuyển nhanh hơn. Các chức năng của nó sẽ được cải thiện qua các lần nâng cấp.
-Khi sử dụng Xe Thám Hiểm, hãy tận dụng các tính năng như tăng tốc, Boost, Drift và Bounce Nhảy, v.v. Trong lúc di chuyển, một lá chắn năng lượng sẽ được triển khai quanh xe, và Resonator sẽ bị buộc phải xuống xe nếu lá chắn biến mất.
+Khi sử dụng Xe Thám Hiểm, hãy tận dụng các tính năng như tăng tốc, Boost, Drift và Bounce Jump, v.v. Trong lúc di chuyển, một lá chắn năng lượng sẽ được triển khai quanh xe, và Resonator sẽ bị buộc phải xuống xe nếu lá chắn biến mất.
 Xe được trang bị mô-đun Adaptive Hook, có thể dùng để thu thập tài nguyên, Sonance Casket và các vật phẩm khác từ xa.
 Xe còn có thể bắt sóng Heart Radio Channel, cho phép cậu thưởng thức những bản nhạc yêu thích khi lái xe.
 Tại Lahai-Roi, cậu sẽ tìm thấy nhiều Challenge Track để thử thách kỹ năng lái xe.</t>
@@ -7184,7 +7184,7 @@
       <c r="M103" t="inlineStr">
         <is>
           <t>Cấp độ tối đa của Cơ sở dữ liệu đã tăng lên 30.
-Hệ thống lên cấp Cơ sở dữ liệu đã được tối ưu. Sau khi Cơ sở dữ liệu lên cấp, ngoài việc Tăng cường Hấp thụ cho Echoes COST 4 (Overlord Class/Calamity), các lần thử Tăng cường Hấp thụ cũng sẽ áp dụng cho Echoes COST 1 (Class Common) và COST 3 (Class Elite).</t>
+Hệ thống lên cấp Cơ sở dữ liệu đã được tối ưu. Sau khi Cơ sở dữ liệu lên cấp, ngoài việc Tăng cường Hấp thụ cho Echo COST 4 (Hạng Overlord/Calamity), các lần thử Tăng cường Hấp thụ cũng sẽ áp dụng cho Echo COST 1 (Hạng Common) và COST 3 (Hạng Elite).</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       <c r="M105" t="inlineStr">
         <is>
           <t>Đây có thể không phải căng-tin lớn nhất ở Solaris, nhưng chắc chắn là tiên tiến nhất. Mỗi bữa ăn đều tuân thủ nghiêm ngặt các tiêu chuẩn an toàn, với giá trị dinh dưỡng được tính toán khoa học, sẵn sàng bảo quản lâu dài ngay cả trong môi trường khắc nghiệt nhất.
-Bình luận phổ biến [Deleted]: An toàn, tinh tế, bảo quản được... nhưng chẳng ngon tí nào.</t>
+Bình luận phổ biến [Đã xóa]: An toàn, tinh tế, bảo quản được... nhưng chẳng ngon tí nào.</t>
         </is>
       </c>
     </row>
@@ -7390,10 +7390,10 @@
       <c r="M106" t="inlineStr">
         <is>
           <t>(Bản ghi âm rời rạc của một đoạn hội thoại ngắn)
-Giọng nói Male: (hào hứng, thở dốc)
-Giọng nói Male: Cái thang máy này... thật khổng lồ! Một kỳ tích trong lịch sử kiến trúc của Solaris.
-Giọng nói Male: Nó nâng đỡ mái vòm hang động, nối liền Học viện và Viện Nghiên Cứu, vận chuyển vật tư không ngừng từ vùng băng giá...
-Giọng nói Nữ: Điển hình dân năm nhất. Đi vài lần nữa là cậu sẽ quen thôi.</t>
+Giọng Nam: (hào hứng, thở dốc)
+Giọng Nam: Cái thang máy này... thật khổng lồ! Một kỳ tích trong lịch sử kiến trúc của Solaris.
+Giọng Nam: Nó nâng đỡ mái vòm hang động, nối liền Học viện và Viện Nghiên cứu, vận chuyển vật tư không ngừng từ vùng băng giá...
+Giọng Nữ: Điển hình dân năm nhất. Đi vài lần nữa là cậu sẽ quen thôi.</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       <c r="M107" t="inlineStr">
         <is>
           <t>...Để thích ứng với địa hình phức tạp và rộng lớn của khu trú ẩn dưới lòng đất, một loại phương tiện đa địa hình mới đã được phát triển.
-Dù được thiết kế chính thức cho các chuyến thám hiểm nghiên cứu, nhưng trong hướng dẫn sử dụng lại không hề có quy định cấm mang nó ra ngoài khuôn viên Startorch Academy để "thử nghiệm".</t>
+Dù được thiết kế chính thức cho các chuyến thám hiểm nghiên cứu, nhưng trong hướng dẫn sử dụng lại không hề có quy định cấm mang nó ra ngoài khuôn viên Học viện Startorch để "thử nghiệm".</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Lâu trước khi Tập thể Spacetrek được thành lập, tộc người du mục tự cung tự cấp Roya đã định cư trong những hang động rộng lớn này. Việc xây dựng Startorch Academy và Viện Nghiên Cứu đều không thể thực hiện nếu thiếu sự trợ giúp của họ.
+          <t>Lâu trước khi Tập thể Spacetrek được thành lập, tộc người du mục tự cung tự cấp Roya đã định cư trong những hang động rộng lớn này. Việc xây dựng Học viện Startorch và Viện Nghiên cứu đều không thể thực hiện nếu thiếu sự trợ giúp của họ.
 Dựa vào những mảnh vỡ cơ khí của ██, người Roya đã xây dựng nên một khu định cư độc nhất vô nhị. Tài giỏi trong thiên văn và niên đại học, họ được cho là đang bảo vệ một sứ mệnh cổ xưa—chờ đợi ngày có thể sửa chữa và đánh thức ██ đang say giấc.</t>
         </is>
       </c>
@@ -7730,9 +7730,9 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Intensity Dư Âm hiện tại: {0}
-Intensity Dư Âm tăng sau mỗi {1} giây, làm mạnh thêm sức tấn công của Echo.
-Mức độ Echo hiện đã tăng thêm: {2}</t>
+          <t>Cường độ Dư Âm hiện tại: {0}
+Cường độ Dư Âm tăng sau mỗi {1} giây, làm mạnh thêm sức tấn công của Tổ Tacet.
+Mức độ Tổ Tacet hiện đã tăng thêm: {2}</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
       <c r="M112" t="inlineStr">
         <is>
           <t>&lt;color=#ddc992&gt;Bộ định tuyến kiểu cũ này chỉ có thể kích hoạt bằng vật liệu đặc biệt thu được từ nhiệm vụ "Khởi Động! Bộ Định Tuyến!".
-Con đường chính nối Startorch Academy và Đài Quan sát Spacetrek. Con đường lầy lội, hoang vắng này vẫn còn lưu lại dấu vết của những đoàn xe từng vật lộn qua đây.&lt;/color&gt;</t>
+Con đường chính nối Học viện Startorch và Đài Quan sát Spacetrek. Con đường lầy lội, hoang vắng này vẫn còn lưu lại dấu vết của những đoàn xe từng vật lộn qua đây.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Con đường ven vách núi được đục vào sườn đá. Cơn Void Storm tàn phá Đài Thiên Văn cũng xóa sổ luôn tuyến đường này, chỉ còn lại tiếng gió hú nơi từng có xe cộ qua lại.</t>
+          <t>Con đường ven vách núi được đục vào sườn đá. Cơn Bão Hư Không tàn phá Đài Thiên Văn cũng xóa sổ luôn tuyến đường này, chỉ còn lại tiếng gió hú nơi từng có xe cộ qua lại.</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Con đường ven vách núi được đục vào sườn đá. Sau khi Void Storm tàn phá đoạn phía bắc, đoạn này cũng dần hoang phế, mặt đường nứt nẻ giờ bị chôn vùi dưới cát và bụi đất.</t>
+          <t>Con đường ven vách núi được đục vào sườn đá. Sau khi Bão Hư Không tàn phá đoạn phía bắc, đoạn này cũng dần hoang phế, mặt đường nứt nẻ giờ bị chôn vùi dưới cát và bụi đất.</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       <c r="M119" t="inlineStr">
         <is>
           <t>Tiến lên… mở rộng… nền móng của Đài Thiên Văn…
-("Sau Cơn Void Storm, nền móng của Spacetrek Observatory bị hư hại nặng. May mắn thay, hầu hết hệ thống chuyển đổi năng lượng phía trên vẫn hoạt động được. Vì vậy, đội đã quyết định thu gọn nền móng để tránh hư hại thêm. Khi có đủ nguồn lực, chúng ta sẽ mở rộng lại và bắt đầu sửa chữa cấu trúc," Dhalifa giải thích!)</t>
+("Sau Cơn Bão Hư Không, nền móng của Đài Thiên Văn Spacetrek bị hư hại nặng. May mắn thay, hầu hết hệ thống chuyển đổi năng lượng phía trên vẫn hoạt động được. Vì vậy, đội đã quyết định thu gọn nền móng để tránh hư hại thêm. Khi có đủ nguồn lực, chúng ta sẽ mở rộng lại và bắt đầu sửa chữa cấu trúc," Dhalifa giải thích!)</t>
         </is>
       </c>
     </row>
@@ -8322,8 +8322,8 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Nền Tảng Treo Suspension là lõi hỗ trợ và điều khiển chính của Đài Thiên Văn. Để khôi phục nó, chúng ta cần không ít tài nguyên và công sức. Hãy cùng nhau vượt qua thử thách này nhé.
-("Nền Tảng Treo Suspension mà chúng ta đang xây dựng sẽ không chỉ hỗ trợ phần thân chính của Spacetrek Observatory, mà còn trở thành không gian làm việc chính cho các nhà nghiên cứu. Tầng trên cùng thậm chí sẽ có một quảng trường mở, nơi mọi người có thể thư giãn và ngắm nhìn cảnh quan Đồng Bằng Etching. Tôi rất mong chờ được thấy nền tảng này sau khi được khôi phục hoàn toàn," Dhalifa nói!)</t>
+          <t>Nền Tảng Treo Lơ Lửng là lõi hỗ trợ và điều khiển chính của Đài Thiên Văn. Để khôi phục nó, chúng ta cần không ít tài nguyên và công sức. Hãy cùng nhau vượt qua thử thách này nhé.
+("Nền Tảng Treo Lơ Lửng mà chúng ta đang xây dựng sẽ không chỉ hỗ trợ phần thân chính của Đài Thiên Văn Spacetrek, mà còn trở thành không gian làm việc chính cho các nhà nghiên cứu. Tầng trên cùng thậm chí sẽ có một quảng trường mở, nơi mọi người có thể thư giãn và ngắm nhìn cảnh quan Đồng Bằng Etching. Tôi rất mong chờ được thấy nền tảng này sau khi được khôi phục hoàn toàn," Dhalifa nói!)</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khi Spacetrek Observatory lần đầu ghi lại hệ sinh thái, khí hậu và cảnh quan của Lahai-Roi, nhiều nhà nghiên cứu đã làm việc không ngừng nghỉ vì nó đã bật khóc. Đó là cách chúng tôi chống lại Void Storm, thứ có thể xóa sổ cả sự tồn tại. Và giờ đây, với sự giúp đỡ của cậu, chúng ta chỉ còn một bước nữa là khôi phục lại nó. Mong cậu cũng sẽ cảm nhận được điều chúng tôi đã cảm nhận trong ngày hôm ấy! (Đó là lời của Dhalifa!)</t>
+          <t>Khi Đài Quan Sát Spacetrek lần đầu ghi lại hệ sinh thái, khí hậu và cảnh quan của Lahai-Roi, nhiều nhà nghiên cứu đã làm việc không ngừng nghỉ vì nó đã bật khóc. Đó là cách chúng tôi chống lại Bão Hư Không, thứ có thể xóa sổ cả sự tồn tại. Và giờ đây, với sự giúp đỡ của cậu, chúng ta chỉ còn một bước nữa là khôi phục lại nó. Mong cậu cũng sẽ cảm nhận được điều chúng tôi đã cảm nhận trong ngày hôm ấy! (Đó là lời của Dhalifa!)</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Giờ khi Spacetrek Observatory hoạt động trở lại, đôi mắt đã nhắm nghiền của Lahai-Roi cuối cùng cũng mở ra. Mọi thứ nó quan sát đều được ghi lại thành dữ liệu hữu hình, dòng thông tin tuôn chảy vào Nền Tảng Suspension như nhịp đập của trái đất. Các nhà nghiên cứu sẽ phân tích, diễn giải và lưu trữ thông tin này để hỗ trợ Spacetrek Collective nghiên cứu hoạt động của Void Storm.</t>
+          <t>Giờ khi Đài Quan Sát Spacetrek hoạt động trở lại, đôi mắt đã nhắm nghiền của Lahai-Roi cuối cùng cũng mở ra. Mọi thứ nó quan sát đều được ghi lại thành dữ liệu hữu hình, dòng thông tin tuôn chảy vào Nền Tảng Suspension như nhịp đập của trái đất. Các nhà nghiên cứu sẽ phân tích, diễn giải và lưu trữ thông tin này để hỗ trợ Spacetrek Collective nghiên cứu hoạt động của Void Storm.</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Network Activity lưới x{0}</t>
+          <t>Nhận &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity30/ActivityInfrastructure/Main/T_IconActivityInfrastructure6Small.T_IconActivityInfrastructure6Small/&gt; Hoạt Động Mạng lưới x{0}</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Con đường chính nối Startorch Academy và Đài quan sát Spacetrek. Học sinh thường dừng chân ở đây để chụp lại bóng dáng khổng lồ của Đài quan sát in trên nền trời xa.</t>
+          <t>Con đường chính nối Học viện Startorch và Đài quan sát Spacetrek. Học sinh thường dừng chân ở đây để chụp lại bóng dáng khổng lồ của Đài quan sát in trên nền trời xa.</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Con đường ven vách núi được đục vào sườn núi, nối Spacetrek Observatory với vùng nam Lahai-Roi rộng lớn. Một thác nước ẩn mình trong sương mù đánh dấu điểm cuối của con đường.</t>
+          <t>Con đường ven vách núi được đục vào sườn núi, nối Đài Quan Sát Spacetrek với vùng nam Lahai-Roi rộng lớn. Một thác nước ẩn mình trong sương mù đánh dấu điểm cuối của con đường.</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Con đường nối Hầm Gió Rít với Startorch Academy. So với các con đường khác gần Học viện, Starleap Ascent có độ dài trung bình và điều kiện đường đa dạng, trở thành một trong những địa điểm chính cho các bài kiểm tra xe máy thám hiểm của học sinh.</t>
+          <t>Con đường nối Hầm Gió Rít với Học viện Startorch. So với các con đường khác gần Học viện, Starleap Ascent có độ dài trung bình và điều kiện đường đa dạng, trở thành một trong những địa điểm chính cho các bài kiểm tra xe máy thám hiểm của học sinh.</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Sau khi gia cố các bức tường đá và lát đường cao tốc, đường hầm giờ đây có thể chịu được tải trọng vận chuyển nặng, rút ngắn hành trình từ Startorch Academy đến phía nam Lahai-Roi. Những cơn gió từng vang vọng ở đây giờ được cho là mang một ý nghĩa khác: chúng là lời chúc phúc của Exostrider dành cho các học sinh Roya trên đường đến Học viện.</t>
+          <t>Sau khi gia cố các bức tường đá và lát đường cao tốc, đường hầm giờ đây có thể chịu được tải trọng vận chuyển nặng, rút ngắn hành trình từ Học viện Startorch đến phía nam Lahai-Roi. Những cơn gió từng vang vọng ở đây giờ được cho là mang một ý nghĩa khác: chúng là lời chúc phúc của Exostrider dành cho các học sinh Roya trên đường đến Học viện.</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Khôi phục Đài quan sát Spacetrek để mở khóa Mô phỏng Thời tiết. Send tín hiệu điều khiển đến Mảng Dự báo Bầu trời để tạo ra thời tiết mô phỏng trên toàn Lahai-Roi.</t>
+          <t>Khôi phục Đài quan sát Spacetrek để mở khóa Mô phỏng Thời tiết. Gửi tín hiệu điều khiển đến Mảng Dự báo Bầu trời để tạo ra thời tiết mô phỏng trên toàn Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Tea đá pha với nước ô liu, thanh mát giải khát. Với một Võ Sĩ, một ly Olive Iced Tea chắc chắn là thức uống lý tưởng sau những giờ tập luyện căng thẳng.</t>
+          <t>Trà đá pha với nước ô liu, thanh mát giải khát. Với một Võ Sĩ, một ly Olive Iced Tea chắc chắn là thức uống lý tưởng sau những giờ tập luyện căng thẳng.</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Nơi này từng lưu giữ cả một bộ sưu tập phim ảnh đa dạng cùng chiếc xe của ông Geisel. Dù những biểu tượng của ước mơ và kỷ niệm ấy đã không còn, giờ đây chiếc xe của cậu và đoạn phim quảng cáo của Startorch Academy đã thay thế, tạo nên hình hài cho những ước mơ và hy vọng mới.</t>
+          <t>Nơi này từng lưu giữ cả một bộ sưu tập phim ảnh đa dạng cùng chiếc xe của ông Geisel. Dù những biểu tượng của ước mơ và kỷ niệm ấy đã không còn, giờ đây chiếc xe của cậu và đoạn phim quảng cáo của Học viện Startorch đã thay thế, tạo nên hình hài cho những ước mơ và hy vọng mới.</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Tại Shop Trang Trí, bạn có thể đổi nhiều món đồ trang trí khác nhau bằng Đồng Tinh Vân kiếm được trong sự kiện. Mỗi món đồ nội thất sẽ yêu cầu số lượng Đồng Tinh Vân khác nhau.</t>
+          <t>Tại Cửa Hàng Trang Trí, bạn có thể đổi nhiều món đồ trang trí khác nhau bằng Đồng Tinh Vân kiếm được trong sự kiện. Mỗi món đồ nội thất sẽ yêu cầu số lượng Đồng Tinh Vân khác nhau.</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Bản sao của "Zapstring", con rối cơ khí của Yinlin. Like mọi nghệ nhân rối, cô tạo ra nhiều con rối khác nhau cho các buổi biểu diễn, nhưng "Zapstring" là con duy nhất cô luôn mang bên mình.</t>
+          <t>Bản sao của "Zapstring", con rối cơ khí của Yinlin. Giống như mọi nghệ nhân rối, cô tạo ra nhiều con rối khác nhau cho các buổi biểu diễn, nhưng "Zapstring" là con duy nhất cô luôn mang bên mình.</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Chính tại đây, Grand Commander Thứ Năm đã dẫn dắt các hiệp sĩ thực hiện cuộc chiến cuối cùng. Không phải chống lại một lãnh chúa bạo ngược, mà là... một Cơn Void Storm có thể xóa sổ mọi sự sống. Họ đã không thể vượt qua nó... hay thực ra là đã?</t>
+          <t>Chính tại đây, Đại Chỉ Huy Thứ Năm đã dẫn dắt các hiệp sĩ thực hiện cuộc chiến cuối cùng. Không phải chống lại một lãnh chúa bạo ngược, mà là... một Cơn Bão Hư Không có thể xóa sổ mọi sự sống. Họ đã không thể vượt qua nó... hay thực ra là đã?</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Nơi đây là khởi đầu, từ rất lâu trước khi họ được gọi là Knights of the Wild. Tại đây, một nhóm Mechascout không còn đường về đã dùng những tia lửa năng lượng cuối cùng để cứu lấy một đứa trẻ.</t>
+          <t>Nơi đây là khởi đầu, từ rất lâu trước khi họ được gọi là Hiệp Sĩ Hoang Dã. Tại đây, một nhóm Mechascout không còn đường về đã dùng những tia lửa năng lượng cuối cùng để cứu lấy một đứa trẻ.</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Grand Commander Thứ Mười Tám... lại mang hình hài một chiếc thùng rác tầm thường. Thế nhưng, chẳng ai dám vứt một mẩu giấy hay hạt quả vào bụng nó. Bên trong lớp vỏ kim loại ấy là những lời ca ngợi dành cho các Knights of the Wild.</t>
+          <t>Đại Chỉ Huy Thứ Mười Tám... lại mang hình hài một chiếc thùng rác tầm thường. Thế nhưng, chẳng ai dám vứt một mẩu giấy hay hạt quả vào bụng nó. Bên trong lớp vỏ kim loại ấy là những lời ca ngợi dành cho các Hiệp Sĩ Hoang Dã.</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Nghe nói Grand Commander Thứ Mười Bảy chỉ là một con người bình thường, chẳng có võ công gì đáng kể. Ấy vậy mà trước khi Void Storm ập đến, chính ông đã dẫn dắt các Hiệp Sĩ trong cuộc chạy trốn tuyệt vọng, đưa họ rời khỏi vùng đất bị nguyền rủa. Nhưng số phận của ông thì...</t>
+          <t>Nghe nói Đại Chỉ Huy Thứ Mười Bảy chỉ là một con người bình thường, chẳng có võ công gì đáng kể. Ấy vậy mà trước khi Bão Hư Không ập đến, chính ông đã dẫn dắt các Hiệp Sĩ trong cuộc chạy trốn tuyệt vọng, đưa họ rời khỏi vùng đất bị nguyền rủa. Nhưng số phận của ông thì...</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Tăng &lt;color=Highlight&gt;15%&lt;/color&gt; Hiệu Quả Healing. Ngoài ra, tăng thêm &lt;color=Highlight&gt;15%&lt;/color&gt; Hiệu Quả Healing cho mỗi &lt;color=Highlight&gt;1%&lt;/color&gt; Tỷ Lệ Tích Lũy Mất Cân Bằng của Resonator.</t>
+          <t>Tăng &lt;color=Highlight&gt;15%&lt;/color&gt; Hiệu Quả Hồi Phục. Ngoài ra, tăng thêm &lt;color=Highlight&gt;15%&lt;/color&gt; Hiệu Quả Hồi Phục cho mỗi &lt;color=Highlight&gt;1%&lt;/color&gt; Tỷ Lệ Tích Lũy Mất Cân Bằng của Resonator.</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Một khu rừng fjord cổ xưa, bị phong ấn dưới lớp băng vĩnh cửu. Để nghiên cứu hệ thực vật tiền sử được bảo tồn trong băng, Viện Nghiên Cứu đã thành lập Upphaf Life Chamber gần đó.</t>
+          <t>Một khu rừng fjord cổ xưa, bị phong ấn dưới lớp băng vĩnh cửu. Để nghiên cứu hệ thực vật tiền sử được bảo tồn trong băng, Viện Nghiên cứu đã thành lập Upphaf Life Chamber gần đó.</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Con Đường Sao để kiếm Journey Points. Đạt các mốc Journey Points để nhận Quà Con Đường Sao, bao gồm Thủy Triều Lấp Lánh, Ấn "Concealed Starlight Giấu", Title "Luật Lệ Của Những Vì Sao", Thủy Triều Rạng Rỡ, và Mẫu Dáng Dù Cao Cấp "Trục Vũ Trụ".</t>
+          <t>Hoàn thành Nhiệm Vụ Con Đường Sao để kiếm Điểm Hành Trình. Đạt các mốc Điểm Hành Trình để nhận Quà Con Đường Sao, bao gồm Lustrous Tide, Ấn "Ánh Sao Ẩn Giấu", Danh Hiệu "Luật Lệ Của Những Vì Sao", Thủy Triều Rạng Rỡ, và Mẫu Dáng Dù Cao Cấp "Trục Vũ Trụ".</t>
         </is>
       </c>
     </row>
@@ -13997,12 +13997,12 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Voyaging Star Chassis Set
-Includes Khung Voyaging Star, Tem Xe "Cô Gái Cưỡi Exostrider" (Cản Trái, Cản Right, Trước/Sau), và Astrites.
+          <t>Bộ Khung Ngôi Sao Lang Thang
+Bao gồm Khung Ngôi Sao Lang Thang, Tem Xe "Cô Gái Cưỡi Exostrider" (Cản Trái, Cản Phải, Trước/Sau), và Astrites.
 Nguyên Nhân Mặt Trăng
-Includes Tem Xe "Nguyên Nhân Mặt Trăng" (Cản Trái, Cản Right, Trước/Sau), và Astrites.
+Bao gồm Tem Xe "Nguyên Nhân Mặt Trăng" (Cản Trái, Cản Phải, Trước/Sau), và Astrites.
 Đỉnh Ngắm Chân Trời
-Includes Tem Xe "Đỉnh Ngắm Chân Trời" (Cản Trái, Cản Right, Trước/Sau), và Astrites.</t>
+Bao gồm Tem Xe "Đỉnh Ngắm Chân Trời" (Cản Trái, Cản Phải, Trước/Sau), và Astrites.</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Weekly Subscription chỉ có thể mua một lần. Sau khi mua và kích hoạt trong thời hạn quy định, gói sẽ có hiệu lực trong 15 ngày. Đăng nhập vào các ngày chỉ định trong thời gian hiệu lực để nhận Lunites, Astrites và Transducers.</t>
+          <t>Gói Đăng Ký Hàng Tuần chỉ có thể mua một lần. Sau khi mua và kích hoạt trong thời hạn quy định, gói sẽ có hiệu lực trong 15 ngày. Đăng nhập vào các ngày chỉ định trong thời gian hiệu lực để nhận Lunites, Astrites và Transducers.</t>
         </is>
       </c>
     </row>
@@ -14271,9 +14271,9 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Data Merge
+          <t>Hợp nhất dữ liệu
 Đã hỗ trợ hợp nhất vào Bộ Sonata đã chọn.
-Modify dữ liệu
+Chỉnh sửa dữ liệu
 Đã bổ sung chỉnh sửa hàng loạt cho Chỉ số chính Echo.</t>
         </is>
       </c>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Những Knights of the Wild, như mọi người vẫn gọi, là những Mechascout lang thang khắp vùng Lahai-Roi, thề bảo vệ những ai gặp nguy hiểm. Nhưng lần này, chính các Hiệp Sĩ lại là những người cần sự trợ giúp.</t>
+          <t>Những Hiệp Sĩ Hoang Dã, như mọi người vẫn gọi, là những Mechascout lang thang khắp vùng Lahai-Roi, thề bảo vệ những ai gặp nguy hiểm. Nhưng lần này, chính các Hiệp Sĩ lại là những người cần sự trợ giúp.</t>
         </is>
       </c>
     </row>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Mã Hóa P=Mã Hóa SapTag=0}&lt;/color&gt; thu thập được sẽ nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Metaphor P=Metaphor SapTag=1}&lt;/color&gt; ngẫu nhiên.</t>
+          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Mã Hóa P=Mã Hóa SapTag=0}&lt;/color&gt; thu thập được sẽ nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Ẩn Dụ P=Ẩn Dụ SapTag=1}&lt;/color&gt; ngẫu nhiên.</t>
         </is>
       </c>
     </row>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Mã Hóa P=Mã Hóa SapTag=0}&lt;/color&gt; thu thập được sẽ nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Metaphor P=Metaphor SapTag=1}&lt;/color&gt; ngẫu nhiên.</t>
+          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Mã Hóa P=Mã Hóa SapTag=0}&lt;/color&gt; thu thập được sẽ nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Ẩn Dụ P=Ẩn Dụ SapTag=1}&lt;/color&gt; ngẫu nhiên.</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Khi bước vào &lt;color=Highlight&gt;Ký Ức Nhiễm Độc&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nightmare Nhiễm Độc&lt;/color&gt;, có {0} xác suất nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Đơn Vị P=Đơn Vị SapTag=1}&lt;/color&gt;.</t>
+          <t>Khi bước vào &lt;color=Highlight&gt;Ký Ức Nhiễm Độc&lt;/color&gt; hoặc &lt;color=Highlight&gt;Ác Mộng Nhiễm Độc&lt;/color&gt;, có {0} xác suất nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Đơn Vị P=Đơn Vị SapTag=1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14599,7 +14599,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Khi bước vào &lt;color=Highlight&gt;Memory of Rest&lt;/color&gt;, có {0} xác suất nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Đơn Vị P=Đơn Vị SapTag=1}&lt;/color&gt;.</t>
+          <t>Khi bước vào &lt;color=Highlight&gt;Ký Ức Nghỉ Ngơi&lt;/color&gt;, có {0} xác suất nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Đơn Vị P=Đơn Vị SapTag=1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Khi bước vào &lt;color=Highlight&gt;Ký Ức Vỡ Tan&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nightmare Vỡ Tan&lt;/color&gt;, có {0} xác suất nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Metaphor P=Metaphor SapTag=1}&lt;/color&gt;.</t>
+          <t>Khi bước vào &lt;color=Highlight&gt;Ký Ức Vỡ Tan&lt;/color&gt; hoặc &lt;color=Highlight&gt;Ác Mộng Vỡ Tan&lt;/color&gt;, có {0} xác suất nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Ẩn Dụ P=Ẩn Dụ SapTag=1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Khi Cube này đi qua điểm giữa, dịch chuyển tất cả Cube không phải Abbowser ở phía trước và phía sau về vị trí của nó. Các Khối sẽ xếp chồng theo vị trí trước đó. Hiệu ứng này chỉ kích hoạt một lần mỗi trận.</t>
+          <t>Khi Khối Lập Phương này đi qua điểm giữa, dịch chuyển tất cả Khối Lập Phương không phải Abbowser ở phía trước và phía sau về vị trí của nó. Các Khối sẽ xếp chồng theo vị trí trước đó. Hiệu ứng này chỉ kích hoạt một lần mỗi trận.</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Chúc mừng Lynae, tân Champion của chúng ta! Ngoài ra, ban tổ chức đã nhanh chóng tịch thu bình sơn xịt ngay sau khi cô rút nó ra. Thật đáng tiếc, phải không nào?</t>
+          <t>Chúc mừng Lynae, tân Quán Quân của chúng ta! Ngoài ra, ban tổ chức đã nhanh chóng tịch thu bình sơn xịt ngay sau khi cô rút nó ra. Thật đáng tiếc, phải không nào?</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Chúc mừng Sigrika đã trở thành Nhà Vô Địch! Trong buổi phỏng vấn, Sigrika đã gửi lời cảm ơn đến gia đình và bạn bè trong bộ tộc Roya, các bạn học và thầy cô tại Startorch Academy, cũng như Soliskin và Exoswarm... Hãy dành một tràng pháo tay chúc mừng chiến thắng của cô ấy!</t>
+          <t>Chúc mừng Sigrika đã trở thành Nhà Vô Địch! Trong buổi phỏng vấn, Sigrika đã gửi lời cảm ơn đến gia đình và bạn bè trong bộ tộc Roya, các bạn học và thầy cô tại Học viện Startorch, cũng như Soliskin và Exoswarm... Hãy dành một tràng pháo tay chúc mừng chiến thắng của cô ấy!</t>
         </is>
       </c>
     </row>
@@ -15639,7 +15639,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Denia đã giành chiến thắng trong trận Chung Kết! Trong bài phát biểu nhận giải, cô gửi lời cảm ơn đến những người bạn tại Startorch Academy, nhờ sự ủng hộ của họ mà cô mới có thể đi xa đến vậy.</t>
+          <t>Denia đã giành chiến thắng trong trận Chung Kết! Trong bài phát biểu nhận giải, cô gửi lời cảm ơn đến những người bạn tại Học viện Startorch, nhờ sự ủng hộ của họ mà cô mới có thể đi xa đến vậy.</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Preliminary chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
+          <t>Vòng Sơ Loại chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Preliminary chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
+          <t>Vòng Sơ Loại chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Preliminary chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
+          <t>Vòng Sơ Loại chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Preliminary chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
+          <t>Vòng Sơ Loại chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Preliminary chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
+          <t>Vòng Sơ Loại chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
         </is>
       </c>
     </row>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Preliminary chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
+          <t>Vòng Sơ Loại chia thành hai hiệp: hiệp đầu và hiệp sau. Kết quả tung Xúc Xắc ở hiệp đầu sẽ quyết định thứ tự xuất phát ở hiệp sau. Sau hiệp sau, 4 người đứng đầu sẽ tiến vào vòng Loại Trực Tiếp, còn 2 người cuối bảng sẽ phải xuống chơi trận Trận Trình Diễn.</t>
         </is>
       </c>
     </row>
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Giải Cubie Derby: Vô Địch đã kết thúc. Xin chân thành cảm ơn tất cả thí sinh và khán giả vì sự ủng hộ nhiệt tình. Hẹn gặp lại các bạn trong tương lai!</t>
+          <t>Giải Đua Cubie: Vô Địch đã kết thúc. Xin chân thành cảm ơn tất cả thí sinh và khán giả vì sự ủng hộ nhiệt tình. Hẹn gặp lại các bạn trong tương lai!</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Những bài test tiêu chuẩn khiến cậu chán ngấy, nhưng một bài test kỹ năng chiến đấu lại khiến máu cậu sôi sục. Vậy thì hãy dốc hết sức và bước vào cuộc đọ sức giành vị trí Huấn Luyện Viên của Bài Kiểm Tra Kỹ Năng Combat B.1.N.G.O.!</t>
+          <t>Những bài kiểm tra tiêu chuẩn khiến cậu chán ngấy, nhưng một bài kiểm tra kỹ năng chiến đấu lại khiến máu cậu sôi sục. Vậy thì hãy dốc hết sức và bước vào cuộc đọ sức giành vị trí Huấn Luyện Viên của Bài Kiểm Tra Kỹ Năng Chiến Đấu B.1.N.G.O.!</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Phát hiện sự sống thực vật cổ đại trong Sealed Fissure! Hãy thu thập thêm Thuốc Restoration Loại-S để tiếp tục Quá trình Restoration. Chúng tôi trông cậy vào cậu, {PlayerName}!</t>
+          <t>Phát hiện sự sống thực vật cổ đại trong Khe Nứt Bị Phong Ấn! Hãy thu thập thêm Thuốc Phục Hồi Loại-S để tiếp tục Quá trình Phục Hồi. Chúng tôi trông cậy vào cậu, {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Giữa không khí lễ hội của Lễ Kỷ Niệm Năm New tại Học Viện Startorch, Hiệu Trưởng Lucilla phát hiện một tần số bí ẩn xuất hiện ở Khu Vực Bóng Tối của Học Viện—một tần số không thuộc về nơi này. Ngươi nghi ngờ đó có thể là "phần thưởng" mà Kiến Trúc Sư Trưởng của Fractsidus từng nhắc đến. Quyết tâm tìm hiểu sự thật đằng sau dị thường này, ngươi cùng Sigrika—một học sinh ngươi gặp ở đó—mạo hiểm tiến vào Khu Vực Bóng Tối...</t>
+          <t>Giữa không khí lễ hội của Lễ Kỷ Niệm Năm Mới tại Học Viện Startorch, Hiệu Trưởng Lucilla phát hiện một tần số bí ẩn xuất hiện ở Khu Vực Bóng Tối của Học Viện—một tần số không thuộc về nơi này. Ngươi nghi ngờ đó có thể là "phần thưởng" mà Kiến Trúc Sư Trưởng của Fractsidus từng nhắc đến. Quyết tâm tìm hiểu sự thật đằng sau dị thường này, ngươi cùng Sigrika—một học sinh ngươi gặp ở đó—mạo hiểm tiến vào Khu Vực Bóng Tối...</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Sau khi New Solar Celebration kết thúc, Lucilla gửi cho ngươi một tin nhắn WavesLine, nói rằng gốc rễ của bất thường ở Dark Side vẫn chưa được giải quyết, và Học viện vẫn chưa hiểu rõ lý do Fractsidus can thiệp vào Dark Side. Giờ đây, Lucilla trông cậy vào ngươi để bảo vệ Học viện và khám phá những bí ẩn. Trong khi đó, một con thỏ kỳ lạ đang đợi ngươi bên trong Dark Side...</t>
+          <t>Sau khi Lễ Hội Mặt Trời Mới kết thúc, Lucilla gửi cho ngươi một tin nhắn WavesLine, nói rằng gốc rễ của bất thường ở Dark Side vẫn chưa được giải quyết, và Học viện vẫn chưa hiểu rõ lý do Fractsidus can thiệp vào Dark Side. Giờ đây, Lucilla trông cậy vào ngươi để bảo vệ Học viện và khám phá những bí ẩn. Trong khi đó, một con thỏ kỳ lạ đang đợi ngươi bên trong Dark Side...</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Gần đây, "Stellar Orbit Beats" đang làm mưa làm gió tại Mind Dive Arcade! Đây chính thức là trò chơi giải trí yêu thích của mọi người ở Academy. Rảnh rỗi giữa giờ học? Rủ bạn bè cùng hòa mình vào nhịp điệu xuyên vũ trụ nào!</t>
+          <t>Gần đây, "Stellar Orbit Beats" đang làm mưa làm gió tại Mind Dive Arcade! Đây chính thức là trò chơi giải trí yêu thích của mọi người ở Học Viện. Rảnh rỗi giữa giờ học? Rủ bạn bè cùng hòa mình vào nhịp điệu xuyên vũ trụ nào!</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Rải rác khắp Lahai-Roi, các Mechscout từng là nơi nương náu cho những người gặp nguy hiểm và được tôn vinh như những Knights of the Wild. Nhưng giờ đây, chính những người bảo vệ này cũng cần sự giúp đỡ của cậu.</t>
+          <t>Rải rác khắp Lahai-Roi, các Mechscout từng là nơi nương náu cho những người gặp nguy hiểm và được tôn vinh như những Hiệp Sĩ Hoang Dã. Nhưng giờ đây, chính những người bảo vệ này cũng cần sự giúp đỡ của cậu.</t>
         </is>
       </c>
     </row>
@@ -17398,7 +17398,7 @@
       <c r="M259" t="inlineStr">
         <is>
           <t>"Dù có mờ ảo và xanh xao đến đâu, những ngày tháng học trò vẫn luôn lấp lánh như viên ngọc dưới dòng sông ký ức. Những câu chuyện ấy trôi dạt giữa các vì sao, là người bạn đồng hành bên ta trong mỗi đêm tĩnh lặng.
-Khi New Solar Celebration bắt đầu, những câu chuyện nhỏ bé mới lại nở rộ giữa bạn và những người bạn..."</t>
+Khi Lễ Hội Mặt Trời Mới bắt đầu, những câu chuyện nhỏ bé mới lại nở rộ giữa bạn và những người bạn..."</t>
         </is>
       </c>
     </row>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Platya, người mang Bình Minh Bờ Đen, đã đến Startorch Academy vì tin đồn về một Ghost Miko—những lời thì thầm dường như vang vọng truyền thuyết về "Nữ Miko" từ quê hương xa xôi của cô. Tò mò, cậu quyết định cùng cô tìm hiểu.</t>
+          <t>Platya, người mang Bình Minh Bờ Đen, đã đến Học viện Startorch vì tin đồn về một Ghost Miko—những lời thì thầm dường như vang vọng truyền thuyết về "Nữ Miko" từ quê hương xa xôi của cô. Tò mò, cậu quyết định cùng cô tìm hiểu.</t>
         </is>
       </c>
     </row>
@@ -17597,11 +17597,11 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Bộ Tem Xe New - Hợp Tác Độc Quyền có mặt tại Cửa hàng từ 9/4/2026 đến 29/4/2026:
+          <t>Bộ Tem Xe Mới - Hợp Tác Độc Quyền có mặt tại Cửa Hàng từ 9/4/2026 đến 29/4/2026:
 Bộ QUEEN
-Includes Bộ Tem Xe (Cản Trái, Cản Right, Trước/Sau) và Astrites.
+Bao gồm Bộ Tem Xe (Cản Trái, Cản Phải, Trước/Sau) và Astrites.
 Bộ VIOLET
-Includes Bộ Tem Xe (Cản Trái, Cản Right, Trước/Sau) và Astrites.</t>
+Bao gồm Bộ Tem Xe (Cản Trái, Cản Phải, Trước/Sau) và Astrites.</t>
         </is>
       </c>
     </row>
@@ -17672,12 +17672,12 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>[Quản Lý Echo]
-Bạn có thể tạo nhiều kế hoạch quản lý Echo dựa trên COST, Sonata Effect và Mainstats.
-Khi nhận được Echo mới, nó sẽ tự động bị khóa hoặc đánh dấu để loại bỏ theo các kế hoạch đã kích hoạt.
-Kế hoạch Quản Lý Echo không ảnh hưởng đến các Echo upgraded.
+          <t>[Quản Lý Tiếng Vọng]
+Bạn có thể tạo nhiều kế hoạch quản lý Tiếng Vọng dựa trên COST, Hiệu Ứng Sonata và Chỉ Số Chính.
+Khi nhận được Tiếng Vọng mới, nó sẽ tự động bị khóa hoặc đánh dấu để loại bỏ theo các kế hoạch đã kích hoạt.
+Kế hoạch Quản Lý Tiếng Vọng không ảnh hưởng đến các Tiếng Vọng đã nâng cấp.
 [Mẫu Có Sẵn, Chia Sẻ &amp; Nhập]
-Bạn có thể nhập các kế hoạch quản lý gợi ý qua tính năng Kế Hoạch Gợi Ý, hoặc nhập cấu hình của các Rover khác qua tính năng Chia Sẻ &amp; Nhập.
+Bạn có thể nhập các kế hoạch quản lý gợi ý qua tính năng Kế Hoạch Gợi Ý, hoặc nhập cấu hình của các Vận Mệnh Giả khác qua tính năng Chia Sẻ &amp; Nhập.
 Sau khi nhập, tất cả các kế hoạch cục bộ sẽ bị ghi đè và kích hoạt.</t>
         </is>
       </c>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Green Rabbit là loài phụ thuộc họ Thỏ Rabbitidae, có ngoại hình tương đồng giữa đực và cái. Chúng có kích thước nhỏ, tai dài hình ống, chi trước ngắn, chi sau khỏe và dài hơn nhiều so với chi trước, màu xanh lục, đuôi chứa Tacetite và đặc điểm sinh thái đặc biệt là không đầu. Phân bố rộng rãi, chủ yếu ở đồng bằng, đồi núi và rừng cây.</t>
+          <t>Thỏ Xanh là loài phụ thuộc họ Thỏ Rabbitidae, có ngoại hình tương đồng giữa đực và cái. Chúng có kích thước nhỏ, tai dài hình ống, chi trước ngắn, chi sau khỏe và dài hơn nhiều so với chi trước, màu xanh lục, đuôi chứa Tacetite và đặc điểm sinh thái đặc biệt là không đầu. Phân bố rộng rãi, chủ yếu ở đồng bằng, đồi núi và rừng cây.</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Bajorn sheep là loài động vật ăn cỏ cỡ lớn thuộc chi Bovidae, sở hữu cặp sừng khổng lồ uốn cong về phía sau, gốc sừng phủ Tacetite, môi đen, hàm dưới trắng, thân màu nâu. Bajorn sheep có cặp sừng đồ sộ, đầu cong ngược, gốc sừng bọc Tacetite, môi đen, hàm dưới trắng, thân nâu với những đốm trắng lớn trên lưng và một ít Tacetite ở cổ. Chúng phân bố rộng ở vùng núi, di chuyển giỏi trên địa hình dốc đứng và chủ yếu ăn rêu cùng các loại thảo mộc nhỏ.</t>
+          <t>Cừu Bajorn là loài động vật ăn cỏ cỡ lớn thuộc chi Bovidae, sở hữu cặp sừng khổng lồ uốn cong về phía sau, gốc sừng phủ Tacetite, môi đen, hàm dưới trắng, thân màu nâu. Cừu Bajorn có cặp sừng đồ sộ, đầu cong ngược, gốc sừng bọc Tacetite, môi đen, hàm dưới trắng, thân nâu với những đốm trắng lớn trên lưng và một ít Tacetite ở cổ. Chúng phân bố rộng ở vùng núi, di chuyển giỏi trên địa hình dốc đứng và chủ yếu ăn rêu cùng các loại thảo mộc nhỏ.</t>
         </is>
       </c>
     </row>
@@ -18135,7 +18135,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Morri Cow là loài động vật ăn cỏ lớn thuộc họ Trâu bò, được con người thuần hóa trước Sự Than Thở và bị bỏ lại trong rừng sau khi Sự Than Thở xảy ra, khi con người dần rời bỏ Rừng Mờ. Ban đầu, Sự Than Thở chỉ là loài ăn cỏ, nhưng để thích nghi với hệ sinh thái của Wuthering Waves, nó bắt đầu ăn các loài Thực Vật Đột Biến và quả của chúng, khiến cơ thể Bò Rừng dần biến dạng theo thời gian.</t>
+          <t>Bò Morri là loài động vật ăn cỏ lớn thuộc họ Trâu bò, được con người thuần hóa trước Sự Than Thở và bị bỏ lại trong rừng sau khi Sự Than Thở xảy ra, khi con người dần rời bỏ Rừng Mờ. Ban đầu, Sự Than Thở chỉ là loài ăn cỏ, nhưng để thích nghi với hệ sinh thái của Wuthering Waves, nó bắt đầu ăn các loài Thực Vật Đột Biến và quả của chúng, khiến cơ thể Bò Rừng dần biến dạng theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Frostwing là loài chim nhỏ sống trong Tacet Field, thuộc chi Bồ câu, họ Hatydidae. Toàn thân màu trắng tinh, đuôi đen phủ đầy Tacetite, mỏ màu tím, màng sáp màu hồng tươi, chân và ngón chân đỏ rực. Chúng rất thích sống thành đàn, thường làm tổ theo nhóm, tụ tập ở những khu vực có sóng cộng hưởng mạnh của Wuthering Waves và phân bố rộng rãi quanh khu vực Tacet Field.</t>
+          <t>Frostwing là loài chim nhỏ sống trong Tổ Tacet, thuộc chi Bồ câu, họ Hatydidae. Toàn thân màu trắng tinh, đuôi đen phủ đầy Tacetite, mỏ màu tím, màng sáp màu hồng tươi, chân và ngón chân đỏ rực. Chúng rất thích sống thành đàn, thường làm tổ theo nhóm, tụ tập ở những khu vực có sóng cộng hưởng mạnh của Wuthering Waves và phân bố rộng rãi quanh khu vực Tổ Tacet.</t>
         </is>
       </c>
     </row>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Silver-Banded Lizard là loài bò sát thuộc họ thằn lằn, bộ Bò sát. Chúng có tứ chi ngắn, nhanh nhẹn, toàn thân phủ vảy da cứng, với các vòng đen trắng xen kẽ, trong đó vòng trắng hẹp hơn. Loài này ưa môi trường ẩm ướt và phân bố rộng rãi trên đất liền khắp thế giới.</t>
+          <t>Thằn Lằn Vằn Bạc là loài bò sát thuộc họ thằn lằn, bộ Bò sát. Chúng có tứ chi ngắn, nhanh nhẹn, toàn thân phủ vảy da cứng, với các vòng đen trắng xen kẽ, trong đó vòng trắng hẹp hơn. Loài này ưa môi trường ẩm ướt và phân bố rộng rãi trên đất liền khắp thế giới.</t>
         </is>
       </c>
     </row>
@@ -18463,8 +18463,8 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Green Pit Lizard là loài bò sát thuộc họ thằn lằn, bộ Bò sát. Chúng có tứ chi ngắn, nhanh nhẹn, thân phủ vảy da cứng, màu xanh sáng và gai thịt trên lưng. Loài này ưa môi trường ẩm ướt và phân bố rộng rãi ở các vùng ven nước, đầm lầy trên toàn thế giới.
-Green Pit Lizard có khả năng thích nghi kém hơn Silver-Banded Lizard và khả năng sinh sản ở mức trung bình. Chúng chủ yếu sống hoang dã trong các khu vực cây cối ven nước và dọc bờ sông trong các thị trấn, thành phố.</t>
+          <t>Thằn Lằn Hố Xanh là loài bò sát thuộc họ thằn lằn, bộ Bò sát. Chúng có tứ chi ngắn, nhanh nhẹn, thân phủ vảy da cứng, màu xanh sáng và gai thịt trên lưng. Loài này ưa môi trường ẩm ướt và phân bố rộng rãi ở các vùng ven nước, đầm lầy trên toàn thế giới.
+Thằn Lằn Hố Xanh có khả năng thích nghi kém hơn Thằn Lằn Vằn Bạc và khả năng sinh sản ở mức trung bình. Chúng chủ yếu sống hoang dã trong các khu vực cây cối ven nước và dọc bờ sông trong các thị trấn, thành phố.</t>
         </is>
       </c>
     </row>
@@ -18529,7 +18529,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Black-Striped Frog là loài lưỡng cư thuộc ngành Dây sống, lớp Lưỡng cư, bộ Noctuidae. Chúng có tứ chi ngắn, thân màu xanh lục với nhiều hoa văn, bụng trắng, hai bên đầu có màng nhĩ hơi lồi, da trơn với vài mụn cóc, và một lượng nhỏ Tacetite kết tủa trên lưng. Phân bố rộng rãi ở sông, hồ, đầm lầy và các môi trường khác, chủ yếu sống trong đám cỏ ven nước.</t>
+          <t>Ếch Sọc Đen là loài lưỡng cư thuộc ngành Dây sống, lớp Lưỡng cư, bộ Noctuidae. Chúng có tứ chi ngắn, thân màu xanh lục với nhiều hoa văn, bụng trắng, hai bên đầu có màng nhĩ hơi lồi, da trơn với vài mụn cóc, và một lượng nhỏ Tacetite kết tủa trên lưng. Phân bố rộng rãi ở sông, hồ, đầm lầy và các môi trường khác, chủ yếu sống trong đám cỏ ven nước.</t>
         </is>
       </c>
     </row>
@@ -18595,7 +18595,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Goldenback Frog là loài lưỡng cư thuộc họ Chordata, lớp Amphibia, bộ Noctuidae. Chúng có tứ chi ngắn, thân màu vàng kim với nhiều hoa văn; bụng trắng, hai bên đầu có màng nhĩ hơi lồi, da trơn láng với vài mụn cóc, và một lượng nhỏ Tacetite kết tủa trên lưng. Loài này phân bố rộng rãi ở sông ngòi, hồ nước, vùng đầm lầy và các môi trường khác, chủ yếu hoạt động ở những bãi cỏ gần nước.
+          <t>Ếch Lưng Vàng là loài lưỡng cư thuộc họ Chordata, lớp Amphibia, bộ Noctuidae. Chúng có tứ chi ngắn, thân màu vàng kim với nhiều hoa văn; bụng trắng, hai bên đầu có màng nhĩ hơi lồi, da trơn láng với vài mụn cóc, và một lượng nhỏ Tacetite kết tủa trên lưng. Loài này phân bố rộng rãi ở sông ngòi, hồ nước, vùng đầm lầy và các môi trường khác, chủ yếu hoạt động ở những bãi cỏ gần nước.
 Loài có màu vàng kim hiếm và ít phổ biến hơn so với loài màu xanh lục sáng, và số lượng ếch đã suy giảm do môi trường sống bị ô nhiễm.</t>
         </is>
       </c>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Phoenix Butterfly là loài bướm lớn thuộc họ Papilionidae, kích thước tương đương một con bướm thông thường. Mỗi cánh trước của nó có một dải vàng-xanh cong, cánh sau có vài đốm vàng ở giữa, một mảng vàng hình lưỡi liềm ở rìa sau, và một phần nhô ra dài, mảnh như đuôi ở cánh sau, đầu đuôi có màu vàng. Chúng thường hoạt động ở những khu vực cây cối um tùm trong rừng rậm hoặc môi trường tương tự, bay lượn theo cặp trên bầu trời cao, hút mật hoa và rất khó bắt.
+          <t>Bướm Phượng Hoàng là loài bướm lớn thuộc họ Papilionidae, kích thước tương đương một con bướm thông thường. Mỗi cánh trước của nó có một dải vàng-xanh cong, cánh sau có vài đốm vàng ở giữa, một mảng vàng hình lưỡi liềm ở rìa sau, và một phần nhô ra dài, mảnh như đuôi ở cánh sau, đầu đuôi có màu vàng. Chúng thường hoạt động ở những khu vực cây cối um tùm trong rừng rậm hoặc môi trường tương tự, bay lượn theo cặp trên bầu trời cao, hút mật hoa và rất khó bắt.
 Nhờ khả năng sinh sản cao và thích nghi tốt với môi trường, đây là loài phổ biến nhất trong ba loại bướm.</t>
         </is>
       </c>
@@ -18729,8 +18729,8 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Butterfly Lông Đỏ thuộc họ Papilionidae, một loài bướm đuôi én cỡ lớn, kích thước tương đương với loài bướm thông thường. Cánh trước và cánh sau đều màu đỏ, gân cánh đen, viền cánh có vài đốm đỏ, gốc cánh có một lượng nhỏ Tacetite. Chúng thường hoạt động trong những khu rừng rậm rạp hoặc môi trường cây cối um tùm, bay lượn theo cặp trên bầu trời cao, hút mật hoa và rất khó bắt.
-Butterfly Lông Đỏ không thích nghi với môi trường tốt như Phoenix Butterfly, số lượng của chúng bị ảnh hưởng lớn bởi sự thay đổi của môi trường và khí hậu. Do đó, cả số lượng lẫn độ hiếm của loài này đều ở mức trung bình trong ba loại bướm.</t>
+          <t>Bướm Lông Đỏ thuộc họ Papilionidae, một loài bướm đuôi én cỡ lớn, kích thước tương đương với loài bướm thông thường. Cánh trước và cánh sau đều màu đỏ, gân cánh đen, viền cánh có vài đốm đỏ, gốc cánh có một lượng nhỏ Tacetite. Chúng thường hoạt động trong những khu rừng rậm rạp hoặc môi trường cây cối um tùm, bay lượn theo cặp trên bầu trời cao, hút mật hoa và rất khó bắt.
+Bướm Lông Đỏ không thích nghi với môi trường tốt như Bướm Phượng Hoàng, số lượng của chúng bị ảnh hưởng lớn bởi sự thay đổi của môi trường và khí hậu. Do đó, cả số lượng lẫn độ hiếm của loài này đều ở mức trung bình trong ba loại bướm.</t>
         </is>
       </c>
     </row>
@@ -18795,7 +18795,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Butterfly Xanh Lông Xanh thuộc họ Papilionidae, chi Papilio. Đây là loài bướm đuôi én cỡ lớn, kích thước tương đương một con bướm trưởng thành. Cả cánh trước và cánh sau đều có màu đỏ, gân cánh đen, viền cánh điểm vài đốm xanh lam, và một lượng nhỏ Tacetite ở gốc cánh. Chúng thường hoạt động trong các khu rừng rậm rạp hoặc môi trường cây cối um tùm, bay lượn thành đôi trên bầu trời cao, hút mật hoa và rất khó bắt. Đa số bướm Xanh Lông Xanh là con đực, số lượng con cái rất hiếm, dẫn đến khả năng sinh sản thấp. Do đó, đây là loài bướm hiếm nhất và có số lượng ít nhất trong ba loại bướm.</t>
+          <t>Bướm Xanh Lông Xanh thuộc họ Papilionidae, chi Papilio. Đây là loài bướm đuôi én cỡ lớn, kích thước tương đương một con bướm trưởng thành. Cả cánh trước và cánh sau đều có màu đỏ, gân cánh đen, viền cánh điểm vài đốm xanh lam, và một lượng nhỏ Tacetite ở gốc cánh. Chúng thường hoạt động trong các khu rừng rậm rạp hoặc môi trường cây cối um tùm, bay lượn thành đôi trên bầu trời cao, hút mật hoa và rất khó bắt. Đa số bướm Xanh Lông Xanh là con đực, số lượng con cái rất hiếm, dẫn đến khả năng sinh sản thấp. Do đó, đây là loài bướm hiếm nhất và có số lượng ít nhất trong ba loại bướm.</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Tricolor là một trong những loài thú cưng phổ biến nhất trong các gia đình trên toàn thế giới, thuộc họ mèo. Chúng có đầu tròn, mặt ngắn, bộ lông ngắn và bóng mượt với ba màu đen, cam và trắng. Tricolor rất năng động, cần không gian rộng để vận động và thường được tìm thấy ở những khu vực thoáng đãng trong thị trấn.</t>
+          <t>Ba Màu là một trong những loài thú cưng phổ biến nhất trong các gia đình trên toàn thế giới, thuộc họ mèo. Chúng có đầu tròn, mặt ngắn, bộ lông ngắn và bóng mượt với ba màu đen, cam và trắng. Ba Màu rất năng động, cần không gian rộng để vận động và thường được tìm thấy ở những khu vực thoáng đãng trong thị trấn.</t>
         </is>
       </c>
     </row>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Snowwhite là một trong những loài thú cưng phổ biến nhất trên thế giới, thuộc họ mèo. Chúng có đầu tròn, mặt ngắn, toàn thân phủ lông trắng muốt, ngắn và bóng mượt. Snowwhite rất năng động, cần không gian rộng để vận động và thường được tìm thấy ở những khu vực thoáng đãng trong thị trấn.</t>
+          <t>Bạch Tuyết là một trong những loài thú cưng phổ biến nhất trên thế giới, thuộc họ mèo. Chúng có đầu tròn, mặt ngắn, toàn thân phủ lông trắng muốt, ngắn và bóng mượt. Bạch Tuyết rất năng động, cần không gian rộng để vận động và thường được tìm thấy ở những khu vực thoáng đãng trong thị trấn.</t>
         </is>
       </c>
     </row>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Baizhi vẫn giữ gìn cặp nhẫn này từ thời còn học ở Huaxu Academy. Chúng giống hệt nhau về hình dáng và phong cách, chỉ khác đôi chút về mức độ hao mòn. Nguồn gốc của chúng vẫn là một bí ẩn—có người bảo đó là kỷ vật của người thân đã khuất, lại có kẻ khẳng định đó là thiết bị công nghệ &lt;te href=850076&gt;Remnant&lt;/te&gt; mà Baizhi và đội của cô chế tạo để củng cố mối liên kết với &lt;te href=850140&gt;You'tan&lt;/te&gt;.
+          <t>Baizhi vẫn giữ gìn cặp nhẫn này từ thời còn học ở Học viện Huaxu. Chúng giống hệt nhau về hình dáng và phong cách, chỉ khác đôi chút về mức độ hao mòn. Nguồn gốc của chúng vẫn là một bí ẩn—có người bảo đó là kỷ vật của người thân đã khuất, lại có kẻ khẳng định đó là thiết bị công nghệ &lt;te href=850076&gt;Remnant&lt;/te&gt; mà Baizhi và đội của cô chế tạo để củng cố mối liên kết với &lt;te href=850140&gt;You'tan&lt;/te&gt;.
 Dù chẳng ai thực sự hiểu vì sao Baizhi trân trọng đôi nhẫn tưởng chừng bình thường này đến vậy, và cô cũng chẳng buồn giải thích, chỉ riêng Baizhi mới biết ý nghĩa thật sự của chúng. Với cô, chúng là hiện thân cho nỗ lực của đội cũ, là lời nhắc nhở đau đáu về những người đồng đội, người thầy đã hy sinh nơi đồng băng giá xa xôi. Những chiếc nhẫn ấy mang theo lời dạy dỗ, kỳ vọng của họ, thôi thúc cô tiếp nối ý chí và tiếp tục nghiên cứu về Sinh Âm Học Remnant.</t>
         </is>
       </c>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Baizhi đã nghiên cứu kỹ lưỡng các mẫu hành vi của &lt;te href=850140&gt;You'tan&lt;/te&gt; và ghi lại dữ liệu chi tiết. Nhưng vẫn còn nhiều bí ẩn xung quanh sinh vật &lt;te href=850076&gt;Remnant&lt;/te&gt; này: Thành phần của nó là gì? Nó đã xuất hiện như thế nào? Và liệu còn có những sinh vật tương tự khác không? Được truyền cảm hứng từ lời đồng nghiệp, Baizhi bắt tay vào dự án mô hình hóa để tái tạo You'tan. Kết quả là một mô hình phức tạp gồm 205 bộ phận. Người ta nói rằng Baizhi có thể lắp ráp nó hoàn hảo, thậm chí nhắm mắt. Dù không tinh xảo như You'tan thật, mô hình này là một sự phân tích và nỗ lực đầy tham vọng nhằm tái tạo sinh vật từ tần số thành hình dạng vật lý.</t>
+          <t>Baizhi đã nghiên cứu kỹ lưỡng các mô hình hành vi của &lt;te href=850140&gt;You'tan&lt;/te&gt; và ghi chép dữ liệu chi tiết. Nhưng vẫn còn nhiều bí ẩn xung quanh Sinh Vật Dư Vết này: Thành phần cấu tạo của nó là gì? Nó ra đời như thế nào? Và liệu còn những sinh vật tương tự khác không? Được truyền cảm hứng từ lời đồng nghiệp, Baizhi bắt tay vào dự án mô phỏng lại You'tan. Kết quả là một mô hình phức tạp gồm 205 bộ phận. Người ta nói Baizhi có thể lắp ráp nó hoàn hảo ngay cả khi nhắm mắt. Dù không tinh xảo bằng You'tan thật, mô hình này là một sự phân tích và nỗ lực đầy tham vọng nhằm tái tạo sinh vật từ tần số đến hình hài vật lý.</t>
         </is>
       </c>
     </row>
@@ -19713,9 +19713,9 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>&lt;te href=850093&gt;Huanglong&lt;/te&gt; đã trao tặng Huân chương Danh dự này cho toàn đội vì những đóng góp trong lĩnh vực &lt;te href=850076&gt;Remnant&lt;/te&gt; Ecoacoustics và tinh thần nghiên cứu dũng cảm. Là người sống sót duy nhất của đội, Baizhi đã nhận huân chương thay mặt họ và giữ nó từ đó đến nay.
-Đây là sự tưởng nhớ và vinh dự.
-Vẫn còn nhiều vùng đất chưa được khám phá trong lĩnh vực khoa học đang chờ đợi những nhà thám hiểm như họ bước vào và cất lên tiếng nói của mình. Humans sẽ đáp lại tích cực với những tiếng nói đó, đó chính là ý nghĩa của nghiên cứu về "&lt;te href=850076&gt;Remnant Energy&lt;/te&gt;."</t>
+          <t>Các quan chức Huanglong đã trao tặng huy chương danh dự này cho cả đội vì những đóng góp trong lĩnh vực Ecoacoustics của Remnant và tinh thần nghiên cứu dũng cảm. Là người sống sót duy nhất của đội, Baizhi đã nhận huy chương thay cho họ và giữ nó từ đó đến nay.
+Đó là kỷ vật và cũng là niềm vinh dự.
+Vẫn còn vô số vùng đất chưa được khám phá trong khoa học đang chờ đợi những nhà thám hiểm như họ bước vào và cất lên tiếng nói. Con người sẽ đáp lại tiếng nói ấy, và đó chính là ý nghĩa của nghiên cứu về "Năng lượng Remnant".</t>
         </is>
       </c>
     </row>
@@ -19783,8 +19783,8 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Lingyang được ông Qixing của Liondance Troupe tặng chiếc đầu lân này như một biểu tượng của danh dự.
-Lingyang tình cờ gia nhập &lt;te href=850130&gt;Liondance Troupe&lt;/te&gt; từ nhỏ, và những buổi biểu diễn múa lân đã giúp cậu ấy giải phóng bản năng hoang dã, mang lại niềm động viên và phước lành cho cộng đồng. Nó cũng giúp Lingyang hòa nhập với người dân &lt;te href=850091&gt;Jinzhou&lt;/te&gt;.
+          <t>Lingyang được ông Qixing của Đoàn Múa Lân tặng chiếc đầu lân này như một biểu tượng của danh dự.
+Lingyang tình cờ gia nhập &lt;te href=850130&gt;Đoàn Múa Lân&lt;/te&gt; từ nhỏ, và những buổi biểu diễn múa lân đã giúp cậu ấy giải phóng bản năng hoang dã, mang lại niềm động viên và phước lành cho cộng đồng. Nó cũng giúp Lingyang hòa nhập với người dân &lt;te href=850091&gt;Jinzhou&lt;/te&gt;.
 Nhờ sự nỗ lực và luyện tập không ngừng, thân hình nhỏ bé của Lingyang đã có thể thể hiện niềm vui, nỗi buồn, những chuyển động và cả nỗi sợ hãi của chú sư tử.
 Dù giờ đây Lingyang đã là một vũ công lân nổi tiếng ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, cậu ấy vẫn luôn mang theo chiếc đầu lân này bên mình.</t>
         </is>
@@ -19853,7 +19853,7 @@
       <c r="M296" t="inlineStr">
         <is>
           <t>Nướng là phương pháp nấu ăn phổ biến ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, nhưng Lingyang luôn không hài lòng vì than củi có thể át mất hương vị tự nhiên của thịt. Quyết tâm tạo ra điều gì đó độc đáo, anh đã thử nghiệm và cuối cùng hoàn thiện món xiên "tái chín" của riêng mình. Bằng cách kết hợp món "Xiên Jinzhou" được yêu thích với gia vị đơn giản nhưng đậm đà, Lingyang đã giữ được độ mềm mại và mượt mà của thịt, đồng thời mang đến một hương vị mới khiến cả thành phố phải say mê. Dù đã chia sẻ kỹ thuật nấu nướng, bí quyết đạt được độ "tái chín" hoàn hảo của Lingyang vẫn không ai sánh kịp. Món ăn bình dị này đã trở thành tác phẩm đặc trưng nhờ sự tận tâm và sáng tạo của anh. 
-"Muốn biết bí quyết nấu nướng của ta à? Chỉ cần chăm chút từng nguyên liệu và điều chỉnh lửa cho phù hợp. Easy mà!"</t>
+"Muốn biết bí quyết nấu nướng của ta à? Chỉ cần chăm chút từng nguyên liệu và điều chỉnh lửa cho phù hợp. Dễ thôi mà!"</t>
         </is>
       </c>
     </row>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Món đặc sản của Encore, làm từ san hô tím ở &lt;te href=850109&gt;Black Shores&lt;/te&gt;, được nấu kỹ với nhiều nguyên liệu khác nhau. Encore luôn cố tạo ra cái gì đó mới mẻ, và lạ thay, hương vị lại ngon đến bất ngờ. Nhưng trông nó kinh dị đến mức phải rất can đảm mới dám thử. Ngay cả Aalto cũng không dám đụng vào.</t>
+          <t>Món đặc sản của Encore, làm từ san hô tím ở &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt;, được nấu kỹ với nhiều nguyên liệu khác nhau. Encore luôn cố tạo ra cái gì đó mới mẻ, và lạ thay, hương vị lại ngon đến bất ngờ. Nhưng trông nó kinh dị đến mức phải rất can đảm mới dám thử. Ngay cả Aalto cũng không dám đụng vào.</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Aalto đã thêm Dodget riêng của mình vào món đồ chơi chơi khăm này. Nó ra mắt lần đầu trong một dịp sinh nhật của Encore, khiến Camellya không hài lòng với gu đồ chơi của Aalto. Vào mỗi dịp sinh nhật của thành viên &lt;te href=850109&gt;Black Shores&lt;/te&gt;, Encore đều bật bài hát sinh nhật đã ghi âm từ món đồ chơi nhỏ này như một bất ngờ nho nhỏ. Dù sao, những bất ngờ không mong đợi và khó chịu là điều thường xuyên xảy ra trong những chuyến phiêu lưu của họ.</t>
+          <t>Aalto đã thêm chút sáng tạo riêng vào món đồ chơi trêu chọc này. Nó ra mắt lần đầu trong một sinh nhật của Encore, khiến Camellya không hài lòng chút nào về gu đồ chơi của Aalto. Ở mỗi bữa tiệc sinh nhật của thành viên Bờ Đen, Encore đều bật bài hát chúc mừng từ món đồ chơi nhỏ này như một bất ngờ nho nhỏ. Dù sao, những bất ngờ bất ngờ và khó chịu cũng là chuyện thường ngày trong những chuyến phiêu lưu của họ.</t>
         </is>
       </c>
     </row>
@@ -20582,7 +20582,7 @@
       <c r="M307" t="inlineStr">
         <is>
           <t>Một viên ngọc quý từng được khảm vào rồi vỡ tan. 
-Màu xanh nguyên bản giờ bị thay thế bởi sắc đỏ rực rỡ, phơi bày bản chất thật sự. Ngày Dragon Đỏ giáng thế, ngọn lửa thịnh nộ đã thiêu rụi quá khứ dối trá của hắn.</t>
+Màu xanh nguyên bản giờ bị thay thế bởi sắc đỏ rực rỡ, phơi bày bản chất thật sự. Ngày Rồng Đỏ giáng thế, ngọn lửa thịnh nộ đã thiêu rụi quá khứ dối trá của hắn.</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Cái Magnifying Glass Điều Tra này được Cục An Ninh Công Cộng trao cho các &lt;te href=850087&gt;Tuần Tra&lt;/te&gt; mới. Tuy nhỏ nhưng rất mạnh, giúp họ tìm ra manh mối ẩn giấu. Yinlin, với tư cách là đặc vụ bí mật, không dùng nó thường xuyên. Nhưng nó vẫn mang ý nghĩa đặc biệt với cô: Là vật tưởng nhớ cha mẹ đã khuất và lời nhắc nhở về thân phận thật của mình.</t>
+          <t>Cái Kính Lúp Điều Tra này được Cục An Ninh Công Cộng trao cho các &lt;te href=850087&gt;Tuần Tra&lt;/te&gt; mới. Tuy nhỏ nhưng rất mạnh, giúp họ tìm ra manh mối ẩn giấu. Yinlin, với tư cách là đặc vụ bí mật, không dùng nó thường xuyên. Nhưng nó vẫn mang ý nghĩa đặc biệt với cô: Là vật tưởng nhớ cha mẹ đã khuất và lời nhắc nhở về thân phận thật của mình.</t>
         </is>
       </c>
     </row>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Một chiếc găng tay chiến đấu cổ xưa, đã ngừng sản xuất từ lâu. Bề ngoài cho thấy dấu hiệu hao mòn rõ rệt do sử dụng nhiều, hầu hết các bộ phận bên trong đều lộ ra. Thế nhưng, nó vẫn được lau chùi và bảo dưỡng cẩn thận đến mức từng đường Dodget và khe hở trên vũ khí vẫn còn sắc Dodget.</t>
+          <t>Một chiếc găng tay chiến đấu cổ xưa, đã ngừng sản xuất từ lâu. Bề ngoài cho thấy dấu hiệu hao mòn rõ rệt do sử dụng nhiều, hầu hết các bộ phận bên trong đều lộ ra. Thế nhưng, nó vẫn được lau chùi và bảo dưỡng cẩn thận đến mức từng đường nét và khe hở trên vũ khí vẫn còn sắc nét.</t>
         </is>
       </c>
     </row>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>&lt;te href=850084&gt;Magistrate&lt;/te&gt; luôn bị công việc dồn dập. Từ quân sự, phòng thủ thành phố đến an ninh dân sự, cô ấy phải lo liệu tất cả. Văn phòng Thành Phố lúc nào cũng chất đầy hồ sơ chờ xử lý, nhưng chỉ riêng chúng thì không đủ để đưa ra phán quyết chính xác. Jinhsi thích có mặt trực tiếp để lắng nghe nguyện vọng của người dân. Để làm được điều đó, cô đã nhờ &lt;te href=850092&gt;Huaxu Academy&lt;/te&gt; tạo ra một danh sách công việc điện tử mà cô có thể truy cập mọi lúc, giúp cô xem xét hồ sơ trong khi xử lý các nhiệm vụ khác.</t>
+          <t>&lt;te href=850084&gt;Magistrate&lt;/te&gt; luôn bị công việc dồn dập. Từ quân sự, phòng thủ thành phố đến an ninh dân sự, cô ấy phải lo liệu tất cả. Văn phòng Thành Phố lúc nào cũng chất đầy hồ sơ chờ xử lý, nhưng chỉ riêng chúng thì không đủ để đưa ra phán quyết chính xác. Jinhsi thích có mặt trực tiếp để lắng nghe nguyện vọng của người dân. Để làm được điều đó, cô đã nhờ &lt;te href=850092&gt;Học Viện Huaxu&lt;/te&gt; tạo ra một danh sách công việc điện tử mà cô có thể truy cập mọi lúc, giúp cô xem xét hồ sơ trong khi xử lý các nhiệm vụ khác.</t>
         </is>
       </c>
     </row>
@@ -21523,10 +21523,10 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Thẻ nhân viên của Xiangli Yao ghi rõ: "Xiangli Yao, Nghiên cứu viên, &lt;te href=850092&gt;Huaxu Academy&lt;/te&gt;," in gọn gàng. 
+          <t>Thẻ nhân viên của Xiangli Yao ghi rõ: "Xiangli Yao, Nghiên cứu viên, &lt;te href=850092&gt;Học viện Huaxu&lt;/te&gt;," in gọn gàng. 
 Phải mất thêm một năm so với các đồng môn ở Học viện, Xiangli Yao mới được đeo chiếc thẻ đơn sơ, gắn chip nhận dạng này trên ngực—một năm trước, cậu đã chọn không tham gia kỳ thi của Học viện, rời khỏi &lt;te href=850091&gt;Jinzhou&lt;/te&gt; để tìm kiếm câu trả lời cho những câu hỏi sâu xa về cuộc đời. Khi đó, cậu chỉ là một thiếu niên đứng trước ngã rẽ, không biết nên đi theo con đường của cha mẹ hay tự mình khai phá. Nhưng một năm sau, trái tim đã dẫn cậu đến một lối đi hoàn toàn khác biệt với họ...
 Ngày đầu tiên trở thành nghiên cứu viên, Xiangli Yao đặt thẻ nhân viên ngay ngắn trên bàn, mở cửa sổ và để tiếng ồn ào của thành phố Jinzhou ùa vào.
-"Huaxu Academy... Nơi này cũng đẹp đấy."</t>
+"Học viện Huaxu... Nơi này cũng đẹp đấy."</t>
         </is>
       </c>
     </row>
@@ -22119,7 +22119,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Ngày Jiyan nhập ngũ, mẹ anh đã tặng một chiếc hộp thuốc hình Terminal. Bà lo sợ anh sẽ trở thành kẻ sát nhân trên chiến trường và nhắc nhở anh về vai trò của một người chữa trị. Sau này, anh dùng nó để đựng những loại thuốc cần thiết, phòng khi cần đến.</t>
+          <t>Ngày Jiyan nhập ngũ, mẹ anh đã tặng một chiếc hộp thuốc hình Thiết bị đầu cuối. Bà lo sợ anh sẽ trở thành kẻ sát nhân trên chiến trường và nhắc nhở anh về vai trò của một người chữa trị. Sau này, anh dùng nó để đựng những loại thuốc cần thiết, phòng khi cần đến.</t>
         </is>
       </c>
     </row>
@@ -22444,7 +22444,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Verina trân trọng chiếc kính bảo hộ thám hiểm của Hiệp hội Tiên phong, những di vật của một chuyến đi và kỷ niệm ấm áp như &lt;te href=850133&gt;Starflower&lt;/te&gt;. Dù giờ đây không còn tác dụng phát hiện nguy hiểm, chúng vẫn mang giá trị tình cảm sâu sắc với cô.</t>
+          <t>Verina trân trọng chiếc kính bảo hộ thám hiểm của Hiệp hội Tiên phong, những di vật của một chuyến đi và kỷ niệm ấm áp như &lt;te href=850133&gt;Hoa Sao&lt;/te&gt;. Dù giờ đây không còn tác dụng phát hiện nguy hiểm, chúng vẫn mang giá trị tình cảm sâu sắc với cô.</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Mỗi khi Verina tham gia thám hiểm hay dã ngoại, cô bé luôn tìm đường tắt để khám phá hoặc tránh Dodge nguy hiểm rình rập nhờ sự giúp đỡ của những người bạn thực vật. Verina vẽ lại tất cả. Đằng sau tấm bản đồ nguệch ngoạc ấy là những bài học quý giá, minh chứng cho việc Verina đang đi theo bước chân của mẹ mình.</t>
+          <t>Mỗi khi Verina tham gia thám hiểm hay dã ngoại, cô bé luôn tìm đường tắt để khám phá hoặc tránh né nguy hiểm rình rập nhờ sự giúp đỡ của những người bạn thực vật. Verina vẽ lại tất cả. Đằng sau tấm bản đồ nguệch ngoạc ấy là những bài học quý giá, minh chứng cho việc Verina đang đi theo bước chân của mẹ mình.</t>
         </is>
       </c>
     </row>
@@ -22845,8 +22845,8 @@
       <c r="M341" t="inlineStr">
         <is>
           <t>Một bản ghi được tạo từ chất liệu thấm đẫm &lt;te href=850076&gt;Năng Lượng Tàn Dư&lt;/te&gt;, có khả năng lưu trữ gần như vô hạn. 
-Nó chứa đựng mọi âm thanh mà The Shorekeeper từng thu thập từ hành tinh này—tiếng bão gào, gió hú, tiếng chim kêu, cá voi hát. Những bản nhạc trải dài vô số kỷ nguyên và những lời thì thầm bằng hơn 50 ngôn ngữ... Mỗi âm thanh là minh chứng cho điều kỳ diệu của sự tồn tại, dấu vết của sự sống, khoa học và những nền văn minh từng hưng thịnh.
-The Shorekeeper đã lưu giữ bản song tấu của cô với Rover ở cuối bản ghi này. Với cô, giai điệu ấy là bằng chứng cho sự tồn tại của họ. Chừng nào bản ghi còn tồn tại và âm thanh của hành tinh này còn vang vọng, nội dung của nó sẽ mãi mãi được mở rộng.</t>
+Nó chứa đựng mọi âm thanh mà Người Gác Bờ từng thu thập từ hành tinh này—tiếng bão gào, gió hú, tiếng chim kêu, cá voi hát. Những bản nhạc trải dài vô số kỷ nguyên và những lời thì thầm bằng hơn 50 ngôn ngữ... Mỗi âm thanh là minh chứng cho điều kỳ diệu của sự tồn tại, dấu vết của sự sống, khoa học và những nền văn minh từng hưng thịnh.
+Người Gác Bờ đã lưu giữ bản song tấu của cô với Rover ở cuối bản ghi này. Với cô, giai điệu ấy là bằng chứng cho sự tồn tại của họ. Chừng nào bản ghi còn tồn tại và âm thanh của hành tinh này còn vang vọng, nội dung của nó sẽ mãi mãi được mở rộng.</t>
         </is>
       </c>
     </row>
@@ -23119,8 +23119,8 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>"Sức nặng của &lt;te href=850091&gt;Jinzhou&lt;/te&gt; vượt xa sức chịu đựng của một mô hình, nhưng bạn có thể cảm nhận gánh nặng bảo vệ Jinzhou một cách chân thực khi sở hữu mô hình Bức Wall Bảo Vệ này." 
-&lt;te href=850085&gt;Ministry of Development&lt;/te&gt; đã hợp tác với một công ty đồ chơi để tạo ra mô hình này, nghe nói là phiên bản giới hạn đầu tiên mà Taoqi đích thân lấy từ một ông trùm đồ chơi danh tiếng.</t>
+          <t>"Sức nặng của &lt;te href=850091&gt;Jinzhou&lt;/te&gt; vượt xa sức chịu đựng của một mô hình, nhưng bạn có thể cảm nhận gánh nặng bảo vệ Jinzhou một cách chân thực khi sở hữu mô hình Bức Tường Bảo Vệ này." 
+&lt;te href=850085&gt;Bộ Phát Triển&lt;/te&gt; đã hợp tác với một công ty đồ chơi để tạo ra mô hình này, nghe nói là phiên bản giới hạn đầu tiên mà Taoqi đích thân lấy từ một ông trùm đồ chơi danh tiếng.</t>
         </is>
       </c>
     </row>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Mô-đun dữ liệu tải về Terminal chứa những quan sát và suy nghĩ của Taoqi về &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, từ những kỷ niệm tuổi thơ đến quyết định bảo vệ thành phố hiện tại. Mọi chi tiết đều được ghi chép tỉ mỉ trong thiết bị nhỏ nhưng mạnh mẽ này. Biết đâu một ngày, nó sẽ thay đổi vận mệnh của Jinzhou.</t>
+          <t>Mô-đun dữ liệu tải về Thiết bị đầu cuối chứa những quan sát và suy nghĩ của Taoqi về &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, từ những kỷ niệm tuổi thơ đến quyết định bảo vệ thành phố hiện tại. Mọi chi tiết đều được ghi chép tỉ mỉ trong thiết bị nhỏ nhưng mạnh mẽ này. Biết đâu một ngày, nó sẽ thay đổi vận mệnh của Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -23515,7 +23515,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Một chiếc vòng tay giám sát phổ tần số do &lt;te href=850109&gt;Black Shores&lt;/te&gt; thiết kế, được tạo ra theo yêu cầu kiên quyết của Camellya.
+          <t>Một chiếc vòng tay giám sát phổ tần số do &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt; thiết kế, được tạo ra theo yêu cầu kiên quyết của Camellya.
 Thiết kế của nó giống như món quà quý giá từ thời xa xưa, trang bị tính năng theo dõi tương tự để người đeo luôn được biết vị trí và an toàn từ xa.
 Camellya hiểu rằng cô không còn là Quý Cô Flora của ngày trước, và cũng không muốn như vậy. Những ngày theo dõi {PlayerName} đã qua, nhưng có sao đâu? Cả hai sẽ làm những gì khiến mình hạnh phúc.
 Với cô, đây là chiếc neo duy nhất trong biển vô nghĩa vô tận này.</t>
@@ -23587,7 +23587,7 @@
       <c r="M352" t="inlineStr">
         <is>
           <t>Bông hoa dành tặng một người đặc biệt.
-Dù là thủ lĩnh, &lt;te href=850111&gt;Modulator&lt;/te&gt;, hay giờ đây là Rover – anh hùng của &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, một người dẫn đường… Camellya chưa bao giờ quan tâm đến danh xưng hay trách nhiệm đi kèm. Nhưng nàng biết mình không thể, và sẽ không bao giờ để quan điểm cá nhân che mờ phán đoán của {Male=anh ấy;Female=cô ấy}.
+Dù là thủ lĩnh, &lt;te href=850111&gt;Modulator&lt;/te&gt;, hay giờ đây là Rover – anh hùng của &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, một người dẫn đường… Camellya chưa bao giờ quan tâm đến danh xưng hay trách nhiệm đi kèm. Nhưng nàng biết mình không thể, và sẽ không bao giờ để quan điểm cá nhân che mờ phán đoán của {Male=his;Female=her}.
 Vì thế, hãy để bông hoa vĩnh cửu này thay lời nói hộ tấm lòng nàng.
 "Nó chỉ nở vì người, mãi mãi và vĩnh hằng."</t>
         </is>
@@ -23657,7 +23657,7 @@
       <c r="M353" t="inlineStr">
         <is>
           <t>Cantarella luôn mang theo lọ thuốc nhỏ này, được trang trí bằng viên ngọc lam sáng rực như viên ngọc cô đeo trên người—biểu tượng của quyền lực. Bên trong là một loại thuốc đặc biệt, do chính tay cô pha chế để xua tan mệt mỏi và xoa dịu những cơn ác mộng.
-Nhưng kể từ khi ngươi đưa cô rời khỏi Sea of Ghosts, những cơn ác mộng đã chấm dứt.
+Nhưng kể từ khi ngươi đưa cô rời khỏi Biển Ma, những cơn ác mộng đã chấm dứt.
 Giờ đây, chiếc lọ này chứa đựng sự chân thành và dịu dàng hiếm có của cô, như ánh sáng dịu nhẹ xuyên qua vực thẳm, phản chiếu những lời thì thầm ẩn giấu trong tiếng sóng vỗ. Nó đã trở thành biểu tượng cho lòng tin mà Cantarella dành cho ngươi—kẻ đã vượt qua những dòng nước tối tăm để chạm đến sâu thẳm trái tim cô.</t>
         </is>
       </c>
@@ -23793,8 +23793,8 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>&lt;te href=850124&gt;Vệ sĩ&lt;/te&gt; của &lt;te href=850084&gt;Magistrate&lt;/te&gt; &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, nổi tiếng với tính cách lạnh lùng.
-Từng được mệnh danh là Asura của Calamity, Sanhua giờ đây là một người bảo vệ trầm lặng. Cô đã học cách giữ bình tĩnh bên trong giữa những tần số hỗn loạn, và những điều từng khiến cô sợ hãi giờ đây trở thành động lực cho quyết tâm của cô.</t>
+          <t>Vệ sĩ của &lt;te href=850084&gt;Magistrate&lt;/te&gt; &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, nổi tiếng với tính cách lạnh lùng.
+Từng được mệnh danh là Asura của Tai Họa, giờ đây Sanhua là một người bảo vệ trầm lặng. Cô đã học cách giữ bình tĩnh bên trong giữa những tần số hỗn loạn, và những thứ từng khiến cô sợ hãi giờ đây lại tiếp thêm quyết tâm cho cô.</t>
         </is>
       </c>
     </row>
@@ -23860,8 +23860,8 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Baizhi là nhà nghiên cứu về &lt;te href=850076&gt;Remnant&lt;/te&gt; Ecoacoustics.
-Ước nguyện từng không thành của Baizhi giờ đây đã trở thành người bạn đồng hành trung thành của cô. Sinh vật Remnant You'tan là nguồn sức mạnh chữa lành của cô, và là trọng tâm nghiên cứu suốt đời.</t>
+          <t>Baizhi là nhà nghiên cứu về Sinh Âm Dư Vết.
+Ước nguyện xưa kia chưa thành của Baizhi giờ đã hóa thân thành người bạn đồng hành trung thành. Sinh Vật Dư Vết You'tan là nguồn sức mạnh chữa lành của cô, và cũng là trọng tâm nghiên cứu cả đời.</t>
         </is>
       </c>
     </row>
@@ -23929,8 +23929,8 @@
       <c r="M357" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Baizhi cho thấy dao động elip ổn định trong miền Thời Gian. Không phát hiện thông số bất thường trong mẫu thử.
-Độ Phản Ứng Cộng Hưởng: High. Tần số của Baizhi có độ ổn định cao, hiện không có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
-Baizhi không có tiền sử Quá Tải, nên không cần thiết phải tư vấn. Tuy nhiên, do mối liên kết chặt chẽ giữa Baizhi và &lt;te href=850076&gt;Sinh Vật Remnant&lt;/te&gt; của cô, nên test định kỳ tình trạng của Sinh Vật Remnant để phòng ngừa rủi ro tiềm ẩn.</t>
+Độ Phản Ứng Cộng Hưởng: Cao. Tần số của Baizhi có độ ổn định cao, hiện không có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
+Baizhi không có tiền sử Quá Tải, nên không cần thiết phải tư vấn. Tuy nhiên, do mối liên kết chặt chẽ giữa Baizhi và &lt;te href=850076&gt;Sinh Vật Tàn Tích&lt;/te&gt; của cô, nên kiểm tra định kỳ tình trạng của Sinh Vật Tàn Tích để phòng ngừa rủi ro tiềm ẩn.</t>
         </is>
       </c>
     </row>
@@ -23995,7 +23995,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Lingyang, một thành viên nhiệt huyết và dũng cảm của &lt;te href=850130&gt;Liondance Troupe&lt;/te&gt; ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, là một vị khách chân thành và giàu lòng trắc ẩn đến từ cộng đồng loài người, sở hữu khả năng thể chất phi thường. Cậu luôn hứng thú với con người và thể hiện điều đó một cách tự nhiên. Với phong cách độc đáo của mình, cậu chính là hiện thân của tinh thần &lt;te href=850131&gt;Múa Lân&lt;/te&gt;.</t>
+          <t>Lingyang, một thành viên nhiệt huyết và dũng cảm của &lt;te href=850130&gt;Đoàn Múa Lân&lt;/te&gt; ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, là một vị khách chân thành và giàu lòng trắc ẩn đến từ cộng đồng loài người, sở hữu khả năng thể chất phi thường. Cậu luôn hứng thú với con người và thể hiện điều đó một cách tự nhiên. Với phong cách độc đáo của mình, cậu chính là hiện thân của tinh thần &lt;te href=850131&gt;Múa Lân&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       <c r="M359" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Zhezhi có mô hình đều đặn với vài dao động bất thường ngắn. Theo dõi dài hạn miền Thời Gian cho thấy sóng vẫn ổn định. Kết quả kiểm tra nằm trong ngưỡng bình thường.
-Mức Độ Cộng Hưởng Tới Hạn: Thường. Tuy nhiên, tần số của Zhezhi thể hiện độ ổn định thấp, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; cao.
+Mức Độ Cộng Hưởng Tới Hạn: Bình thường. Tuy nhiên, tần số của Zhezhi thể hiện độ ổn định thấp, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; cao.
 Hồ sơ không ghi nhận tiền sử Quá Tải.
 Khuyến nghị kiểm tra định kỳ và tư vấn tâm lý.</t>
         </is>
@@ -24139,11 +24139,11 @@
         <is>
           <t>["Trích từ Hồ Sơ Nội Bộ Gia Tộc Montelli - Quyền Truy Cập Được Chia Sẻ]
 Mật danh: Opal
-Biểu đồ dạng sóng của thành viên này cho thấy dao động hình elip. Mô hình miền thời gian đều đặn, không phát hiện dấu hiệu dao động bất thường. Kết quả test được đánh giá nằm trong giai đoạn bình thường.
-Độ Tới Hạn Cộng Hưởng: High. Thành viên này sở hữu độ ổn định cao với rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; cực thấp.
+Biểu đồ dạng sóng của thành viên này cho thấy dao động hình elip. Mô hình miền thời gian đều đặn, không phát hiện dấu hiệu dao động bất thường. Kết quả kiểm tra được đánh giá nằm trong giai đoạn bình thường.
+Độ Tới Hạn Cộng Hưởng: Cao. Thành viên này sở hữu độ ổn định cao với rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; cực thấp.
 Hồ sơ không ghi nhận tiền sử Quá Tải.
 Hiện tại không cần thiết phải tư vấn tâm lý.
-&lt;i&gt;Thật tao nhã làm sao! Quý bà Carlo... Không, thành viên này luôn thể hiện quá đỗi hoàn hảo, ngay cả trong bài test này... Quả là quá đỗi tao nhã!&lt;/i&gt;</t>
+&lt;i&gt;Thật tao nhã làm sao! Quý bà Carlo... Không, thành viên này luôn thể hiện quá đỗi hoàn hảo, ngay cả trong bài kiểm tra này... Quả là quá đỗi tao nhã!&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -24278,7 +24278,7 @@
       <c r="M362" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Chixia cho thấy dao động elip ổn định trong miền Thời gian, không có dấu hiệu bất thường. Sau kiểm tra, tất cả kết quả đều nằm trong ngưỡng bình thường. 
-Độ Tới Hạn Cộng Hưởng: High. Tần số của Chixia thể hiện độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
+Độ Tới Hạn Cộng Hưởng: Cao. Tần số của Chixia thể hiện độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
 Chixia chưa từng có tiền sử Quá Tải. Kiểm tra định kỳ được khuyến nghị, còn tư vấn tâm lý hiện tại chưa cần thiết.</t>
         </is>
       </c>
@@ -24344,7 +24344,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Một cô bé đi cùng hai con Wooly đen trắng. Encore, cố vấn đến từ &lt;te href=850109&gt;Black Shores&lt;/te&gt;, mơ ước tạo ra những câu chuyện hạnh phúc bằng kẹo, cổ tích và trí tưởng tượng của mình.</t>
+          <t>Một cô bé đi cùng hai con Wooly đen trắng. Encore, cố vấn đến từ &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt;, mơ ước tạo ra những câu chuyện hạnh phúc bằng kẹo, cổ tích và trí tưởng tượng của mình.</t>
         </is>
       </c>
     </row>
@@ -24483,7 +24483,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Mortefi, chuyên gia hàng đầu về Nghiên cứu Ứng dụng Tacetite và là thành viên của Department An ninh Học viện, sở hữu khả năng độc đáo biến sự uất ức tích tụ thành ngọn lửa thiêu đốt.
+          <t>Mortefi, chuyên gia hàng đầu về Nghiên cứu Ứng dụng Tacetite và là thành viên của Cục An ninh Học viện, sở hữu khả năng độc đáo biến sự uất ức tích tụ thành ngọn lửa thiêu đốt.
 Từ cơn thịnh nộ bùng cháy thiêu rụi tất cả, rồng đỏ sẽ giáng thế.</t>
         </is>
       </c>
@@ -24693,15 +24693,15 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>[Đơn Xin Dừng Chương Trình "Freedom Vui Đùa" Của &lt;te href=850108&gt;Đoàn Kẻ Ngốc&lt;/te&gt; Tại &lt;te href=850097&gt;Ragunna&lt;/te&gt;]
+          <t>[Đơn Xin Dừng Chương Trình "Tự Do Vui Đùa" Của &lt;te href=850108&gt;Đoàn Kẻ Ngốc&lt;/te&gt; Tại &lt;te href=850097&gt;Ragunna&lt;/te&gt;]
 ...
 Nghệ Sĩ Chính: Brant
-Biểu đồ dạng sóng của đối tượng cho thấy dao động hình elip. Mô hình miền thời gian đều đặn, không phát hiện dấu hiệu dao động bất thường. Kết quả test nằm trong phạm vi pha bình thường.
-Độ Ổn Định Cộng Hưởng: High. Đối tượng thử nghiệm này thể hiện độ ổn định cao với nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; thấp.
+Biểu đồ dạng sóng của đối tượng cho thấy dao động hình elip. Mô hình miền thời gian đều đặn, không phát hiện dấu hiệu dao động bất thường. Kết quả kiểm tra nằm trong phạm vi pha bình thường.
+Độ Ổn Định Cộng Hưởng: Cao. Đối tượng thử nghiệm này thể hiện độ ổn định cao với nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; thấp.
 Hồ sơ ghi nhận không có tiền sử Quá Tải.
 ...
 Kết Quả Phê Duyệt: Ổn Định. Đơn xin của Đoàn Kẻ Ngốc đã được chấp thuận. Họ sẽ chịu trách nhiệm hoàn toàn cho mọi sự cố bất ngờ trong buổi biểu diễn.
-&lt;i&gt;Ghi chú từ một vị thuyền trưởng nào đó: Đánh dấu lời ta đi, sẽ chẳng có gì trục trặc đâu!&lt;/i&gt;</t>
+&lt;i&gt;Ghi chú từ một vị thuyền trưởng nào đó: Đánh dấu lời tao đi, sẽ chẳng có gì trục trặc đâu!&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -24775,7 +24775,7 @@
           <t>Ghi chú của Bác sĩ Đoàn Benir (Không đánh số)
 Tôi vẫn nhớ như in đêm đó, như thể mới chỉ xảy ra ngày hôm qua. Đây là thử thách thực sự đầu tiên của tôi sau khi gia nhập đoàn. Mây đen bao phủ biển cả, mưa như trút nước, những con sóng khổng lồ đe dọa nhấn chìm con tàu bất cứ lúc nào. Chúng tôi bị quăng quật như những mảnh gỗ trôi, người lái tàu lạc mất trong hỗn loạn, con tàu xoay vòng trong bão tố. Tôi co rúm trong cabin, run rẩy vì nỗi sợ thấm vào từng thớ thịt.
 Rồi tôi nhìn thấy ông.
-Ở đó, trên đỉnh cột buồm, thuyền trưởng đứng hiên ngang. &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; trên ngực ông sáng rực như ngọn lửa Thánh Elmo, một ngọn hải đăng chỉ đường cho chúng tôi.
+Ở đó, trên đỉnh cột buồm, thuyền trưởng đứng hiên ngang. &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; trên ngực ông sáng rực như ngọn lửa Thánh Elmo, một ngọn hải đăng chỉ đường cho chúng tôi.
 "Bình tĩnh nào, các bạn!" Tôi nghe thấy giọng ông át cả tiếng gió gào thét, "Nghe lệnh của ta! Bẻ lái sang mạn phải!"
 Toàn bộ thủy thủ đoàn lập tức tập hợp, sự hỗn loạn biến mất khi họ trở về vị trí với tinh thần tập trung hơn. Tôi nhanh chóng ghi lại trong sổ: Dù không có công cụ để xác nhận, nhưng tôi chắc chắn một điều—Thuyền trưởng Brant là một Resonator bẩm sinh. Ngọn lửa ông tạo ra có thể soi sáng con đường cho chúng ta, ngay cả trong bóng tối bao trùm biển cả!
 &lt;i&gt;Thật thú vị, tôi thường thấy thuyền trưởng xoay vòng trên không trong trận chiến. Đó có phải là mẹo để tăng cường khả năng định hướng, hay bí quyết lèo lái trên biển của ông? Tôi rất muốn có ai đó dám hỏi ông. Tôi đang rất tò mò!&lt;/i&gt;</t>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Nhà Nghiên cứu Chính tại &lt;te href=850091&gt;Jinzhou&lt;/te&gt; &lt;te href=850092&gt;Huaxu Academy&lt;/te&gt;, đồng thời là nhà khoa học đa ngành trẻ nhất của Học viện. 
+          <t>Nhà Nghiên cứu Chính tại &lt;te href=850091&gt;Jinzhou&lt;/te&gt; &lt;te href=850092&gt;Học viện Huaxu&lt;/te&gt;, đồng thời là nhà khoa học đa ngành trẻ nhất của Học viện. 
 Một tâm hồn dịu dàng với trí tuệ sắc bén, niềm đam mê không ngừng nghỉ với Cơ học Tự động luôn mang lại những phát hiện và hiểu biết mang tính xây dựng.</t>
         </is>
       </c>
@@ -25253,7 +25253,7 @@
       <c r="M376" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Xiangli Yao có dao động hình elip. Mô hình miền Thời Gian ổn định, không xuất hiện sóng bất thường.
-Mức Độ Cộng Hưởng Tới Hạn: High. Tần số của Xiangli Yao thể hiện độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
+Mức Độ Cộng Hưởng Tới Hạn: Cao. Tần số của Xiangli Yao thể hiện độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
 Hồ sơ ghi nhận không có tiền sử Quá Tải.
 Khuyến nghị kiểm tra định kỳ, hiện không cần tư vấn tâm lý.</t>
         </is>
@@ -25457,7 +25457,7 @@
       <c r="M379" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Aalto cho thấy dao động elip ổn định trong miền Thời Gian, không có dấu hiệu bất thường. Kiểm tra cho thấy tất cả kết quả đều nằm trong ngưỡng bình thường.
-Mức Độ Cộng Hưởng Tới Hạn: Medium. Tần số của Resonator Aalto thể hiện độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; thấp.
+Mức Độ Cộng Hưởng Tới Hạn: Trung bình. Tần số của Resonator Aalto thể hiện độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; thấp.
 Resonator Aalto đã biến mất giữa chừng trong quá trình chẩn đoán Quá Tải, do đó không thu thập được lịch sử Quá Tải.</t>
         </is>
       </c>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Jiyan, thủ lĩnh của &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt;, hành động nhanh nhẹn và quyết đoán với lòng chính nghĩa. Anh sở hữu khả năng triệu hồi một Qingloong hùng mạnh từ gió, khiến anh trở nên bất khả chiến bại trên chiến trường.</t>
+          <t>Jiyan, thủ lĩnh của &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt;, hành động nhanh nhẹn và quyết đoán với lòng chính nghĩa. Anh sở hữu khả năng triệu hồi một Thanh Long hùng mạnh từ gió, khiến anh trở nên bất khả chiến bại trên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -25657,7 +25657,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Jianxin, một nữ đạo sĩ và truyền nhân của &lt;te href=850134&gt;Fengyiquan&lt;/te&gt;, đã cống hiến cả cuộc đời để chinh phục võ học đỉnh cao. Với khả năng thu nhận và chuyển hóa Khí xung quanh, cô có thể tạo ra những lá chắn bảo vệ, thanh tẩy cả thân tâm.</t>
+          <t>Jianxin, một nữ đạo sĩ và truyền nhân của &lt;te href=850134&gt;Phong Ý Quyền&lt;/te&gt;, đã cống hiến cả cuộc đời để chinh phục võ học đỉnh cao. Với khả năng thu nhận và chuyển hóa Khí xung quanh, cô có thể tạo ra những lá chắn bảo vệ, thanh tẩy cả thân tâm.</t>
         </is>
       </c>
     </row>
@@ -25725,8 +25725,8 @@
       <c r="M383" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Jianxin cho thấy miền Thời Gian ổn định, khớp hoàn hảo với các mẫu dao động tiêu chuẩn. Không phát hiện thông số bất thường trong mẫu thử.
-Độ Phản Ứng Cộng Hưởng: High. Tần số của Jianxin có độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
-Jianxin không có tiền sử Quá Tải. Không cần thiết phải tư vấn hay test định kỳ.</t>
+Độ Phản Ứng Cộng Hưởng: Cao. Tần số của Jianxin có độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
+Jianxin không có tiền sử Quá Tải. Không cần thiết phải tư vấn hay kiểm tra định kỳ.</t>
         </is>
       </c>
     </row>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Journal của Veron Toccata—Trưởng gia tộc Toccata
+          <t>Nhật ký của Veron Toccata—Trưởng gia tộc Toccata
 Tôi không biết đây là phước lành hay lời nguyền giáng xuống con mình.
 Con bé đã thành thạo vô số nhạc cụ một cách dễ dàng. Nó bảo với tôi rằng những nốt nhạc trên bản nhạc không chỉ là âm thanh, mà còn là một chuỗi những khung cảnh: đó là câu chuyện của những nhạc cụ và người chơi chúng... Nó nắm tay tôi và chia sẻ khả năng cảm nhận ấy, và chính lúc đó, tôi phát hiện Ciaccona có thể tái tạo những khía cạnh của thế giới qua giai điệu. Đó là một thế giới do chính con bé tạo ra.
 &lt;i&gt;Chỉ cần cảm nhận được những giai điệu ấy, Ciaccona có thể biến thơ ca và âm nhạc của mình thành bất cứ thứ gì. Con bé có sự tò mò bẩm sinh với mọi thứ, khiến nó dễ dàng đồng cảm với câu chuyện và trải nghiệm của người khác. Tôi lo sợ món quà này sẽ mang lại bất hạnh cho con. Rằng một ngày nào đó, nó sẽ nghe thấy những tiếng vọng ẩn mình trong bóng tối.&lt;/i&gt;</t>
@@ -25932,7 +25932,7 @@
       <c r="M386" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Verina cho thấy dao động hình elip ổn định trong miền thời gian, không có dạng sóng bất thường. Kết quả kiểm tra đều nằm trong giới hạn bình thường.
-Mức Độ Cộng Hưởng Tới Hạn: Low, độ ổn định cao. Kết quả kiểm tra nằm trong giới hạn bình thường, không có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
+Mức Độ Cộng Hưởng Tới Hạn: Thấp, độ ổn định cao. Kết quả kiểm tra nằm trong giới hạn bình thường, không có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
 &lt;i&gt;Ghi chú: Trạng thái cảm xúc và ý chí của Verina nhìn chung rất ổn định, chỉ dao động nhẹ và ngắn khi cô rời xa môi trường tự nhiên. Kết quả kiểm tra cho thấy các thực vật cộng sinh của cô có khả năng truyền một dải tần số đặc biệt đến Verina, giúp cô nhanh chóng trở lại trạng thái tinh thần ổn định. Đây là một trường hợp hiếm gặp trong mối quan hệ giữa Resonator và thực vật cộng sinh, có giá trị tham khảo cho các nghiên cứu liên quan.&lt;/i&gt;</t>
         </is>
       </c>
@@ -26069,7 +26069,7 @@
       <c r="M388" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Lumi cho thấy dao động hình elip. Mô hình miền thời gian đều đặn, không phát hiện sóng bất thường.
-Độ Ổn Định Cộng Hưởng: High. Lumi sở hữu độ ổn định cao với nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
+Độ Ổn Định Cộng Hưởng: Cao. Lumi sở hữu độ ổn định cao với nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
 Hồ sơ cho thấy không có tiền sử Quá Tải.
 Khuyến nghị kiểm tra định kỳ, hiện không cần tư vấn tâm lý.</t>
         </is>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>The Shorekeeper, người bảo vệ &lt;te href=850109&gt;Bờ Đen&lt;/te&gt;—danh xưng này từng là tất cả đối với cô ấy. 
+          <t>Người Gác Bờ, người bảo vệ &lt;te href=850109&gt;Bờ Đen&lt;/te&gt;—danh xưng này từng là tất cả đối với cô ấy. 
 Nhưng khát khao, mối quan hệ, cảm xúc... Cô ấy chỉ thực sự hiểu ra những điều đó sau khi gặp cậu.</t>
         </is>
       </c>
@@ -26203,7 +26203,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Phoebe, &lt;te href=850100&gt;Acolyte&lt;/te&gt; của &lt;te href=850099&gt;Giáo Đoàn Vực Sâu&lt;/te&gt;, là một thiếu nữ với lòng thành kính lặng thầm. Với trái tim nhân hậu, cô luôn tận tụy hoàn thành nhiệm vụ. Những lời cầu nguyện của cô, như ánh sáng mà cô mang theo, đem lại sự an ủi và bình yên cho tất cả.</t>
+          <t>Phoebe, &lt;te href=850100&gt;Tín Đồ&lt;/te&gt; của &lt;te href=850099&gt;Giáo Đoàn Vực Sâu&lt;/te&gt;, là một thiếu nữ với lòng thành kính lặng thầm. Với trái tim nhân hậu, cô luôn tận tụy hoàn thành nhiệm vụ. Những lời cầu nguyện của cô, như ánh sáng mà cô mang theo, đem lại sự an ủi và bình yên cho tất cả.</t>
         </is>
       </c>
     </row>
@@ -26274,11 +26274,11 @@
       <c r="M391" t="inlineStr">
         <is>
           <t>[
-Profile nhân viên Averardo Vault—Quyền truy cập xác nhận]
-Biểu đồ dạng sóng của nhân viên này có dao động hình elip. Mô hình miền Thời gian đều đặn và không phát hiện dấu hiệu dao động bất thường. Kết quả test được đánh giá nằm trong giai đoạn bình thường.
-Độ Tới Hạn Cộng Hưởng: High. Nhân viên này sở hữu độ ổn định cao với rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; cực thấp.
-Profile cho thấy không có tiền sử Quá Tải. Hiện không cần tư vấn tâm lý.
-&lt;i&gt;"Thật lòng mà nói, tôi không ngạc nhiên chút nào với kết quả này. Sức chịu đựng tinh thần của cô Zani có lẽ còn vững chãi hơn cả bức tường chống nổ của Hầm! Với tất cả áp lực cô ấy phải gánh vác ở công việc, tôi chẳng ngạc nhiên nếu cô ấy đã tìm ra vài cách giải tỏa căng thẳng cực kỳ hiệu quả. Tôi sẽ hỏi cô ấy về chuyện đó sau khi xong việc hôm nay. Thật tuyệt nếu có thể chia sẻ phương pháp của cô ấy với Resonators khác trong gia đình."—Records nhớ Bộ phận Nghiên cứu&lt;/i&gt;
+Hồ sơ nhân viên Hầm Averardo—Quyền truy cập xác nhận]
+Biểu đồ dạng sóng của nhân viên này có dao động hình elip. Mô hình miền Thời gian đều đặn và không phát hiện dấu hiệu dao động bất thường. Kết quả kiểm tra được đánh giá nằm trong giai đoạn bình thường.
+Độ Tới Hạn Cộng Hưởng: Cao. Nhân viên này sở hữu độ ổn định cao với rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; cực thấp.
+Hồ sơ cho thấy không có tiền sử Quá Tải. Hiện không cần tư vấn tâm lý.
+&lt;i&gt;"Thật lòng mà nói, tôi không ngạc nhiên chút nào với kết quả này. Sức chịu đựng tinh thần của cô Zani có lẽ còn vững chãi hơn cả bức tường chống nổ của Hầm! Với tất cả áp lực cô ấy phải gánh vác ở công việc, tôi chẳng ngạc nhiên nếu cô ấy đã tìm ra vài cách giải tỏa căng thẳng cực kỳ hiệu quả. Tôi sẽ hỏi cô ấy về chuyện đó sau khi xong việc hôm nay. Thật tuyệt nếu có thể chia sẻ phương pháp của cô ấy với các Resonator khác trong gia đình."—Bản ghi nhớ Bộ phận Nghiên cứu&lt;/i&gt;
 &lt;i&gt;"Phương pháp giải tỏa căng thẳng của tôi à? À thì... đôi khi tôi làm thêm... ừm, vài việc tình nguyện ngoài giờ. Thế có tính không?"—Câu trả lời của Zani&lt;/i&gt;</t>
         </is>
       </c>
@@ -26344,7 +26344,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Taoqi là giám đốc phòng thủ biên giới của &lt;te href=850085&gt;Ministry of Development&lt;/te&gt;. Dù vẻ ngoài có vẻ thong dong, cô luôn chứng tỏ mình là người đáng tin cậy và sẵn sàng giúp đỡ mọi người. Taoqi không chỉ là đồng nghiệp đáng tin cậy, mà còn là người bạn tâm tình mà ai cũng có thể tin tưởng.</t>
+          <t>Taoqi là giám đốc phòng thủ biên giới của &lt;te href=850085&gt;Bộ Phát Triển&lt;/te&gt;. Dù vẻ ngoài có vẻ thong dong, cô luôn chứng tỏ mình là người đáng tin cậy và sẵn sàng giúp đỡ mọi người. Taoqi không chỉ là đồng nghiệp đáng tin cậy, mà còn là người bạn tâm tình mà ai cũng có thể tin tưởng.</t>
         </is>
       </c>
     </row>
@@ -26412,7 +26412,7 @@
       <c r="M393" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Taoqi cho thấy dao động hình sin ổn định trong miền thời gian, không có dạng sóng bất thường. Kết quả kiểm tra đều nằm trong giới hạn bình thường.
-Mức Độ Cộng Hưởng Tới Hạn: Medium. Tần số của Taoqi thể hiện độ ổn định cao với nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; thấp.
+Mức Độ Cộng Hưởng Tới Hạn: Trung bình. Tần số của Taoqi thể hiện độ ổn định cao với nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; thấp.
 Chưa ghi nhận tiền sử Quá Tải của Taoqi. Đề nghị kiểm tra định kỳ, tư vấn tâm lý hiện không cần thiết.</t>
         </is>
       </c>
@@ -26550,7 +26550,7 @@
       <c r="M395" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Danjin cho thấy dao động zigzag. Mô hình miền thời gian không đều. Cả giá trị đỉnh trên và dưới đều cao, gần chạm ngưỡng Tới Hạn. Dạng sóng xuất hiện nhiều đoạn mờ và bất thường.
-Mức Độ Cộng Hưởng Tới Hạn: Low, độ ổn định kém. Nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; vẫn còn.
+Mức Độ Cộng Hưởng Tới Hạn: Thấp, độ ổn định kém. Nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; vẫn còn.
 Danjin không có tiền sử Quá Tải được ghi nhận. Tuy nhiên, trong lần Thức Tỉnh đầu tiên, cô suýt chạm ngưỡng Cộng Hưởng Tới Hạn. Điều này khiến máu cô rơi vào trạng thái bùng nổ và phản ứng Dao Động Tần Số cực kỳ nhạy cảm. Danjin mất kiểm soát hành vi, làm tràn một phần Năng Lượng Tần Số. Không có thương vong, nhưng sự cố được xếp vào mức nguy hiểm cấp 2 (mã EX61453).
 Phân tích chẩn đoán cho thấy dao động tần số của cô bắt nguồn từ cú kích động dữ dội trong thời gian ngắn. Hậu quả vẫn còn rõ rệt. Do đó, vẫn có khả năng nhỏ Danjin rơi vào trạng thái cuồng nộ khi tâm trạng bất ổn.
 Đánh giá sâu hơn cho thấy rủi ro Quá Tải của Danjin liên quan mật thiết đến trạng thái cảm xúc, tiềm ẩn nguy cơ cao. Khuyến nghị theo dõi sát sao tình trạng tâm lý và thể chất, đồng thời tiến hành tư vấn và kiểm tra định kỳ.</t>
@@ -26697,7 +26697,7 @@
         <is>
           <t>Câu chuyện của Sanhua bắt đầu từ tuyết.
 Nơi cô sinh ra đã bị hủy diệt bởi một thảm họa &lt;te href=850080&gt;Waveworn&lt;/te&gt;, bị cuốn vào cơn bão tuyết khắc nghiệt cùng sự xuất hiện của những &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; chết chóc.
-Chỉ trong chốc lát, mọi sinh mạng đều bị nghiền nát bởi cơn bão dị thường, rồi bị tái tạo thành một TD khổng lồ đứng sừng sững trên ngọn núi tuyết hóa thành &lt;te href=850078&gt;Tacet Field&lt;/te&gt;. Cảnh tượng vừa kinh hoàng vừa kỳ vĩ, khi TD ấy như một vị thần và ác quỷ cùng hiện diện, trầm mặc nhìn xuống cảnh hoang tàn. Nó giống như một bức tượng Asura khổng lồ.
+Chỉ trong chốc lát, mọi sinh mạng đều bị nghiền nát bởi cơn bão dị thường, rồi bị tái tạo thành một TD khổng lồ đứng sừng sững trên ngọn núi tuyết hóa thành &lt;te href=850078&gt;Tổ Tacet&lt;/te&gt;. Cảnh tượng vừa kinh hoàng vừa kỳ vĩ, khi TD ấy như một vị thần và ác quỷ cùng hiện diện, trầm mặc nhìn xuống cảnh hoang tàn. Nó giống như một bức tượng Asura khổng lồ.
 &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; đã dốc hết sức để đánh bại TD khổng lồ ấy. Cuối cùng, nó sụp đổ trong tiếng gầm thét chói tai. Khi dọn dẹp chiến trường, họ bất ngờ tìm thấy một đứa bé sơ sinh bị đóng băng giữa đống đổ nát, cơ thể lạnh ngắt, da tái xanh.
 Đứa bé vẫn còn thở, dù rất yếu ớt.
 Không ai hiểu nổi làm sao nó có thể sống sót qua thảm họa ấy, và cũng chẳng ai có thời gian để suy nghĩ. Những người lính lau vết máu trên tay, nhẹ nhàng bế đứa bé lên. Họ reo lên: "Chúng ta tìm thấy một đứa bé! Một người sống sót! Nó còn sống!"
@@ -26783,7 +26783,7 @@
         <is>
           <t>Sanhua đã từng thấy tuyết.
 Trong thời gian lưu đày, cô đi qua nhiều nơi. Từ những ngọn núi xa xôi đến những cánh đồng hoang vu, cô đứng trên vách đá nhìn ra vùng đất hoang tàn, chưa từng được khám phá.
-Cô chứng kiến những vết nứt hình ngôi sao lan rộng khắp mặt đất – những Echo, nơi &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; liên tục được sinh ra. Chúng ăn mòn vùng đất mà nhân loại dựa vào để sinh tồn, giống như cách chúng từng ăn mòn đôi mắt cô.
+Cô chứng kiến những vết nứt hình ngôi sao lan rộng khắp mặt đất – những Tổ Tacet, nơi &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; liên tục được sinh ra. Chúng ăn mòn vùng đất mà nhân loại dựa vào để sinh tồn, giống như cách chúng từng ăn mòn đôi mắt cô.
 Sanhua cố gắng tiêu diệt lũ quái vật nhưng không tìm thấy chút bình yên nào. Tiếng ồn hỗn loạn không ngừng hành hạ cô ngày đêm. Động lực duy nhất của cô là sống sót, thúc đẩy cô tiến về phía trước dù giác quan luôn bị tấn công.
 Cô như một cánh diều lơ lửng trên hoang mạc, chỉ được dẫn dắt bởi sợi dây mỏng manh tưởng chừng sẽ đứt bất cứ lúc nào. Cô để tuyết vùi dập mình, lạc lõng và không phương hướng. Nơi nào cô đi qua, bão tuyết cũng tàn phá mọi thứ trên đường. Cô trở thành một tai họa.
 Khi danh tiếng của Sanhua lan rộng, người ta tìm đến cô. Cô không biết họ là ai, hay tại sao họ muốn giết mình. Cô dần nhận ra phải kìm hãm con quỷ bên trong, nhưng hoảng loạn luôn chiếm ưu thế, và cô chỉ biết chiến đấu rồi bỏ chạy trong tuyệt vọng.
@@ -26874,24 +26874,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Sanhua một lần nữa đứng trên chiến trường, nơi máu và lửa đan xen, sẵn sàng chiến đấu cho những gì đã bị cướp đi khỏi cô. Nhiều năm trước, họ đã lấy đi đôi mắt và ngôi nhà xưa của cô, khi cô không thể chống trả. Nhưng giờ đây, cô đã trở lại chiến trường như một chiến binh, với tuyết như lời nguyền, như lưỡi kiếm của cô.
-Đôi mắt cô bắt đầu mỏi mệt vì những tần số &lt;te href=850081&gt;TD&lt;/te&gt; quá mạnh, và đôi tai cô tràn ngập những tiếng thét điếc tai. Xuyên qua bão tuyết, cô nhìn thấy một cảnh tượng kinh hoàng giống như cơn ác mộng trước đây, điều mà cô đã không mơ thấy trong nhiều năm.
-Hàng trăm xác chết chồng chất tạo thành một Asura khổng lồ trước mặt cô, nhưng khi nhìn kỹ hơn, cô nhận ra khuôn mặt của những người cô từng gọi là đồng đội...
-Cô bị mắc kẹt trong ảo giác, bất lực nhìn con quỷ bên trong mình nuốt chửng cô với sức mạnh tàn bạo. Khả năng từng là nguồn sức mạnh của cô giờ đây lại điều khiển và nuốt chửng cô. Lời nguyền ban cho cô sức mạnh dường như vô dụng trước sức mạnh áp đảo của &lt;te href=850075&gt;Lament&lt;/te&gt;.
-"...Rốt cuộc, chẳng có gì thay đổi cả."
-Sanhua gục ngã vì kiệt sức, bị áp đảo bởi quái vật và ảo giác. Cô lẩm bẩm một mình khi ngã xuống đất.
-Cô không còn đếm được mình đã chịu bao nhiêu vết thương, chỉ cảm nhận được hơi ấm đang dần rời xa cơ thể. Cô lại trở về cơn ác mộng thời thơ ấu, một lần nữa nằm trên cánh đồng tuyết. Cái lạnh nuốt chửng cơ thể cô khi cô tan vào mặt đất băng giá.
-Khi thế giới chìm vào trạng thái hoàn toàn tĩnh lặng và bóng tối, một đốm trắng lọt vào tầm nhìn mờ ảo của cô.
-"...Tuyết..."
-Sanhua với tay ra, khao khát chạm vào cái lạnh đó, nhưng đầu ngón tay cô lại chạm vào hơi ấm.
-...Không, đó không phải là bông tuyết.
-Sanhua cố gắng chớp mắt khi hình ảnh rõ ràng của một cô gái dần hiện ra trước mắt. Đó là một tần số mà cô chưa từng thấy trước đây.
-Cô gái đứng trước Sanhua, che chở cho cô khỏi nguy hiểm. Sấm chớp dường như chảy trên đầu ngón tay cô. Cơn bão tuyết hỗn loạn quanh Sanhua bị hút về phía cô, và cô dẫn dắt những tần số đó, dần dần đưa chúng về trạng thái ổn định. Các mùa thay đổi xung quanh họ, sấm sét và gió xa xăm báo hiệu sự xuất hiện. Like một đứa trẻ thần thánh đáp lại lời cầu nguyện, cô tiêu diệt tất cả Tacet Discords bằng tia sét chói lòa.
-Sau khi băng tan, những tiếng thét đau đớn trong tai Sanhua dần lắng xuống. Cô không còn nghe thấy tiếng la hét đau đớn của chiến trường, mà là tiếng gió thổi, tiếng chim hót và sự hồi sinh của đất đai. Đó là lúc cô cuối cùng thoát khỏi đêm tuyết đó, và thời gian từng bị đóng băng trong cuộc đời cô bắt đầu trôi chảy trở lại.
-Đó là lúc Sanhua cuối cùng hiểu được nghiệp chướng dành cho mình.
-"Chỉ với nghiệp của một người, mới có thể sinh ra nhân quả." Jinhsi đã cho Sanhua thấy sức mạnh của sự tái sinh trong sự hủy diệt. Jinhsi... Cô ấy có thể là ánh sáng dẫn đường cho tất cả mọi người trong thời khắc tàn khốc này.
-Tương lai mà Jinhsi đã thể hiện chính là nơi nghiệp chướng của cô nằm. Ánh sáng mà cô đã theo đuổi trong bóng tối suốt thời gian qua.
-Sanhua lại cầm kiếm lên. Lần này, cô đã biến quỷ dữ của mình thành sức mạnh để bảo vệ.</t>
+          <t>Sanhua một lần nữa đứng trên chiến trường, nơi máu và lửa đan xen, sẵn sàng chiến đấu vì những gì đã bị cướp đi khỏi cô. Nhiều năm trước, chúng đã lấy đi đôi mắt và quê hương của cô, khi cô còn không thể chống cự. Nhưng giờ đây, cô đứng đây như một chiến binh, với tuyết như lời nguyền, như lưỡi kiếm của mình.</t>
         </is>
       </c>
     </row>
@@ -26976,7 +26959,7 @@
 Lịch trình của Baizhi được lên kế hoạch tỉ mỉ: thứ Hai và thứ Tư dành để giám sát &lt;te href=850077&gt;Sonoro Sphere&lt;/te&gt; nhân tạo, thứ Sáu tập trung phân tích dải tần số &lt;te href=850076&gt;Remnant&lt;/te&gt;, còn thời gian còn lại dành cho nghiên cứu thực địa, quan sát sinh học Remnant và tổng hợp các trường hợp. Cô điều chỉnh kế hoạch khi cần, tiến về phía trước với sự chính xác và mục đích rõ ràng.
 Baizhi luôn giữ được sự điềm tĩnh và tự chủ, không hề nao núng trước công việc chưa hoàn thành hay những vấn đề hóc búa. Cô miệt mài nghiên cứu cho đến khi nắm bắt chúng một cách dễ dàng. Sự bình thản ấy khiến người khác khó lòng tiếp cận cô. Với vẻ mặt lạnh lùng và giọng điệu xa cách, cô vô tình tạo ra một khoảng cách. Mọi người không khỏi cảm thấy như mình đang bị đẩy ra xa.
 "Báo cáo tuần trước của cậu chưa được nộp đúng hạn."
-"À... Yes... Tôi, ừm... Mẫu &lt;te href=850082&gt;Echo&lt;/te&gt; gốc đã bị nhiễm bẩn. Tôi phải..."
+"À... Vâng... Tôi, ừm... Mẫu &lt;te href=850082&gt;Echo&lt;/te&gt; gốc đã bị nhiễm bẩn. Tôi phải..."
 "Ư... Xin lỗi! Không, tôi thành thật xin lỗi vì sự cẩu thả của mình! Tôi... Tôi sẽ bù đắp..."
 Nhìn Baizhi tiến lại gần, nhà nghiên cứu báo cáo vội nắm chặt áo, cúi đầu thấp hơn nữa. Nhưng ngay sau đó, một lát mẫu đã xử lý được đưa đến trước mặt anh.
 "Tôi đoán mẫu từ Fission Junrock có thể thay thế được chứ?"
@@ -27065,14 +27048,14 @@
 Baizhi, 11 tuổi, quan sát viên bi khi nó một lần nữa dừng lại đúng vị trí đã định. Cô kết luận rằng dù có phức tạp đến đâu, viên bi vẫn sẽ luôn lăn không kiểm soát đến điểm cuối đã được định sẵn theo thiết kế của thiết bị. Điều này gợi nhớ đến một giả thuyết lý thuyết trong cuốn sách cô mới đọc: xuyên suốt lịch sử, các nền văn minh nhân loại đều không thể vượt qua nút thắt của cỗ máy này và cuối cùng đều đi đến diệt vong. Không có ngoại lệ.
 Nếu kết quả luôn nhất quán như vậy, thì mọi chuyện đã xảy ra chẳng phải chỉ là sự lặp lại có thể đoán trước hay sao? Liệu có thực sự tồn tại ý nghĩa nào trong tất cả những điều này?
 Baizhi bị câu hỏi đó ám ảnh, còn cha mẹ cô thì lo lắng vì một lý do khác. Dù đam mê tri thức của con gái đáng ngưỡng mộ, nhưng sự say mê các khái niệm lý thuyết đã khiến Baizhi xa rời thực tại. Cô dành hàng giờ đọc những cuốn sách bí truyền và chạy mô phỏng thay vì tận hưởng cuộc sống hay kết bạn.
-Vài ngày sau, Baizhi nhận được lời mời đến căn cứ thám hiểm khoa học của Huaxu Academy. Chiều hôm đó, cô nhìn thấy một thiết bị lớn và phức tạp hơn bất cứ thứ gì từng thấy—các bộ phận tượng trưng cho những biến số khác nhau, kết nối với nhau như một hệ thống hữu cơ phức tạp. Thế nhưng, dù hoành tráng đến đâu, thiết bị vẫn chưa hoàn thiện và quá bất định để trở thành "viên bi" trong kế hoạch của cô. Với ánh mắt trầm tư, Baizhi kiểm tra từng bộ phận và đưa ra giả thuyết về cách nó hoạt động.
+Vài ngày sau, Baizhi nhận được lời mời đến căn cứ thám hiểm khoa học của Học viện Huaxu. Chiều hôm đó, cô nhìn thấy một thiết bị lớn và phức tạp hơn bất cứ thứ gì từng thấy—các bộ phận tượng trưng cho những biến số khác nhau, kết nối với nhau như một hệ thống hữu cơ phức tạp. Thế nhưng, dù hoành tráng đến đâu, thiết bị vẫn chưa hoàn thiện và quá bất định để trở thành "viên bi" trong kế hoạch của cô. Với ánh mắt trầm tư, Baizhi kiểm tra từng bộ phận và đưa ra giả thuyết về cách nó hoạt động.
 "Cháu thấy thế nào? Nhóm chúng ta dự định sẽ hoàn thành nó vào một ngày nào đó."
 Người đứng đầu nhóm, vừa trở về sau một trong vô số chuyến thám hiểm khoa học gian khổ mà ông dẫn đầu, mỉm cười ấm áp với Baizhi.
 "Chỗ đó... Nếu thiết kế như vậy, năng lượng còn lại sẽ không đủ để truyền tải thông tin đi xa hơn."
 "À. Vậy là cháu đã phát hiện ra vấn đề rồi... Giám đốc nói không sai về cháu. Cháu thực sự có tài! Thế này nhé, cháu có muốn tham gia cùng chúng ta không?"
 "Bất kỳ viên bi nào lăn cũng chỉ có một kết cục: dừng lại ở một vị trí nhất định. Nhưng cháu không thấy thiết kế của chú sẽ kết thúc ở đâu cả."
 "Chú sẽ nói là, nó sẽ đến một nơi... hiện tại chưa biết, nhưng một ngày nào đó có thể biết được? Chú đồng ý rằng phải có điểm kết thúc. Còn việc nó nên kết thúc ở đâu... Có lẽ cháu có thể cùng chúng ta tìm ra câu trả lời."
-Vừa dứt lời, cánh cửa hé mở đột nhiên bật tung, lộ ra những thành viên còn lại trong nhóm đang núp sau đó. Họ lảo đảo bước vào phòng, mặt ngươi ngượng ngùng nhưng háo hức chờ câu trả lời của Baizhi về việc tham gia nhiệm vụ.
+Vừa dứt lời, cánh cửa hé mở đột nhiên bật tung, lộ ra những thành viên còn lại trong nhóm đang núp sau đó. Họ lảo đảo bước vào phòng, mặt mày ngượng ngùng nhưng háo hức chờ câu trả lời của Baizhi về việc tham gia nhiệm vụ.
 Khoảnh khắc đó, Baizhi cảm thấy như nghe thấy tiếng lách cách nhẹ của một viên bi được đặt vào điểm xuất phát.</t>
         </is>
       </c>
@@ -27150,20 +27133,20 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Vào năm thứ tư trong chuyến thám hiểm khoa học, Baizhi lần đầu tiên chạm trán với băng nhóm &lt;te href=850076&gt;Remnant&lt;/te&gt; ấy.
-Lúc đó, đam mê nghiên cứu của Baizhi đang ở đỉnh cao. Không còn giam mình trong những trang sách, cô hòa mình vào mọi ngóc ngách của nền văn minh cùng đoàn thám hiểm khoa học.
+          <t>Vào năm thứ tư trong chuyến thám hiểm khoa học, Bạch Chi lần đầu tiên chạm trán với băng nhóm &lt;te href=850076&gt;Remnant&lt;/te&gt; ấy.
+Lúc đó, đam mê nghiên cứu của Bạch Chi đang ở đỉnh cao. Không còn giam mình trong những trang sách, cô hòa mình vào mọi ngóc ngách của nền văn minh cùng đoàn thám hiểm khoa học.
 Khi bước chân vào môi trường băng giá, cô mới nhận ra cái lạnh thực sự không thể đơn thuần định nghĩa bằng con số "-25°C". Nó hiện hữu qua những lớp tuyết trắng vô tận, những cơn run rẩy len lỏi qua lớp đồ bảo hộ, và tiếng gõ tuyệt vọng của những thiết bị đông cứng. Lý thuyết chỉ là khung xương trơ trụi, cần những cảm xúc và trải nghiệm thực tế để thấu hiểu.
-Baizhi tận tụy theo chân đoàn đến các địa điểm khác, không chỉ là những tàn tích bình thường mà còn là những nơi kỳ ảo tràn ngập Năng Lượng Remnant—thông tin thuần khiết và hoàn chỉnh, nhưng vẫn luôn lảng tránh, bất khả xâm phạm. Dù công nghệ tiên tiến đến đâu, họ vẫn không thể nắm bắt hay phân tích được sức mạnh bí ẩn ấy.
-Chuyến thám hiểm thứ chín của Baizhi đến &lt;te href=850077&gt;Sonoro Sphere&lt;/te&gt; đã mở ra một bước đột phá.
+Bạch Chi tận tụy theo chân đoàn đến các địa điểm khác, không chỉ là những tàn tích bình thường mà còn là những nơi kỳ ảo tràn ngập Năng Lượng Remnant—thông tin thuần khiết và hoàn chỉnh, nhưng vẫn luôn lảng tránh, bất khả xâm phạm. Dù công nghệ tiên tiến đến đâu, họ vẫn không thể nắm bắt hay phân tích được sức mạnh bí ẩn ấy.
+Chuyến thám hiểm thứ chín của Bạch Chi đến &lt;te href=850077&gt;Sonoro Sphere&lt;/te&gt; đã mở ra một bước đột phá.
 Những tòa nhà bên trong không hề méo mó hay phản chiếu thực tại; vật liệu cấu thành chúng vẫn là điều bí ẩn.
-Từ trên cao, ánh sáng len lỏi qua một lỗ hổng trên mái vòm, phủ lên mọi thứ một lớp lấp lánh như ngọc trai. Sự xuất hiện của Baizhi và đoàn dường như đã kích hoạt một cơ chế nào đó. Những công trình hình học vốn lơ lửng bắt đầu thay đổi vị trí nhanh chóng, tạo thành những hình ảnh độc đáo của ký hiệu và con số.
-Baizhi không thể giải mã mục đích của Sonoro Sphere, cũng không biết mình đang chứng kiến quá khứ, hiện tại, hay một tương lai chưa biết. Nhưng bản năng nghiên cứu đã thôi thúc cô, buộc cô phải ghi lại từng chi tiết. Đây có thể là bước đột phá cho một lý thuyết mới—
-Các thiết bị khảo sát hiển thị sự dao động tần số trực tiếp. Baizhi gạt bỏ mọi phiền nhiễu, tập trung vào màn hình. Những lý thuyết và cảm xúc tích lũy bấy lâu nay chính là chìa khóa cho khoảnh khắc này.
+Từ trên cao, ánh sáng len lỏi qua một lỗ hổng trên mái vòm, phủ lên mọi thứ một lớp lấp lánh như ngọc trai. Sự xuất hiện của Bạch Chi và đoàn dường như đã kích hoạt một cơ chế nào đó. Những công trình hình học vốn lơ lửng bắt đầu thay đổi vị trí nhanh chóng, tạo thành những hình ảnh độc đáo của ký hiệu và con số.
+Bạch Chi không thể giải mã mục đích của Sonoro Sphere, cũng không biết mình đang chứng kiến quá khứ, hiện tại, hay một tương lai chưa biết. Nhưng bản năng nghiên cứu đã thôi thúc cô, buộc cô phải ghi lại từng chi tiết. Đây có thể là bước đột phá cho một lý thuyết mới—
+Các thiết bị khảo sát hiển thị sự dao động tần số trực tiếp. Bạch Chi gạt bỏ mọi phiền nhiễu, tập trung vào màn hình. Những lý thuyết và cảm xúc tích lũy bấy lâu nay chính là chìa khóa cho khoảnh khắc này.
 Khoảng cách càng ngắn, năng lượng tiêu hao càng thấp. Hai điểm tạo thành một đường thẳng, dẫn thẳng đến nguồn.
-Giống như xây dựng một kênh thiết bị, Baizhi chọn hai đầu mút của đoạn mở rộng, nối chúng thành một đường thẳng, rồi đưa thiết bị lấy mẫu về trung tâm nơi ánh sáng tụ lại—
+Giống như xây dựng một kênh thiết bị, Bạch Chi chọn hai đầu mút của đoạn mở rộng, nối chúng thành một đường thẳng, rồi đưa thiết bị lấy mẫu về trung tâm nơi ánh sáng tụ lại—
 Ánh sáng cuồn cuộn đáp lại hành động của cô, cô đặc lại thành một quả cầu ánh sáng trắng tinh khiết.
 Băng Remnant từ đó đã bị bắt giữ và hiện hình, trọn vẹn nhưng như một chiếc vỏ rỗng, thuần khiết và không một tì vết.
-Lúc đó, Baizhi không hề hay biết, nó sẽ mãi mãi đi theo cô và định hình cả cuộc đời nghiên cứu của mình.</t>
+Lúc đó, Bạch Chi không hề hay biết, nó sẽ mãi mãi đi theo cô và định hình cả cuộc đời nghiên cứu của mình.</t>
         </is>
       </c>
     </row>
@@ -27247,12 +27230,12 @@
 "Biết rằng ước nguyện khó thành hiện thực, vậy tại sao lại phải ước? Hành động này thậm chí còn không có đối tượng rõ ràng. Một khi đã ước, liệu có ai đáp lại không? Ai sẽ đáp lại?" Trước những câu hỏi chân thành của Baizhi, đồng đội cô lại một lần nữa im lặng. May mắn thay, sau ngàn ngày bên nhau, họ hiểu rằng sự nghiêm túc và cách nói vòng vo của cô chỉ là cách cô tìm kiếm sự thật, tránh mâu thuẫn khi đánh giá hay phát biểu.
 Dù Baizhi chưa bao giờ tự mình ước nguyện, cô vẫn luôn đứng bên cạnh đồng đội khi họ ước dưới ánh nến, sao băng hay bất cứ thứ gì.
 Dù bối rối, cô vẫn cố gắng hiểu họ và ở bên họ, như cách họ đã làm với cô.
-"Please, mong rằng chúng ta có thể giải mã hoàn toàn bí ẩn của &lt;te href=850076&gt;Remnant&lt;/te&gt; Creature!"
+"Làm ơn, mong rằng chúng ta có thể giải mã hoàn toàn bí ẩn của &lt;te href=850076&gt;Remnant&lt;/te&gt; Creature!"
 "Có thể làm được, nhưng khó lòng trong đời chúng ta."
 "Ừm, đúng là thế... nhưng vẫn thật đáng buồn! Đừng suy nghĩ quá nhiều, ước nguyện và thực tại là hai chuyện khác nhau... Dù sao thì khi nào có ước nguyện, cậu sẽ hiểu thôi!"
 Trong sự im lặng lạnh lẽo của cánh đồng băng giá, ngày định mệnh ấy đã đến.
 Thế giới sụp đổ không báo trước, như thường lệ. Những hình ảnh sống động bị &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; xé nát, đôi mắt từng nói về tương lai giờ đã lạnh ngắt. Baizhi cảm nhận mạch đập yếu dần, suy nghĩ hỗn loạn. Tại sao lại thế này? Đã mất quá nhiều trong cuộc tìm kiếm &lt;te href=850077&gt;Sonoro Sphere&lt;/te&gt;. Không thể kết thúc như vậy... Cô không thể tưởng tượng một tương lai không có họ.
-"Please... mong họ có thể tỉnh lại."
+"Làm ơn... mong họ có thể tỉnh lại."
 Cuối cùng, cô cũng ước nguyện, nhưng không biết ai có thể đáp lại.
 Khi Sonoro Sphere sụp đổ, Tacet Discord ào tới. Một mớ cảm xúc hỗn độn trào dâng trong cô, không thể ngăn cản khao khát cháy bỏng muốn mọi người tỉnh lại, trở về bên cô. Cô mong họ mở mắt như trước kia...
 Ngay lúc đó, một &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; xuất hiện trên người cô, và một Remnant Creature giống như hoa Quỳnh hiện ra trước mặt, như thể đáp lại ước nguyện của cô.
@@ -27419,14 +27402,14 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>&lt;te href=850131&gt;Múa Lân&lt;/te&gt; ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt; có lượng khán giả rất đông đảo. Dù là những sự kiện lớn như lễ nhập môn cho tân sinh viên và lễ khai mạc, hay những dịp thân mật như sinh nhật của người cao tuổi và lễ thôi nôi cho trẻ nhỏ, luôn có những khoảnh khắc cần đến nghi thức ăn mừng, và đó là lý do &lt;te href=850130&gt;Liondance Troupe&lt;/te&gt; luôn thu hút được lượng khách hàng ổn định.
-Với tư cách là vũ công múa lân hàng đầu, vai trò của anh không chỉ giới hạn ở những màn trình diễn gay cấn và đôi chút mạo hiểm trên Cột Hoa Mai. Việc sáng tạo các tiết mục múa lân cá nhân hóa là một phần quan trọng trong công việc của anh, đảm bảo những màn trình diễn ấn tượng và để lại dấu ấn sâu sắc trong lòng khách hàng.
-Lingyang thích tương tác với khách hàng, tìm hiểu sâu nhu cầu của họ để tạo ra một tiết mục múa lân độc đáo. Nhưng ngoài công việc, đó còn là niềm đam mê cá nhân. Đối với anh, câu chuyện của mỗi người là một kho báu chờ được khai phá, và anh tận hưởng việc khám phá chúng. Sự tò mò chân thành của anh thường khiến khách hàng mở lòng và chia sẻ những suy nghĩ thật sự. Điều này đôi khi khiến một số người tự hỏi liệu họ có đang ở đúng chỗ không – phải chăng Liondance Troupe đã bắt đầu cung cấp dịch vụ tư vấn tâm lý?
-Liondance Troupe hoạt động trong một thế giới với lịch trình dày đặc, những thay đổi vào phút chót và những tình huống khẩn cấp bất ngờ. Việc cân bằng xung đột và mâu thuẫn là một thách thức thường xuyên, vì một sai lầm có thể đồng nghĩa với việc mất đi những khách hàng quý giá. Do đó, chìa khóa thành công của họ nằm ở việc thấu hiểu và giải quyết cảm xúc của mỗi khách hàng. Lingyang đã thành thạo nghệ thuật đàm phán này, biến nó thành một trong những kỹ năng nổi bật của mình.
-May mắn thay, Lingyang còn có một cách khác để đối phó với những khách hàng khó tính: tặng Lời Chúc May Mắn. Với nụ cười rạng rỡ và những lời chúc chân thành, Lingyang có thể khiến ngay cả những khách hàng khó tính nhất cũng phải nhượng bộ đôi chút. Dần dần, bộ sưu tập &lt;i&gt;Lời Chúc May Mắn&lt;/i&gt; của anh đã trở thành tài liệu đọc bắt buộc đối với các vũ công múa lân đồng nghiệp, biến "tặng lời chúc may mắn cho mọi người" thành một đặc trưng của đoàn.
-"Gặp ai cũng chúc may mắn. Chắc hẳn anh đến từ Liondance Troupe rồi, phải không? Mời vào!"
-Tuy nhiên, lời chúc may mắn của Lingyang không phải là mẫu chung cho tất cả. Chúng phải chân thành và được cá nhân hóa cho người nhận. Dù đã trở thành thói quen của Liondance Troupe, Lingyang vẫn nỗ lực để mang đến những lời chúc chân thành và riêng biệt. Anh tin chắc rằng những lời chúc này sẽ mang lại may mắn cho người nhận.
-Nếu bạn gặp một vũ công múa lân đang tặng bạn những lời chúc may mắn, đừng nghi ngờ. Hãy đón nhận những lời chúc tinh khiết và chân thành đó, vì đó là cách tốt nhất để đáp lại một tâm hồn tốt bụng và thân thiện.</t>
+          <t>Múa Lân ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt; thu hút đông đảo khán giả. Từ những sự kiện lớn như lễ nhập môn tân sinh viên, lễ khai mạc, đến những dịp thân mật như sinh nhật người cao tuổi hay lễ thôi nôi của trẻ nhỏ, luôn có những khoảnh khắc cần đến nghi thức chúc mừng, và đó là lý do &lt;te href=850130&gt;Đoàn Múa Lân&lt;/te&gt; luôn có lượng khách hàng ổn định.
+Là vũ công lân hàng đầu, vai trò của cậu không chỉ dừng lại ở những màn trình diễn gay cấn và đôi chút mạo hiểm trên Cột Hoa Mai. Tạo ra những tiết mục múa lân độc đáo, phù hợp với từng khách hàng là một phần quan trọng trong công việc của cậu, đảm bảo mỗi màn trình diễn đều để lại ấn tượng sâu sắc.
+Lingyang thích tương tác với khách hàng, tìm hiểu sâu nhu cầu của họ để tạo ra một tiết mục múa lân riêng biệt. Nhưng ngoài công việc, đó còn là niềm đam mê cá nhân. Với cậu, câu chuyện của mỗi người là một kho báu chờ được khai phá, và cậu thích thú khi dần khám phá chúng. Sự tò mò chân thành của cậu thường khiến khách hàng mở lòng chia sẻ những suy nghĩ thật sự. Điều này đôi khi khiến họ tự hỏi liệu mình có nhầm địa chỉ không – phải chăng Đoàn Múa Lân đã bắt đầu cung cấp dịch vụ tư vấn tâm lý?
+Đoàn Múa Lân hoạt động trong một thế giới với lịch trình dày đặc, thay đổi vào phút chót và những tình huống khẩn cấp bất ngờ. Giải quyết mâu thuẫn và xung đột là thách thức thường trực, vì chỉ một sai lầm nhỏ cũng có thể khiến họ mất đi những khách hàng quan trọng. Vì vậy, chìa khóa thành công của họ nằm ở việc thấu hiểu và đáp ứng cảm xúc của từng khách hàng. Lingyang đã thành thạo nghệ thuật đàm phán này, biến nó thành một trong những "chiến tích" của mình.
+May mắn thay, Lingyang còn có một cách khác để đối phó với những khách hàng khó tính: tặng Lời Chúc May Mắn. Với nụ cười rạng rỡ và những lời chúc chân thành, Lingyang có thể khiến cả những khách hàng khó tính nhất cũng phải nhượng bộ đôi chút. Dần dần, &lt;i&gt;Bộ Sưu Tập Lời Chúc May Mắn&lt;/i&gt; của cậu đã trở thành tài liệu không thể thiếu đối với các vũ công lân đồng nghiệp, biến "tặng lời chúc may mắn cho mọi người" thành đặc trưng của đoàn.
+"Gặp ai cũng chúc may mắn à? Chắc hẳn cậu đến từ Đoàn Múa Lân rồi. Mời vào đi!"
+Tuy nhiên, lời chúc may mắn của Lingyang không phải là những câu sáo rỗng. Chúng phải chân thành và được cá nhân hóa cho người nhận. Dù đã trở thành thói quen của Đoàn Múa Lân, Lingyang vẫn luôn nỗ lực để mỗi lời chúc đều xuất phát từ tâm và mang dấu ấn riêng. Cậu tin chắc rằng những lời chúc này sẽ mang lại may mắn cho người nhận.
+Nếu gặp một vũ công lân tặng bạn lời chúc may mắn, đừng nghi ngờ. Hãy đón nhận những lời chúc trong sáng và chân thành ấy, vì đó là cách tốt nhất để đáp lại một tâm hồn tốt bụng và thân thiện.</t>
         </is>
       </c>
     </row>
@@ -27506,22 +27489,22 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Nói về chuyện Lingyang gia nhập &lt;te href=850130&gt;Liondance Troupe&lt;/te&gt;, chúng ta phải quay lại cái ngày "bình thường" ấy, khi một buổi biểu diễn &lt;te href=850131&gt;múa lân&lt;/te&gt; tại Nhà hát &lt;te href=850091&gt;Jinzhou&lt;/te&gt; vừa kết thúc. Nhân viên đang tất bật dọn dẹp đạo cụ sân khấu thì một gã thanh niên trông kỳ lạ từ trên mái nhà rơi xuống. Nói chính xác hơn, không phải "rơi" mà là "đâm sầm" xuống.
-Hóa ra, đó là một "tai nạn" được dàn dựng kỹ càng. Lingyang đã lên kế hoạch tiếp cận Liondance Troupe từ trước. Nhưng điều cậu không ngờ tới là mái nhà, nhất là sau một trận mưa, lại trơn trượt hơn cành cây nhiều.
-Lúc đó, Lingyang chưa thông thạo ngôn ngữ loài người, thậm chí còn chẳng có nổi một cái tên. Suốt một thời gian dài, các thành viên trong Liondance Troupe chỉ gọi cậu là "thằng nhóc".
+          <t>Nói về chuyện Lingyang gia nhập &lt;te href=850130&gt;Đoàn Múa Lân&lt;/te&gt;, chúng ta phải quay lại cái ngày "bình thường" ấy, khi một buổi biểu diễn &lt;te href=850131&gt;múa lân&lt;/te&gt; tại Nhà hát &lt;te href=850091&gt;Jinzhou&lt;/te&gt; vừa kết thúc. Nhân viên đang tất bật dọn dẹp đạo cụ sân khấu thì một gã thanh niên trông kỳ lạ từ trên mái nhà rơi xuống. Nói chính xác hơn, không phải "rơi" mà là "đâm sầm" xuống.
+Hóa ra, đó là một "tai nạn" được dàn dựng kỹ càng. Lingyang đã lên kế hoạch tiếp cận Đoàn Múa Lân từ trước. Nhưng điều cậu không ngờ tới là mái nhà, nhất là sau một trận mưa, lại trơn trượt hơn cành cây nhiều.
+Lúc đó, Lingyang chưa thông thạo ngôn ngữ loài người, thậm chí còn chẳng có nổi một cái tên. Suốt một thời gian dài, các thành viên trong Đoàn Múa Lân chỉ gọi cậu là "thằng nhóc".
 Dù đã cố gắng hết sức, Lingyang vẫn không thể giao tiếp với mọi người trong đoàn. Thế là cậu đành múa lân một cách vụng về bằng cái đầu lân nhặt được đâu đó.
 Mỗi khi nhớ lại khoảnh khắc ấy, các thành viên trong đoàn lại bật cười và nói rằng trông Lingyang giống đang khoe nanh khoe vuốt hơn là múa lân truyền thống.
 Dù ý định của cậu đã được hiểu, nhưng ngoại hình kỳ lạ của Lingyang vẫn khiến cả đoàn tranh cãi nảy lửa.
-Cuối cùng, hai bậc trưởng lão, ông Wufang và ông Qixing – những người mà ngay cả lãnh đạo hiện tại của Liondance Troupe cũng phải gọi là "Master" – đã quyết định nhận Lingyang vào đoàn.
+Cuối cùng, hai bậc trưởng lão, ông Wufang và ông Qixing – những người mà ngay cả lãnh đạo hiện tại của Đoàn Múa Lân cũng phải gọi là "Sư phụ" – đã quyết định nhận Lingyang vào đoàn.
 Lingyang đã nhiều lần hỏi lý do tại sao họ lại nhận mình, nhưng chỉ nhận được những câu trả lời mập mờ:
 "Haha, có lẽ vì tai và đuôi của cậu giống với loài sư tử cát tường huyền thoại ấy mà."
 Thỉnh thoảng, khi sư phụ ngủ say, Lingyang lại nghe thấy vài lời nói mê trong giấc mơ: "'Sư Tử Lớn'... Ta đã làm được... Lời hứa của ta..."
 Dưới sự chỉ dạy của sư phụ, Lingyang bắt đầu hành trình học tập chính thức: tìm hiểu về múa lân, thư pháp, và cách giao tiếp với con người.
 Để giúp Lingyang kiểm soát sức mạnh hung bạo trong cơ thể, cậu được dạy một bộ quyền pháp cổ xưa từ &lt;te href=850093&gt;Huanglong&lt;/te&gt;, được cho là có thể điều hòa luồng khí và là nền tảng của múa lân. Nhờ khổ luyện không ngừng, Lingyang chính thức được trao danh hiệu "&lt;te href=850132&gt;Đầu Lân&lt;/te&gt;".
 Ở Jinzhou, "Đầu Lân" mang nhiều ý nghĩa. Với người thường, đó có thể là "đầu lân" trong màn biểu diễn, hoặc người dẫn dắt. Còn với những người múa lân, đó là một giấc mơ chung – khát vọng trở thành "chúa tể của loài sư tử" thông qua sự khổ luyện và hoàn thiện kỹ năng múa lân.
-"Ta sinh ra đã mang trong mình sức mạnh này và rèn giũa kỹ năng săn mồi nơi hoang dã. Nhưng múa lân không chỉ đơn thuần là sức mạnh – tư thế, bước chân, nhịp điệu, sự phối hợp với đồng đội... Không phải chuyện một sớm một chiều là học được. Master luôn nhấn mạnh múa lân có ý nghĩa rất lớn với người dân Jinzhou, và ta không khỏi lo lắng liệu mình có đáp ứng được kỳ vọng của họ không. Để xứng đáng với danh hiệu 'Đầu Lân', ta biết mình phải nỗ lực nhiều hơn nữa."
+"Ta sinh ra đã mang trong mình sức mạnh này và rèn giũa kỹ năng săn mồi nơi hoang dã. Nhưng múa lân không chỉ đơn thuần là sức mạnh – tư thế, bước chân, nhịp điệu, sự phối hợp với đồng đội... Không phải chuyện một sớm một chiều là học được. Sư phụ luôn nhấn mạnh múa lân có ý nghĩa rất lớn với người dân Jinzhou, và ta không khỏi lo lắng liệu mình có đáp ứng được kỳ vọng của họ không. Để xứng đáng với danh hiệu 'Đầu Lân', ta biết mình phải nỗ lực nhiều hơn nữa."
 Theo lời các sư phụ, Lingyang không chỉ có tài năng. Quan trọng hơn, cậu luôn khao khát tiến bộ không ngừng.
-Mỗi động tác mới học được, mỗi buổi luyện tập kéo dài đến khi trời đầy sao, Lingyang đứng trên Plum Blossom Pole ở Trung Nguyên. Cậu nhìn bóng mình in trên mặt nước, như đang suy tư hay thách thức giới hạn của bản thân. Giữa những cánh hoa rơi, chàng Đầu Lân trẻ tuổi say sưa nhảy múa trên cột, tạo nên một cảnh tượng độc đáo trong vùng.</t>
+Mỗi động tác mới học được, mỗi buổi luyện tập kéo dài đến khi trời đầy sao, Lingyang đứng trên Cột Mận Hoa ở Trung Nguyên. Cậu nhìn bóng mình in trên mặt nước, như đang suy tư hay thách thức giới hạn của bản thân. Giữa những cánh hoa rơi, chàng Đầu Lân trẻ tuổi say sưa nhảy múa trên cột, tạo nên một cảnh tượng độc đáo trong vùng.</t>
         </is>
       </c>
     </row>
@@ -27600,8 +27583,8 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Không thể nhắc đến Trung Nguyên mà không nhớ đến đợt huấn luyện mùa đông hàng năm của &lt;te href=850130&gt;Liondance Troupe&lt;/te&gt;.
-Vào mùa đông, khi không có biểu diễn, Liondance Troupe tập trung tại Taoyuan Vale để tập luyện chuyên sâu. Công tác chuẩn bị này rất quan trọng cho màn trình diễn tại "Diễu Hành Năm New" - một sự kiện trọng đại ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, tượng trưng cho việc tiễn năm cũ và đón năm mới. Dù là mùa nghỉ, cả đoàn vẫn miệt mài luyện tập, trau chuốt nhân vật, mài giũa kỹ năng, chế tác đạo cụ và tập dượt tiết mục mới. Không ai dám lơ là trong thời điểm quan trọng này. Mặt khác, vì phải rời thành phố để đến nơi hoang dã, Lingyang có cơ hội sống đúng với bản năng của mình.
+          <t>Không thể nhắc đến Trung Nguyên mà không nhớ đến đợt huấn luyện mùa đông hàng năm của &lt;te href=850130&gt;Đoàn Múa Lân&lt;/te&gt;.
+Vào mùa đông, khi không có biểu diễn, Đoàn Múa Lân tập trung tại Thung Lũng Đào Nguyên để tập luyện chuyên sâu. Công tác chuẩn bị này rất quan trọng cho màn trình diễn tại "Diễu Hành Năm Mới" - một sự kiện trọng đại ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, tượng trưng cho việc tiễn năm cũ và đón năm mới. Dù là mùa nghỉ, cả đoàn vẫn miệt mài luyện tập, trau chuốt nhân vật, mài giũa kỹ năng, chế tác đạo cụ và tập dượt tiết mục mới. Không ai dám lơ là trong thời điểm quan trọng này. Mặt khác, vì phải rời thành phố để đến nơi hoang dã, Lingyang có cơ hội sống đúng với bản năng của mình.
 Dù giá lạnh mùa đông, sự sôi nổi bẩm sinh khiến Lingyang luôn năng động, giống như những mãnh thú trên núi gần đó.
 Khi tuyết phủ trắng đất, chúng săn mồi một cách háo hức. Mỗi lần nghe tiếng gầm gừ của thú dữ hay tiếng kêu cứu từ xa, Lingyang lại lao vào rừng trong giờ nghỉ để giải quyết mối đe dọa. Cậu chiến đấu với bọn thú tấn công bằng sự tàn bạo và hung dữ, xé xác chúng trong nháy mắt.
 Những người được cứu sống rất biết ơn, nhưng thái độ của họ lại đầy sợ hãi.
@@ -27710,7 +27693,7 @@
 "C-Chào anh! Em muốn mua sơn ạ! Sáu hộp Malachite Green số 3, năm hộp Azurite Blue số 3, năm hộp Vermilion, ba hộp Indigo, ba hộp Ochre, ba hộp Gamboge, và hai hộp Golden Yellow. Cảm ơn anh!"
 Thở phào vì đã nói trôi chảy không vấp váp, Zhezhi hít một hơi thật sâu để lấy lại bình tĩnh. Nhưng khi ngẩng đầu lên, cô gặp ánh mắt của người nhân viên đang bước ra từ phòng sau, trông có vẻ ngạc nhiên.
 "Chào em. Anh có thể giúp gì không?" Giọng anh nhẹ nhàng trái ngược hẳn với những gì Zhezhi tưởng tượng.
-Nhận ra lời mình nói lúc nãy chẳng ai nghe thấy, cô đứng sững lại. "Uhh... Dạ... em..."
+Nhận ra lời mình nói lúc nãy chẳng ai nghe thấy, cô đứng sững lại. "Ơ... Dạ... em..."
 "Em tìm mua dụng cụ vẽ gì à?"
 "D-Dạ... sơn... em..."
 "Mấy loại mới ra à? Đang rất hot đấy."
@@ -27802,7 +27785,7 @@
 Lớn lên trong bầu không khí đậm chất đồ cổ, tình yêu của Youhu dành cho chúng ngày càng nở rộ. Cô say mê mọi thứ về chúng, tiếp thu những kiến thức thẩm định khô khan, tối nghĩa nhất với ánh mắt lấp lánh. Nhưng điều cô yêu thích nhất là nghe cha mẹ kể những câu chuyện về đồ cổ.
 Tiếng chuông cổ ngân vang sâu thẳm, mang theo ký ức của những thời xa xưa, khi người ta quỳ gối trước tượng vàng cầu nguyện cho bình an của gia đình.
 Những bức chạm khắc trên đá miêu tả những chàng trai dũng cảm giương cung, xua đuổi &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; để bảo vệ dân chúng.
-Bản tính hoạt bát của Youhu tỏa sáng khi cô đắm chìm trong thế giới đồ cổ, vết &lt;te href=850072&gt;Echo&lt;/te&gt; trên cánh tay lấp lánh mờ ảo, soi sáng đôi mắt cô.
+Bản tính hoạt bát của Youhu tỏa sáng khi cô đắm chìm trong thế giới đồ cổ, vết &lt;te href=850072&gt;Tổ Tacet&lt;/te&gt; trên cánh tay lấp lánh mờ ảo, soi sáng đôi mắt cô.
 Trong mỗi món đồ cổ, cô nhìn thấy một mảnh lịch sử và thoáng thấy tàn tích của một nền văn minh. Phép màu ấy vẫn còn mê hoặc cô cho đến tận ngày nay.
 Chenpi, sư phụ của Youhu, thường khen ngợi tài năng của cô. "Thật lòng mà nói, kiến thức về đồ cổ của con còn thiếu hệ thống. Nhưng đừng lo, ta sẽ dạy con tất cả những gì cần biết."
 "Điều thực sự quý giá là lòng tôn trọng lịch sử trong những món đồ cổ này và sự nhạy bén của con. Nói cách khác, con sinh ra là để làm nghề này."
@@ -27896,13 +27879,13 @@
 Ban đầu, hành động của cô vấp phải sự hoài nghi, nhưng dần dần, phong thái chắc chắn của Carlotta đã lay chuyển những người đấu giá và định hình lựa chọn của họ. Dường như cô có một chiến lược độc đáo dựa trên lý thuyết nghệ thuật, cảm quan thẩm mỹ và tầm nhìn thị trường. Nhưng cô sắp tiến thêm một bước xa hơn để vươn tới những tầm cao mới.
 Và rồi, khoảnh khắc ấy đã đến, ngay tại đó...
 Trong những giây cuối cùng của phiên đấu, Carlotta lại giơ biển đấu giá, khiến những người xung quanh sửng sốt. Thấy vậy, gã đàn ông phô trương lập tức nâng giá cao hơn.
-Countdown. Đấu giá. Countdown. Đấu giá... Phiên đấu lao về phía trước, mỗi lần trả giá dồn dập và nhanh hơn lần trước, đẩy cảm xúc của mọi người lên đến đỉnh điểm nghẹt thở. Người phụ nữ trong bộ đồ cũ kỹ trợn tròn mắt trước những con số tăng vọt. Cậu bé hít thở không kịp khi ngoái đầu qua lại theo nhịp đấu giá điên cuồng.
+Đếm ngược. Đấu giá. Đếm ngược. Đấu giá... Phiên đấu lao về phía trước, mỗi lần trả giá dồn dập và nhanh hơn lần trước, đẩy cảm xúc của mọi người lên đến đỉnh điểm nghẹt thở. Người phụ nữ trong bộ đồ cũ kỹ trợn tròn mắt trước những con số tăng vọt. Cậu bé hít thở không kịp khi ngoái đầu qua lại theo nhịp đấu giá điên cuồng.
 Ngay khi chiếc búa của người đấu giá sắp sửa hạ xuống, Carlotta vẫy tay về phía đối thủ với nụ cười tiếc nuối. "Thật bất ngờ khi lại có người nhận ra giá trị đích thực của bức tranh này. Sự sẵn lòng bỏ ra số tiền lớn như vậy... Nó xứng đáng thuộc về anh."
 Sự kiện kết thúc, nhưng Carlotta vẫn còn vài việc phải giải quyết.
 Cô quan sát gã đàn ông rời đi cùng bức tranh trước khi lui vào một góc yên tĩnh. Cậu bé từng liếc nhìn cô trước đó tiến lại gần.
 "Con đã lỡ miệng nói rằng Carlotta &lt;te href=850101&gt;Montelli&lt;/te&gt; để mắt tới một kiệt tác. Đúng như cô dặn, thưa cô."
 Carlotta mỉm cười và thưởng cho cậu bé. Nếu cậu ta vẫn ngoan ngoãn, cô không ngại sẽ tin tưởng giao phó thêm vài việc vặt vãnh trong tương lai. Còn người phụ nữ vẫn còn lảng vảng gần đó...
-"Carlotta, cháu rất biết ơn những gì cô đã làm cho cháu và cha cháu. It's just... chỉ là..." Người phụ nữ ngập ngừng, tìm kiếm từ ngữ thích hợp. Carlotta không để lỡ cơ hội.
+"Carlotta, cháu rất biết ơn những gì cô đã làm cho cháu và cha cháu. Chỉ là... chỉ là..." Người phụ nữ ngập ngừng, tìm kiếm từ ngữ thích hợp. Carlotta không để lỡ cơ hội.
 "Không, tác phẩm đã được bán với giá hợp lý. Ta đã dùng phương pháp của mình, nhưng tranh của cha cô thực sự đáng giá như vậy. Đôi khi, người ta chỉ thiếu kiên nhẫn thôi."
 Mọi người đều đạt được điều mình muốn. Cô cũng vậy.
 Với suy nghĩ đó, Carlotta rời khỏi phòng đấu giá, biến mất vào màn đêm và cơn mưa.</t>
@@ -27990,27 +27973,27 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Đêm đó, mưa đến bất chợt.
-Nước tràn ngập đường phố và làm cho những khoảnh khắc cuối cùng trước nửa đêm trở nên thê lương hơn. Carlotta ngước mắt nhìn những bóng mờ nhạt qua ánh sáng yếu ớt xuyên qua màn mưa. Phải chăng cô cũng chỉ là một cái bóng trong cơn mưa tầm tã? Yes... Một cái bóng gặt hái sinh mạng để đòi lại công bằng cho quá khứ.
-Mưa sẽ không ngăn cô tìm kiếm người mà cô đang truy lùng.
-Nhấp... Nhấp... Nhấp. Tiếng giày cao gót trên mặt đường ngày càng gần. Một cánh cửa kẽo kẹt mở ra, và Carlotta bước vào. Cô đã băng qua &lt;te href=850097&gt;Ragunna&lt;/te&gt; để tìm người đàn ông đang đứng trước mặt mình, gần như đã bị thời gian lãng quên. Lời cô nói ngắn gọn, "Thẳng thắn mà nói, tôi đến nhân danh &lt;te href=850101&gt;The Montellis&lt;/te&gt; để đọc cáo phó cho ông."
+          <t>Đêm đó, cơn mưa đến bất chợt.
+Nước tràn ngập đường phố, nhấn chìm những khoảnh khắc cuối cùng trước nửa đêm trong nỗi thống khổ sâu thẳm. Carlotta ngước mắt lên, cố nhìn xuyên qua những bóng mờ ảo trong ánh sáng yếu ớt xuyên qua màn mưa. Phải chăng cô cũng chỉ là một cái bóng trong cơn mưa tầm tã? Đúng vậy... Một cái bóng gặt hái mạng sống để đòi lại công bằng cho quá khứ.
+Mưa sẽ không ngăn cô tìm được kẻ cô cần.
+Cạch... cạch... cạch. Tiếng giày gót nhọn trên mặt đường dần đến gần. Một cánh cửa kẽo kẹt mở ra, và Carlotta bước vào. Cô đã băng qua &lt;te href=850097&gt;Ragunna&lt;/te&gt; để tìm đến người đàn ông đứng trước mặt mình, một kẻ gần như bị thời gian lãng quên. Lời cô nói ngắn gọn: "Thẳng thắn mà nói, tôi đến đây nhân danh &lt;te href=850101&gt;Montellis&lt;/te&gt; để đọc cáo phó cho ông."
 "Tôi biết cô sẽ đến."
-Mái tóc ông điểm bạc, khuôn mặt in hằn dấu vết của thời gian và hối tiếc. Giọng ông điềm tĩnh khi nhìn Carlotta một cách trống rỗng.
-"The Montellis không quên món nợ máu. Sớm muộn gì tôi cũng biết mình sẽ bị tìm ra."
-Một ô cửa sổ trong phòng hé mở, gió lạnh lẻn vào mang theo cái rét của đêm. Ông già run rẩy, nhưng sự yếu đuối của ông chỉ khiến Carlotta thêm khó chịu. Ông nói như thể mình chưa từng âm mưu chống lại The Montellis và lấy lòng &lt;te href=850094&gt;Fisalias&lt;/te&gt;. Như thể ông chưa từng dàn xếp vụ đột kích vào trụ sở Montelli khiến bao nhiêu người thiệt mạng, ngay cả sau khi gia đình đã đồng ý thỏa thuận về West End.
-Carlotta đáp lại một cách sắc bén.
-"Ông biết hậu quả của những hành động của mình."
-"Bah! Bọn The Montellis các người chẳng bao giờ thay đổi. Mười năm rồi. Mọi chuyện đã kết thúc. Các người đã lấy lại West End, còn tôi thì trốn như chuột trong hang. Tôi sống trong sợ hãi rằng bất cứ đêm mưa nào, cũng có thể có ai đó như cô lẻn vào và kết liễu đời tôi."
-Ông già thở dài, Dodget mặt trở nên cứng rắn. Tay ông bất ngờ vươn ra tìm vũ khí giấu kín.
-Carlotta không nói gì. Viên pha lê của cô biến thành khẩu súng trong một mối đe dọa im lặng nhưng chết người.
-Đối với Carlotta, đây không phải là về trả thù, mà là về những món nợ chưa trả và danh dự đã mất. Bất kỳ Montelli nào cũng có thể chết, nhưng miễn là còn một Montelli sống sót, gia đình sẽ không sụp đổ. Niềm tin tuyệt đối của một Montelli vào đồng tộc mang lại cho họ sự bình yên để hy sinh vì lợi ích của gia đình. Nếu họ ngã xuống, sẽ có người khác tiếp nối và hoàn thành nhiệm vụ. Vì vậy, ngay cả sau mười năm, món nợ này vẫn phải được thanh toán. Chỉ khi đó, mọi chuyện mới thực sự kết thúc. Đây không bao giờ là vấn đề tiền bạc hay sự kết thúc, mà là về lòng trung thành và cam kết.
-Bang! Một "viên ngọc" khác vỡ tan thành mảnh vụn.
-Ông già đổ gục xuống sàn. Ông ngước nhìn, quyết tâm giữ Carlotta trong tầm mắt, nhưng ông không còn cử động được nữa.
-"Ho... ho... Cô chưa thắng đâu... trò chơi này không kết thúc... bằng cái chết..."
-Yes. Đó là một trò chơi chỉ kết thúc khi đã cạn kiệt.
-Carlotta lặp lại suy nghĩ đó khi bước ra đường. Không khí đêm nhẹ nhàng lướt qua má cô, mang theo sự im lặng vang vọng từ căn phòng.
-Cô đóng cửa lại. Trước khi làm vậy, một tờ giấy với dòng chữ "Nợ đã trả" rơi nhẹ xuống bên chân ông già.
-Và thế... nơi có cái chết bên trong, bên ngoài sẽ luôn là Ragunna.</t>
+Mái tóc ông điểm bạc, khuôn mặt in hằn dấu vết của thời gian và hối tiếc. Giọng ông điềm tĩnh khi nhìn Carlotta với ánh mắt trống rỗng.
+"Nhà Montellis không bao giờ quên món nợ máu. Sớm muộn gì tôi cũng biết mình sẽ bị tìm ra."
+Một ô cửa sổ trong phòng hé mở, gió lạnh lẻn vào mang theo cái rét của màn đêm. Ông già run rẩy, nhưng sự yếu đuối của ông chỉ khiến Carlotta thêm bực bội. Ông nói như thể mình chưa từng âm mưu chống lại nhà Montellis và lấy lòng &lt;te href=850094&gt;Fisalias&lt;/te&gt;. Như thể ông chưa từng đứng sau vụ đột kích vào tổng hành dinh Montellis, cướp đi sinh mạng của biết bao người, ngay cả sau khi gia tộc đã đồng ý thỏa thuận về West End.
+Carlotta đáp lại bằng giọng sắc bén.
+"Ông biết hậu quả của những việc mình làm."
+"Phù! Nhà Montellis các người chẳng bao giờ thay đổi. Mười năm rồi. Mọi chuyện đã kết thúc. Các người đã lấy lại West End, còn tôi thì trốn như chuột trong hang. Tôi sống trong sợ hãi, lo rằng bất cứ đêm mưa nào, cũng sẽ có kẻ như cô lẻn vào kết liễu đời tôi."
+Ông già thở dài, nét mặt trở nên cứng rắn. Tay ông bất ngờ vươn ra tìm vũ khí giấu kín.
+Carlotta không nói gì. Viên pha lê trên tay cô biến thành một khẩu súng trong im lặng, nhưng đầy đe dọa chết chóc.
+Với Carlotta, đây không phải là trả thù, mà là những món nợ chưa trả và danh dự đã mất. Bất kỳ ai trong nhà Montellis có thể ngã xuống, nhưng miễn còn một người Montellis đứng vững, gia tộc sẽ không bao giờ sụp đổ. Niềm tin tuyệt đối của một Montellis vào đồng tộc cho họ sự bình yên để hy sinh vì lợi ích của gia đình. Nếu họ ngã xuống, sẽ có người khác tiếp nối và hoàn thành nhiệm vụ. Vì vậy, dù đã mười năm trôi qua, món nợ này vẫn phải được thanh toán. Chỉ khi đó, mọi chuyện mới thực sự kết thúc. Đây không bao giờ là vấn đề tiền bạc hay sự kết thúc, mà là lòng trung thành và sự tận tụy.
+Bẵng! Một "viên ngọc" nữa vỡ tan thành mảnh vụn.
+Ông già đổ gục xuống sàn. Ông cố ngước lên, quyết giữ Carlotta trong tầm mắt, nhưng cơ thể không còn cử động được nữa.
+"Khụ... khụ... Cô chưa thắng đâu... trò chơi này không kết thúc... bằng cái chết..."
+Đúng vậy. Đó là một trò chơi chỉ kết thúc khi cạn kiệt.
+Carlotta lặp lại suy nghĩ đó khi bước ra đường. Gió đêm nhẹ nhàng lướt qua má cô, cuốn đi sự im lặng vang vọng trong căn phòng.
+Cô đóng cửa lại. Trước khi cửa đóng hẳn, một mảnh giấy với dòng chữ "Món nợ đã thanh toán" rơi nhẹ xuống bên chân ông già.
+Và thế... nơi có cái chết bên trong, bên ngoài vẫn luôn là Ragunna.</t>
         </is>
       </c>
     </row>
@@ -28091,7 +28074,7 @@
         <is>
           <t>Lúc chạng vạng, cơn mưa cuối cùng cũng ngừng rơi.
 Ánh hoàng hôn dịu dàng phủ lên Carlotta khi cô nhâm nhi ly cà phê bên bến cảng. Thủy triều lên xuống, những gợn sóng vàng óng phản chiếu chu kỳ bất tận của ngày và đêm ở Ragunna. Không có đích đến cụ thể, cô lang thang, dừng chân bất chợt. Đây không phải là điều cô thường làm, nhưng trong tương lai, có lẽ cô sẽ biến nó thành thói quen, giống như việc cô đã bắt đầu tìm kiếm những phần thuộc về riêng Carlotta, tách biệt khỏi dòng họ &lt;te href=850101&gt;Montelli&lt;/te&gt;.
-Sau khi cùng vị khách quý danh dự ăn mừng &lt;te href=850102&gt;Carnevale&lt;/te&gt;, và vạch trần sự phản bội của Capollo với sự giúp đỡ của {Male=anh;Female=chị} ấy, Carlotta cuối cùng đã hiểu được điều mà ông nội không thể diễn tả trọn vẹn trong đêm mưa ấy.
+Sau khi cùng vị khách quý danh dự ăn mừng &lt;te href=850102&gt;Carnevale&lt;/te&gt;, và vạch trần sự phản bội của Capollo với sự giúp đỡ của {Male=He;Female=She} ấy, Carlotta cuối cùng đã hiểu được điều mà ông nội không thể diễn tả trọn vẹn trong đêm mưa ấy.
 Ông lo lắng rằng cô có thể làm những việc vì gia tộc mà trái với nguyên tắc của mình. Ông nội không vạch ra con đường nào cho cô dựa trên quá khứ của ông. Ông chỉ mong cô đừng bị mắc kẹt trong những khuôn mẫu đã định sẵn.
 Nhưng sự thật phức tạp hơn thế nhiều.
 Quyết định tiếp tục làm Người Thừa Hành của cô chắc chắn xuất phát từ lợi ích của gia tộc. Nhưng mỗi bước dẫn đến quyết định ấy đều là lựa chọn cô tự nguyện đưa ra, và cuối cùng, đó là tất cả những gì quan trọng. Cô chưa bao giờ là kẻ bị ràng buộc bởi luật lệ. Không phải trước đây. Không phải bây giờ. Và cũng sẽ không bao giờ.
@@ -28100,7 +28083,7 @@
 Một cuộc đời cống hiến để tạo nên một kiệt tác duy nhất, định hình—Carlotta đã chứng kiến nhiều cuộc đời như thế.
 Tấm thảm tương lai của cô là một chủ đề hấp dẫn hơn nhiều, và cô sẵn sàng dệt nên nó, từng sợi từng sợi. Để nắm bắt bản chất của chính mình, cô sẽ tiếp tục cắt gọt, sắp xếp, và chồng lớp... cho đến khi có thể gọi đó là một tác phẩm nghệ thuật đủ sâu sắc.
 Nhưng hiện tại, cô muốn cho phép mình một chút tự hào nhỏ bé.
-Carlotta chưa sẵn sàng gánh vác những phần chỉ tồn tại trong những khoảng lặng của tâm trí mình... Nhưng có lẽ {PlayerName} sẽ là ngoại lệ. Đúng vậy, cô vẫn thích gọi {Male=anh;Female=chị} ấy là Mắt Mèo. Họ đã từng sát cánh bên nhau một thời gian, nhưng cuối cùng, chẳng ai trong số họ có thể dừng bước vì người kia. {Male=Anh;Female=Chị} ấy đã thẳng thắn chỉ ra "sự hoàn hảo thái quá" của cô, và vì vậy, để giữ lời hứa "bớt dè dặt hơn", Carlotta sẽ dệt Mắt Mèo vào câu chuyện của mình. Cô không thể thoát khỏi cảm giác rằng số phận vẫn chưa buông tha họ. Còn khi nào, như thế nào, hay những cuộc phiêu lưu mới nào sẽ diễn ra giữa họ... cô gần như không thể chờ đợi.
+Carlotta chưa sẵn sàng gánh vác những phần chỉ tồn tại trong những khoảng lặng của tâm trí mình... Nhưng có lẽ {PlayerName} sẽ là ngoại lệ. Đúng vậy, cô vẫn thích gọi {Male=him;Female=her} ấy là Mắt Mèo. Họ đã từng sát cánh bên nhau một thời gian, nhưng cuối cùng, chẳng ai trong số họ có thể dừng bước vì người kia. {Male=He;Female=She} ấy đã thẳng thắn chỉ ra "sự hoàn hảo thái quá" của cô, và vì vậy, để giữ lời hứa "bớt dè dặt hơn", Carlotta sẽ dệt Mắt Mèo vào câu chuyện của mình. Cô không thể thoát khỏi cảm giác rằng số phận vẫn chưa buông tha họ. Còn khi nào, như thế nào, hay những cuộc phiêu lưu mới nào sẽ diễn ra giữa họ... cô gần như không thể chờ đợi.
 Xa xa, một chiếc Gondola lướt trên mặt nước tĩnh lặng, trở về bến. Tiếng gọi nhau giữa những người trên thuyền và trên bờ đánh dấu những âm vang cuối cùng của ngày tàn. Sau cơn mưa, chẳng ai biết được điều gì đã xảy ra trong bóng tối của đêm. Hiện tại, chỉ có ánh sáng cuối cùng của ngày lướt nhẹ trên làn da cô, khép lại chu kỳ của ngày.
 Cô uống ngụm cuối cùng trong ly, quay người, và bước vào bóng tối đang dần bao trùm.
 Trong sự tĩnh lặng của thế giới, cô sẽ nhảy điệu nhảy của riêng mình.</t>
@@ -28263,7 +28246,7 @@
 "Nếu ai cũng làm ẩn danh, làm sao người ta biết gọi ai khi gặp nguy hiểm lần sau?"
 "Một anh hùng phải xưng danh thật to để mọi người nhớ mãi!"
 Đó là mục tiêu cô đặt ra từ ngày đầu tiên quyết tâm trở thành anh hùng.
-Từ nhỏ, Chixia đã say mê những siêu anh hùng như Speedster và Fiamma trong các vở kịch Anh Hùng. Tên của họ gợi lên lòng dũng cảm và sự an ủi. Cô mơ ước tạo nên cái tên anh hùng của riêng mình, một cái tên sẽ được lưu danh muôn đời. Mỗi lần giúp đỡ ai đó, Chixia luôn để lại dấu ấn của mình, thậm chí còn dạy trẻ con viết tên cô từng Dodget một.
+Từ nhỏ, Chixia đã say mê những siêu anh hùng như Speedster và Fiamma trong các vở kịch Anh Hùng. Tên của họ gợi lên lòng dũng cảm và sự an ủi. Cô mơ ước tạo nên cái tên anh hùng của riêng mình, một cái tên sẽ được lưu danh muôn đời. Mỗi lần giúp đỡ ai đó, Chixia luôn để lại dấu ấn của mình, thậm chí còn dạy trẻ con viết tên cô từng nét một.
 Và rồi, tên của cô lan truyền khắp &lt;te href=850091&gt;Jinzhou&lt;/te&gt; như ngọn lửa hoang dã. Tên cô trở thành một phần không thể thiếu trong thành phố, mọi người không ngừng gọi "Chixia" mỗi khi cần giúp đỡ. Những thương nhân ngoại quốc không nói được tiếng địa phương lại nhầm "Chixia" là lời chào thông dụng. Vì ai cũng hô to như vậy, sao không theo xu hướng?
 Dù có quyết tâm sắt đá và ngọn lửa nhiệt huyết, Chixia vẫn không tránh khỏi lo lắng. Cô đã dũng cảm chiến đấu với bọn cướp, &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;, và những kẻ khả nghi mặc đồ đỏ ở ngoại ô Jinzhou. Nhưng hiểm nguy luôn xuất hiện bất ngờ, dù cô đã cố gắng bảo vệ thành phố.
 Liệu cô đã thực sự xứng đáng với danh hiệu anh hùng trong mắt mọi người? Dù còn nhiều nghi ngờ, Chixia vẫn tìm thấy niềm an ủi trong những nụ cười của những người cô bảo vệ. Trong khoảnh khắc ấy, mọi lo âu tan biến như chưa từng tồn tại.
@@ -28513,13 +28496,13 @@
       <c r="M417" t="inlineStr">
         <is>
           <t>Các đồng nghiệp của Chixia đã rất ngạc nhiên trước quyết định trở thành Nhân viên Tuần tra Cộng đồng của cô vào ngày tốt nghiệp khóa huấn luyện. 
-Cô đã trải qua không ít khó khăn mới được gia nhập Cục An ninh Public, sau nhiều lần trượt kỳ thi tuyển. Chixia còn nổi tiếng với lòng nhiệt huyết theo đuổi chủ nghĩa anh hùng. Nhiều người cứ ngỡ cô đang nhắm tới một vị trí cao hơn, nên lựa chọn của cô khiến họ không khỏi băn khoăn.
+Cô đã trải qua không ít khó khăn mới được gia nhập Cục An ninh Công cộng, sau nhiều lần trượt kỳ thi tuyển. Chixia còn nổi tiếng với lòng nhiệt huyết theo đuổi chủ nghĩa anh hùng. Nhiều người cứ ngỡ cô đang nhắm tới một vị trí cao hơn, nên lựa chọn của cô khiến họ không khỏi băn khoăn.
 Khi được hỏi về quyết định này, Chixia chỉ cười tươi đáp: "Tớ không thể rời xa &lt;te href=850091&gt;Jinzhou&lt;/te&gt; được. Mì cay, nhà hát, và những người bạn của tớ: Jiu, Qianqian, Ali..."
 Nhưng lý do thực sự đằng sau lựa chọn ấy lại là một câu chuyện phức tạp, khó lòng diễn tả bằng lời. Chỉ có Chixia mới hiểu hết ý nghĩa sâu xa trong quyết định của mình.
 Ngọn lửa nhiệt huyết trong cô được thắp lên từ thuở ấu thơ, nhen nhóm từ những ngọn đuốc của gia đình, và bùng cháy mạnh mẽ hơn qua những hình ảnh anh hùng mà cô thấy trên sân khấu. Trong một đêm giông bão tối tăm, ngọn lửa ấy suýt nữa đã tắt lịm, nhưng rồi một tia sét đã thổi bùng nó lên rực rỡ nhất.
-Hôm ấy, cô bé Chixia dũng cảm cầm đuốc, giả làm Fiamma để đuổi bọn cướp. Nhưng mọi nỗ lực của cô đều vô ích khi một tên trong bọn nhấc bổng cô lên và Dodgem xuống cạnh Ali, người bạn bị bắt làm con tin. Chixia dang tay che chở cho Ali, nhắm mắt sợ hãi. Bỗng nhiên, một tiếng sét chói tai vang lên, và khi cô rụt rè mở mắt, tia chớp đã giáng xuống bọn cướp, khiến chúng ngã lăn quay.
+Hôm ấy, cô bé Chixia dũng cảm cầm đuốc, giả làm Fiamma để đuổi bọn cướp. Nhưng mọi nỗ lực của cô đều vô ích khi một tên trong bọn nhấc bổng cô lên và ném xuống cạnh Ali, người bạn bị bắt làm con tin. Chixia dang tay che chở cho Ali, nhắm mắt sợ hãi. Bỗng nhiên, một tiếng sét chói tai vang lên, và khi cô rụt rè mở mắt, tia chớp đã giáng xuống bọn cướp, khiến chúng ngã lăn quay.
 Giữa những tia chớp loé sáng, cô nhìn thấy chiếc huy hiệu sáng rực trên ngực vị cứu tinh của mình.
-Nhiều năm sau, Chixia cuối cùng cũng vượt qua kỳ thi tuyển vào Cục An ninh Public, mong muốn được đi theo dấu chân của những người anh hùng ấy. Thế nhưng, người bí ẩn đã sử dụng tia sét kia đã biến mất không dấu vết. Theo thời gian, cô dần hiểu tại sao người đó phải ẩn mình, và tại sao cô không phù hợp để trở thành một trong số họ.
+Nhiều năm sau, Chixia cuối cùng cũng vượt qua kỳ thi tuyển vào Cục An ninh Công cộng, mong muốn được đi theo dấu chân của những người anh hùng ấy. Thế nhưng, người bí ẩn đã sử dụng tia sét kia đã biến mất không dấu vết. Theo thời gian, cô dần hiểu tại sao người đó phải ẩn mình, và tại sao cô không phù hợp để trở thành một trong số họ.
 Và rồi, cô nhìn vào lựa chọn "Nhân viên Tuần tra Cộng đồng" – vị trí ít người theo đuổi nhất – và đánh dấu quyết định bên cạnh nó. Dù không thể trở thành tia sét, nhưng vẫn có điều gì đó mà cô phù hợp nhất để làm: bảo vệ cuộc sống bình dị nhưng quý giá của người dân.</t>
         </is>
       </c>
@@ -28842,21 +28825,21 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Là Nhà Tư Vấn vĩ đại của &lt;te href=850109&gt;Black Shores&lt;/te&gt; như hiện tại, thế mà Encore vẫn không chịu cư xử như một cô gái đã trưởng thành. Đối với cô, trưởng thành đồng nghĩa với việc phải từ biệt những câu chuyện trước giờ đi ngủ, một viễn cảnh mà cô kiên quyết từ chối. Ý nghĩ chìm vào giấc ngủ với những giấc mơ trống rỗng, tối tăm thay vì những sắc màu rực rỡ của những câu chuyện kỳ diệu khiến cô không thể chấp nhận được.
-May mắn thay, những người lớn ở Black Shores đều sẵn lòng chiều theo cô. Nhưng có một vấn đề—trong số những người lớn bận rộn ấy, ai có thể dành thời gian để kể cho Encore một câu chuyện ngắn trước khi ngủ? Đúng lúc đó, Cloudy giơ chiếc tay mềm mại nhỏ xinh của mình lên, ngay sau đó là bàn tay mềm mại tối màu của Cosmos.
-Tối hôm ấy, Cloudy mang đến cho Encore câu chuyện cổ tích về Ngôi Nhà Candy.
+          <t>Là Nhà Tư Vấn vĩ đại của &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt; như hiện tại, thế mà Encore vẫn không chịu cư xử như một cô gái đã trưởng thành. Đối với cô, trưởng thành đồng nghĩa với việc phải từ biệt những câu chuyện trước giờ đi ngủ, một viễn cảnh mà cô kiên quyết từ chối. Ý nghĩ chìm vào giấc ngủ với những giấc mơ trống rỗng, tối tăm thay vì những sắc màu rực rỡ của những câu chuyện kỳ diệu khiến cô không thể chấp nhận được.
+May mắn thay, những người lớn ở Bờ Biển Đen đều sẵn lòng chiều theo cô. Nhưng có một vấn đề—trong số những người lớn bận rộn ấy, ai có thể dành thời gian để kể cho Encore một câu chuyện ngắn trước khi ngủ? Đúng lúc đó, Cloudy giơ chiếc tay mềm mại nhỏ xinh của mình lên, ngay sau đó là bàn tay mềm mại tối màu của Cosmos.
+Tối hôm ấy, Cloudy mang đến cho Encore câu chuyện cổ tích về Ngôi Nhà Kẹo.
 "Rồi... rồi..." Giọng Cloudy nhỏ dần, nhẹ nhàng hơn. Ôi không, hình như nó đã quên mất đoạn tiếp theo. Lo lắng, Cloudy liếc nhìn người bạn đồng hành, kéo chăn lên che mình để giấu đi sự xấu hổ tột độ.
 "Tớ biết! Tớ biết!" Cosmos hào hứng đẩy Cloudy sang một bên, đứng bên giường Encore và tự hào tiếp tục câu chuyện. "Rồi, Đại Encore vĩ đại, được ngọn lửa rực cháy phù hộ, đã đánh bại con mèo xấu xa kia! Bộ lông bẩn thỉu của nó cháy sém hết rồi!"
 "Thế còn bạn bè của Đại Encore thì sao?"
 "Tất nhiên là mọi người đều an toàn nhờ có Đại Encore rồi. Từ đó về sau, mọi người sống hạnh phúc mà không còn lo sợ con mèo xấu xa kia nữa!"
 Encore chìm đắm trong câu chuyện cho đến khi mí mắt cô nặng trĩu trước lời mời gọi của giấc ngủ. Cô muốn nói thêm rằng "Mẹ Giám Đốc KHÔNG phải là con mèo xấu xa đâu," nhưng cô đã quá mệt để nói trọn câu. Cuối cùng, Cloudy và Cosmos, bị bối rối bởi lời lẩm bẩm phản đối của Encore, cũng chui vào chăn mềm mại cùng cô, và cả ba chìm vào giấc ngủ sâu.
-Trong giấc mơ, Encore thấy mình trở lại trại trẻ mồ côi, đứng trước Ngôi Nhà Candy bị ngọn lửa thiêu đốt.
+Trong giấc mơ, Encore thấy mình trở lại trại trẻ mồ côi, đứng trước Ngôi Nhà Kẹo bị ngọn lửa thiêu đốt.
 Mái nhà tan chảy trong biển lửa, si-rô sôi sùng sục chảy xuống con mèo đen đang hấp hối, khiến nỗi đau của nó càng thêm tột cùng. Con vật ấy là biểu tượng ghê tởm cho chính tội lỗi của nó. Encore chứng kiến cái chết của nó, hậu quả tất yếu của những hành động độc ác.
 Thế nhưng, Thần Chết không dễ dàng tha thứ cho linh hồn tội lỗi ấy, kẻ đã nhúng tay vào máu của những sinh linh vô tội. Hắn chọn cách tra tấn nó, tận hưởng lời thú tội miễn cưỡng của kẻ tội đồ.
 Những tiếng thét đau đớn vang vọng khắp khu rừng. Tất cả sinh vật, từ linh cẩu hung dữ đến quạ kiêu ngạo, đều co rúm lại trong sợ hãi. Ở nơi tĩnh lặng này, chỉ còn Encore và những linh hồn đang hấp hối chịu đựng.
 "Chắc là đau lắm..." Ngọn lửa rực cháy chiếu sáng khuôn mặt Encore khi cô tiến lại gần con mèo đang hấp hối. Cô nhẹ nhàng áp má vào thân thể nó, dùng đôi bàn tay nhỏ bé đầy sẹo của mình vuốt ve bộ lông.
-Con mèo khổng lồ oán giận Encore vì đã phá hỏng kế hoạch của nó, và nó mong cô cũng cảm thấy như vậy. Xét cho cùng, tội ác của nó đủ tàn nhẫn để khiến mọi người căm ghét. Nhưng why? Tại sao từ bàn tay nhỏ bé của Encore, nó chỉ cảm nhận được sự ấm áp và nỗi buồn?
-Ngọn lửa điên cuồng nhảy múa quanh Ngôi Nhà Candy, như thể quyết tâm thiêu rụi tất cả. Thế nhưng, Encore không hề sợ hãi. Cô dựa vào con mèo khổng lồ và bắt đầu hát một bài hát ru.
+Con mèo khổng lồ oán giận Encore vì đã phá hỏng kế hoạch của nó, và nó mong cô cũng cảm thấy như vậy. Xét cho cùng, tội ác của nó đủ tàn nhẫn để khiến mọi người căm ghét. Nhưng tại sao? Tại sao từ bàn tay nhỏ bé của Encore, nó chỉ cảm nhận được sự ấm áp và nỗi buồn?
+Ngọn lửa điên cuồng nhảy múa quanh Ngôi Nhà Kẹo, như thể quyết tâm thiêu rụi tất cả. Thế nhưng, Encore không hề sợ hãi. Cô dựa vào con mèo khổng lồ và bắt đầu hát một bài hát ru.
 Đó là giai điệu mà con mèo đã từng nghe khi Encore và những đứa trẻ khác trong trại trẻ mồ côi gọi nó là "Mẹ Giám Đốc". Nó đã hát bài hát ấy vô số lần cho từng đứa con của mình.
 Encore tiếp tục hát, giọng cô khàn đi, cho đến khi ngọn lửa rực cháy tắt hẳn, cho đến khi ánh bình minh đầu tiên ló dạng trên bầu trời. Cô cảm nhận được ánh nắng ấm áp trên đầu ngón tay, và "phép màu" của con mèo dần tan biến, biến mất vào màn sương mờ ảo của khu rừng.
 Nhìn xuống, con mèo to lớn, xấu xí ngày nào đã biến thành một chú mèo con nhỏ bé, cuộn tròn trong vòng tay Encore, ngủ say sưa.
@@ -28945,7 +28928,7 @@
 'Chú này kỳ lạ thật. Encore không hiểu chú nói gì cả.' Đặt truyện sang một bên, Encore quan sát Aalto, bắt chước sự soi mói của ông. Với cô, Aalto trông như một chú chó to, hay có khi là sói—một con sói xám hiền lành, không hề nhe nanh với cô.
 'Ồ phải, cháu là Encore. Đúng rồi. Cháu chính là người ta tìm. Khoan! Sao cháu lại gọi ta là chú? Nhìn kỹ lại đi. Ta có già đến thế à?' Vẻ mặt buồn bã của Aalto chỉ khiến Encore cười khúc khích. Có lẽ vì buồn chán trong bệnh viện, cô quyết định trêu chọc người lớn kỳ lạ này thêm chút nữa.
 'Được rồi, để Encore nhìn kỹ lại... Ừ! Chú vẫn là ông già to xác! Một ông chú!
-Aalto thở dài ngao ngán. 'Trời ơi...' Ông tiếp tục, 'Thôi nào, nói gì đó dễ thương đi. Đây đâu phải việc dễ dàng, biết không? Ta còn phải lo cho mấy đứa nhỏ khác ở trại trẻ nữa.' Ông cầu khẩn, biết rằng bị một đứa trẻ trêu chọc chẳng là gì so với trách nhiệm của mình với &lt;te href=850109&gt;Black Shores&lt;/te&gt;.
+Aalto thở dài ngao ngán. 'Trời ơi...' Ông tiếp tục, 'Thôi nào, nói gì đó dễ thương đi. Đây đâu phải việc dễ dàng, biết không? Ta còn phải lo cho mấy đứa nhỏ khác ở trại trẻ nữa.' Ông cầu khẩn, biết rằng bị một đứa trẻ trêu chọc chẳng là gì so với trách nhiệm của mình với &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt;.
 'Dù sao, quay lại vấn đề chính. Cháu có đi với ta không, cô bé?' Giọng Aalto chuyển từ đùa giỡn sang nghiêm túc, nhưng nhanh chóng trở lại vẻ hài hước thường lệ, 'Cháu muốn kẹo gì cũng được. À... nhưng đừng ăn nhiều quá. Hỏng răng đấy.'
 'Nghe khả nghi quá,' Encore đáp, đôi mắt sáng long lanh tò mò. Thay vì trả lời câu hỏi của Aalto, cô nhấc Cosmos và Cloudy lên, áp sát vào tai. 'Các bạn Lông Xù? Các bạn có gì muốn nói với Encore không? Hmm... Ồ, thật sao? Vậy ông chú kỳ lạ này thực ra là người tốt? Không đời nào!'
 'Này, ta sẽ bỏ qua việc cháu gọi ta là chú, nhưng 'không đời nào' là sao? Ta không trông giống một người tốt hoàn hảo à?'
@@ -29026,7 +29009,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Là Nghiên cứu viên Quốc tế duy nhất tại &lt;te href=850092&gt;Huaxu Academy&lt;/te&gt;, Mortefi thu hút rất nhiều sự chú ý từ người dân địa phương.
+          <t>Là Nghiên cứu viên Quốc tế duy nhất tại &lt;te href=850092&gt;Học viện Huaxu&lt;/te&gt;, Mortefi thu hút rất nhiều sự chú ý từ người dân địa phương.
 Niềm đam mê nhạc cổ điển, thói quen thưởng thức bữa trà chiều cùng món tráng miệng tinh tế, và cuối cùng là nỗi ám ảnh gần như bệnh lý với sự sạch sẽ... Những chi tiết này đủ để nói lên xuất thân quý tộc của Mortefi.
 Mortefi thừa nhận rằng gia cảnh đã góp phần hình thành tính cách của ông, nhưng đó không phải là yếu tố duy nhất.
 Một giả thuyết cho rằng mọi bản nhạc đều đã được sáng tác sẵn, và nhiệm vụ của các nhạc sĩ là khám phá ra những giai điệu đó. Tương tự, các nhà khoa học dành cả đời để cố hiểu những "giai điệu" của vũ trụ. Mortefi lấy cảm hứng từ sự chính xác và hài hòa của nhạc cổ điển cho nghiên cứu của mình.
@@ -29105,7 +29088,7 @@
       <c r="M424" t="inlineStr">
         <is>
           <t>Dù thỉnh thoảng trông đáng sợ, Mortefi không phải kiểu người dễ nổi nóng. 
-Thay vào đó, hắn chỉ dùng cái lưỡi sắc bén của mình vào những lúc cấp bách, nhất là khi đồng nghiệp gặp phải khách hàng vô lý và bất hợp lý. Trong những tình huống đó, Mortefi luôn đảm bảo họ phải nếm trải đủ "kho vũ khí ngôn từ" của hắn. Những phép ẩn dụ rối rắm và điển tích văn học mà giới thượng lưu Liên bang New ưa chuộng, cùng với những từ lóng &lt;te href=850093&gt;Huanglong&lt;/te&gt; mới nhất, có thể khiến người ta hoa mắt chóng mặt. 
+Thay vào đó, hắn chỉ dùng cái lưỡi sắc bén của mình vào những lúc cấp bách, nhất là khi đồng nghiệp gặp phải khách hàng vô lý và bất hợp lý. Trong những tình huống đó, Mortefi luôn đảm bảo họ phải nếm trải đủ "kho vũ khí ngôn từ" của hắn. Những phép ẩn dụ rối rắm và điển tích văn học mà giới thượng lưu Liên bang Mới ưa chuộng, cùng với những từ lóng &lt;te href=850093&gt;Huanglong&lt;/te&gt; mới nhất, có thể khiến người ta hoa mắt chóng mặt. 
 Muốn hiểu thấu thông điệp ẩn sau những lời châm chọc cay độc của Mortefi, có lẽ phải tự mình trải nghiệm. Nhưng rồi, có những bí ẩn tốt hơn là nên để yên. Người ta thậm chí còn biên soạn những câu châm biếm của Mortefi thành những tờ ghi chú tiện lợi, mang theo bên mình như đạn dược để chống lại những tình huống bất công mà họ không tìm được lời phản kháng. 
 Mortefi đã có lúc cứng họng khi phát hiện ra điều này. Hắn cười khẩy, bất lực: "Không phải họ không biết nói gì, mà là áp lực xã hội và những quy chuẩn văn hóa đã bịt miệng họ. Là kẻ ngoài cuộc, không bị ràng buộc bởi những quy tắc của Huanglong, ta chỉ tình cờ có thể nói thay họ mà thôi." 
 Không vướng bận nghĩa vụ xã hội hay vấn đề tài chính, quả thật một người như Mortefi - kẻ ngoại quốc với xuất thân thượng lưu - có thể tự do đến vậy. 
@@ -29265,10 +29248,10 @@
           <t>Tuổi thơ của Mortefi ngột ngạt, bị giam cầm bởi những quy chuẩn đạo đức giả của giới thượng lưu và sự thờ ơ của cha mẹ.
 Bị nhốt trong căn phòng học u ám, cậu chỉ còn cách trút giận lên đồ đạc trong nhà. Nhưng ngay cả hành động nổi loạn nhỏ nhoi ấy cũng nhanh chóng mất đi ý nghĩa khi cha mẹ cậu chỉ đơn giản thay thế những món đồ bị phá hủy. Chúng luôn mới tinh, sáng bóng, được sắp xếp gọn gàng, như một lời nhắc nhở không ngừng về sự phản kháng vô nghĩa của Mortefi.
 Những khoảnh khắc yên bình duy nhất cậu có được là khi tháo dỡ và lắp ráp lại những món đồ cơ khí. Một hình thức giao tiếp độc đáo giữa con người và máy móc đã mang đến cho cậu sự bình yên cần thiết: trong những khoảnh khắc ấy, cậu có thể tin tưởng mà không nghi ngờ, là chính mình mà không cần nịnh hót, và không còn phải chịu đựng những cơn giận vô cớ. Trong thế giới của bánh răng và trục quay, không có chỗ cho sự mơ hồ. Nếu máy móc trục trặc, cậu chỉ cần xác định và giải quyết vấn đề từng bước một.
-Cha mẹ Mortefi không la mắng khi phát hiện cậu làm gì; thay vào đó, họ tự hào. Sự sùng bái công nghệ đã ăn sâu vào máu của mọi công dân Liên bang New, và tài năng của cậu được công nhận là một tài sản quý giá.
+Cha mẹ Mortefi không la mắng khi phát hiện cậu làm gì; thay vào đó, họ tự hào. Sự sùng bái công nghệ đã ăn sâu vào máu của mọi công dân Liên bang Mới, và tài năng của cậu được công nhận là một tài sản quý giá.
 Với sự hỗ trợ của họ, Mortefi có được những nguồn tài nguyên hiếm có, sự hướng dẫn của những bậc thầy hàng đầu và cơ hội tham gia các sự kiện nghiên cứu danh tiếng. Cậu nhận được vô số lời khen ngợi và được tôn vinh là thần đồng khoa học trẻ nhất đất nước.
 ...Cho đến khi mọi thứ thay đổi khi cậu gặp một chàng trai trẻ.
-Đến tận bây giờ, Mortefi vẫn nhớ rõ cuộc gặp gỡ đó tại Triển lãm Thế giới của Liên bang New, khi cậu mới 17 tuổi.
+Đến tận bây giờ, Mortefi vẫn nhớ rõ cuộc gặp gỡ đó tại Triển lãm Thế giới của Liên bang Mới, khi cậu mới 17 tuổi.
 Đó là một kiệt tác, được chế tác từ những vật liệu rẻ tiền nhưng lại sở hữu độ ổn định của những vật liệu cao cấp nhất. Thiết kế tưởng chừng đơn giản ấy lại đáng để nghiên cứu sâu, với vô số bài báo viết về nó. Dù đơn giản và tiết kiệm, nó vẫn vượt trội hơn tất cả phát minh của Mortefi về tính thực tiễn và khả năng ứng dụng. Đó là một bước đột phá thực sự cho nhân loại, một thiên tài đích thực.
 Mortefi nhìn chằm chằm vào chàng trai trẻ trong đám đông, người dường như cảm nhận được ánh mắt của cậu và quay lại đối diện. 
 Giữa tiếng reo hò và tiếng ồn ào chói tai, cậu chỉ kịp ghi nhớ nơi xuất thân của chàng trai ấy: &lt;te href=850093&gt;Huanglong&lt;/te&gt;.</t>
@@ -29350,13 +29333,13 @@
       <c r="M427" t="inlineStr">
         <is>
           <t>Trước khi Wutherology chính thức trở thành một nhánh của khoa học hiện đại, công nghệ Tacetite từng bị coi là "phép thuật".
-Ít ai biết tại sao Mortefi rời bỏ New Federation vào ngày lễ trưởng thành của mình, hay anh đã trải qua những gì trên đường đến &lt;te href=850093&gt;Huanglong&lt;/te&gt;... Và giờ đây, anh say mê nghiên cứu Tacetite đến mức cuồng nhiệt.
-"Ta vừa cải tiến mô-đun Tacetite trong khẩu súng này, chỉ một chút thôi. Giờ nó có thể xuất ra công suất gấp trăm lần. Nhưng phải tuân thủ đúng 100 quy tắc vận hành này..."
+Ít ai biết tại sao Mortefi rời bỏ Liên Bang Mới vào ngày lễ trưởng thành của mình, hay anh đã trải qua những gì trên đường đến &lt;te href=850093&gt;Huanglong&lt;/te&gt;... Và giờ đây, anh say mê nghiên cứu Tacetite đến mức cuồng nhiệt.
+"Tao vừa cải tiến mô-đun Tacetite trong khẩu súng này, chỉ một chút thôi. Giờ nó có thể xuất ra công suất gấp trăm lần. Nhưng phải tuân thủ đúng 100 quy tắc vận hành này..."
 "Chờ đã, nếu không làm theo thì sao?"
 "Năng lượng Tacetite đủ sức nhổ bật cả thành phố này lên và đưa nó lên thiên đường đấy."
 "..."
-"Tsk. Nhìn cái mặt cậu kìa? Ta chỉ chịu trách nhiệm cung cấp thứ cậu cần và giải thích cần thiết. Còn dùng nó như thế nào là quyền của cậu."
-Những trường hợp tương tự không hiếm, cuối cùng khiến &lt;te href=850092&gt;Huaxu Academy&lt;/te&gt; nằm trong danh sách theo dõi đặc biệt của các Giám đốc tại &lt;te href=850085&gt;Bộ Phát triển&lt;/te&gt;. Động lực không ngừng nghỉ ấy đã thúc đẩy Wutherology phát triển vượt bậc, nhưng cũng phải trả giá.
+"Tsk. Nhìn cái mặt cậu kìa? Tao chỉ chịu trách nhiệm cung cấp thứ cậu cần và giải thích cần thiết. Còn dùng nó như thế nào là quyền của cậu."
+Những trường hợp tương tự không hiếm, cuối cùng khiến &lt;te href=850092&gt;Học viện Huaxu&lt;/te&gt; nằm trong danh sách theo dõi đặc biệt của các Giám đốc tại &lt;te href=850085&gt;Bộ Phát triển&lt;/te&gt;. Động lực không ngừng nghỉ ấy đã thúc đẩy Wutherology phát triển vượt bậc, nhưng cũng phải trả giá.
 Cuối cùng, ngay cả các học giả khác trong viện cũng bắt đầu lo lắng cho Mortefi, người thường xuyên thức trắng nhiều đêm để theo đuổi sự hoàn hảo. Anh làm việc không ngừng nghỉ, nhưng với tốc độ này, anh có nguy cơ cạn kiệt sức lực như ngọn lửa tự thiêu.
 Mortefi vẫn nhớ lời nhắc nhở của thầy mình: luôn nhớ mục tiêu của mình là gì. Có lẽ, anh chỉ đang tìm niềm vui trong việc trò chuyện với máy móc.
 Nếu một ngày ngọn lửa ấy tắt, anh hy vọng sẽ để lại di sản tri thức cho thế hệ sau. Để ngọn lửa ấy cháy sáng hơn, soi đường cho những người đi sau.
@@ -29445,7 +29428,7 @@
         <is>
           <t>Dạo gần đây, những ai đến Tòa Thị Chính hiếm khi còn thấy được vị Cố Vấn huyền thoại, Changli, như lời đồn đại.
 Dù Cố Vấn Changli chưa bao giờ là một nhân vật công chúng, nhưng với tư cách là trợ thủ đắc lực nhất của &lt;te href=850091&gt;Magistrate&lt;/te&gt; &lt;te href=850084&gt;Jinzhou&lt;/te&gt;, bà được mọi người ở Jinzhou biết đến. Thế nhưng, những lời đồn đại bất an và kỳ lạ về bà lại ngày càng nhiều.
-Người ta nói rằng, khi còn ở kinh đô, Cố Vấn Changli đã đề xuất cải tạo các &lt;te href=850126&gt;Home Tạm Trú&lt;/te&gt; trên toàn Huanglong để cung cấp nơi ở tốt hơn cho những người tị nạn mất nhà cửa sau hậu quả của &lt;te href=850075&gt;Lament&lt;/te&gt;; bà còn thúc đẩy giảm thuế thương mại ở Jinzhou và phân bổ lương thực, tài chính để giúp Jinzhou phục hồi sau trận Chiến Dưới Trăng Lưỡi Liềm.
+Người ta nói rằng, khi còn ở kinh đô, Cố Vấn Changli đã đề xuất cải tạo các &lt;te href=850126&gt;Nhà Tạm Trú&lt;/te&gt; trên toàn Huanglong để cung cấp nơi ở tốt hơn cho những người tị nạn mất nhà cửa sau hậu quả của &lt;te href=850075&gt;Lament&lt;/te&gt;; bà còn thúc đẩy giảm thuế thương mại ở Jinzhou và phân bổ lương thực, tài chính để giúp Jinzhou phục hồi sau trận Chiến Dưới Trăng Lưỡi Liềm.
 Người ta nói rằng ngay khi Cố Vấn Changli đặt chân đến Tòa Thị Chính, bà đã dễ dàng giải quyết hai băng cướp lâu năm quanh Jinzhou chỉ bằng một cuộc trò chuyện và một cái "bẫy hiển nhiên". Chỉ thế thôi cũng đủ khiến hai băng nhóm nghi ngờ lẫn nhau và tự diệt đến mức không còn là mối đe dọa.
 Người ta nói rằng Cố Vấn Changli không trở thành Cố Vấn sau khi &lt;te href=850083&gt;Sentinel&lt;/te&gt; chọn Magistrate Jinzhou, mà từ lâu bà đã tình nguyện đến Jinzhou, dạy dỗ Jinhsi còn trẻ, và giúp cô gánh vác trọng trách quá sức với một đứa trẻ.
 "Có thật không? Tôi nghe nói những việc đó là do Tổng Thư Ký tiền nhiệm thực hiện, còn bà chỉ bị giáng chức ra biên ải vì đã đắc tội với thế lực cũ thôi?"
@@ -29455,7 +29438,7 @@
 Những lời đồn đại về vị Magistrate mới của Jinzhou, người được Sentinel chọn, lan nhanh như lửa cháy. Một cô gái trẻ, dường như còn chưa đủ tuổi, lại nắm giữ vị trí quyền lực này. Có người thì thầm rằng Changli có quá nhiều ảnh hưởng và đang tìm cách lật đổ Magistrate hiện tại để chiếm quyền.
 Sau buổi lễ, Changli giao lại quyền lực cho Jinhsi và trở thành Cố Vấn của cô. Trong ba năm, cuộc sống của mọi người ở Jinzhou được cải thiện, và họ biết ơn Magistrate. Nhưng không ai biết được Changli đã giúp đỡ bao nhiêu trong bóng tối.
 Những ai từng gặp Changli đều nói rằng bà luôn nở nụ cười dịu dàng, đối xử công bằng với mọi người từ tướng lĩnh đến binh lính, nhưng khi ở một mình, bà lại toát ra một khí chất uy nghiêm khiến người khác không dám bén mảng.
-"Lần trước tôi gặp Cố Vấn Changli ở &lt;te href=850089&gt;Patrol Station&lt;/te&gt;, bà ấy dường như rất quan tâm đến mấy cái cây trong sân, không hiểu sao... Tôi cứ nghĩ bà có việc quan trọng phải làm, nhưng bà lại dành cả buổi chiều... để ngắm kiến bò..."
+"Lần trước tôi gặp Cố Vấn Changli ở &lt;te href=850089&gt;Trạm Tuần Tra&lt;/te&gt;, bà ấy dường như rất quan tâm đến mấy cái cây trong sân, không hiểu sao... Tôi cứ nghĩ bà có việc quan trọng phải làm, nhưng bà lại dành cả buổi chiều... để ngắm kiến bò..."
 "Rồi sao?"
 "Rồi một tên tội phạm truy nã tự dưng đến đầu thú! Ban đầu chúng tôi còn cảnh giác, nghĩ là bẫy. Nhưng khi Cố Vấn Changli xuất hiện, tên tội phạm sợ đến mức thú tội tất cả, kể cả những vụ án chưa phá được. Đó là vụ án lớn nhất trong sự nghiệp của tôi..."
 "Còn Cố Vấn Changli thì sao?"
@@ -29651,8 +29634,8 @@
         <is>
           <t>Công việc ở Nhà Sách Yanqing đã trở lại bình thường, dòng người yêu sách qua lại tấp nập, nhưng cô bé thường ngồi lặng lẽ đọc sách giữa những kệ sách đã biến mất.
 Thật bất ngờ, một tuần sau, cô bé quay lại.
-"Đây là tất cả tiền của cháu. Cháu xin thề, cháu tự kiếm được đấy! Xin lỗi vì đã đốt mấy cuốn sách... Chỉ có chú là còn giữ những cuốn cháu cần. Please, cho cháu..."
-Cô bé cắn môi, rụt rè đặt những đồng &lt;te href=850104&gt;Shell Credit&lt;/te&gt; vụn vặt trong tay lên quầy. Dáng người nhỏ bé của em còn không cao bằng mặt quầy, chỉ lộ ra nửa đầu. Em nhón chân, người run run, nhưng đôi mắt sáng và cứng cỏi vẫn không rời khỏi ông, không hề Dodge.
+"Đây là tất cả tiền của cháu. Cháu xin thề, cháu tự kiếm được đấy! Xin lỗi vì đã đốt mấy cuốn sách... Chỉ có chú là còn giữ những cuốn cháu cần. Làm ơn, cho cháu..."
+Cô bé cắn môi, rụt rè đặt những đồng &lt;te href=850104&gt;Shell Credit&lt;/te&gt; vụn vặt trong tay lên quầy. Dáng người nhỏ bé của em còn không cao bằng mặt quầy, chỉ lộ ra nửa đầu. Em nhón chân, người run run, nhưng đôi mắt sáng và cứng cỏi vẫn không rời khỏi ông, không hề né tránh.
 "...Được rồi."
 Sau bao ngày, cơn giận của Changqing đã nguôi ngoi từ lâu. Ông vẫy tay, "Đi đi, cầm tiền về, đừng làm phiền việc kinh doanh của ta nữa."
 Cô bé cúi đầu, lặng lẽ rời đi. Em cứ dừng lại ngoái nhìn liên tục trên đường đi. Changqing thở dài, lặng nhìn dáng vẻ gầy gò, quần áo sờn rách của em. Ông đứng dậy, lấy một chiếc đèn và đưa cho cô bé cùng chiếc chìa khóa dự phòng của cửa hàng.
@@ -29667,7 +29650,7 @@
 Một ngày nọ, cô bé biến mất. Tin đồn lan truyền—liệu em có bị &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; bắt đi? Hay đã gục ngã vì thương tích trên đường đến kinh thành?
 Nhìn thấy họa tiết ngọn lửa trên lá thư, Changqing bỗng cảm thấy một tia hy vọng. Liệu em có còn sống?
 "Xin lỗi?"
-Dòng hồi tưởng của Changqing bị ngắt quãng bởi một quý cô cao ráo, thanh lịch đứng trước quầy. Đôi mắt dịu dàng và mái tóc màu lửa, như lông vũ của một loài chim thần thoại, khẽ đung đưa trong gió. Cô đặt vài đồng Shell Credit lên quầy và mỉm cười hỏi: "Thưa chú, chỉ có chú là còn giữ những cuốn sách cháu cần. Please, cho cháu mượn được không?"
+Dòng hồi tưởng của Changqing bị ngắt quãng bởi một quý cô cao ráo, thanh lịch đứng trước quầy. Đôi mắt dịu dàng và mái tóc màu lửa, như lông vũ của một loài chim thần thoại, khẽ đung đưa trong gió. Cô đặt vài đồng Shell Credit lên quầy và mỉm cười hỏi: "Thưa chú, chỉ có chú là còn giữ những cuốn sách cháu cần. Làm ơn, cho cháu mượn được không?"
 Từ một cô bé yếu đuối, em đã trở thành Tổng Thư Ký trẻ trung, tự tin, nổi tiếng khắp nơi. Khi ánh mặt trời buổi sáng tràn ngập căn phòng, ông chủ hiệu sách già mỉm cười và ra hiệu cho cô tiếp tục đọc.
 "Cứ đọc đi... Dù không trả tiền cũng được. Giờ ta cũng chẳng ép được con nữa đâu."</t>
         </is>
@@ -29751,17 +29734,17 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Master Xuanmiao đã tìm kiếm một người nào đó suốt thời gian qua.
+          <t>Sư phụ Xuanmiao đã tìm kiếm một người nào đó suốt thời gian qua.
 Cô bé Changli theo chân vị sư phụ già cỗi của mình băng qua những vùng đất của &lt;te href=850093&gt;Huanglong&lt;/te&gt;. Dù ban đầu ông miễn cưỡng nhận thêm đệ tử, nhưng vị trưởng lão đáng kính ấy đã dốc hết tâm huyết truyền lại từng chút tri thức quý báu cho cô trong khoảng thời gian hạn hẹp còn lại.
-Master Xuanmiao là một người đam mê cờ vây. Trong những giờ nghỉ giữa hành trình mệt mỏi, họ thường dừng chân bên đường để đấu những ván cờ căng thẳng. Những lúc ấy không chỉ để giải trí, ông còn dùng làm cơ hội dạy dỗ Changli, truyền đạt cho cô những bài học về tư duy chiến lược và sự vận động của quyền lực trong từng nước đi. Đôi khi, ông phân tích một ván cờ dở dang với cô, nhưng dường như ông luôn không hoàn toàn hài lòng với câu trả lời của cô.
+Sư phụ Xuanmiao là một người đam mê cờ vây. Trong những giờ nghỉ giữa hành trình mệt mỏi, họ thường dừng chân bên đường để đấu những ván cờ căng thẳng. Những lúc ấy không chỉ để giải trí, ông còn dùng làm cơ hội dạy dỗ Changli, truyền đạt cho cô những bài học về tư duy chiến lược và sự vận động của quyền lực trong từng nước đi. Đôi khi, ông phân tích một ván cờ dở dang với cô, nhưng dường như ông luôn không hoàn toàn hài lòng với câu trả lời của cô.
 Chính trong những khoảnh khắc đó, ông thường nhắc đến một người bạn cũ, ám chỉ về một nhiệm vụ tìm lại người ấy thông qua việc dạy dỗ Changli. Dù Changli tò mò về danh tính và nơi ở của người bí ẩn này, sư phụ chỉ lắc đầu và nói: "Thời điểm vẫn chưa đến."
 Vào ngày ông cảm nhận được khoảnh khắc cuối cùng đang đến gần, ông giao phó cho Changli cuốn ghi chép ván cờ và nhật ký quý giá của mình. Với vẻ trang nghiêm, ông nói với người đệ tử trung thành: "Trong ván cờ dở dang này, con sẽ tìm thấy chân lý tối thượng."
 Và thế là, Changli tiếp bước di sản của sư phụ Xuanmiao, bước tiếp con đường phía trước.
-"...Một sinh linh từ cõi trời giáng thế, mang trong mình sức mạnh vô biên của vũ trụ, ôm ấp tiếng vọng đầu tiên..."
+"...Một sinh linh từ cõi trời giáng thế, mang trong mình sức mạnh vô biên của vũ trụ, ôm ấp Echo đầu tiên..."
 "...Hình bóng bí ẩn với đôi mắt vàng giữa những đám mây xoáy và ánh sáng phai mờ..."
 "...Bên cạnh &lt;te href=850083&gt;Sentinel&lt;/te&gt; Jué một cách kiên định, trong mối quan hệ đồng hành thân thiết..."
 Theo những ghi chép trong nhật ký của người thầy quá cố, cô tiếp tục cuộc tìm kiếm, phát hiện ra dấu vết của nhân vật bí ẩn ấy ở những nơi không ngờ tới. Đôi khi là những câu chuyện hấp dẫn từ những người kể chuyện lão luyện, đôi khi chỉ là những mảnh vụn thu thập từ kho lưu trữ cổ xưa. Như một người bảo hộ thầm lặng, nhân vật này đã trở thành chiếc neo vững chắc giữa biển động, dẫn dắt nhân loại vượt qua đống đổ nát của những thảm họa quá khứ hướng tới một chân trời hy vọng. Những dấu ấn họ để lại đan xen thành một sợi chỉ mong manh nhưng không thể phá vỡ, bắc cầu qua những khoảng thời gian và lịch sử vượt xa tuổi thọ của một đời người.
-Cô từng được nghe rằng những dấu hiệu về sự xuất hiện của &lt;i&gt;người ấy&lt;/i&gt; sẽ không thể bị bỏ lỡ. Rằng người ấy có sức mạnh thực sự thay đổi thế giới. Tuy nhiên, tầm nhìn của cô về một thế giới hòa bình và thịnh vượng không chỉ dựa vào sự mong đợi mơ hồ về một vị cứu tinh. Hiểu rằng để biến ước mơ thành hiện thực, cô cần có được quyền lực và ảnh hưởng to lớn, cô đã lên đường khám phá nhiều vùng đất, đắm chìm trong tri thức và kiên trì vượt qua mọi thử thách để đáp ứng kỳ vọng đặt lên vai mình.
+Cô từng được nghe rằng những dấu hiệu về sự xuất hiện của *người ấy* sẽ không thể bị bỏ lỡ. Rằng người ấy có sức mạnh thực sự thay đổi thế giới. Tuy nhiên, tầm nhìn của cô về một thế giới hòa bình và thịnh vượng không chỉ dựa vào sự mong đợi mơ hồ về một vị cứu tinh. Hiểu rằng để biến ước mơ thành hiện thực, cô cần có được quyền lực và ảnh hưởng to lớn, cô đã lên đường khám phá nhiều vùng đất, đắm chìm trong tri thức và kiên trì vượt qua mọi thử thách để đáp ứng kỳ vọng đặt lên vai mình.
 Khi đảm nhận vị trí Tổng Thư ký danh giá, cuối cùng cô cũng được bước vào &lt;te href=850117&gt;Thư viện Lớn&lt;/te&gt; uy nghiêm. Trong kho tàng kiến thức vô tận nơi đây, cô đã phát hiện ra một manh mối quan trọng: một gợi ý dẫn cô đến &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, một thành phố biên giới của Huanglong.
 Từ đó, mọi chuyện diễn ra đúng như Sentinel Jué đã tiên đoán. Người cô tìm kiếm đã xuất hiện ở Jinzhou và bảo vệ thành phố khỏi một Threnodian hồi sinh. Hình bóng mơ hồ từ những ghi chép và huyền thoại cổ xưa giờ đây đã trở nên rõ ràng và sống động trong tâm trí cô.
 Vào ngày định mệnh ấy, cô trở về Jinzhou từ Mingting, kinh đô của Huanglong. Cô nhìn thấy vị khách quý của Jinzhou đang đứng đợi ở bến phà dưới cơn mưa, với vẻ mặt đầy lo lắng.
@@ -29849,18 +29832,18 @@
         <is>
           <t>Một tiếng sấm nổ làm gián đoạn nhịp điệu pha chế của người pha rượu, và cơn mưa như trút nước ngay sau đó lập tức cuốn đi chút vui cuối cùng của đám thực khách. Quán rượu giờ đây chẳng khác gì một nơi trú ẩn ẩm ướt, chẳng còn câu chuyện nào đáng kể. Người pha rượu lắc ly từ tốn, tiếng đá va vào nhau nhỏ đến mức khó nghe. Khách khứa ngáp dài liên tục, như thể ngay cả rượu cũng mất đi hương vị.
 "Này này... chẳng giống quán rượu chút nào nhỉ, các bạn?" Một chàng trai trẻ bước vào, mang theo luồng gió ẩm ướt và mùi mưa mặn. Hắn đi thẳng đến quầy bar, giật lấy chiếc ly rỗng của một thực khách bên cạnh.
-"Ê! Ngươi làm cái—"
-"Suỵt..." chàng trai ngắt lời, thản nhiên Dodgem một nắm &lt;te href=850104&gt;Shell Credits&lt;/te&gt; vào lọ tiền tip của người pha rượu. "Đổ đầy ly cho tôi đi. Đâu phải ngày nào tôi cũng vào quán rượu đâu. Chắc hẳn ở đây có thứ gì đó... thú vị hơn chứ?"
+"Ê! Mày làm cái—"
+"Suỵt..." chàng trai ngắt lời, thản nhiên ném một nắm &lt;te href=850104&gt;Shell Credits&lt;/te&gt; vào lọ tiền tip của người pha rượu. "Đổ đầy ly cho tôi đi. Đâu phải ngày nào tôi cũng vào quán rượu đâu. Chắc hẳn ở đây có thứ gì đó... thú vị hơn chứ?"
 "Thú vị? Anh đùa à. Nhìn ra ngoài kìa, mưa chẳng có vẻ gì là sẽ tạnh. Đừng có mà hỏi về thực đơn. Nhạt như nước ốc, mà giá còn đắt gấp đôi."
 "Tất nhiên, tôi vừa từ ngoài mưa vào mà. Nhìn này, tóc tôi sắp chìm trong nước rồi. Nhưng dù trong bão tố, vẫn có những câu chuyện để kể. Như tấm áp phích truy nã đáng yêu này." Hắn nhanh tay giật lấy tấm áp phích từ tay thực khách.
 "À, chúng tôi đã bàn về chuyện này rồi. Gì đó về kẻ Bất Tử Trở Về, đeo mặt nạ kỳ lạ... Hắn đã làm gì nhỉ...?"
 "Hắn và đồng đội vượt qua màn sương mù dày đặc tiếng hát của nàng tiên cá, vớt lên những bản nhạc từ vực sâu đại dương. Họ cứu những cánh buồm của tàu Pilgrim bị sóng lớn lật úp và đoạt lại hàng hóa bị cướp từ tay hải tặc!"
-"Hmm... Chẳng đúng tí nào, phải không? Anh chỉ đang kể chuyện thôi mà!"
+"Hừm... Chẳng đúng tí nào, phải không? Anh chỉ đang kể chuyện thôi mà!"
 "Ha, tất nhiên là chuyện rồi!" Hắn cười lớn, giơ ly lên, "Uống đi, bạn tôi, và tôi sẽ kể cho mọi người nghe câu chuyện thật về kẻ Bất Tử Trở Về!"
 Ly chạm nhau kêu leng keng. Trong nháy mắt, quán rượu ảm đạm biến thành sân khấu của trí tưởng tượng. Brant giật chiếc mũ của thực khách đội lên đầu người pha rượu, mắt sáng rực khi tặng bông hồng người pha rượu hằng mong đợi cho người phụ nữ bên cạnh. Người pha rượu, giờ đội mũ, hóa thân thành người lái tàu. Ông khách hói trở thành thủy thủ, bắn đại bác vào &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; từ biển động. Người phụ nữ nhận hoa bỗng nhảy múa say sưa. Với từng câu chuyện của chàng trai, thực khách như bị cuốn vào câu chuyện mê hoặc ấy.
 Bữa tiệc chấm dứt đột ngột khi cánh cửa bị đạp bật tung.
-"Giờ thì &lt;i&gt;mới&lt;/i&gt; đúng là quán rượu!" Tên cầm đầu toán xâm nhập cười khẩy, giơ cao tấm áp phích truy nã. "Bắt lấy hắn, các người. Lần này tiền thưởng gấp đôi!"
-"Để dành cho lần sau nhé!" Với một cái cúi chào giả vờ, chàng trai Dodgem lên không một chiếc mặt nạ bốc cháy ngọn lửa tím, rồi biến mất trong sự hỗn loạn.
+"Giờ thì mới đúng là quán rượu!" Tên cầm đầu toán xâm nhập cười khẩy, giơ cao tấm áp phích truy nã. "Bắt lấy hắn, các người. Lần này tiền thưởng gấp đôi!"
+"Để dành cho lần sau nhé!" Với một cái cúi chào giả vờ, chàng trai ném lên không một chiếc mặt nạ bốc cháy ngọn lửa tím, rồi biến mất trong sự hỗn loạn.
 Khi khói bụi tan đi, quán rượu ngập tràn ruy băng sặc sỡ, bóng bay và những món quà vương vãi từ biển cả.
 Thực khách nhặt lên những món quà vương vãi. Ngạc nhiên thay, mỗi món đều là một tấm vé xem biểu diễn của &lt;te href=850108&gt;Đoàn Kẻ Ngốc Nghệ Sĩ&lt;/te&gt;.</t>
         </is>
@@ -30029,12 +30012,12 @@
       <c r="M434" t="inlineStr">
         <is>
           <t>Đêm khuya, Brant ngồi bên đống lửa trại, sắp xếp mọi thứ cần thiết cho buổi diễn.
-Đầu tiên là những chiếc mặt nạ. Anh đánh bóng từng chiếc một cách tỉ mỉ, thỉnh thoảng lại đeo lên diễn thử một cảnh. Qua bao năm, Brant đã hóa thân vào vô số vai: người anh hùng bất khả chiến bại, chú hề hài hước, quý tộc phô trương, triều thần mưu mô, thậm chí cả &lt;te href=850100&gt;Acolyte&lt;/te&gt; ngoan đạo. Anh dừng lại, nụ cười nhạt thoáng hiện trên môi khi nghĩ về điều đó. Với anh, đó chẳng phải là những trải nghiệm dễ chịu gì.
-Anh ghét cay ghét đắng bọn triều thần. Cả bọn Acolyte nữa. Nhưng trên sân khấu, anh trở thành từng nhân vật đó một cách trọn vẹn, chôn giấu con người thật của mình sau lớp mặt nạ và bước vào cuộc đời của họ. Anh tôn trọng sân khấu và mọi vai diễn mình đảm nhận, bởi anh biết sân khấu chính là đại dương của mình.
+Đầu tiên là những chiếc mặt nạ. Anh đánh bóng từng chiếc một cách tỉ mỉ, thỉnh thoảng lại đeo lên diễn thử một cảnh. Qua bao năm, Brant đã hóa thân vào vô số vai: người anh hùng bất khả chiến bại, chú hề hài hước, quý tộc phô trương, triều thần mưu mô, thậm chí cả &lt;te href=850100&gt;Tín Đồ&lt;/te&gt; ngoan đạo. Anh dừng lại, nụ cười nhạt thoáng hiện trên môi khi nghĩ về điều đó. Với anh, đó chẳng phải là những trải nghiệm dễ chịu gì.
+Anh ghét cay ghét đắng bọn triều thần. Cả bọn Tín Đồ nữa. Nhưng trên sân khấu, anh trở thành từng nhân vật đó một cách trọn vẹn, chôn giấu con người thật của mình sau lớp mặt nạ và bước vào cuộc đời của họ. Anh tôn trọng sân khấu và mọi vai diễn mình đảm nhận, bởi anh biết sân khấu chính là đại dương của mình.
 Sau khi xong mặt nạ, anh chuyển sang phục trang, ủi từng bộ một cách cẩn thận.
 Trang phục phải hoàn hảo dưới ánh đèn sân khấu. Không chỉ vì vai diễn, mà còn vì khán giả. Để mang lại nụ cười cho họ, tôn trọng là nguyên tắc đầu tiên. Vì thế, anh là phẳng từng nếp gấp, không để sót một nếp nhăn nào. Anh biết tiếng vỗ tay chính là đại dương của mình.
 Cuối cùng, anh bắt đầu sắp xếp đạo cụ sân khấu.
-Thanh kiếm của người anh hùng, trống lục lạc của chú hề, huy hiệu gia tộc của quý tộc, vương trượng của triều thần, cuốn kinh thánh của Acolyte, và rồi... một chiếc hộp gỗ nhỏ.
+Thanh kiếm của người anh hùng, trống lục lạc của chú hề, huy hiệu gia tộc của quý tộc, vương trượng của triều thần, cuốn kinh thánh của Tín Đồ, và rồi... một chiếc hộp gỗ nhỏ.
 Chiếc hộp mà cha mẹ anh để lại. Trên đó khắc hình một con nhạn biển, lời nhắc thầm lặng về cái tên mà anh đã chôn sâu từ lâu. Bên trong, những đường vân xoáy của hóa thạch Ammonoid như một minh chứng cho chuyến phiêu lưu đầu tiên của anh. Nó đã đồng hành cùng anh qua từng ngày đêm trên con tàu Pilgrim's Sail, chứng kiến bệnh tật, đau khổ và chia ly. Hóa thạch vẫn ở bên anh, nhắc nhở anh đừng bao giờ quên những gì mình đã thấy.
 Một lời nhắc nhở để quan sát cuộc sống ngoài sân khấu.
 Một lời nhắc nhở để nhìn thấy sự chân thành đằng sau màn diễn.
@@ -30151,7 +30134,7 @@
 Tiếng reo hò vang lên như màn cuối vừa được vén lên để diễn lại.
 Trong ánh bình minh vàng rực, họ thấy ông—Thuyền trưởng Brant của họ, cưỡi trên đầu con quái vật biển khổng lồ trở về trong chiến thắng.
 "Các bạn ơi, hãy chào đón người bạn mới của chúng ta, Lario! Giờ chúng ta có một con tàu mới rồi!"
-Rồi đây, họ sẽ dựng sân khấu trên lưng con quái vật. Sau này, họ cũng sẽ phát hiện ra Lario không phải một Discord bình thường, mà là một Pliosaurus Somnii hiếm có. Cùng nhau, họ sẽ đi khắp &lt;te href=850096&gt;Rinascita&lt;/te&gt;, kể những câu chuyện của mình cho mọi người nghe.
+Rồi đây, họ sẽ dựng sân khấu trên lưng con quái vật. Sau này, họ cũng sẽ phát hiện ra Lario không phải một Tacet Discord bình thường, mà là một Pliosaurus Somnii hiếm có. Cùng nhau, họ sẽ đi khắp &lt;te href=850096&gt;Rinascita&lt;/te&gt;, kể những câu chuyện của mình cho mọi người nghe.
 Nhưng lúc này, Brant đứng hiên ngang trên lưng quái vật, chào đoàn thủy thủ. "Và đây, bạn ơi, là một màn mở đầu hoàn hảo! Bây giờ, hãy vỗ tay nào!"
 "BRAVO! BRAVO!"</t>
         </is>
@@ -30231,7 +30214,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Đêm hội tưng bừng suốt đêm cuối cùng cũng đã khép lại. Tại Square Tự do, những mảnh kim tuyến và dải ruy băng vẫn lấp lánh mờ ảo trong ánh bình minh. Người qua đường thì thầm về màn trình diễn đêm qua, với họ, đó chỉ là một màn trình diễn thoáng qua. Nhưng đối với những người nghệ sĩ trên sân khấu, màn hạ màn không chỉ là kết thúc, mà còn đánh dấu sự khởi đầu của điều gì đó mới.
+          <t>Đêm hội tưng bừng suốt đêm cuối cùng cũng đã khép lại. Tại Quảng trường Tự do, những mảnh kim tuyến và dải ruy băng vẫn lấp lánh mờ ảo trong ánh bình minh. Người qua đường thì thầm về màn trình diễn đêm qua, với họ, đó chỉ là một màn trình diễn thoáng qua. Nhưng đối với những người nghệ sĩ trên sân khấu, màn hạ màn không chỉ là kết thúc, mà còn đánh dấu sự khởi đầu của điều gì đó mới.
 Lần đầu tiên sau bao năm, họ có thể tự do đi lại trên những con phố của &lt;te href=850097&gt;Ragunna&lt;/te&gt;, trở về những mái nhà đã xa cách từ lâu. Khi ánh đèn sân khấu tắt đi, họ reo hò cho chính mình, bởi trong khoảnh khắc đó, họ đã giành lại niềm vui giản dị là được đứng trên mặt đất vững chắc một lần nữa.
 Nhưng giờ đây, khi đã đặt chân lên đất liền, những kẻ ngốc nghếch như họ sẽ làm gì? Đêm đó, thuyền trưởng đã trò chuyện chân thành với nhiều người trong đoàn. Một số quyết định ra đi, trở về với gia đình mà họ đã nhớ thương. Với những lời chúc phúc và cái ôm ấm áp, thuyền trưởng chúc họ hạnh phúc trong cuộc sống mới. Số khác chọn ở lại cùng đoàn, háo hức khám phá những chân trời mới, và thuyền trưởng vui vẻ chào đón sự đồng hành của họ. Còn những người cảm thấy lạc lõng, không biết bước tiếp theo, thuyền trưởng cho họ thời gian nghỉ ngơi.
 "Dù sao," ông cười tinh nghịch, "khi lễ hội kết thúc, cũng cần thời gian để dọn dẹp những mảnh kim tuyến mà."
@@ -30405,7 +30388,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Nhiều người Lưu Đày bị chặn đứng trên con đường tìm kiếm việc làm chính đáng ở New Federation, phải đối mặt với sự phân biệt đối xử và định kiến vô tận.
+          <t>Nhiều người Lưu Đày bị chặn đứng trên con đường tìm kiếm việc làm chính đáng ở Liên Bang Mới, phải đối mặt với sự phân biệt đối xử và định kiến vô tận.
 Họ đành dựng trại ở vùng ngoại ô đất nước, và nơi họ tụ tập trở thành "Khu Vực Vô Pháp".
 Để sinh tồn tốt hơn, những người Lưu Đày ở Khu Vực Vô Pháp đã thành lập nhiều băng đảng khác nhau.
 Hồi đó, một băng đảng tên "Kẻ Dưới Đáy" nhanh chóng nổi lên.
@@ -30415,7 +30398,7 @@
 Thời gian không hề thương xót ai ở Khu Vực Vô Pháp. Ở đó, ai sống sót là do chính mình.
 Cuối cùng, cậu bé thủ lĩnh quyết định một lần nữa nắm lấy vận mệnh vào tay mình, đánh cược tất cả trong một canh bạc táo bạo để giành lấy quyền lực.
 ...
-Nhiều năm sau, New Federation phát động chiến tranh chống lại "Kẻ Dưới Đáy", băng đảng cuối cùng ở Khu Vực Vô Pháp. Trong một bước ngoặt bất ngờ, một nhóm lính đánh thuê mới mang tên "Ghost Hounds" đã thôn tính "Kẻ Dưới Đáy" chỉ sau một đêm và chấm dứt sự hỗn loạn.
+Nhiều năm sau, Liên Bang Mới phát động chiến tranh chống lại "Kẻ Dưới Đáy", băng đảng cuối cùng ở Khu Vực Vô Pháp. Trong một bước ngoặt bất ngờ, một nhóm lính đánh thuê mới mang tên "Ghost Hounds" đã thôn tính "Kẻ Dưới Đáy" chỉ sau một đêm và chấm dứt sự hỗn loạn.
 Chỉ đến lúc đó, mọi người mới phát hiện ra thủ lĩnh của nhóm lính đánh thuê có cùng tên với cậu bé thủ lĩnh cũ của "Kẻ Dưới Đáy".
 Hắn đã trở lại dưới hình hài kinh hoàng, gần như một bóng ma. Hắn bị bao quanh bởi những gai bóng tối, và đi cùng những bóng ma đáng sợ.
 Lần này, hắn sẽ vươn tới đỉnh cao, hoàn thành những gì trước đây hắn đã thất bại vì ngây thơ, vì lòng thương xót và do dự.
@@ -30606,7 +30589,7 @@
 Những con người này đã cho ông thấy rằng đau buồn không phải là cách duy nhất để tưởng nhớ người đã khuất. Ăn mừng cuộc sống cũng là một cách mạnh mẽ để nói lời tạm biệt.
 "Không tệ nếu đặt căn cứ lâu dài của Ghost Hounds ở thành phố này," Calcharo nghĩ.
 Rồi một điều bất thường làm gián đoạn dòng suy nghĩ của ông.
-Mây đen kéo đến, sấm chớp nổi lên... Đó là điềm báo của một &lt;te href=850078&gt;Tacet Field&lt;/te&gt; đang hình thành.
+Mây đen kéo đến, sấm chớp nổi lên... Đó là điềm báo của một &lt;te href=850078&gt;Tổ Tacet&lt;/te&gt; đang hình thành.
 Nếu một ngày ông và đồng đội có thể sống dưới ánh mặt trời, thì nhiệm vụ của ông là xua tan bóng tối, càng nhiều càng tốt, trước khi bước ngoặt đó đến.
 Calcharo rút kiếm và bước vào màn đêm. Đằng sau ông, ánh đèn thành phố vẫn lung linh với sự sống động và thịnh vượng.</t>
         </is>
@@ -30700,21 +30683,21 @@
         <is>
           <t>Đội &lt;te href=850087&gt;Patrollers&lt;/te&gt;, với bộ đồng phục thống nhất, rất được cư dân &lt;te href=850091&gt;Jinzhou&lt;/te&gt; biết đến. Nhiệm vụ của họ là duy trì pháp luật và trật tự, đồng thời bảo vệ sự an toàn cho người dân cùng tài sản của họ.
 Tuy nhiên, cũng có một số Patrollers không thể mặc đồng phục. Họ không được phép tiết lộ danh tính một cách dễ dàng.
-Những cá nhân này, được gọi là Agent Mật, hoạt động bí mật để thâm nhập vào các tổ chức tội phạm, thu thập bằng chứng về các hoạt động phi pháp, hoặc ngăn chặn những hành vi bất chính, tất cả đều trong khi giữ kín danh tính.
+Những cá nhân này, được gọi là Đặc Vụ Mật, hoạt động bí mật để thâm nhập vào các tổ chức tội phạm, thu thập bằng chứng về các hoạt động phi pháp, hoặc ngăn chặn những hành vi bất chính, tất cả đều trong khi giữ kín danh tính.
 Thay vì giải quyết những vụ trộm vặt, họ thường phải đối mặt với những tên tội phạm nguy hiểm và độc ác. Và nếu danh tính bị lộ, điều đó thường dẫn đến thất bại trong nhiệm vụ, thậm chí là mất mạng.
 ...
-"Thằng nào bình thường mà lại muốn làm Agent Mật chứ?" Tên đầu lĩnh nhóm lưu manh hét lên, đồng thời đâm mạnh con dao vào chiếc bàn vỡ nát. Mọi người xung quanh bật cười ầm ĩ trong kho hàng mờ tối.
-"Có thằng nào là gián điệp của Patrollers ở đây không? Lên tiếng đi, ta sẽ dành chỗ ngồi đẹp cho tụi ngươi trong bữa tiệc mừng."
+"Thằng nào bình thường mà lại muốn làm Đặc Vụ Mật chứ?" Tên đầu lĩnh nhóm lưu manh hét lên, đồng thời đâm mạnh con dao vào chiếc bàn vỡ nát. Mọi người xung quanh bật cười ầm ĩ trong kho hàng mờ tối.
+"Có thằng nào là gián điệp của Patrollers ở đây không? Lên tiếng đi, tao sẽ dành chỗ ngồi đẹp cho tụi mày trong bữa tiệc mừng."
 Cả nhóm lại cười rộ lên, dù không ai ngăn được việc liếc mắt nhìn nhau.
 "Theo tin tức của chúng ta, một đoàn hộ tống sẽ rời Jinchou tối nay với hàng hóa giá trị. Nhờ những tin đồn mà chúng ta tung ra, chủ hàng đã không hợp tác với &lt;te href=850090&gt;Lollo Logistics&lt;/te&gt;."
 "Làm tốt lắm, Ming," tên đầu lĩnh vỗ vai tên đồng bọn trông nhếch nhác, hắn ta cười khẩy đáp lại.
-"However hắn ta thuê cả một nhóm Resonators làm vệ sĩ..."
-"Đừng lo. Này, thằng mới, đến lượt ngươi rồi đấy."
+"Nhưng mà hắn ta thuê cả một nhóm Resonator làm vệ sĩ..."
+"Đừng lo. Này, thằng mới, đến lượt mày rồi đấy."
 Tên đầu lĩnh quay sang góc phòng, nơi một người phụ nữ với mái tóc đỏ rực và nụ cười tinh quái đang ngồi.
 "Ông chủ... tôi muốn hỏi, con nhỏ này có thực sự đánh được không? Tôi không muốn cả băng bị hạ gục chỉ vì một con bé trông như không thắng nổi tôi đâu."
 Miệng Ming cong lên thành nụ cười ranh mãnh khi hắn với tay về phía cánh tay của người phụ nữ. Nhưng ngay khi ngón tay sắp chạm vào làn da mịn màng của cô, hắn đột nhiên đông cứng.
-"C-Cái gì thế này? Con đàn bà khốn kiếp! Ngươi đã làm gì ta?"
-Tên đầu lĩnh nhóm lưu manh cau ngươi, vung tay bực bội khi thấy những sợi điện sáng rực quấn quanh người Ming.
+"C-Cái gì thế này? Con đàn bà khốn kiếp! Mày đã làm gì tao?"
+Tên đầu lĩnh nhóm lưu manh cau mày, vung tay bực bội khi thấy những sợi điện sáng rực quấn quanh người Ming.
 "Thôi tha cho hắn đi, vì tôi. Hắn chỉ còn cái miệng lưỡi sắc bén thôi. Để dành trò chơi của cô cho sau nhé."
 Người phụ nữ bình tĩnh vén tóc, và những sợi điện lập tức biến mất khỏi người Ming.
 "Được rồi, bắt đầu thôi nào. Lên đường đi các chàng trai, đến lúc làm ăn lớn rồi!"
@@ -30801,7 +30784,7 @@
 "Bà đừng lo, không ai biết con thật sự là ai. Với họ, con chỉ là một công dân bình thường. Thầy Người Gỗ sẽ tạo một danh tính giả cho con mà."
 "Có thể vậy, nhưng bà không muốn mất đi người thân thêm lần nào nữa... Con hãy ở lại Hội Séance đi. Đừng đi đâu cả."
 Người Gỗ gập sổ tay lại và ra hiệu cho Quý Bà Guan dừng lại. "Cứ làm đi, Yinlin. Nghiên cứu của ta đã đến giai đoạn then chốt và xung đột với Cục An Ninh Công Cộng &lt;te href=850091&gt;Jinzhou&lt;/te&gt; là điều không tránh khỏi. Có người trong hàng ngũ cấp cao của họ sẽ rất có lợi cho chúng ta."
-"Không, con muốn trở thành Agent Mật... giống như bố mẹ con. Con muốn tiếp nối lý tưởng của họ theo cách này."
+"Không, con muốn trở thành Đặc Vụ Mật... giống như bố mẹ con. Con muốn tiếp nối lý tưởng của họ theo cách này."
 Cô không thể nhìn thấy khuôn mặt sau chiếc mặt nạ của Người Gỗ, thứ mà ông chưa bao giờ tháo ra trước mặt cô từ khi cô còn nhỏ. Nhưng cô kịp nhận ra những cảm xúc phức tạp lóe lên trong đôi mắt ông - điều gì đó hiếm hoi và khó nắm bắt.
 Sau một hồi im lặng, ông cuối cùng gật đầu. "Trước khi ta đưa bố mẹ con trở lại bằng những con rối, con có quyền làm bất cứ điều gì con muốn... Một khi kế hoạch của ta thành công, chúng ta sẽ trả thù Cục An Ninh Công Cộng và tiêu diệt tất cả những kẻ phản bội họ trong một đòn duy nhất!"
 Yinlin định nói gì đó nhưng Người Gỗ đã quay lại chú tâm vào con rối đang chế tác. Cuối cùng, cô chỉ gật đầu im lặng rồi quay đi, biết rằng từ đây, họ sẽ đi trên những con đường riêng.</t>
@@ -30884,7 +30867,7 @@
 Chỉ qua vài động tác và cú đấm, Yuanwu đã có thể đánh giá tình trạng thể chất hiện tại của khách và đề xuất một kế hoạch tập luyện phù hợp.
 "Tư thế của cậu đang gù, bước đi thiếu vững... Cơ lưng dưới có vẻ căng quá. Thử tập bộ động tác này: ba cú đấm chậm rồi một cú nhanh. Sẽ giúp cậu thoải mái hơn đấy."
 Sau khi tập luyện theo hướng dẫn, khách hàng sẽ cảm thấy thư thái cả về thể chất lẫn tinh thần. Trước khi ra về, Yuanwu luôn tiễn khách với sự quan tâm chân thành, như một người bạn cũ.
-"Đỡ hơn chưa? That's good. Nhớ đừng để bản thân căng thẳng quá trong những ngày bình thường nhé. Cầm theo gói trà này, sẽ giúp cậu thư giãn đấy."
+"Đỡ hơn chưa? Tốt rồi. Nhớ đừng để bản thân căng thẳng quá trong những ngày bình thường nhé. Cầm theo gói trà này, sẽ giúp cậu thư giãn đấy."
 Trong số vô vàn phòng tập boxing lớn nhỏ ở Jinzhou, chỉ có phòng tập của Yuanwu luôn giữ được sự yêu mến bền lâu như vậy.</t>
         </is>
       </c>
@@ -30962,19 +30945,19 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Người ta kể rằng chủ nhân của Võ Đường Yuanwu sẵn sàng giúp đỡ khách hàng với bất kỳ rắc rối nào, kể cả những chuyện chẳng liên quan gì đến tập luyện.
-Một hôm, Mahe – một khách hàng thường tập trung và tận tụy trong buổi tập – bỗng trở nên sa sút. Yuanwu nhận ra điều đó và hỏi thăm anh có chuyện gì không. Vẻ mặt Mahe u ám khi dẫn Yuanwu đến tủ đồ của phòng tập, nơi anh lấy ra một chiếc đĩa ăn tinh xảo từ đồ đạc của mình.
-Chiếc đĩa có viền hoa nhỏ màu đỏ xếp thành vòng tròn. Yuanwu nhận ra đó là món đồ tráng men thủ công từ nước ngoài. Những bông hoa hoàn hảo, chỉ thiếu một mảnh nhỏ của viền vàng. Cả chiếc đĩa trông như chưa hoàn thiện mà không có nó.
+          <t>Người ta kể rằng chủ nhân của Võ Đường Nguyên Vũ sẵn sàng giúp đỡ khách hàng với bất kỳ rắc rối nào, kể cả những chuyện chẳng liên quan gì đến tập luyện.
+Một hôm, Mahe – một khách hàng thường tập trung và tận tụy trong buổi tập – bỗng trở nên sa sút. Nguyên Vũ nhận ra điều đó và hỏi thăm anh có chuyện gì không. Vẻ mặt Mahe u ám khi dẫn Nguyên Vũ đến tủ đồ của phòng tập, nơi anh lấy ra một chiếc đĩa ăn tinh xảo từ đồ đạc của mình.
+Chiếc đĩa có viền hoa nhỏ màu đỏ xếp thành vòng tròn. Nguyên Vũ nhận ra đó là món đồ tráng men thủ công từ nước ngoài. Những bông hoa hoàn hảo, chỉ thiếu một mảnh nhỏ của viền vàng. Cả chiếc đĩa trông như chưa hoàn thiện mà không có nó.
 Đó là món quà Mahe chuẩn bị tặng Panhua. Vài năm trước, khi nhà hàng Panhua khai trương, Mahe đã hứa sẽ tìm chiếc đĩa đẹp nhất thế giới để đựng những món ăn ngon nhất. Dù sau đó hai người chia tay vì bất đồng lý tưởng, Mahe vẫn không quên lời hứa.
 Anh kiên định với lý tưởng của mình, nhưng không thể buông bỏ tình cảm dành cho cô.
 Nhiều năm trời, anh tìm kiếm chiếc đĩa hoàn hảo – không quá lòe loẹt, cũng không quá đơn điệu. Cuối cùng, ánh mắt anh dừng lại ở chiếc đĩa giản dị mà thanh lịch này – trắng muốt với những bông hoa đỏ. Nó vừa vặn đến lạ.
 Chiếc đĩa rất đắt, và anh phải vất vả mới xoay đủ tiền để mua. Nỗi lo lắng dâng trào khi anh phân vân có nên tặng hay không. Liệu có phù hợp không? Hay cứ gửi đi thôi? Trong lúc do dự, một mảnh viền vàng trang trí trên đĩa bỗng dưng mất tích. Anh hỏi khắp các cửa hàng ở Jinzhou, nhưng họ hoặc không rành đồ sứ nhập khẩu, hoặc không dám mạo hiểm sửa món đồ quý giá ấy. Mahe rơi vào thế bí.
-Sau khi nghe Mahe tâm sự, Yuanwu nhẹ nhàng cầm chiếc đĩa lên, bảo anh quay lại sau một tuần.
+Sau khi nghe Mahe tâm sự, Nguyên Vũ nhẹ nhàng cầm chiếc đĩa lên, bảo anh quay lại sau một tuần.
 Khi Mahe trở lại, những bông hoa vẫn xếp tròn hoàn hảo, không hề có dấu vết sửa chữa.
-Đổi lại, Yuanwu chỉ yêu cầu Mahe đưa mình và chiếc đĩa đã sửa đến nhà hàng Panhua dùng bữa.
+Đổi lại, Nguyên Vũ chỉ yêu cầu Mahe đưa mình và chiếc đĩa đã sửa đến nhà hàng Panhua dùng bữa.
 Trên chiếc đĩa xinh đẹp với những bông hoa men rực rỡ, những món ăn cay nồng, thơm phức trông càng hấp dẫn. Hôm ấy, nụ cười của Panhua đặc biệt quyến rũ, còn Mahe – vốn ít nói – cũng nở nụ cười. Thật sự là một bữa tối đáng nhớ.
 Dù võ đường có đông khách đến đâu, nhiều người vẫn cho rằng nhận công việc như vậy với giá rẻ là một sự đánh đổi không đáng.
-Nhưng Yuanwu chỉ nhún vai cười, như thể tiền bạc chẳng là gì với ông.</t>
+Nhưng Nguyên Vũ chỉ nhún vai cười, như thể tiền bạc chẳng là gì với ông.</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31110,7 @@
       <c r="M446" t="inlineStr">
         <is>
           <t>Điểm nổi bật khiến Võ Đường Quyền Vũ khác biệt so với các nơi khác chính là sự thoải mái.
-Dưới sự hướng dẫn của Ông Chủ Quyền Vũ, các học viên tập luyện theo từng bài quyền, kết thúc buổi tập bằng việc lau mồ hôi và thưởng thức một ấm trà. Thật thư thái! Dù luyện tập &lt;te href=850114&gt;Leihuangquan&lt;/te&gt; mạnh mẽ, &lt;te href=850114&gt;Tiên Phong Quyền&lt;/te&gt; nhanh nhẹn, hay &lt;te href=850114&gt;Tam Phục Quyền&lt;/te&gt; linh hoạt, Ông Chủ Quyền Vũ đều kết hợp mỗi loại quyền với một loại trà đặc biệt, mang lại lợi ích tương hỗ. Sau khi tập luyện, các học viên nhâm nhi trà nóng, thư giãn cơ bắp, thúc đẩy tuần hoàn và xua tan mệt mỏi.
+Dưới sự hướng dẫn của Ông Chủ Quyền Vũ, các học viên tập luyện theo từng bài quyền, kết thúc buổi tập bằng việc lau mồ hôi và thưởng thức một ấm trà. Thật thư thái! Dù luyện tập &lt;te href=850114&gt;Lôi Hoàng Quyền&lt;/te&gt; mạnh mẽ, &lt;te href=850114&gt;Tiên Phong Quyền&lt;/te&gt; nhanh nhẹn, hay &lt;te href=850114&gt;Tam Phục Quyền&lt;/te&gt; linh hoạt, Ông Chủ Quyền Vũ đều kết hợp mỗi loại quyền với một loại trà đặc biệt, mang lại lợi ích tương hỗ. Sau khi tập luyện, các học viên nhâm nhi trà nóng, thư giãn cơ bắp, thúc đẩy tuần hoàn và xua tan mệt mỏi.
 Ông Chủ Quyền Vũ đã tự tay thử nghiệm các công thức trà này trước khi giao cho quán trà bên cạnh, giúp họ phát đạt với doanh thu bùng nổ. Đơn đặt trà thường phải đặt trước vài tháng, thỉnh thoảng có chậm trễ, nhưng đơn hàng của Ông Chủ Quyền Vũ luôn được giao đúng hẹn. Có người đồn đoán Ông Chủ Quyền Vũ không phải là một ông chủ võ đường bình thường, nhàn hạ như vẻ ngoài, mà là một tay trùm đứng sau nhiều doanh nghiệp. Liệu loại trà được săn đón này có phải chỉ là một phần trong đế chế kinh doanh của ông?
 Khi bị chất vấn, Ông Chủ Quyền Vũ chỉ mỉm cười, đưa cho một tách trà và nói: "Đừng chạy theo những ảo ảnh. Uống trà đi, thư giãn nào. Đổ mồ hôi nhiều hơn, suy đoán ít thôi." Sau một buổi tập và một tách trà, mũi ngửi đầy hương thơm tươi mát, những nghi ngờ và lo âu tan biến cùng những giọt mồ hôi. Câu hỏi về sự giàu có của Ông Chủ Quyền Vũ hay cách ông tích lũy tài sản trở nên vô nghĩa. Một cảm giác thư thái sâu lắng bao trùm toàn thân, xua tan những toan tính phù phiếm trong giây lát.
 Trên đời này, hầu hết mọi thứ đều cần nhịp điệu và sự cân bằng. Khi mệt mỏi, hãy nghỉ ngơi và thưởng thức trà. Đó là khoảnh khắc để tạm dừng, nạp lại năng lượng, rồi tiếp tục hành trình.</t>
@@ -31209,8 +31192,8 @@
           <t>Jinzhou, ở vùng biên ải, thường gợi lên hình ảnh những vùng đất hoang vu và dãy núi cằn cỗi.
 Có lần, một thương nhân được giao nhiệm vụ đến &lt;te href=850091&gt;Jinzhou&lt;/te&gt;. "Tôi không khỏe," ông ta từ chối ngay. "Đi đến đó chắc tôi chết dọc đường mất." Người đồng nghiệp mỉm cười đáp: "Đến rồi cậu sẽ biết thế nào."
 Miễn cưỡng, hai người lên đường đến Jinzhou. Họ vượt qua vô số vùng đất hoang tàn và rừng rậm nguy hiểm cho đến khi cuối cùng cũng đến được một nơi đẹp như tranh vẽ, với núi non xanh tươi và dòng nước trong veo.
-Đứng cuối con đường rừng là những cánh cổng thành cao vút. Soldiers gác niềm nở chào đón, kiểm tra giấy tờ nhanh gọn rồi cho họ vào.
-Bước vào Jinzhou, một bức tranh sinh động về cuộc sống hiện ra trước mắt. Trái với tưởng tượng, thành phố nhộn nhịp như một trung tâm sầm uất, không hề có chút hoang tàn hay ảm đạm nào. Giữa những công trình kiến trúc tinh tế và những hồ nước yên bình đầy cá đủ màu sắc, họ khám phá ra một khung cảnh quyến rũ không kém gì những vùng đất trù phú trong nội địa. Đắm chìm trong không khí sôi động, họ thưởng thức Tea Kungfu ở quán trà Liuxian, nếm thử món đặc sản ở nhà hàng Panhua, và hòa mình vào các buổi biểu diễn tại Nhà hát Jinzhou. Mỗi trải nghiệm đều xua tan mệt mỏi, thay vào đó là nguồn năng lượng sôi nổi của Jinzhou và sự hiếu khách ấm áp của người dân nơi đây.
+Đứng cuối con đường rừng là những cánh cổng thành cao vút. Những người lính gác niềm nở chào đón, kiểm tra giấy tờ nhanh gọn rồi cho họ vào.
+Bước vào Jinzhou, một bức tranh sinh động về cuộc sống hiện ra trước mắt. Trái với tưởng tượng, thành phố nhộn nhịp như một trung tâm sầm uất, không hề có chút hoang tàn hay ảm đạm nào. Giữa những công trình kiến trúc tinh tế và những hồ nước yên bình đầy cá đủ màu sắc, họ khám phá ra một khung cảnh quyến rũ không kém gì những vùng đất trù phú trong nội địa. Đắm chìm trong không khí sôi động, họ thưởng thức Trà Kungfu ở quán trà Liuxian, nếm thử món đặc sản ở nhà hàng Panhua, và hòa mình vào các buổi biểu diễn tại Nhà hát Jinzhou. Mỗi trải nghiệm đều xua tan mệt mỏi, thay vào đó là nguồn năng lượng sôi nổi của Jinzhou và sự hiếu khách ấm áp của người dân nơi đây.
 "Không thể tin nổi! Ai ngờ một thành phố biên ải lại thịnh vượng đến thế? Giống như một thiên đường vậy. Phải tốn biết bao công sức mới xây dựng được những công trình đẹp đẽ như thế này."
 "Quan &lt;te href=850084&gt;Magistrate&lt;/te&gt; của chúng tôi luôn dạy rằng lao động là quý. Dù hoàn cảnh nào, chỉ cần quyết tâm và nỗ lực, ai cũng có thể đạt được ước mơ. Vậy nên dù núi non cằn cỗi hay &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; hoành hành, chúng tôi vẫn xây dựng tổ ấm và tận hưởng những ngày tháng tốt đẹp trước khi khó khăn ập đến."
 "Thật tuyệt vời khi các cậu làm được điều đó. Không dễ dàng gì, nhưng mỗi người đều đã góp sức. Đáng nể thật đấy."
@@ -31299,9 +31282,9 @@
 Dù luôn mỉm cười và dịu dàng, Jinhsi vẫn ý thức rằng nếu không có kết quả thực tế, hành động của nàng có thể bị coi là thiếu chân thành hoặc thờ ơ với nỗi khổ của dân. Để thay đổi điều đó, nàng quyết tâm trở thành một Thị Trưởng chủ động, không ngừng nỗ lực giải quyết những lo âu của họ và dẫn dắt họ đến cuộc sống bình yên, hạnh phúc.
 Trong khi &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; chiến đấu anh dũng bảo vệ Jinzhou, một cuộc chiến khác, không kém phần cam go, đang diễn ra bên trong thành.
 Gia đình các chiến binh vật lộn với nỗi lo âu. Sự lo lắng cho sự an nguy của người thân đã đảo lộn cuộc sống thường nhật của họ.
-Thật không may, sự can thiệp vào &lt;te href=850078&gt;Tacet Field&lt;/te&gt; đã cản trở liên lạc thời gian thực với các chiến binh. Để ứng phó, Jinhsi đã triển khai dịch vụ chuyển phát nhanh kết hợp với &lt;te href=850085&gt;Ministry of Development&lt;/te&gt; và &lt;te href=850090&gt;Lollo Logistics&lt;/te&gt;. Những lá thư miễn phí được chuyển đến tay gia đình các chiến binh một cách nhanh chóng nhờ Lollo Logistics, trong khi Ministry of Development xây dựng các tuyến đường tắt để vận chuyển hiệu quả. Điều này đã phần nào xoa dịu nỗi lo của các gia đình muốn biết tin tức về người thân đang phục vụ trong quân đội.
-Một vấn đề cấp bách khác mà Jinhsi giải quyết là an ủi những gia đình mất người thân trong chiến trận. Nàng đã phối hợp với Ministry of War và Ministry of Development để xây dựng một kế hoạch toàn diện.
-Thành phố tôn vinh những chiến binh đã ngã xuống bằng cách tăng tiền bồi thường cho gia đình họ và xây dựng bức tường tưởng niệm tại Knell Square. Những tấm bia khắc tên họ được làm từ loại quặng tốt nhất, có thể chống chọi với thời gian và mang lại sự an ủi trong nhiều thế kỷ. Midnight Rangers có thể không chiến đấu vì danh dự, nhưng sự hy sinh của họ xứng đáng được ghi nhớ. Với sự hoàn thành của Knell Square, người dân có thêm một nơi để tưởng niệm và tìm kiếm sự an ủi trong nỗi mất mát.
+Thật không may, sự can thiệp vào &lt;te href=850078&gt;Tổ Tacet&lt;/te&gt; đã cản trở liên lạc thời gian thực với các chiến binh. Để ứng phó, Jinhsi đã triển khai dịch vụ chuyển phát nhanh kết hợp với &lt;te href=850085&gt;Bộ Phát Triển&lt;/te&gt; và &lt;te href=850090&gt;Lollo Logistics&lt;/te&gt;. Những lá thư miễn phí được chuyển đến tay gia đình các chiến binh một cách nhanh chóng nhờ Lollo Logistics, trong khi Bộ Phát Triển xây dựng các tuyến đường tắt để vận chuyển hiệu quả. Điều này đã phần nào xoa dịu nỗi lo của các gia đình muốn biết tin tức về người thân đang phục vụ trong quân đội.
+Một vấn đề cấp bách khác mà Jinhsi giải quyết là an ủi những gia đình mất người thân trong chiến trận. Nàng đã phối hợp với Bộ Chiến Tranh và Bộ Phát Triển để xây dựng một kế hoạch toàn diện.
+Thành phố tôn vinh những chiến binh đã ngã xuống bằng cách tăng tiền bồi thường cho gia đình họ và xây dựng bức tường tưởng niệm tại Quảng trường Knell. Những tấm bia khắc tên họ được làm từ loại quặng tốt nhất, có thể chống chọi với thời gian và mang lại sự an ủi trong nhiều thế kỷ. Midnight Rangers có thể không chiến đấu vì danh dự, nhưng sự hy sinh của họ xứng đáng được ghi nhớ. Với sự hoàn thành của Quảng trường Knell, người dân có thêm một nơi để tưởng niệm và tìm kiếm sự an ủi trong nỗi mất mát.
 Trong tất cả những nỗ lực an ủi và giải quyết hậu quả này, Jinhsi luôn dẫn đầu bằng tấm gương của mình. Mỗi khi nhìn thấy nụ cười dịu dàng của nàng, người dân đều biết rằng nàng sẽ đưa ra những chính sách mang lại niềm vui, giống như chính nụ cười ấy. Sự ấm áp đó như một liều thuốc chữa lành vết thương chiến tranh, giúp người dân Jinzhou vượt qua những thời khắc khó khăn.</t>
         </is>
       </c>
@@ -31389,16 +31372,16 @@
           <t>Jinhsi có một tính khí cực kỳ tốt; dù trong hoàn cảnh nào, cô luôn giữ nụ cười duyên dáng và dịu dàng, hầu như chưa ai từng thấy cô nổi giận.
 "Liệu &lt;te href=850084&gt;Thị Trưởng&lt;/te&gt; của chúng ta có biết nổi giận là gì không nhỉ? Cô ấy lúc nào cũng điềm tĩnh, dù chuyện gì xảy ra đi nữa."
 "Nói thật, mình cũng thắc mắc điều đó. Không biết cô ấy trông thế nào khi nổi giận nhỉ?"
-"Ta đã thấy rồi," Shi, một thợ mỏ thường xuyên sống khép kín và chỉ tập trung vào công việc, đáp.
+"Tao đã thấy rồi," Shi, một thợ mỏ thường xuyên sống khép kín và chỉ tập trung vào công việc, đáp.
 Đó là một mùa đông cực kỳ khắc nghiệt. Nhà thầu viện cớ sử dụng thiết bị quá mức, đòi một khoản tiền lớn từ dự án khai thác mỏ, khiến các thợ mỏ chẳng còn gì sau bao tháng ngày lao động.
-Vừa trải qua những trận chiến đẫm máu, thế giới chìm trong hỗn loạn. Nhu cầu xây dựng dân sự tăng vọt, kéo theo nhu cầu về quặng tăng cao. Thế nhưng, thiết bị thăm dò của &lt;te href=850085&gt;Ministry of Development&lt;/te&gt; lại không đủ, buộc họ phải thuê dụng cụ từ tư nhân. Nhưng nhà thầu lại là một kẻ trục lợi, đến lúc thanh toán thì lật mặt không trả. Tệ hơn, hắn còn là chủ tịch Phòng Thương Mại, nắm độc quyền thiết bị thăm dò trên thị trường và chẳng coi ai ra gì, kể cả quan chức.
+Vừa trải qua những trận chiến đẫm máu, thế giới chìm trong hỗn loạn. Nhu cầu xây dựng dân sự tăng vọt, kéo theo nhu cầu về quặng tăng cao. Thế nhưng, thiết bị thăm dò của &lt;te href=850085&gt;Bộ Phát Triển&lt;/te&gt; lại không đủ, buộc họ phải thuê dụng cụ từ tư nhân. Nhưng nhà thầu lại là một kẻ trục lợi, đến lúc thanh toán thì lật mặt không trả. Tệ hơn, hắn còn là chủ tịch Phòng Thương Mại, nắm độc quyền thiết bị thăm dò trên thị trường và chẳng coi ai ra gì, kể cả quan chức.
 Sau một năm vất vả, Shi đã trông chờ khoản tiền đó để đón một cái Tết vui vẻ bên gia đình. Nhưng giờ đây, ước mơ đơn giản ấy dường như đã tan biến. Nhìn đôi bàn tay chai sạn, thô ráp của mình, Shi nhớ lại lời đồng nghiệp Debiao: "…Làm lương thiện chẳng bao giờ no bụng đâu. Chúng ta phải hành động, đòi lại những gì xứng đáng – tiền của chính mình."
 Dưới màn đêm, Shi cùng các công nhân đồng nghiệp lẻn vào dinh thự của gã thương gia. Áp tai vào cửa, Shi lắng nghe động tĩnh bên trong, sẵn sàng xông vào khi có cơ hội.
-"Ông Zhu, tôi đến thông báo một tin," giọng một cô gái trẻ vang lên từ bên trong, nhẹ nhàng nhưng mang theo một sự lạnh lẽo khó tả. "Ông đã bị khai trừ khỏi Phòng Thương Mại, và giấy phép kinh doanh của ông đã bị thu hồi. Từ nay, ông bị cấm tham gia mọi hoạt động thương mại tại &lt;te href=850091&gt;Jinzhou&lt;/te&gt;."
+"Ông Chu, tôi đến thông báo một tin," giọng một cô gái trẻ vang lên từ bên trong, nhẹ nhàng nhưng mang theo một sự lạnh lẽo khó tả. "Ông đã bị khai trừ khỏi Phòng Thương Mại, và giấy phép kinh doanh của ông đã bị thu hồi. Từ nay, ông bị cấm tham gia mọi hoạt động thương mại tại &lt;te href=850091&gt;Jinzhou&lt;/te&gt;."
 "Hả? Buồn cười thật. Chúng ta đang ở Jinzhou, một thành phố nổi tiếng tuân thủ pháp luật. Vì cô mới nhậm chức, Thị Trưởng à, tôi sẽ bỏ qua sự thiếu hiểu biết của cô. Để tôi nói cho mà nghe: trục xuất một chủ tịch Phòng Thương Mại ở đây phải mất ít nhất hai tuần, còn thu hồi giấy phép kinh doanh thì phải có bằng chứng! Không có bằng chứng, không thể thu hồi. Đơn giản vậy thôi."
-"Vì ông đã nhắc đến pháp luật, vậy chúng ta hãy bàn về nó. Theo Điều 180 của Luật Thương Mại Jinzhou, trục xuất một chủ tịch Phòng Thương Mại cần có chữ ký của hơn nửa số thành viên, cùng với chữ ký của Bộ Trưởng Thương Mại và Giám đốc Ministry of Development. Việc xin phê duyệt từ Thị Trưởng có thể mất thời gian. Do đó, tôi đích thân đến đây để thông báo, nhằm đẩy nhanh việc trả lương cho công nhân."
+"Vì ông đã nhắc đến pháp luật, vậy chúng ta hãy bàn về nó. Theo Điều 180 của Luật Thương Mại Jinzhou, trục xuất một chủ tịch Phòng Thương Mại cần có chữ ký của hơn nửa số thành viên, cùng với chữ ký của Bộ Trưởng Thương Mại và Giám đốc Bộ Phát Triển. Việc xin phê duyệt từ Thị Trưởng có thể mất thời gian. Do đó, tôi đích thân đến đây để thông báo, nhằm đẩy nhanh việc trả lương cho công nhân."
 "Về bằng chứng ông yêu cầu… &lt;te href=850089&gt;Đồn Tuần Tra&lt;/te&gt; đã thu thập và nộp lên Hội Đồng Pháp Lệnh. Tôi luôn chuẩn bị sẵn sàng."
-"Khi tôi rời đi, hãy nhớ rằng sự độc quyền thiết bị thăm dò của ông đã chấm dứt. Ministry of Development đã đẩy nhanh sản xuất và thiết bị mới đã về đến nơi hôm nay. Sự độc quyền của ông sẽ không kéo dài được đâu."
+"Khi tôi rời đi, hãy nhớ rằng sự độc quyền thiết bị thăm dò của ông đã chấm dứt. Bộ Phát Triển đã đẩy nhanh sản xuất và thiết bị mới đã về đến nơi hôm nay. Sự độc quyền của ông sẽ không kéo dài được đâu."
 Mải mê với tiếng ồn ào bên trong, Shi bỏ lỡ phần còn lại của cuộc trò chuyện. Dường như có ai đó đang cố biện hộ, nhưng Shi biết rằng trước những bằng chứng áp đảo và sự chuẩn bị kỹ lưỡng, mọi nỗ lực đều vô ích.
 Chẳng bao lâu sau, họ nhận được thông báo về khoản thanh toán xứng đáng trên Thiết bị đầu cuối của mình. Cuối cùng, họ cũng có thể đón Tết trong hạnh phúc.
 Sau đó, những sự việc tương tự không còn xảy ra nữa khi Thị Trưởng Jinhsi ban hành luật mới cấm độc quyền và sửa đổi quy trình thanh toán: tiền lương của công nhân sẽ được trả trước khi nhà thầu nhận được khoản thanh toán của mình.
@@ -31492,7 +31475,7 @@
 Từng là nơi yên bình, Núi Phụng Hoàng giờ đây đầy bất ổn, sự tĩnh lặng bị phá vỡ bởi nguy cơ của &lt;te href=850083&gt;Sentinel&lt;/te&gt; và tay chân của Fractsidus. Với khát khao mang lại hòa bình cho Jinzhou, vị thị trưởng trẻ một mình bước vào cuộc chiến, đối mặt với muôn vàn khó khăn trong khi tìm kiếm thông tin về Sentinel.
 Vượt qua nghịch cảnh mà không hề hấn gì là điều không dễ dàng, ngay cả với một người có ý chí mạnh mẽ như Jinhsi. Nhưng mỗi khi cảm thấy nản lòng hay lạc lối trong nghi ngờ, cô lại nhớ đến một người nào đó. Khi tỉnh dậy, người ấy nhanh chóng nắm bắt tình hình phức tạp, kiên nhẫn chờ đợi quyết định của cô. Jinhsi tin chắc rằng họ sẽ cùng nhau dẫn dắt Jinzhou đến một tương lai tươi sáng hơn.
 Trên sân thượng Tòa Thị Chính, Jinhsi, vị thị trưởng trở về, nhìn vị khách quý với vẻ nhẹ nhõm và vui mừng. Gật đầu chào, cô thốt lên những lời đã tập luyện hàng nghìn lần:
-"It's been three days."
+"Đã ba ngày rồi."
 "Cả hai ta đều đến đúng hẹn."
 "Hãy để tôi chính thức giới thiệu bản thân. Tôi là Jinhsi... Thật vui khi được gặp cậu, Rover."</t>
         </is>
@@ -31790,15 +31773,15 @@
 "Tạp chí mới à?"
 "Ừ, họ gửi tặng tớ bản mẫu."
 "Ghen tỵ quá! Tớ ước gì mình có thể làm việc nhanh như cậu, vừa viết bài lia lịa vừa đi học. Trời ạ." Hắn vung tay lên rồi cười toe toét, "Chắc cậu đã nắm chắc suất vào Học viện Hoàng gia rồi. Vậy, cậu sẽ chọn đâu?"
-Nói rồi, hắn Dodgem qua một lon nước ngọt.
+Nói rồi, hắn ném qua một lon nước ngọt.
 Chiếc lon vẽ một vòng cung hoàn hảo trong không khí, rơi gọn vào tay Xiangli Yao.
 "Ngọt quá," cậu học sinh gương mẫu thở dài, nổi tiếng với lối sống lành mạnh, nhưng vẫn mỉm cười mở lon, "Nói về chuyện đó..."
 Một khoảng lặng ngắn ngủi. Rồi Xiangli lắc đầu nhẹ, "Tớ vẫn chưa quyết định."
-Bạn cậu nhướn ngươi, ngạc nhiên, "Lạ nhỉ. Tớ tưởng cậu đã quyết rồi chứ. Chắc các giáo sư đang giành giật cậu đấy."
+Bạn cậu nhướn mày, ngạc nhiên, "Lạ nhỉ. Tớ tưởng cậu đã quyết rồi chứ. Chắc các giáo sư đang giành giật cậu đấy."
 "Vẫn còn vài điều tớ chưa hiểu rõ."
 "Là gì...?"
 "Giới hạn. Giới hạn của sự thật," Xiangli Yao nói chậm rãi, xoay một khối lập phương trong tay, "Pascar, cậu có nghĩ rằng loài người sẽ tự kiềm chế bản thân trong việc theo đuổi giới hạn của sự thật không?"
-"Maybe. Thế giới này đầy rẫy những nhà khoa học điên rồ mà, ai biết được."
+"Có thể. Thế giới này đầy rẫy những nhà khoa học điên rồ mà, ai biết được."
 "Chúng ta đuổi theo những vì sao, chỉ để rồi ngã xuống dưới chúng. Giới hạn định hình tầm nhìn của ta... nhưng nếu không có nó, làm sao ta biết mình đang tiến bộ?"
 "Thôi... quan điểm của cậu và tớ khác nhau, và tớ sẽ giữ im lặng để tránh cãi nhau. Nhưng mà tất cả những điều này có liên quan gì đến việc nhập học của cậu? Cậu đang cố đánh trống lảng à?"
 Xiangli Yao mỉm cười nhẹ, "Có đấy. Sau khi cha tớ theo đuổi con đường riêng của ông, tớ hầu như không nghe tin tức gì về ông nữa. Nhưng tớ đã tìm ra vài manh mối... Có lẽ chúng sẽ dẫn tớ đến Tòa án Savantae, nơi ông đã tìm kiếm."
@@ -31889,8 +31872,8 @@
 Xiangli Yao kiểm tra những gì còn lại, cân nhắc lựa chọn, và cuối cùng quyết định tiến sâu hơn vào tàn tích.
 Lâu rồi anh ta đã rời xa biên giới &lt;te href=850093&gt;Huanglong&lt;/te&gt;, và quay lại lần nữa để khám phá thêm sẽ cực kỳ khó khăn. Sau khi khảo sát mặt đất khi đến nơi, vị học giả trẻ suy đoán rằng những tàn tích này, giống như những nơi trước đó, cũng không còn nhiều thời gian tồn tại.
 Tuy nhiên, bên trong điều kiện lại tốt hơn nhiều. Phần lớn các thiết bị đều được bảo quản nguyên vẹn. Dòng chất lỏng xanh lam cuồn cuộn lưu thông trong các đường ống của mọi cơ cấu với sức sống vượt xa cả những người sáng tạo ra chúng. Mỗi cơ cấu, chính xác, bền bỉ và tinh xảo, đều được Xiangli Yao ghi chép cẩn thận khi nhận ra những khác biệt tinh tế so với công nghệ hiện có của Huanglong.
-Càng khám phá, anh càng bị cuốn vào một niềm hứng khởi không thể kìm Dodgen. Như một thi sĩ say men rượu ngon, Xiangli Yao như say sưa trong dòng tri thức bao quanh mình.
-Terminal của anh đã mất kết nối với thế giới bên ngoài, nhưng anh vẫn cố gắng ghi lại mọi thứ. Niềm đam mê với cơ khí, lĩnh vực mà Savantae đã đạt đến đỉnh cao, khiến anh tự hỏi liệu cha mình có biết đến những sáng tạo này không, và giờ ông đang ở đâu trên con đường theo đuổi những vì sao.
+Càng khám phá, anh càng bị cuốn vào một niềm hứng khởi không thể kìm nén. Như một thi sĩ say men rượu ngon, Xiangli Yao như say sưa trong dòng tri thức bao quanh mình.
+Thiết bị đầu cuối của anh đã mất kết nối với thế giới bên ngoài, nhưng anh vẫn cố gắng ghi lại mọi thứ. Niềm đam mê với cơ khí, lĩnh vực mà Savantae đã đạt đến đỉnh cao, khiến anh tự hỏi liệu cha mình có biết đến những sáng tạo này không, và giờ ông đang ở đâu trên con đường theo đuổi những vì sao.
 Tuy nhiên, giữa những điều kỳ diệu, dấu hiệu của một sự xâm nhập kỳ lạ dần hiện rõ. Kể từ sau &lt;te href=850075&gt;Lament&lt;/te&gt;, hầu hết công nghệ lẽ ra đã trở về trạng thái sơ khai. Nhưng ở đây, những cấu trúc từng quen thuộc lại mang dấu vết biến đổi xa lạ, chống lại sự xói mòn mà vẫn toát lên vẻ tinh tế vượt trội so với các sáng tạo khác của Savantae.
 Càng đi sâu vào tàn tích, những bất thường càng gia tăng. Ghi chép của Xiangli Yao chậm lại. Việc phân biệt giữa những bất thường và thiết kế gốc đòi hỏi sự tỉ mỉ. Cuối cùng, anh đưa ra một phỏng đoán: Những người ở đây đang cố tạo ra một loại cánh cửa.
 Một cánh cửa. Một lối đi. Một... cánh cổng.
@@ -32169,12 +32152,12 @@
 ...Cho đến ngày định mệnh ấy.
 Năm mười một tuổi, cuộc sống yên bình của cô bị xé nát bởi một cuộc tấn công tàn nhẫn của bọn Lưu Vong khi đang đi cùng đoàn xe gia đình. Thực tại tàn khốc của cái chết và sự độc ác khiến cô choáng váng, phải chạy trốn và nương náu giữa những người xa lạ ở một khu định cư lạ lẫm. Những con người kiên cường này sống dựa vào đất đai, cảnh giác nhưng đầy sáng tạo. Cô buộc phải tự lập, thích nghi với thế giới khắc nghiệt này từ khi còn rất nhỏ. Cô không biết liệu họ có giống những kẻ tấn công tàn nhẫn kia hay không. Sự cảnh giác thường trực của những người định cư khiến cô tự hỏi liệu có an toàn khi tin tưởng ai đó không. Mặc quần áo đẹp, lại một mình, cô nổi bật giữa họ, và họ cũng nghi ngờ cô. Liệu đây có phải là cái bẫy?
 Cuối cùng, họ vẫn đưa thức ăn cho cô, và cô nhận lấy, dù chưa từng thấy thứ gì như vậy.
-Kindness vẫn đâm chồi ngay cả trên mảnh đất cằn cỗi nhất. Dương Dương muốn đền đáp sự tin tưởng mà họ dành cho mình, nhưng kiến thức của cô chẳng giúp ích gì trong hoang dã, và kỹ năng kiếm thuật của cô quá non nớt trước hiểm nguy thực sự. Mọi thứ đều xa lạ với cô, thế nhưng đây lại là thực tại mà hầu hết mọi người phải đối mặt. Thực tại ấy thật đau đớn đến nghẹt thở.
+Lòng tốt vẫn đâm chồi ngay cả trên mảnh đất cằn cỗi nhất. Dương Dương muốn đền đáp sự tin tưởng mà họ dành cho mình, nhưng kiến thức của cô chẳng giúp ích gì trong hoang dã, và kỹ năng kiếm thuật của cô quá non nớt trước hiểm nguy thực sự. Mọi thứ đều xa lạ với cô, thế nhưng đây lại là thực tại mà hầu hết mọi người phải đối mặt. Thực tại ấy thật đau đớn đến nghẹt thở.
 "Bà ơi, bà... sống như thế này lâu chưa?" Khi Dương Dương cố giúp một bà lão phân loại những nguồn tài nguyên ít ỏi họ có, cô không thể không hỏi câu đột ngột ấy.
 "Ừ, sao? Cô nương thành thị. Sốc à? Thư giãn đi. Mọi chuyện rồi sẽ ổn thôi."
 "Nhưng khi nào? Liệu có ngày nào mọi thứ thực sự tốt đẹp hơn không?"
-"Tất nhiên. Làm sao điều tốt đẹp đến nếu chính mình còn không tin? Chúng ta cũng nghi ngờ ngươi, nhưng vẫn chọn tin. Với ngươi cũng vậy. Phải có niềm tin vào cái gì đó trong đời. Dù không biết kết quả sẽ ra sao. Đó mới là niềm tin."
-"Khi nào ư? Hừm, có khi phải đợi đến lúc ngươi lớn lên, nhóc à."
+"Tất nhiên. Làm sao điều tốt đẹp đến nếu chính mình còn không tin? Chúng tao cũng nghi ngờ mày, nhưng vẫn chọn tin. Với mày cũng vậy. Phải có niềm tin vào cái gì đó trong đời. Dù không biết kết quả sẽ ra sao. Đó mới là niềm tin."
+"Khi nào ư? Hừm, có khi phải đợi đến lúc mày lớn lên, nhóc à."
 Vậy nên, có lẽ Dương Dương chưa trải qua đủ khổ đau. Hoặc có lẽ, xu hướng trao đi lòng tốt không dựa trên kinh nghiệm, mà đã nằm sẵn trong tính cách của mỗi người.
 Trong những tình huống tối tăm nhất, vẫn có người trao đi lòng tốt chỉ vì người khác chọn tin tưởng họ. Và chính điều đó sẽ khơi dậy thêm nhiều hành động tốt đẹp khác.
 Kể từ đó, Dương Dương luôn dành lòng tốt cho những người xa lạ, bắt nguồn từ lần gặp gỡ ấy.
@@ -32355,7 +32338,7 @@
 Cô tìm đến mẹ để xin lời khuyên: &lt;i&gt;Mẹ ơi, mẹ muốn con kế thừa gia nghiệp của gia đình không? Hay mẹ muốn con làm gì? Con có thể thử bất cứ điều gì và sẽ nỗ lực hết mình. Dù cuộc đời có vô vàn khả năng, cuối cùng chúng ta cũng chỉ có thể chọn một con đường, phải không?&lt;/i&gt;
 Mẹ nhìn cô với ánh mắt yêu thương và nói: &lt;i&gt;Con yêu à, chính vì thế mà con không nên tìm câu trả lời từ mẹ, mà hãy tự hỏi trái tim mình. Đây là một câu hỏi khó, nhưng con không cần vội vàng tìm đáp án.&lt;/i&gt;
 Vậy là Dương Dương ôm câu hỏi ấy, kiên nhẫn chờ đợi một câu trả lời dường như luôn lảng tránh cô. Cô chờ đợi khi trở về từ khu định cư hoang tàn, khi thoát khỏi vực sâu, khi chán ngán sự bao bọc quá mức của gia đình. Khát khao được bước ra thế giới, trải nghiệm sự khắc nghiệt của nó ngày càng mãnh liệt, không còn muốn làm chiếc lá trôi dạt vô định. Cô muốn gánh vác thực tại, thay vì trốn tránh nó.
-Đúng lúc đó, một cuộc phục kích bất ngờ ở vùng hoang dã khiến thương vong nặng nề do &lt;te href=850081&gt;Discord&lt;/te&gt; tấn công tiền tuyến. Tin tức về thảm kịch này nhanh chóng lan truyền khắp thành phố, khơi dậy nỗi đau thương, phẫn nộ và tuyệt vọng trong lòng người dân. Cảm xúc dâng trào, mọi người tụ tập quanh đống lửa. Nước mắt tuôn rơi, tiếng khóc nghẹn ngào vang vọng trong đêm. Nhưng đến sáng, nỗi đau trở thành thứ xa xỉ khi cuộc sống trở lại bình thường.
+Đúng lúc đó, một cuộc phục kích bất ngờ ở vùng hoang dã khiến thương vong nặng nề do &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; tấn công tiền tuyến. Tin tức về thảm kịch này nhanh chóng lan truyền khắp thành phố, khơi dậy nỗi đau thương, phẫn nộ và tuyệt vọng trong lòng người dân. Cảm xúc dâng trào, mọi người tụ tập quanh đống lửa. Nước mắt tuôn rơi, tiếng khóc nghẹn ngào vang vọng trong đêm. Nhưng đến sáng, nỗi đau trở thành thứ xa xỉ khi cuộc sống trở lại bình thường.
 Dương Dương đứng giữa họ, nước mắt lăn dài trên má. Cô không mất mát gì cá nhân, nhưng chứng kiến nỗi đau của họ và niềm vui của những đứa trẻ được cứu đã lay động tâm can cô. Đó là khoảnh khắc thay đổi, khi cô nhận ra sứ mệnh thực sự của mình: bảo vệ người khác, như cách cô đã từng được bảo vệ. Cô muốn che chở họ khỏi bất hạnh, mang đến hy vọng cho một tương lai tươi sáng hơn.
 Đêm nhập học với tư cách &lt;te href=850139&gt;Outrider&lt;/te&gt;, Dương Dương đứng bên rìa Jinzhou, nhìn lên bầu trời và những cư dân tấp nập dưới kia. Nghi ngờ len lỏi trong tâm trí cô khi tự hỏi liệu mình có đủ sức bảo vệ những con người đầy sức sống này – trách nhiệm mà cô luôn mơ ước.
 Những dòng Suối từ xa ôm lấy Dương Dương trong vòng tay dịu dàng, xua tan những nghi ngờ cuối cùng trong cô.
@@ -32447,14 +32430,14 @@
 "Xin lỗi ông, cháu không nhận tiền hưu của người già đâu."
 Mọi người đều nghĩ rằng họ chưa đưa ra mức giá đủ hấp dẫn để Aalto móc hầu bao, nhưng thực ra, hắn chỉ đang đợi đúng người mua mà thôi.
 Rồi một ngày nọ, người mua đó xuất hiện, khoác trên mình lớp áo choàng dày đặc. Hắn ta đồng ý giao dịch với Aalto với mức giá thấp đến bất ngờ. Ai nấy đều ngỡ ngàng trước sự dễ dãi của Aalto.
-Vài ngày sau, một màn hình điện tử tại văn phòng sở cảnh sát New Federation phát sóng tin tức mới nhất: băng trộm truy nã lâu nay cuối cùng đã bị bắt.
+Vài ngày sau, một màn hình điện tử tại văn phòng sở cảnh sát Liên Bang Mới phát sóng tin tức mới nhất: băng trộm truy nã lâu nay cuối cùng đã bị bắt.
 Một làn sương mù len lỏi vào văn phòng cảnh sát trưởng, che mờ màn hình.
 "Đủ rồi đấy. Đến lúc giải quyết giao dịch của chúng ta."
 Cảnh sát trưởng đập một tập tài liệu cùng một vali đầy Credits lên bàn.
 "Ông giỏi thật đấy. Nói xem, Aalto, làm sao ông chắc chắn họ sẽ cắn câu? Rêu rao thông tin về kho báu huyền thoại giữa thanh thiên bạch nhật, không sợ bị nghi ngờ à?"
 "Đừng đánh giá thấp những con bạc ham tiền. Họ sẵn sàng đánh đổi tất cả, kể cả mạng sống. Lợi nhuận đáng để họ mạo hiểm mà."
 Cảnh sát trưởng đẩy tập tài liệu và vali về phía Aalto.
-"Đây là thù lao của ông, cùng danh sách tên ông yêu cầu. Pleasure doing business."
+"Đây là thù lao của ông, cùng danh sách tên ông yêu cầu. Hân hạnh được hợp tác."
 "Tôi cũng vậy."
 Aalto mở vali, lấy ra một đồng Shell Credit duy nhất và tung lên không trung. Trước khi đồng tiền chạm đất, hắn đã hóa thành sương mù, biến mất khỏi tầm mắt.</t>
         </is>
@@ -32546,7 +32529,7 @@
 Aalto nhanh chóng đến giúp đỡ nạn nhân, đưa họ đến nơi an toàn bằng một cử chỉ nhẹ nhàng. Với thái độ điềm tĩnh, ông dựng lại chiếc ghế bị đổ và thản nhiên vòng tay qua vai tên lưu manh đang nổi giận.
 *"Nghe này, anh bạn, mọi thứ đều có luật lệ cả. Luật của tôi đây, xem này: 'Ai đến trước được phục vụ trước. Không xô đẩy.' Tôi phải làm sao khi anh phá vỡ hai luật cùng lúc?"*
 Tên lưu manh giật tay ra, *"Nếu sếp chúng tôi muốn gặp ai, thì người đó phải đến. Đó là luật của chúng tôi."*
-Mist phủ kín đám đông khi lời của Aalto vừa dứt. Ông nhanh chóng gây hỗn loạn, khiến đám lưu manh hoảng sợ quay sang tấn công lẫn nhau.
+Sương mù phủ kín đám đông khi lời của Aalto vừa dứt. Ông nhanh chóng gây hỗn loạn, khiến đám lưu manh hoảng sợ quay sang tấn công lẫn nhau.
 *"Ôi, xin lỗi nhé. Tôi quên mất một luật nữa: 'Không được ép buộc giao dịch.' Lần sau nhớ bảo sếp đừng phá luật nữa. Không có luật thì làm ăn kiểu gì được."*
 Cúi đầu xấu hổ, đám lưu manh bỏ chạy, để lại Aalto với nụ cười chào đón như thường lệ.
 *"Được rồi! Quay lại chuyện của chúng ta nào. Ông muốn hỏi gì nữa nhỉ?"*</t>
@@ -32636,7 +32619,7 @@
 Một số người có thể nổi giận vì yêu cầu nghe có vẻ vô lý đó, nhưng Aalto chỉ cần mỉm cười lịch sự và chỉ tay ra cửa.
 "Thưa quý khách, đã bao giờ nghe câu 'lịch sự làm nên giàu có' chưa? Ngài nên chú ý lời ăn tiếng nói chút. Với lại, đây chỉ là chuyện làm ăn, không phải từ thiện. Nếu ngài không rảnh lo khoản thanh toán, thì tiếc là chúng ta đành hẹn lần khác vậy."
 Có lần, một cậu bé rách rưới đi đi lại lại trước cửa Aalto suốt mấy ngày liền.
-"Này cậu bé, mặt ngươi ủ rũ thế? Để ta đoán xem. Mất chó à?"
+"Này cậu bé, mặt mày ủ rũ thế? Để ta đoán xem. Mất chó à?"
 "Ồ! Bác biết hết mọi thứ thật đấy! Vậy bác có biết Pebbles đi đâu không?"
 "Cậu biết đấy, trên đời này không có bữa trưa nào miễn phí cả. Muốn ta giúp thì phải trả tiền."
 Cậu bé lắc đầu thất vọng, "Nhưng cháu chẳng có gì cả."
@@ -32717,15 +32700,15 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>"Chào mừng đến với &lt;te href=850109&gt;The Black Shores&lt;/te&gt;! Cậu muốn bắt đầu bằng việc tưới hoa, hay cứu nhân loại nào?
-The Black Shores nằm trên một hòn đảo hẻo lánh. Ngoài những cơn gió mùa, dòng chảy và đàn bướm thường xuyên ghé thăm, hòn đảo này chỉ đón nhận sự lên xuống của thủy triều. Khu vực bí ẩn này không hề xuất hiện trên bất kỳ bản đồ thế giới nào.
+          <t>"Chào mừng đến với &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt;! Cậu muốn bắt đầu bằng việc tưới hoa, hay cứu nhân loại nào?
+Bờ Biển Đen nằm trên một hòn đảo hẻo lánh. Ngoài những cơn gió mùa, dòng chảy và đàn bướm thường xuyên ghé thăm, hòn đảo này chỉ đón nhận sự lên xuống của thủy triều. Khu vực bí ẩn này không hề xuất hiện trên bất kỳ bản đồ thế giới nào.
 Tổ chức bí mật này cống hiến cho mục tiêu cao cả: cứu rỗi thế giới – thứ mà người ta chỉ dám mơ tới trong truyện cổ tích.
 Chẳng trách nhiều người khó lòng tin Aalto, một kẻ có vẻ ngoài bất cần và khó nắm bắt, lại gắn liền với tổ chức bí ẩn này.
 Muốn hiểu Aalto thật sự, cậu phải nhìn xuyên qua lớp vỏ bí ẩn để thấy trái tim nhân hậu và kiên định bên trong.
-Anh biết rõ sương mù của mình không bao giờ che giấu được những vết thương vĩnh viễn mà &lt;te href=850075&gt;Lament&lt;/te&gt; gây ra cho hành tinh này.
-Đó là lý do anh sẵn sàng đồng ý hợp tác lâu dài với The Black Shores ngay từ lần đầu đặt chân lên đảo qua lời mời.
-Cho đến nay, anh đã cung cấp cho The Black Shores vô số thông tin tình báo và giúp họ tuyển mộ những ứng viên đáng tin cậy để củng cố Tổ Tư Duy.
-Anh sẽ hỗ trợ The Black Shores thực hiện các kế hoạch... Cho đến khi &lt;i&gt;người đó&lt;i&gt; trở lại."</t>
+Anh biết rõ sương mù của mình không bao giờ che giấu được những vết thương vĩnh viễn mà &lt;te href=850075&gt;Lời Than Vãn&lt;/te&gt; gây ra cho hành tinh này.
+Đó là lý do anh sẵn sàng đồng ý hợp tác lâu dài với Bờ Biển Đen ngay từ lần đầu đặt chân lên đảo qua lời mời.
+Cho đến nay, anh đã cung cấp cho Bờ Biển Đen vô số thông tin tình báo và giúp họ tuyển mộ những ứng viên đáng tin cậy để củng cố Tổ Tư Duy.
+Anh sẽ hỗ trợ Bờ Biển Đen thực hiện các kế hoạch... Cho đến khi &lt;i&gt;người đó&lt;i&gt; trở lại."</t>
         </is>
       </c>
     </row>
@@ -32798,15 +32781,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Khi được hỏi về tuổi thơ của mình, Jiyan nhớ lại vô số ký ức: mùi thuốc men, ánh đèn sáng rực của phòng phẫu thuật, âm thanh va chạm của các thiết bị y tế, và hành lang nơi đã diễn ra biết bao cuộc chia ly.
-Sinh ra trong một gia đình y khoa, Jiyan trở thành trợ lý của mẹ mình từ năm 10 tuổi. Cậu xuất sắc trong các kỹ năng y học và được bệnh nhân yêu mến không chỉ vì chuyên môn, mà còn vì khả năng tuyệt vời trong việc xoa dịu nỗi buồn và đáp ứng nhu cầu của họ.
-Dù sở hữu tài năng y thuật xuất chúng, vẫn có những sinh mạng mà Jiyan không thể kéo lại từ cửa tử thần—bệnh nhân cuối cùng cậu không thể cứu được là Beiwang, người bạn và người thầy của cậu, bị thương nặng bởi &lt;te href=850081&gt;Discords&lt;/te&gt;.
-Ban đầu, Jiyan chỉ biết Beiwang như một bệnh nhân của mình, trong số nhiều &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; khác phải đến gặp bác sĩ sau những trận chiến chống lại những đợt tấn công dồn dập của Discords đang hoành hành khắp vùng đất.
-Beiwang rất ấn tượng trước trí tuệ và trực giác của Jiyan, điều này khiến ông chia sẻ những chi tiết về các cuộc hành quân của Midnight Rangers và cung cấp những bài học quân sự. Ngược lại, Jiyan tích cực đóng góp kỹ năng phân tích của mình vào các cuộc thảo luận chiến lược, dù chưa từng trực tiếp trải qua trận chiến. Những góc nhìn độc đáo của cậu đã thổi sức sống mới vào các cuộc trò chuyện, mang đến cho Beiwang một cái nhìn mới mẻ và đầy hứng khởi.
-Cái chết của Beiwang đã thắp lên một tia lửa biến đổi trong Jiyan—nỗi u sầu, sự thất vọng và hối tiếc của cậu đã hóa thành sức mạnh để cầm ngọn giáo trên chiến trường.
-Jiyan bắt đầu nhận ra rằng &lt;te href=850075&gt;Lament&lt;/te&gt; là một căn bệnh ăn sâu vào huyết mạch của thế giới đến mức ngay cả những dụng cụ y tế tinh vi nhất hay những bác sĩ tài giỏi nhất cũng không thể loại bỏ được. Nhận thức này đã thúc đẩy cậu tìm cách chữa lành thế giới bằng một con đường khác—cậu cầm vũ khí và chiến đấu trực diện với Discords, với quyết tâm không gì lay chuyển.
-Giờ đây, chỉ còn chiếc túi đựng thuốc hình bầu nậm đeo trên thắt lưng là dấu hiệu cho thấy cậu từng là một thầy thuốc. Có rất nhiều đồn đoán về những gì bên trong chiếc túi đó, có người nói cậu dùng những viên ngọc đường để dỗ dành trẻ em, người khác lại bảo cậu uống từ đó sau mỗi trận chiến.
-Nếu có ai hỏi Jiyan về điều này, cậu sẽ trả lời thẳng thắn: "Chỉ là vài loại thuốc thông thường, phòng khi có ai cần đến."</t>
+          <t>Khi được hỏi về tuổi thơ, Jiyan nhớ lại vô số ký ức: mùi thuốc men, ánh đèn sáng rực của phòng phẫu thuật, tiếng va chạm của các thiết bị y tế, và hành lang nơi bao lời từ biệt đã được trao gửi.</t>
         </is>
       </c>
     </row>
@@ -32888,14 +32863,14 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Giữa không khí náo nhiệt của &lt;te href=850129&gt;Hội Riverside Games&lt;/te&gt; ở Jinzhou, một nhóm thanh niên đứng quây quần bên nhau.
+          <t>Giữa không khí náo nhiệt của &lt;te href=850129&gt;Hội Trò Chơi Bên Sông&lt;/te&gt; ở Jinzhou, một nhóm thanh niên đứng quây quần bên nhau.
 "Chuyện là thế này. Đội trưởng chúng tôi có việc gấp phải giải quyết, nên đội thiếu một người cho cuộc đua. Nếu cậu không tham gia, có khi chúng tôi phải bỏ cuộc đấy."
-"Please, giúp chúng tôi đi. Chúng tôi đã luyện tập vất vả cho cuộc đua Tiếp Sức Gulpuff mà. Xin cậu..."
+"Làm ơn, giúp chúng tôi đi. Chúng tôi đã luyện tập vất vả cho cuộc đua Tiếp Sức Gulpuff mà. Xin cậu..."
 "Ừ, xin cậu đi, Jiyan!" họ đồng thanh van nài, giọng đầy khẩn thiết.
 Đứng giữa đám đông là một chàng trai mắt sáng. Gặp ánh nhìn chân thành của họ, cậu gật đầu đồng ý. Thế là một đội tạm thời được thành lập.
 Chàng trai hỏi thăm tình hình từng thành viên và thứ tự chạy tiếp sức. Sau đó, cậu quyết định điều chỉnh chiến thuật và đảm nhận vị trí chạy cuối.
-Hội Trò Chơi ban đầu được tổ chức để xoa dịu căng thẳng cho người dân Jinzhou sau chiến thắng đầu tiên trước đợt bùng phát &lt;te href=850081&gt;Discord&lt;/te&gt;, giờ đã trở thành sự kiện lớn của &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, trong đó cuộc đua Tiếp Sức Gulpuff là một trong những điểm nhấn lớn nhất.
-Tiếng còi vang lên. Các vận động viên xuất phát, khéo léo Dodge chướng ngại vật trên lưng Gulpuff của mình. Dọc bờ sông, đám đông cổ vũ ầm ĩ.
+Hội Trò Chơi ban đầu được tổ chức để xoa dịu căng thẳng cho người dân Jinzhou sau chiến thắng đầu tiên trước đợt bùng phát &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;, giờ đã trở thành sự kiện lớn của &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, trong đó cuộc đua Tiếp Sức Gulpuff là một trong những điểm nhấn lớn nhất.
+Tiếng còi vang lên. Các vận động viên xuất phát, khéo léo né tránh chướng ngại vật trên lưng Gulpuff của mình. Dọc bờ sông, đám đông cổ vũ ầm ĩ.
 Thế nhưng, một sai lầm xảy ra khi trao gậy giữa người chạy thứ nhất và thứ hai, khiến đội tạm thời bị bỏ xa.
 "Ôi, có vẻ đội này gặp trục trặc rồi! Là đội tạm thời nên phối hợp có phần thiếu ăn ý. Tiếc thật đấy!"
 Bình luận viên chuyển sự chú ý sang ba đội dẫn đầu.
@@ -32994,7 +32969,7 @@
 Dù đã đưa ra lời đề nghị, cô bé vẫn tiếp tục ăn, chớp mắt nhìn ông một cách thờ ơ, như thể chẳng hiểu ông đang nói gì.
 Sau khi đã quyết tâm với lời hứa của mình, Shiling đứng dậy và bắt đầu leo núi. Ông thỉnh thoảng ngoái lại, hy vọng cô bé sẽ đổi ý, nhưng nàng vẫn đứng nguyên tại chỗ, chỉ tập trung vào bữa ăn của mình.
 Thất vọng, Shiling đành bỏ mặc cô bé và tiếp tục lên đỉnh. Khi ông gần đến phái trên núi, tiếng cười khúc khích vang lên từ gần cổng sảnh. Lại gần, ông thấy các đệ tử của mình đang cúi xuống, đưa nước cho cô bé mà ông vừa bỏ lại.
-"Master, ngài đã về. Nhìn kìa, đứa trẻ này tự leo núi lên đây đấy."
+"Sư phụ, ngài đã về. Nhìn kìa, đứa trẻ này tự leo núi lên đây đấy."
 "C-Cô bé đến từ khi nào thế?"
 "Con không biết. Con đã ở đây một lúc rồi, mà cô bé đến trước con."
 Không nói thêm lời nào, Shiling đưa tay ra với cô bé vẫn đứng im, không hiểu ý nghĩa của cử chỉ đó.
@@ -33075,17 +33050,17 @@
       <c r="M467" t="inlineStr">
         <is>
           <t>Cô gái ấy hiểu rõ mục đích cuộc đời mình: hoàn thiện từng động tác một. Tất cả những gì cô muốn là thành thạo võ thuật của mình, điều đòi hỏi sự tập trung và cống hiến cao độ. Đó là mức độ tập trung mà hầu hết mọi người không thể đạt được, nhưng với cô, đó là mục tiêu tối thượng.
-"Master Đức Khanh, còn chỗ nào con làm sai nữa không ạ?"
+"Sư phụ Đức Khanh, còn chỗ nào con làm sai nữa không ạ?"
 "Ba chỗ. Đây, thầy sẽ làm mẫu lại một lần nữa. Con chú ý nhé. Không cần nhớ hết ngay đâu, miễn là cuối cùng con làm đúng là được."
 "Tiềm Tâm, trễ rồi. Ngày mai tập tiếp đi."
-"Con tập xong chỗ này rồi sẽ về! Master cứ về nghỉ trước đi ạ!"
+"Con tập xong chỗ này rồi sẽ về! Sư phụ cứ về nghỉ trước đi ạ!"
 Trong sân tập chìm dần vào bóng tối, cô gái không ngừng lặp lại từng động tác. Từ thận trọng đến nhanh nhẹn, cô luyện tập cho đến khi mọi thứ trở thành bản năng.
 Trái tim thuần khiết của cô gái dẫn lối cho mọi lựa chọn, không chút sợ hãi hay yếu đuối. Tâm trí cô đơn giản, nhưng kiên định không lay chuyển.
 "Tiềm Tâm, hắn quá mạnh. Chúng ta chạy đi. Để hắn lấy mấy thứ đồ đó đi."
 Nhưng Kiếm Tâm đã chuẩn bị tinh thần chiến đấu, "Con không bỏ đi đâu. Tuy biết mình không phải đối thủ, nhưng con vẫn muốn thử một lần."
 "Gì chứ? Thử à? Đừng đùa nữa! Chúng ta chạy đi!"
 "Con sẽ cố lấy lại đồ mà không bị thương."
-"Khoan! Trời ơi... Lại thế rồi..."</t>
+"Đợi đã! Trời ơi... Lại thế rồi..."</t>
         </is>
       </c>
     </row>
@@ -33176,14 +33151,14 @@
 "Yêu thương là bản chất con người, nhưng ngươi lại không biết yêu," Nhậm Phúc nhìn thẳng vào mắt nàng và nói, "Ngươi thuần khiết đến cực điểm, nhưng bên trong lại trống rỗng." 
 "Con biết yêu thương mà. Con kính trọng sư phụ, tuân theo lễ nghĩa, tôn kính các bậc trưởng lão trong môn phái, luôn cố gắng giúp đỡ họ." 
 "Khi ta nói 'yêu thương', ta muốn nói đến việc giúp đỡ những người khốn khó và quan tâm đến những con người đau khổ trong thế giới đầy rối ren này," Nhậm Phúc giải thích. 
-"Master Thạch Linh từng nói điều tương tự. Nhưng làm vậy thì được gì?" Kiếm Tâm thắc mắc. 
+"Sư phụ Thạch Linh từng nói điều tương tự. Nhưng làm vậy thì được gì?" Kiếm Tâm thắc mắc. 
 "Bậc thánh nhân giỏi nhất giác ngộ trên chiến trường, bậc thánh nhân tầm trung giác ngộ nơi chốn phồn hoa, còn bậc thánh nhân thấp kém nhất giác ngộ trong ẩn dật. Đạo không thể đạt được chỉ bằng cô độc hay thiền định. Chính qua những tương tác thực tế với đời sống, con người mới có thể đạt được cả tự do tinh thần lẫn thăng hoa thể xác. Theo đuổi lợi ích cá nhân mà thiếu thiền định là con đường sai lầm của Đạo. Thay vào đó, hãy tìm kiếm cái nhìn sâu sắc về con đường của mình và phấn đấu hoàn thiện trong mọi mặt của cuộc sống." 
 "Vậy làm sao con có thể học được cách yêu thương?" Kiếm Tâm hỏi. 
 "Ngươi chưa bao giờ rời khỏi ngọn núi này phải không?" Nhậm Phúc hỏi. 
 "Dạ chưa," Kiếm Tâm đáp. 
 "Có lẽ trước đây chưa phải lúc ngươi rời đi. Nhưng giờ thì đã đến lúc. Làm sao ngươi có thể đạt Đạo nếu không thực sự trải nghiệm thế giới?" 
 Nhậm Phúc ngồi xuống bên cạnh Kiếm Tâm, và hai người trò chuyện rất lâu trên cầu về ý nghĩa của việc yêu thương con người. 
-"Master Nhậm Phúc, lâu rồi không gặp!" 
+"Sư phụ Nhậm Phúc, lâu rồi không gặp!" 
 "Kiếm Tâm, đường ta lại gặp nhau, sao không cùng ta giúp đỡ những người khốn khó?" 
 "Dạ vâng!" 
 Khi nghe lời cảm ơn chân thành và cảm nhận cái bắt tay ấm áp của những bàn tay xa lạ, Kiếm Tâm biết rằng hành động của mình đã tạo nên một tác động nhỏ bé. Nụ cười nở trên môi nàng, xua tan mọi bối rối trước đó.</t>
@@ -33271,7 +33246,7 @@
 Kiến Tân chu du khắp nơi, làm việc chăm chỉ và dùng tiền kiếm được để tự nuôi sống bản thân cũng như giúp đỡ người khác. Dù là việc nhỏ nhất, cô cũng làm với sự tận tâm và quyết tâm, dần xây dựng được danh tiếng vững chắc.
 "Này Kiến Tân, nhờ có cậu mà lượng khách của quán tăng lên nhiều đấy! À, cậu có thể chia sẻ mấy công thức ăn kiêng đó không? Khách rất thích, chúng ta có thể biến nó thành món đặc sản của quán. Đây là tiền lương tháng này của cậu, tiếp tục phát huy nhé!"
 "Tất nhiên! Để tôi viết lại cho cậu."
-"Từ khi cậu làm ở đây, quán sạch sẽ hẳn ra. Bạn're amazing! May mắn quá khi có cậu."
+"Từ khi cậu làm ở đây, quán sạch sẽ hẳn ra. Cậu thật tuyệt vời! May mắn quá khi có cậu."
 "Tôi dùng vài mẹo dọn dẹp học được từ công việc trước. Cậu muốn tôi viết lại luôn không?"
 "À mà này, cậu có biết vị khách vừa rồi trả tiền bằng một phát minh mới của Học viện không? Một tấm thẻ bạc!"
 "Thẻ? Thẻ gì? Ông ta trả tiền kiểu gì?"
@@ -33279,7 +33254,7 @@
 "Đợi đã, đó không phải đồ thật đâu. Ông ta lừa cậu để ăn không đấy."
 "Gì cơ? Vậy là không phải phát minh mới à... Tôi sẽ đi tìm ông ta đòi lại tiền."
 "Cẩn thận nhé, đừng đánh ông ta quá đau! Không đáng đâu!"
-"Tôi sẽ không làm quá đà đâu. Don't worry!"</t>
+"Tôi sẽ không làm quá đà đâu. Đừng lo!"</t>
         </is>
       </c>
     </row>
@@ -33432,7 +33407,7 @@
         <is>
           <t>Với cây bút lông trong tay, cô bé nghiêng người trên bàn, cảm nhận cái lạnh kim loại của ngòi bút chạm vào đầu ngón tay khi những ý tưởng dần khô héo trong sa mạc cằn cỗi của cảm hứng.
 Bên ngoài cửa sổ là đám đông tấp nập, chim chóc, gió và những &lt;te href=850100&gt;Acolytes&lt;/te&gt; đang cầu nguyện... Trong mắt Ciaccona, đó đều là những cảnh vật có thể biến thành từ ngữ và dấu câu, thế nhưng chúng lại không chịu nối kết thành câu văn. Những từ ngữ ấy đặt cạnh nhau chỉ còn vỏn vẹn cái vỏ rỗng tuếch. Chẳng có chút thi vị nào ở đây cả.
-"Lady Ciaccona, tôi có thể làm phiền cô một chút được không?" Một người hầu gái gõ cửa, bước vào phòng sau khi nhận được cái gật đầu của cô bé.
+"Tiểu thư Ciaccona, tôi có thể làm phiền cô một chút được không?" Một người hầu gái gõ cửa, bước vào phòng sau khi nhận được cái gật đầu của cô bé.
 "Tôi muốn nhờ cô một việc, vì cô rất giỏi dùng từ. Cô có thể giúp tôi viết một lá thư không? Cho gia đình tôi."
 Ciaccona ra hiệu cho người hầu ngồi xuống và bắt đầu viết lên tờ giấy trắng: "Gửi..."
 Khi người hầu nhận được thư hồi âm từ nhà, cô chia sẻ với Ciaccona. Cả hai cùng nhau viết lá thư thứ hai...
@@ -33680,7 +33655,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>"Music tự thân không mang cảm xúc. Chính trái tim mới ban cho nó ý nghĩa. Vậy nên, thính giả ơi, hãy nói cho ta biết. Bản nhạc này đã khơi gợi điều gì trong ngươi?"
+          <t>"Âm nhạc tự thân không mang cảm xúc. Chính trái tim mới ban cho nó ý nghĩa. Vậy nên, thính giả ơi, hãy nói cho ta biết. Bản nhạc này đã khơi gợi điều gì trong ngươi?"
 Tại thị trấn Egla, vô số người gặp gỡ rồi chia ly theo từng khoảnh khắc trôi qua. Là một nghệ sĩ lang thang, Ciaccona luôn là kẻ quan sát những câu chuyện, chứng kiến khởi đầu, diễn biến và kết thúc của chúng...
 Cho đến một buổi sáng nọ, khi nàng thoáng thấy một kẻ ngoại lai dưới ánh bình minh, nàng biết rằng một giai điệu mới sắp cất lên.
 Đó là lần đầu Ciaccona trò chuyện với ngươi. Nhưng với nàng, có lẽ hai ta đã từng gặp nhau từ trước đó.
@@ -33768,7 +33743,7 @@
 "Rồi một ngày, chuyện đó thật sự xảy ra. Và phải nói là... buồn cười. Một anh chàng trong đội rất thích nấm, đi hái vài cây bỏ vào nồi canh. Verina ôm chặt cái nồi như thể mạng sống của cô ấy phụ thuộc vào đó. Lúc chúng tôi chạy đến, hai người đã cãi nhau ỏm tỏi rồi."
 "Anh chàng kia khoe khoang với Verina về kinh nghiệm sống hoang dã của mình. Chúa ơi, không biết đầu óc anh ta nghĩ gì, tưởng có thể nói chuyện hơn được cô nàng thực vật học của chúng tôi! Verina trải hết nấm ra, bắt đầu gọi tên từng vòng, mũ, cuống của từng cây một. Đi khám phá lâu, chúng tôi đều hiểu cô ấy muốn nói nấm này có độc. Kiến thức của cô ấy về nấm còn hơn cả chúng tôi, thậm chí còn giảng giải ngay tại chỗ, dạy chúng tôi cách phân biệt từng loại. Đó mới là bài học thực sự."
 "Xong xuôi, cô ấy còn gõ gõ vào một khúc gỗ như một giáo viên, rồi hỏi chúng tôi có hiểu hết không. Chúng tôi nhìn nhau, ngớ ra, rồi phá lên cười, khiến cô ấy phát điên."
-"T-Tại sao các anh lại cười... Em nói sai chỗ nào à? Hừ... Sob" Cô ấy hoảng hốt đến mức bắt đầu nhặt lại nấm trong nồi, kiểm tra từng cây một, trong khi chúng tôi đã vỗ tay khen ngợi. Rồi tôi hét lên, "Bravo Đó là nhà thực vật học của chúng ta, mọi người ơi!"
+"T-Tại sao các anh lại cười... Em nói sai chỗ nào à? Hừ... Hức..." Cô ấy hoảng hốt đến mức bắt đầu nhặt lại nấm trong nồi, kiểm tra từng cây một, trong khi chúng tôi đã vỗ tay khen ngợi. Rồi tôi hét lên, "Tuyệt vời! Đó là nhà thực vật học của chúng ta, mọi người ơi!"
 "Từ đó, Verina vẫn nhớ lại ngày hôm đó và cảm thấy xấu hổ vô cùng; cô ấy thà chui đầu vào nồi nấm còn hơn. Nhưng mỗi khi nói về thực vật, cô ấy vẫn cẩn thận và kiên nhẫn đưa ra ý kiến của mình."</t>
         </is>
       </c>
@@ -34007,7 +33982,7 @@
         <is>
           <t>Là một cô gái bình thường, Verina cũng có những lúc buồn phiền.
 Việc trồng trọt thực vật chẳng bao giờ đoán trước được. Thường xuyên, Verina thức dậy và thấy những hạt giống khô héo trong đĩa petri sau một đêm nghỉ ngơi. Rồi sau cả ngày làm việc không ngừng nghỉ, cô lại nhận ra mình đã bỏ bữa trưa. Những lúc như thế, cô nhớ bố mẹ da diết.
-"Nếu bố mẹ vẫn còn ở đây, con đã không phải lo lắng về tất cả những điều này..." Verina nghĩ. Một bữa trưa nóng hổi, đầy đủ sẽ chờ cô ngay khi bước vào cửa, và cô sẽ nhận được mọi sự giúp đỡ kịp thời mỗi khi muốn tìm hiểu điều gì đó. Nhưng tất cả những điều đó giờ chỉ còn là ký ức, nằm lại trong những ghi chép mà cô đã đánh mất từ lâu khi rời khỏi Liên bang New.
+"Nếu bố mẹ vẫn còn ở đây, con đã không phải lo lắng về tất cả những điều này..." Verina nghĩ. Một bữa trưa nóng hổi, đầy đủ sẽ chờ cô ngay khi bước vào cửa, và cô sẽ nhận được mọi sự giúp đỡ kịp thời mỗi khi muốn tìm hiểu điều gì đó. Nhưng tất cả những điều đó giờ chỉ còn là ký ức, nằm lại trong những ghi chép mà cô đã đánh mất từ lâu khi rời khỏi Liên bang Mới.
 Giờ đây, cô phải tự vực dậy và sống một mình.
 Đôi khi, cô tự hỏi: &lt;i&gt;Liệu những công việc mình đã làm có ý nghĩa gì không? Cuộc sống mình đang sống có ý nghĩa gì không?&lt;i&gt;
 Nhưng rồi, cô luôn tìm thấy câu trả lời trong những cây cối đang phát triển tươi tốt.
@@ -34093,7 +34068,7 @@
 Sau những ngày dài làm việc, cô hiểu tầm quan trọng của việc nghỉ ngơi đối với cả bản thân lẫn những cây hoa của mình. Cô gạt bỏ mọi suy nghĩ, cầm cuốn sổ ghi chép phiêu lưu và bước ra khám phá những con phố &lt;te href=850091&gt;Jinzhou&lt;/te&gt;.
 Jinzhou khác xa quê hương cô ở Tân Liên Bang. Ở đây không có giá hoa đắt đỏ hay những cuộc thi hoa phức tạp. Khi lang thang qua những con hẻm nhộn nhịp, Verina cảm thấy một sự thanh thản thực sự. Hơi nước bốc lên từ các quầy hàng rong và những người mua sắm tấp nập xung quanh mang đến cảm giác bình yên quen thuộc cho thành phố mới này.
 "Tốt lắm, tốt lắm." Khi bước đi trên đường, Verina tự nhủ. Những ký ức ùa về: những ngày nghiên cứu thực vật cùng bố mẹ, và nỗi cô đơn đau đớn sau khi họ ra đi. Nhưng giờ đây, tự đứng trên đôi chân của mình, cô cuối cùng cũng có thể tự thưởng cho mình một kỳ nghỉ yên bình. Sau những tháng ngày dài cô độc, cô đã trưởng thành theo cách của riêng mình.
-Rồi cô nhìn thấy bạn bè đang vẫy tay gọi: Chixia và Yangyang đang tiến về phía cô với những ly Salted Milk Tea mới mua trên tay. Có lẽ &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; cũng đang có một kỳ nghỉ nhỏ. Verina vội vàng lục túi xách, lấy ra vài bó hoa nhỏ hình ngôi sao.
+Rồi cô nhìn thấy bạn bè đang vẫy tay gọi: Chixia và Yangyang đang tiến về phía cô với những ly Trà Sữa Muối mới mua trên tay. Có lẽ &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; cũng đang có một kỳ nghỉ nhỏ. Verina vội vàng lục túi xách, lấy ra vài bó hoa nhỏ hình ngôi sao.
 Đây là món quà quý giá nhất mà Verina có thể tặng bạn bè. Cô đã mất quá nhiều thời gian để lựa chọn, và trong khi những bông &lt;te href=850133&gt;Starflowers&lt;/te&gt; chờ đợi những khoảnh khắc và ánh nắng đẹp nhất, cô cũng đã chờ đợi ánh nắng mang lại cho mình sự ấm áp.
 Giờ đây, khi nhìn thấy ánh nắng của mình, Verina chạy về phía bạn bè.
 Con đường phía trước còn dài, và sẽ mất thời gian để những bông hoa nở rộ.
@@ -34171,16 +34146,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Bên ngoài một ngôi nhà cũ ở Yuezhou có một đám sậy bên hồ. Về phía bắc, mặt nước thu hẹp lại; về phía nam, nó mở rộng ra, giống như một quả lê bị bổ đôi, với mặt hồ lấp lánh dưới bầu trời đêm.
-Không khí mùa hè nặng trĩu hơi nóng, ru ngủ cả thế giới trong cơn mơ màng uể oải.
-Trong sự tĩnh lặng của buổi tối, Lumi nằm gọn trong vòng tay mẹ trên chiếc ghế bập bênh bên cửa sổ. Đôi mí mắt cô bé nặng trĩu khi lim dim nhìn ra ngoài. Làn gió nhẹ từ chiếc quạt lướt qua làn da, khiến cô bé nheo mắt trong thỏa mãn. Tiếng ve sầu râm ran khắp sân, và Lumi càng thu mình gần mẹ hơn, được ru ngủ bởi những âm thanh êm đềm của ngôi làng.
-Nơi nhỏ bé này là Changzhuang. Không ai còn nhớ rõ tại sao nó lại có cái tên đó, nhưng dần dần, mọi người đã quen với cái tên này.
-Những thảm họa sau &lt;te href=850075&gt;Lament&lt;/te&gt; đã lan rộng khắp &lt;te href=850093&gt;Huanglong&lt;/te&gt;. Ngay cả ở đây, sâu trong núi rừng Yuezhou, chúng cũng để lại dấu ấn không thể phai mờ bằng cách cắt đứt ngôi làng khỏi thế giới bên ngoài—công nghệ sụp đổ, và dân làng quay về với lối sống cũ—canh tác, săn bắn, sinh tồn như tổ tiên họ từng làm. Cuộc sống bị chi phối bởi sự mọc và lặn của mặt trời. Theo thời gian, người dân Changzhuang đã quen với sự bình yên và giản dị của lối sống này.
-Ngày Lumi chào đời, cả ngôi nhà bừng sáng. Đứa bé được quấn tã phát ra ánh sáng dịu nhẹ, thu hút ánh nhìn của mọi người trong làng. Họ tụ tập ngoài sân, tò mò muốn nhìn thấy đứa trẻ mới sinh tỏa sáng như một ngọn hải đăng nhỏ. Resonators rất hiếm ở đây, và những người như Lumi, với sức mạnh bẩm sinh như vậy, còn hiếm hơn. Nhưng trong một ngôi làng yên bình như Changzhuang, không có thử thách lớn lao nào cần đến một Resonators nhí để giải quyết. Vì vậy, Lumi lớn lên vô tư, giống như những đứa trẻ bình thường khác trong làng. Cô bé học cách sống trên núi và đồng ruộng—cách theo dõi dấu vết động vật hoang dã và phân biệt loại cây nào có thể làm dịu cơn đói.
-Người dân Changzhuang thích nghỉ mát dưới bóng cây. Khi Lumi chạy qua những tán cây cùng bạn bè, ánh sáng bẩm sinh của cô bé nhấp nháy như đang nhảy múa vui vẻ. Những người lớn tuổi trong làng trìu mến gọi cô là "Nắng", còn bạn bè thì đặt cho cô biệt danh "Lumi Đom Đóm". Thế nhưng, Lumi thường tự hỏi về món quà kỳ lạ của mình, không biết nó có ý nghĩa gì. Thường thì nó chỉ gây phiền toái. Trong những chuyến đi săn, ánh sáng của cô bé loé lên không kiểm soát, làm kinh động con mồi.
-Sau khi bị yêu cầu tạm ngừng tham gia săn bắn, trái tim Lumi chùng xuống với nỗi thất vọng. Một mình cô lang thang đến đầm lầy bên đám sậy và ngồi xuống. Ánh sáng của cô bé nhấp nháy, mờ đi rồi lại sáng lên khi cô luyện tập, cố gắng kiểm soát nó. Cuối cùng, cô bé kiệt sức và thiếp đi. Dù gặp khó khăn, Lumi không hề cảm thấy vội vã.
-Cuộc sống ở Changzhuang diễn ra chậm rãi, và luôn có thời gian để trưởng thành và học hỏi.
-Mặt hồ lấp lánh lại trở về với bóng tối. Gió đêm đưa tiếng ếch nhái đi xa. Tomorrow lại là một ngày mới.</t>
+          <t>Bên ngoài một ngôi nhà cổ ở Việt Châu là đám sậy bên hồ. Phía bắc, mặt nước thu hẹp; phía nam, nó mở rộng ra, tựa như quả lê bị bổ đôi, mặt hồ lấp lánh dưới bầu trời đêm.</t>
         </is>
       </c>
     </row>
@@ -34458,25 +34424,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Kể từ khi kết nối với thế giới bên ngoài được khôi phục, Changzhuang đã trải qua một sự thay đổi đáng kể. Những tòa nhà và tiện nghi mới mọc lên khắp nơi, thế nhưng khi Lumi trở về nhà, cô lại cảm thấy một làn sóng hoài niệm sâu sắc.
-Có lẽ những người khao khát sự thay đổi đã rời đi từ lâu, như Lumi từng làm, còn những người ở lại vẫn giữ nguyên những thói quen và nhịp sống thường ngày. Mặt trời đang dần lặn, và khi cô đi qua ngôi làng, khói từ những bếp lửa nấu ăn bay lên lười biếng trên bầu trời, hòa quyện với tiếng cười và tiếng vo ve của côn trùng buổi tối.
-Bố mẹ cô chào đón cô trở về, đặt trước mặt cô một bát mì nóng hổi—thịt thì nhiều, nước dùng đậm đà, thêm một thìa dầu ớt thơm lừng.
-Lumi ăn ngấu nghiến, hơi nóng làm đôi má cô ửng hồng khi cô húp sợi mì một cách háo hức. Mẹ cô cười khẽ, đưa cho cô một cốc nước.
-"Ăn từ từ thôi, Lumi, không ai giành đồ ăn của con đâu," mẹ cô trêu.
-Sau khi uống một ngụm nước và nước dùng, cô ngả người ra sau, thở dài một cách thỏa mãn.
-Bố cô, ngồi gần đó, gõ nhẹ chiếc tẩu thuốc. "Đi xa lâu rồi nhỉ? Công việc thế nào?"
-Lumi mỉm cười. "Vất vả lắm, nhưng mọi thứ đang dần tốt lên. Có một người đã giúp con rất nhiều—một anh hùng đến từ &lt;te href=850091&gt;Jinzhou&lt;/te&gt; đấy!"
-Mẹ cô nhướn ngươi, vẻ thích thú. "Ồ? Con gái chúng ta giờ giao thiệp với cả những nhân vật quan trọng rồi à?"
-Lumi cười, đôi mắt sáng lên. "Thật mà! Con gặp khó khăn trong công việc, nhưng nhờ {Male=anh ấy;Female=cô ấy}, con đã xoay chuyển được tình thế. Đây là những gì đã xảy ra…"
-Sáng hôm sau, khi ngôi làng vẫn còn chìm trong sự tĩnh lặng của bình minh, Lumi rời nhà để tận hưởng cảnh sắc buổi sáng trên những cánh đồng. Nơi đây không hề thay đổi đến mức không thể nhận ra. Nó vẫn mang những dấu vết của nơi đã từng tôi luyện nên cô.
-Cô lang thang không mục đích, chìm trong suy nghĩ cho đến khi một cái vỗ nhẹ vào vai kéo cô trở lại hiện tại.
-"Lumi? Con làm gì ở tận đây thế?" Lumi chớp mắt và quay lại, thấy Zhangzhang, người bạn thuở nhỏ, đang đứng sau cô với nụ cười trên môi.
-"À, Zhangzhang! Con chỉ… nhớ lại thôi. Lâu rồi không gặp," Lumi nhìn về con đường mới được lát uốn lượn qua những ngọn đồi. "Con còn chẳng biết mình đang ở đâu nữa."
-Zhangzhang cười. "Ừ, con đường mới làm xong đấy—mượt hơn trước nhiều, phải không? Đây từng là nơi con thích nhất, con còn nhớ không?" Cô chuyển ánh mắt về phía con đường và tiếp tục, "Nhưng ít người qua lại lắm. Nhưng nghe nói đội &lt;te href=850090&gt;Lollo Logistics&lt;/te&gt; của con thường xuyên ghé thăm đấy." Zhangzhang dừng lại, vẻ tò mò, "Nhân tiện, dạo này con có đi đâu thú vị không? Có gì hay ho kể cho mình nghe đi? Biết đâu, mình cũng đang nghĩ đến việc rời khỏi đây để khám phá thế giới…"
-Lumi gật đầu và bắt đầu kể lại những chuyến phiêu lưu gần đây của mình, chia sẻ những câu chuyện về những thành phố xa xôi và những vùng đất lạ lẫm với người bạn thuở nhỏ.
-Khi họ chia tay, Lumi tìm thấy một hòn đá bên đường và ngồi lên, chống cằm lên tay khi ngước nhìn bầu trời. Cô biết rằng mình phải tiếp tục tiến về phía trước—chỉ có như vậy, cô mới được thấy những điều mới mẻ, mang lại sự thay đổi và tạo nên sự khác biệt cho người khác.
-Khi màn đêm dần tan, ánh sáng đầu tiên của bình minh tràn ngập những ngọn núi đang say giấc.
-Nơi xa xa, tại nơi con đường núi giao với bầu trời, bóng dáng quen thuộc của một chiếc xe Lollo Logistics, lấp lánh dưới ánh mặt trời, đang tiến về phía Changzhuang.</t>
+          <t>Kể từ khi kết nối với thế giới bên ngoài được khôi phục, Trường Trang đã trải qua một sự thay đổi lớn lao. Những tòa nhà mới và tiện nghi mọc lên khắp nơi, thế nhưng khi Lumi trở về nhà, cô lại cảm thấy một làn sóng hoài niệm dâng trề trong lòng.</t>
         </is>
       </c>
     </row>
@@ -34564,28 +34512,28 @@
       <c r="M484" t="inlineStr">
         <is>
           <t>&lt;i&gt;Kẻ mộng mị ban ngày đã nhìn thấy mặt trời trong đêm.&lt;/i&gt;
-Trước khi bị giam cầm dưới lòng đất làm lõi của Tethys, Shorekeeper từng du hành vượt ra ngoài &lt;te href=850109&gt;Black Shores&lt;/te&gt;.
-Lúc ấy, nền văn minh đang tiến bước vững chắc. Bộ điều biến Thiên Văn &lt;te href=850111&gt;Modulator&lt;/te&gt; đã thành lập một tổ chức mang tên Black Shores, chiêu mộ những thành viên mới được Tethys tuyển chọn. Trong khi đó, Shorekeeper tập trung tái tạo và phân tích những Reverberation mà họ mang về, hoàn tất các phép tính của mình.
+Trước khi bị giam cầm dưới lòng đất làm lõi của Tethys, Shorekeeper từng du hành vượt ra ngoài &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt;.
+Lúc ấy, nền văn minh đang tiến bước vững chắc. Bộ điều biến Thiên Văn &lt;te href=850111&gt;Modulator&lt;/te&gt; đã thành lập một tổ chức mang tên Bờ Biển Đen, chiêu mộ những thành viên mới được Tethys tuyển chọn. Trong khi đó, Shorekeeper tập trung tái tạo và phân tích những Reverberation mà họ mang về, hoàn tất các phép tính của mình.
 Như một người quan sát toàn tri, Shorekeeper có thể truy vết dữ liệu để theo dõi hành vi của bất kỳ ai vào bất kỳ lúc nào trong &lt;te href=850077&gt;Sonoros&lt;/te&gt; mà cô tái tạo. Cô cố gắng phân loại và giải thích con người như bất kỳ hiện tượng nào khác, nhưng nhanh chóng nhận ra mình bị họ làm cho bối rối.
 Tại sao họ lại khóc trong cả niềm vui lẫn nỗi buồn? Tại sao hành động của họ lại thường mâu thuẫn với khát khao? Tại sao lại theo đuổi điều họ biết sẽ hối tiếc, hay kiên trì với điều bất khả thi? Sao họ có thể dễ dàng làm hại người khác, nhưng lại sẵn sàng hy sinh bản thân không chút do dự? Mỗi lần Shorekeeper tưởng mình đã gần hiểu ra, một sự kiện bất ngờ lại lật đổ mọi kết luận của cô. Dù bối rối, cô tự hỏi liệu sự bối rối ấy có quan trọng không—dù sao, nó cũng không ngăn cô hoàn thành nhiệm vụ. Nhưng rồi, Bộ điều biến Thiên Văn giao cho cô một nhiệm vụ: những dấu hiệu của một &lt;te href=850075&gt;Lament&lt;/te&gt; sắp xảy ra đã xuất hiện, cần phải nghiên cứu thực địa để thu thập dữ liệu phân tích. Họ sẽ cùng nhau đi và... xem còn có thể làm gì hơn.
 Shorekeeper theo Modulator băng qua những cánh đồng của vùng đất ấy. Đó là mùa gặt—đất dưới chân mềm mà chắc, những bông lúa nặng trĩu chín vàng, gió mang theo hương thơm ngọt ngào của lúa chín. Cô hiểu những điều này, nhưng tận mắt chứng kiến lại khác hẳn. Chìm đắm trong những cảm giác xa lạ, Shorekeeper không hề nhận ra biểu cảm của mình phản ánh sự tò mò và ngạc nhiên của một đứa trẻ lần đầu bước ra khỏi nhà. Modulator trò chuyện thân mật với người dân địa phương, những cuộc đối thoại tràn ngập tiếng địa phương và nhịp sống thường nhật. Một bà lão tốt bụng mời họ thức ăn tự làm. Da bà sần sùi, trong khi đứa bé bà bế trên tay có những ngón tay nhỏ ấm áp, đẫm mồ hôi.
 Nhưng đúng như &lt;te href=850110&gt;Tethys&lt;/te&gt; dự đoán, những điềm báo ấy chẳng mấy chốc trở thành hiện thực, đập tan bầu không khí yên bình thoáng qua.
 Những con người từng thân thiện giờ đây chìm trong tuyệt vọng—đánh nhau giành giật tài nguyên, gào thét trong đau đớn, khuôn mặt méo mó vì tuyệt vọng và sợ hãi. Lần đầu tiên, Shorekeeper tận mắt chứng kiến Lament, không phải qua Sonoros, mà là hiện thực trần trụi, choáng ngợp.
-Điều khiến cô ngạc nhiên hơn cả là Modulator. {Male=Anh;Female=Chị} ấy dẫn dắt tất cả Resonators chống lại &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;, động viên mọi người cố gắng cầm cự đến khi quân tiếp viện tới. {Male=Anh;Female=Chị} ấy đang cố thay đổi một tương lai đã được định sẵn, nhưng tại sao lại phải nỗ lực đến thế vì một nhóm người xa lạ? Shorekeeper nhớ lại chỉ thị của hệ thống Tethys:
+Điều khiến cô ngạc nhiên hơn cả là Modulator. {Male=his;Female=her} ấy dẫn dắt tất cả Resonator chống lại &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;, động viên mọi người cố gắng cầm cự đến khi quân tiếp viện tới. {Male=He;Female=She} ấy đang cố thay đổi một tương lai đã được định sẵn, nhưng tại sao lại phải nỗ lực đến thế vì một nhóm người xa lạ? Shorekeeper nhớ lại chỉ thị của hệ thống Tethys:
 "Một tương lai đã bị thay đổi thì chắc chắn sẽ bị thay đổi. Không nên cố gắng thay đổi những kết cục đã được định trước."
 "Tôi không thể đứng nhìn mà không làm gì. Nếu cái giá của ngày mai là như thế này, tôi tự hỏi liệu ngày mai ấy có đáng giá không." Giọng Modulator ánh vàng kiên định.
 "...Không thể xử lý. Nhưng tôi sẽ ưu tiên nhu cầu của anh." Shorekeeper đáp, đồng thời mở rộng Stellarealm để chữa lành và bảo vệ.
-Night buông xuống, quân tiếp viện cuối cùng cũng tới. Ngay khi chuẩn bị rời đi, một đứa trẻ mất cha mẹ chặn đường họ.
+Đêm buông xuống, quân tiếp viện cuối cùng cũng tới. Ngay khi chuẩn bị rời đi, một đứa trẻ mất cha mẹ chặn đường họ.
 "Đ-đợi đã, các anh đi đâu? Con muốn đi cùng... để chiến đấu với lũ quái vật kia!"
-Nhìn đôi mắt sáng ngời của đứa trẻ, Modulator cúi xuống và chỉ vào bông Blake Bloom trên {Male=áo anh;Female=áo chị}.
+Nhìn đôi mắt sáng ngời của đứa trẻ, Modulator cúi xuống và chỉ vào bông Blake Bloom trên {Male=his;Female=her}.
 "Những gì chúng ta sắp làm quá nguy hiểm với con. Nhưng nếu con vẫn muốn gia nhập khi lớn lên, hãy tìm người đeo bông hoa này."
-Khi con tàu rời bến, Shorekeeper nhìn đứa trẻ vẫy tay từ bến tàu. Human vẫn khiến cô bối rối, nhưng lần này, cô cố gắng bày tỏ sự bối rối ấy với người bên cạnh.
+Khi con tàu rời bến, Shorekeeper nhìn đứa trẻ vẫy tay từ bến tàu. Con người vẫn khiến cô bối rối, nhưng lần này, cô cố gắng bày tỏ sự bối rối ấy với người bên cạnh.
 "Tethys không dự đoán điều này. Đứa trẻ ấy không phải ứng viên chúng ta cần."
-"Không phải mọi thứ đều cần lệnh của Tethys. Human không bị ràng buộc bởi những giới hạn như vậy. Cậu bé ấy có thể chưa cần thiết bây giờ, nhưng theo thời gian... cậu ấy sẽ tìm ra con đường của riêng mình."
+"Không phải mọi thứ đều cần lệnh của Tethys. Con người không bị ràng buộc bởi những giới hạn như vậy. Cậu bé ấy có thể chưa cần thiết bây giờ, nhưng theo thời gian... cậu ấy sẽ tìm ra con đường của riêng mình."
 "Quyền được lựa chọn tự do quan trọng hơn bất kỳ câu trả lời nào. Đó là điều tôi muốn cho em thấy."
 "Tôi muốn em tự mình trải nghiệm những điều này. Chúng ta không phải dữ liệu hay khái niệm trừu tượng trong hồ sơ—em có thể coi chúng ta là bạn đồng hành."
 "Bạn đồng hành..." Shorekeeper lặp lại từ ấy, suy ngẫm về ý nghĩa của nó. Những gì Modulator nói không phải mệnh lệnh, cũng chẳng phải câu trả lời. Thế nhưng từ lúc đó, một sự mong đợi thầm kín, khó hiểu bắt đầu nhen nhóm trong cô.
-"Human quả là sinh vật phức tạp... Tôi chưa hiểu họ, nhưng tôi hy vọng, một ngày nào đó, tôi sẽ hiểu."</t>
+"Con người quả là sinh vật phức tạp... Tôi chưa hiểu họ, nhưng tôi hy vọng, một ngày nào đó, tôi sẽ hiểu."</t>
         </is>
       </c>
     </row>
@@ -34667,22 +34615,22 @@
       <c r="M485" t="inlineStr">
         <is>
           <t>&lt;i&gt;Đừng thương tiếc nơi ta yên nghỉ; ta không ở đó, cũng chẳng rời đi.&lt;/i&gt;
-Khi những cỗ máy nhắc đến cái tên "Delone," The Shorekeeper lập tức nhớ lại tất cả những gì gắn liền với nó. Điều này không chỉ bởi khả năng tự nhiên của bà trong việc lưu trữ và ghi chép thông tin, mà vì Delone rất đặc biệt—bà là một trong số ít người tự mình tìm đến &lt;te href=850109&gt;Black Shores&lt;/te&gt;.
-Lần đầu The Shorekeeper gặp cô, Delone là một cô gái tràn đầy nhiệt huyết. Cô phàn nàn về việc tìm đến Black Shores khó khăn đến thế nào, rồi nhướn ngươi với vẻ tự hào. "Tôi biết mà! Chắc chắn mọi người đang tập hợp để chiến đấu chống lại &lt;te href=850075&gt;Những Lời Than Khóc&lt;/te&gt; và ngăn chặn những bất thường tiếp diễn!"
-Lúc đó, &lt;te href=850111&gt;Bộ Điều Chỉnh&lt;/te&gt; Thiên Văn, người từng nắm quyền lực tối cao tại Black Shores, vẫn chưa vắng bóng lâu, và The Shorekeeper vẫn có thể lên mặt đất. Khi cô gái nhiệt thành ấy nắm lấy tay bà, quyết tâm gia nhập Black Shores hiện rõ trên từng ngón tay, The Shorekeeper không biết phải đáp lại thế nào. Bà cảm nhận được bàn tay ấm nóng của cô—nóng rực như ngọn lửa trong đôi mắt ấy.
-The Shorekeeper đã cho Delone đủ tư cách tham gia kỳ thi tuyển, dù điều đó đi ngược với quy trình tuyển dụng của &lt;te href=850110&gt;Tethys&lt;/te&gt;. Bà nhớ lại lời Bộ Điều Chỉnh từng nói: "Humans không bị ràng buộc bởi những quy tắc cứng nhắc… Chúng ta không phải dữ liệu hay khái niệm trừu tượng trong hồ sơ." The Shorekeeper tin rằng Bộ Điều Chỉnh hẳn cũng sẽ làm như vậy, chỉ để giữ lại ngọn lửa nhiệt huyết đang bừng cháy trong cô gái ấy. Cuối cùng, Delone đã vượt qua kỳ thi và trở thành thành viên chính thức của Black Shores.
-The Shorekeeper không ngờ rằng họ lại gặp nhau trong hoàn cảnh đau thương đến thế.
-Hơn một thập kỷ trôi qua, cô gái từng rực lửa ấy giờ đã trưởng thành thành một người phụ nữ điềm tĩnh. Nhưng giờ đây, cô đang với tay về phía The Shorekeeper bằng bàn tay run rẩy, sinh mệnh đang tuột khỏi vết thương trầm trọng. The Shorekeeper nhìn thấy rõ ràng. Sinh mệnh của Delone đang dần tắt, và chỉ có một kết cục duy nhất.
+Khi những cỗ máy nhắc đến cái tên "Delone," Người Gác Bờ lập tức nhớ lại tất cả những gì gắn liền với nó. Điều này không chỉ bởi khả năng tự nhiên của bà trong việc lưu trữ và ghi chép thông tin, mà vì Delone rất đặc biệt—bà là một trong số ít người tự mình tìm đến &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt;.
+Lần đầu Người Gác Bờ gặp cô, Delone là một cô gái tràn đầy nhiệt huyết. Cô phàn nàn về việc tìm đến Bờ Biển Đen khó khăn đến thế nào, rồi nhướn mày với vẻ tự hào. "Tôi biết mà! Chắc chắn mọi người đang tập hợp để chiến đấu chống lại &lt;te href=850075&gt;Những Lời Than Khóc&lt;/te&gt; và ngăn chặn những bất thường tiếp diễn!"
+Lúc đó, &lt;te href=850111&gt;Bộ Điều Chỉnh&lt;/te&gt; Thiên Văn, người từng nắm quyền lực tối cao tại Bờ Biển Đen, vẫn chưa vắng bóng lâu, và Người Gác Bờ vẫn có thể lên mặt đất. Khi cô gái nhiệt thành ấy nắm lấy tay bà, quyết tâm gia nhập Bờ Biển Đen hiện rõ trên từng ngón tay, Người Gác Bờ không biết phải đáp lại thế nào. Bà cảm nhận được bàn tay ấm nóng của cô—nóng rực như ngọn lửa trong đôi mắt ấy.
+Người Gác Bờ đã cho Delone đủ tư cách tham gia kỳ thi tuyển, dù điều đó đi ngược với quy trình tuyển dụng của &lt;te href=850110&gt;Tethys&lt;/te&gt;. Bà nhớ lại lời Bộ Điều Chỉnh từng nói: "Con người không bị ràng buộc bởi những quy tắc cứng nhắc… Chúng ta không phải dữ liệu hay khái niệm trừu tượng trong hồ sơ." Người Gác Bờ tin rằng Bộ Điều Chỉnh hẳn cũng sẽ làm như vậy, chỉ để giữ lại ngọn lửa nhiệt huyết đang bừng cháy trong cô gái ấy. Cuối cùng, Delone đã vượt qua kỳ thi và trở thành thành viên chính thức của Bờ Biển Đen.
+Người Gác Bờ không ngờ rằng họ lại gặp nhau trong hoàn cảnh đau thương đến thế.
+Hơn một thập kỷ trôi qua, cô gái từng rực lửa ấy giờ đã trưởng thành thành một người phụ nữ điềm tĩnh. Nhưng giờ đây, cô đang với tay về phía Người Gác Bờ bằng bàn tay run rẩy, sinh mệnh đang tuột khỏi vết thương trầm trọng. Người Gác Bờ nhìn thấy rõ ràng. Sinh mệnh của Delone đang dần tắt, và chỉ có một kết cục duy nhất.
 "Tôi đã làm được rồi," Delone mỉm cười yếu ớt. "Tôi đã hạ gục tám &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; trong một lần Lời Than Khóc. Nhưng Twala... họ không may mắn như vậy. Tôi là người duy nhất còn lại mang dữ liệu về."
-Giờ phút chia ly đang đến gần. Những thành viên khác, không biết danh tính thật của The Shorekeeper, tưởng bà là bạn thân của Delone và để họ có không gian cho khoảnh khắc cuối cùng.
+Giờ phút chia ly đang đến gần. Những thành viên khác, không biết danh tính thật của Người Gác Bờ, tưởng bà là bạn thân của Delone và để họ có không gian cho khoảnh khắc cuối cùng.
 "Đã bao nhiêu thời gian trôi qua... Tôi... giờ tôi già rồi... nhưng bà vẫn y như xưa."
-"Tôi đã làm tốt chứ? Tôi không làm bà thất vọng phải không?" Giọng Delone run rẩy vì yếu đuối, nhưng đôi mắt vẫn sáng rực như lần đầu họ gặp nhau. Bộ Điều Chỉnh sẽ làm gì nhỉ? The Shorekeeper không biết—không có câu trả lời rõ ràng, không có tấm gương nào để noi theo. Nhưng khi nhìn vào đôi mắt ấy, bà cảm thấy có gì đó nặng trĩu trong lồng ngực, một cảm xúc khó tả đang dâng trào. Nó thôi thúc bà phá vỡ quy tắc một lần nữa, như cách bà đã làm bao năm trước.
+"Tôi đã làm tốt chứ? Tôi không làm bà thất vọng phải không?" Giọng Delone run rẩy vì yếu đuối, nhưng đôi mắt vẫn sáng rực như lần đầu họ gặp nhau. Bộ Điều Chỉnh sẽ làm gì nhỉ? Người Gác Bờ không biết—không có câu trả lời rõ ràng, không có tấm gương nào để noi theo. Nhưng khi nhìn vào đôi mắt ấy, bà cảm thấy có gì đó nặng trĩu trong lồng ngực, một cảm xúc khó tả đang dâng trào. Nó thôi thúc bà phá vỡ quy tắc một lần nữa, như cách bà đã làm bao năm trước.
 "Con đã làm rất tốt. Rất tốt."
-The Shorekeeper trả lời, và lần này, bà nắm lấy tay Delone. Bằng cách nào đó, bà biết cử chỉ này có thể mang lại chút an ủi cho cô, như cách nó đã làm bao năm về trước.
-"Cảm ơn bà... Cảm ơn bà, The Shorekeeper," Delone thì thầm, giọng tràn ngập sự thanh thản. Rồi cô lẩm bẩm, "Những vì sao... chúng sáng quá. Liệu tôi có trở thành một trong số chúng... sau này không? Có quá nhiều điều tôi sẽ không được thấy, nhưng bà sẽ... họ sẽ..."
+Người Gác Bờ trả lời, và lần này, bà nắm lấy tay Delone. Bằng cách nào đó, bà biết cử chỉ này có thể mang lại chút an ủi cho cô, như cách nó đã làm bao năm về trước.
+"Cảm ơn bà... Cảm ơn bà, Người Gác Bờ," Delone thì thầm, giọng tràn ngập sự thanh thản. Rồi cô lẩm bẩm, "Những vì sao... chúng sáng quá. Liệu tôi có trở thành một trong số chúng... sau này không? Có quá nhiều điều tôi sẽ không được thấy, nhưng bà sẽ... họ sẽ..."
 Một giọt nước mắt lăn xuống, mang theo hơi ấm cuối cùng của cô.
-Đúng như lời Delone nói, The Shorekeeper đã biến đổi tần số của những người đã khuất thành một "ngôi sao," để lại chúng trong chòm sao dữ liệu. Bà không nhớ mình đã bắt đầu làm điều này từ khi nào. Thời gian đã làm héo úa những bông hoa Blake và xói mòn Black Shores—nó cũng đã cướp đi sinh mạng của những người đáng được ghi nhớ. Những vì sao lấp lánh trên bầu trời giờ đây là nơi yên nghỉ duy nhất cho những linh hồn đã ngã xuống.
-Dưới bầu trời đầy sao, The Shorekeeper đứng trên bờ, đắm chìm trong ánh sáng của chúng, và nhìn ra biển cả. Liệu Bộ Điều Chỉnh có đúng khi giao phó quyền lực ấy cho bà? Bà đã làm đủ để chăm sóc Black Shores như lời dặn dò chưa? Câu trả lời cho những câu hỏi ấy giờ nằm ở người đã ra đi... Tất cả những gì còn lại cho bà là sự chờ đợi dường như vô tận. Và thế là bà chờ đợi, vì thời gian là thứ duy nhất bà có thừa.</t>
+Đúng như lời Delone nói, Người Gác Bờ đã biến đổi tần số của những người đã khuất thành một "ngôi sao," để lại chúng trong chòm sao dữ liệu. Bà không nhớ mình đã bắt đầu làm điều này từ khi nào. Thời gian đã làm héo úa những bông hoa Blake và xói mòn Bờ Biển Đen—nó cũng đã cướp đi sinh mạng của những người đáng được ghi nhớ. Những vì sao lấp lánh trên bầu trời giờ đây là nơi yên nghỉ duy nhất cho những linh hồn đã ngã xuống.
+Dưới bầu trời đầy sao, Người Gác Bờ đứng trên bờ, đắm chìm trong ánh sáng của chúng, và nhìn ra biển cả. Liệu Bộ Điều Chỉnh có đúng khi giao phó quyền lực ấy cho bà? Bà đã làm đủ để chăm sóc Bờ Biển Đen như lời dặn dò chưa? Câu trả lời cho những câu hỏi ấy giờ nằm ở người đã ra đi... Tất cả những gì còn lại cho bà là sự chờ đợi dường như vô tận. Và thế là bà chờ đợi, vì thời gian là thứ duy nhất bà có thừa.</t>
         </is>
       </c>
     </row>
@@ -34786,10 +34734,10 @@
       <c r="M486" t="inlineStr">
         <is>
           <t>&lt;i&gt;Ta trao cho ngươi phần lõi tinh túy nhất mà ta đã gìn giữ cẩn thận—một tâm hồn chưa từng bị lời nói vấy bẩn, chưa từng bị mộng mị đánh đổi, và vượt lên trên thời gian, niềm vui lẫn nghịch cảnh.&lt;/i&gt;
-Cứu trợ thảm họa thôi chưa đủ để cứu những kẻ khốn khổ. Thay vì thu thập dữ liệu một cách thụ động sau mỗi &lt;te href=850075&gt;Lament&lt;/te&gt;, &lt;te href=850111&gt;Modulator&lt;/te&gt; đã tìm cách ngăn chặn thảm họa ngay từ đầu. {Male=Hắn;Female=Nàng} dẫn dắt Shorekeeper và các thành viên khác đưa ra cảnh báo và biện pháp phòng ngừa, dù kết quả chẳng mấy khả quan.
+Cứu trợ thảm họa thôi chưa đủ để cứu những kẻ khốn khổ. Thay vì thu thập dữ liệu một cách thụ động sau mỗi &lt;te href=850075&gt;Lament&lt;/te&gt;, &lt;te href=850111&gt;Modulator&lt;/te&gt; đã tìm cách ngăn chặn thảm họa ngay từ đầu. {Male=him;Female=her} dẫn dắt Shorekeeper và các thành viên khác đưa ra cảnh báo và biện pháp phòng ngừa, dù kết quả chẳng mấy khả quan.
 Để thoát khỏi vòng lặp Möbius và tạo ra một thực tại mới, Modulator đã đề xuất một kế hoạch táo bạo.
 Giờ phút chia ly đã cận kề.
-Modulator quyết định xóa bỏ mọi ký ức và vượt ra ngoài Black Shores để tìm kiếm giải pháp khả thi. Những người từng đi theo bước chân Modulator đương nhiên lại chọn đi theo {Male=hắn;Female=nàng} lần nữa.
+Modulator quyết định xóa bỏ mọi ký ức và vượt ra ngoài Black Shores để tìm kiếm giải pháp khả thi. Những người từng đi theo bước chân Modulator đương nhiên lại chọn đi theo {Male=him;Female=her} lần nữa.
 Chỉ còn Shorekeeper ở lại.
 Điều đó là cần thiết, bởi có những việc chỉ kẻ ở lại mới làm được. Tương lai mà Black Shores theo đuổi đối lập với logic của &lt;te href=850110&gt;Tethys&lt;/te&gt;—dùng chính Lament làm công cụ chống lại nó—và cần một lõi để hỗ trợ dịch thuật và tính toán. Shorekeeper, người đã tiếp nhận quyền hạn chuyển giao từ Modulator, là lựa chọn phù hợp nhất.
 Mọi người đều đã đưa ra lựa chọn của mình, và Shorekeeper cũng vậy. Là một thực thể năng lượng, nàng quyết định trở thành mạch dẫn cho mọi dữ liệu Reverberation, luân chuyển qua lõi của mình vào Tethys. Mỗi lần phân tích, tái tạo, hay truy vết, nàng không còn là kẻ đứng ngoài nữa—mà là người trải qua những thảm họa y như những gì dữ liệu ghi lại.
@@ -34907,7 +34855,7 @@
       <c r="M487" t="inlineStr">
         <is>
           <t>&lt;i&gt;Ngươi tựa như màn đêm, với sự tĩnh lặng và những vì sao.&lt;/i&gt;
-Cuộc chờ đợi dài đằng đẵng cuối cùng cũng kết thúc khi &lt;te href=850111&gt;Modulator&lt;/te&gt; trở về. Đúng như lời hứa, {Male=anh;Female=cô} đã tìm đường trở lại Bờ Đen. Dù {Male=anh;Female=cô} đã mất đi ký ức, những lựa chọn của {Male=anh;Female=cô} vẫn không thay đổi—cùng nhau, họ sửa chữa những sai lầm của &lt;te href=850110&gt;Tethys&lt;/te&gt; và mang lại bình yên cho những linh hồn bị giam cầm trong &lt;te href=850141&gt;Necrostar&lt;/te&gt;.
+Cuộc chờ đợi dài đằng đẵng cuối cùng cũng kết thúc khi &lt;te href=850111&gt;Modulator&lt;/te&gt; trở về. Đúng như lời hứa, {Male=his;Female=her} đã tìm đường trở lại Bờ Đen. Dù {Male=anh;Female=cô} đã mất đi ký ức, những lựa chọn của {Male=anh;Female=cô} vẫn không thay đổi—cùng nhau, họ sửa chữa những sai lầm của &lt;te href=850110&gt;Tethys&lt;/te&gt; và mang lại bình yên cho những linh hồn bị giam cầm trong &lt;te href=850141&gt;Necrostar&lt;/te&gt;.
 Tuy nhiên, giữa niềm vui chiến thắng, Shorekeeper cảm thấy có điều gì đó hơn cả niềm hạnh phúc thuần khiết—một sự bất an thầm kín. Những con đường mà Tethys, Modulator, và cả chính cô đã vạch ra giờ đã đi đến hồi kết. Cô nên đi đâu tiếp theo? Trong khi những người khác say sưa ăn mừng, cô lặng lẽ rút lui về bờ biển quen thuộc.
 Shorekeeper lang thang dọc bờ cát như cô vẫn thường làm. Thói quen này hình thành trong thời gian chờ đợi Modulator trở về. Giấc ngủ chẳng có ý nghĩa gì với cô. Thay vào đó, cô thích thức để quan sát bờ biển và ghi nhớ tất cả những gì thời gian đã khắc ghi nơi đây. Dù sao, cũng cần có ai đó giữ gìn ký ức cho đến khi Modulator trở về.
 Đêm nay không khác gì những đêm khác. Thời gian dưới lòng đất như ngừng trôi, những vì sao trên bầu trời vẫn vẹn nguyên. Khi con đường trước mặt trải dài và sóng biển vỗ nhẹ vào chân, cô với tay về phía chân trời vô hình. Dù cảm giác như mình lại rơi vào trạng thái chờ đợi, không biết phải làm gì tiếp theo, nhưng sâu thẳm trong lòng, cô biết có điều gì đó đã thay đổi.
@@ -35026,9 +34974,9 @@
 Khi các Acolyte khác cùng La Guardia kéo đến, vụ hỗn loạn đã kết thúc.
 "Ừ, ừ, tôi đã tận mắt chứng kiến! Cô ấy hạ gục hai gã to con chỉ bằng một cái gõ gậy! Rồi tự nhiên một con Plushie Echo khổng lồ xuất hiện và tha họ đi! Trông cô ấy còn trẻ, nhưng không thể đánh giá qua vẻ ngoài đâu..."
 Một thực khách ở lại giúp dọn dẹp hậu quả kể lại với vẻ hào hứng.
-Acolyte trưởng rút Terminal ra để báo cáo, nhưng phát hiện đã có một báo cáo gửi đến Order, ghi lại sự việc và nơi hai người bị đưa đi.
+Acolyte trưởng rút Thiết bị đầu cuối ra để báo cáo, nhưng phát hiện đã có một báo cáo gửi đến Order, ghi lại sự việc và nơi hai người bị đưa đi.
 "Vậy... có nghĩa là mọi chuyện đã được giải quyết rồi à?"
-"Đương nhiên." Acolyte cất Terminal đi với vẻ chắc chắn.
+"Đương nhiên." Acolyte cất Thiết bị đầu cuối đi với vẻ chắc chắn.
 "Hãy để Acolyte Phoebe lo. Cô ấy xử lý những chuyện này giỏi hơn ai hết."</t>
         </is>
       </c>
@@ -35119,7 +35067,7 @@
       <c r="M489" t="inlineStr">
         <is>
           <t>&lt;i&gt;Gửi ngài Claremont,
-Tôi thành thật xin lỗi vì đã chậm trễ liên lạc. Tôi đang phải giải quyết quá nhiều việc, đến mức không thể sắp xếp nổi. Với lòng nặng trĩu, tôi buộc phải báo cho ngài tin buồn này: đối tác của chúng ta, gia đình Marinos, đã bị &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; tấn công trên đường đến Liên bang New. Rất tiếc, họ đã không qua khỏi. Mong &lt;te href=850083&gt;Sentinel&lt;/te&gt; dẫn dắt linh hồn họ về nơi an nghỉ.
+Tôi thành thật xin lỗi vì đã chậm trễ liên lạc. Tôi đang phải giải quyết quá nhiều việc, đến mức không thể sắp xếp nổi. Với lòng nặng trĩu, tôi buộc phải báo cho ngài tin buồn này: đối tác của chúng ta, gia đình Marinos, đã bị &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; tấn công trên đường đến Liên bang Mới. Rất tiếc, họ đã không qua khỏi. Mong &lt;te href=850083&gt;Sentinel&lt;/te&gt; dẫn dắt linh hồn họ về nơi an nghỉ.
 Về khoản thanh toán cho lô hàng bị chìm, theo thỏa thuận trước đây, tôi đã bắt đầu thanh lý tài sản còn lại của gia đình Marino. Đây là biện pháp bất đắc dĩ. Ngài và tôi đều hiểu chúng ta đã đầu tư bao nhiêu vào thương vụ đó. Giờ đây, khi chẳng còn gì để duy trì, tôi chỉ còn cách cố gắng lấp đầy khoảng trống này bằng mọi giá.
 Ngài chắc vẫn còn nhớ Phoebe. Cô bé tội nghiệp đã mất cả cha lẫn mẹ. Giờ đây, em không còn nơi nào để về, mà tôi lại thường xuyên phải đi công tác, không thể chăm sóc em như em đáng được hưởng. Tôi nghe nói ngài có mối quan hệ thân thiết với một người họ hàng xa của gia đình Marinos, và tôi mong ngài có thể cân nhắc cho em một mái ấm...
 &lt;/i&gt;
@@ -35135,14 +35083,14 @@
 "...Tôi nghe nói gia đình Marinos vẫn chưa trả hết nợ. Chúng tôi không muốn các chủ nợ cứ đến gõ cửa nhà mình. Mong ngài thông cảm."
 ...
 "Chị Isabella đừng buồn nữa."
-Một cây kem bỗng được đưa ra trước mặt tôi. Một nhóm &lt;te href=850082&gt;Echoes&lt;/te&gt; nhỏ đã xuất hiện xung quanh mà tôi không hề hay biết, mỗi đứa đều cầm kem và kẹo dành cho khách du lịch. Chúng vây quanh tôi, hay đúng hơn là vây quanh Phoebe.
+Một cây kem bỗng được đưa ra trước mặt tôi. Một nhóm &lt;te href=850082&gt;Echo&lt;/te&gt; nhỏ đã xuất hiện xung quanh mà tôi không hề hay biết, mỗi đứa đều cầm kem và kẹo dành cho khách du lịch. Chúng vây quanh tôi, hay đúng hơn là vây quanh Phoebe.
 "Cháu biết người lớn bận rộn lắm, giống như bố mẹ cháu vậy. Họ luôn về nhà rất muộn."
 Tôi nhìn chằm chằm vào cây kem đang tan chảy, bất ngờ vì chính đứa trẻ nhỏ bé này lại đang an ủi &lt;i&gt;tôi&lt;/i&gt;.
 Gia đình Marinos, với lòng tốt của họ, đã giúp trại trẻ vượt qua thời kỳ đen tối nhất của Dark Tide. Thế mà giờ đây, tôi lại không thể tìm được một mái ấm tử tế cho con gái họ. Đáng lẽ em phải được mỉm cười trong vòng tay cha mẹ, sống một cuộc đời bình yên, hạnh phúc, không lo âu.
 "Không sao đâu ạ, cháu... có thể sống cùng mọi người mà. Cháu vui khi được ở bên mọi người."
 Khi tôi im lặng quá lâu, cô bé ngước lên nhìn tôi, nở một nụ cười dịu dàng, gần như an ủi. Tim tôi chợt thắt lại.
 "Mọi người sẽ ở bên nhau mãi phải không, chị Isabella? Các &lt;te href=850100&gt;Acolyte&lt;/te&gt; nói Sentinel luôn ở bên chúng ta, giữ cho chúng ta không bao giờ xa rời nhau."
-Em nói những lời ấy với sự chắc chắn đến kỳ lạ. Cuối cùng, tôi chỉ còn biết nuốt nước mắt, kìm Dodgen xúc động và ôm em thật chặt.
+Em nói những lời ấy với sự chắc chắn đến kỳ lạ. Cuối cùng, tôi chỉ còn biết nuốt nước mắt, kìm nén xúc động và ôm em thật chặt.
 "Được rồi... vậy chúng ta về nhà thôi. Về nhà nào."</t>
         </is>
       </c>
@@ -35227,26 +35175,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Cơn bão giữa đêm khuya dường như hút cạn từng giọt nước cuối cùng ở &lt;te href=850097&gt;Ragunna&lt;/te&gt;. Tia chớp lóe sáng trên bầu trời, đổ bóng hình mạng nhện lên cô bé đang cuộn tròn trong chăn.
-Phoebe không thể chợp mắt. Mỗi lần nhắm mắt lại, cô lại thấy biển cả cuộn trào dữ dội. Ở đó, một con tàu cô đơn sẽ không bao giờ trở về nhà, và cô đang chìm cùng với nó.
-Vào những đêm như thế này, cha cô thường lén đặt chiếc mề đay có chân dung của &lt;te href=850083&gt;Sentinel&lt;/te&gt; dưới gối, nói rằng Đấng Tối Cao sẽ dẫn dắt cô qua những cơn bão trong giấc mơ đến một bến bờ an toàn. Mẹ cô thì đặt một bó hoa cúc bên giường và kể cho cô nghe những câu chuyện trước khi ngủ. Bà thường nói rằng Sentinel phái các Thiên Sứ đến bảo vệ những đứa trẻ dũng cảm và tốt bụng như cô.
-Nhưng giờ đây, các &lt;te href=850100&gt;Acolytes&lt;/te&gt; chỉ vỗ đầu cô và nói rằng cô cũng giống như bao đứa trẻ khác. Mỗi &lt;te href=850096&gt;Rinascitan&lt;/te&gt; đều phải chịu đựng đau khổ trước khi có thể nhận được sự tha thứ của Sentinel vào cuối cùng.
-Có lần, khi Phoebe nhìn lén qua vai một Acolyte, cô lần đầu tiên nhìn thấy bức tượng uy nghi của Sentinel. Cái nhìn thoáng qua chiếc đuôi cá uốn lượn khổng lồ khiến cô hoảng sợ trong giây lát, nhưng bàn tay dịu dàng của Acolyte đặt lên vai và lời cầu nguyện nhẹ nhàng, vững chãi đã giúp trấn an trái tim đang run rẩy của cô.
-Cô được dẫn vào một căn phòng ấm áp, sáng sủa. Các Acolytes đối xử với cô rất tử tế, nhưng cô biết họ có lẽ thích những đứa trẻ không gây rắc rối hơn.
-Phoebe cố nhớ lại bài hát ru mà mẹ cô thường hát, cố gắng để giai điệu ấy vang lên trong tâm trí, át đi tiếng gào thét của cơn bão bên ngoài.
-Nhưng tiếng sấm sét và mưa không ngừng vẫn kéo cô trở lại đêm tối đó.
-Cô đã lén lên một con tàu buôn, nhìn qua ô cửa sổ khoang hàng để quan sát đường chân trời xa xăm. Khi bố mẹ cô trở về, cánh buồm của họ sẽ xuất hiện từ hướng đó. Cô không muốn chờ đợi thêm nữa. Lần này, cô sẽ dũng cảm và tự mình đi tìm họ.
-Nhưng biển cả không hề dịu dàng như mẹ cô miêu tả trong những câu chuyện. Cô bắt đầu nghe thấy tiếng bước chân vội vã trên boong tàu, tiếng ồn ào ngày càng trở nên hoảng loạn cho đến khi tiếng hét vang lên khi con tàu bị bão cuốn đi. Con tàu bắt đầu chìm.
-Phoebe gào khóc gọi bố mẹ, nhưng những con sóng dữ dội dường như thì thầm rằng họ sẽ không bao giờ trở lại.
-Nước biển lạnh giá nhấn chìm cô, và trong tầm nhìn mờ dần, cô nhìn thấy chiếc mề đay của cha mình biến mất vào bóng tối sâu thẳm của biển cả.
-Khi mở mắt ra lần nữa, cô đang nằm trên bờ biển, ướt sũng. Một &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; sáng lên trên chân cô. Những Acolytes tìm thấy cô nói rằng không ai có thể sống sót sau một vùng biển nguy hiểm như vậy, huống chi là một cô bé. Họ tin rằng đó là phước lành từ Sentinel.
-Nhưng Phoebe mờ nhạt nhớ rằng có thứ gì đó đã cứu cô. Một sự hiện diện dịu dàng như làn gió nhẹ, đã nâng cô lên mặt nước và đặt cô nhẹ nhàng lên bờ, thì thầm với cô...
-&lt;i&gt;Don't be afraid. Ta ở đây.&lt;/i&gt;
-Có gì đó kéo Phoebe ra khỏi giấc mơ. Cô cảm thấy chiếc giường hơi xê dịch, như thể có thứ gì đó mềm mại và mịn màng đã Dodgep vào bên cạnh cô. Nó mang theo hơi ẩm của mưa và mùi hương hoa cúc.
-Rồi Phoebe nhìn thấy đôi mắt cúc áo và đôi tai mềm mại, cụp xuống—đó là &lt;te href=850082&gt;Echo&lt;/te&gt; hoang lạc mà cô đã gặp ở Whisperwind Haven vào đầu ngày hôm đó. Cô đã gỡ sợi dây diều đang quấn lấy nó, và đặt tên cho nó là Brenno. Sau đó, Brenno giới thiệu Phoebe với nhiều người bạn của nó, đưa cô đi ngắm mây trên những sườn đồi, lau nước mắt cho cô, và thậm chí còn kết một vòng hoa xinh đẹp cho cô.
-&lt;i&gt;Đừng buồn nữa, Phoebe.&lt;/i&gt;
-Thân thể Plushie cảm thấy ấm áp và mềm mại. Trong cơn mơ màng, Phoebe cảm nhận được một sự hiện diện quen thuộc, mờ nhạt. Nó giống như làn gió.
-Cô vùi mặt vào bộ lông mềm mại của Plushie và từ từ chìm vào giấc ngủ bình yên.</t>
+          <t>Cơn bão giữa đêm khuya dường như muốn rút cạn từng giọt nước cuối cùng ở &lt;te href=850097&gt;Ragunna&lt;/te&gt;. Tia chớp lóe lên trên bầu trời, phủ bóng hình mạng nhện lên cô bé đang co ro trong chăn.</t>
         </is>
       </c>
     </row>
@@ -35339,28 +35268,28 @@
           <t>Khi Phoebe thức dậy, cô cảm thấy một vệt ẩm ướt còn vương ở khóe mắt.
 "Ơn đức của &lt;te href=850083&gt;Sentinel&lt;/te&gt;, lại một ngày mới để thức dậy và tỏa sáng!"
 Cô nhảy khỏi giường và nhanh chóng phủi phẳng chăn ga. Chiếc giường nhỏ từng gắn bó với tuổi thơ cô vẫn trông quen thuộc như ngày nào. Phoebe vỗ nhẹ vào má vài cái để xua đi cơn buồn ngủ còn sót lại trước khi lao vào công việc của ngày mới.
-Trại trẻ mồ côi sẽ tổ chức một buổi lễ nhỏ, và cô đã cùng với &lt;te href=850100&gt;Acolyte&lt;/te&gt; cấp trên giúp chuẩn bị. Đây sẽ là lần đầu cô trở lại kể từ khi trở thành Acolyte Tập Sự. Tối hôm trước, cô đã trò chuyện với các em nhỏ rất lâu. Có lẽ vì thế mà cô mới mơ về quá khứ.
+Trại trẻ mồ côi sẽ tổ chức một buổi lễ nhỏ, và cô đã cùng với &lt;te href=850100&gt;Tín Đồ&lt;/te&gt; cấp trên giúp chuẩn bị. Đây sẽ là lần đầu cô trở lại kể từ khi trở thành Tín Đồ Tập Sự. Tối hôm trước, cô đã trò chuyện với các em nhỏ rất lâu. Có lẽ vì thế mà cô mới mơ về quá khứ.
 Mọi người đều khen cô giờ đây trông thật chững chạc và trưởng thành. Cô không thể để họ thất vọng.
-Sau buổi cầu nguyện sáng, Phoebe bắt đầu chuẩn bị những vật dụng cần thiết cho buổi lễ. Cuộc sống của một Acolyte tuy bận rộn nhưng rất ý nghĩa. Với cô, việc theo sát kế hoạch và nhìn thấy thành quả khiến cô cảm thấy an tâm và hài lòng. Khi mặt trời lên cao, cô và các Acolyte khác đã biến căn phòng ăn đơn sơ thành một không gian rực rỡ sắc màu. Phoebe bày trà và bánh kẹo ra, nhìn những đứa trẻ mặc quần áo mới được giặt ủi cẩn thận bởi &lt;te href=850082&gt;Echoes&lt;/te&gt;, háo hức chạy đến vòng tay người chăm sóc để nhận những món quà được gói ghém kỹ lưỡng.
+Sau buổi cầu nguyện sáng, Phoebe bắt đầu chuẩn bị những vật dụng cần thiết cho buổi lễ. Cuộc sống của một Tín Đồ tuy bận rộn nhưng rất ý nghĩa. Với cô, việc theo sát kế hoạch và nhìn thấy thành quả khiến cô cảm thấy an tâm và hài lòng. Khi mặt trời lên cao, cô và các Tín Đồ khác đã biến căn phòng ăn đơn sơ thành một không gian rực rỡ sắc màu. Phoebe bày trà và bánh kẹo ra, nhìn những đứa trẻ mặc quần áo mới được giặt ủi cẩn thận bởi &lt;te href=850082&gt;Echoes&lt;/te&gt;, háo hức chạy đến vòng tay người chăm sóc để nhận những món quà được gói ghém kỹ lưỡng.
 Xúc động trước khung cảnh ấm áp này, Phoebe không khỏi mỉm cười.
 Cô nhớ lại cha mình luôn mua quà cho cô vào điểm dừng chân đầu tiên trong mỗi chuyến công tác. Mẹ cô thì luôn nghĩ ra một câu chuyện về món quà đó. Đôi khi là những cuộc phiêu lưu ly kỳ, đôi khi lại là những câu chuyện kể trước khi đi ngủ dịu dàng. Món quà yêu thích của cô là một con thỏ nhồi bông màu hồng. Trong câu chuyện, cô là một nhạc công thanh lịch.
 Khi những ký ức đau buồn của quá khứ dần phai mờ, Phoebe chỉ còn nhớ về những khoảnh khắc tươi sáng, hạnh phúc.
-Một Echoes nhỏ kéo tay áo cô, tự hào khoe quả bóng lớn mà nó vừa làm được. Theo bản năng, cô đưa tay vỗ nhẹ vào đầu nó.
-"Acolyte Tập Sự Phoebe!"
-Giọng nghiêm khắc của cấp trên khiến Phoebe giật mình. Cô vội rút tay lại, nhìn Echoes nhỏ lủi đi với vẻ buồn bã. Ánh mắt sắc bén của cấp trên như xuyên thấu tâm can cô.
+Một Echo nhỏ kéo tay áo cô, tự hào khoe quả bóng lớn mà nó vừa làm được. Theo bản năng, cô đưa tay vỗ nhẹ vào đầu nó.
+"Tín Đồ Tập Sự Phoebe!"
+Giọng nghiêm khắc của cấp trên khiến Phoebe giật mình. Cô vội rút tay lại, nhìn Echo nhỏ lủi đi với vẻ buồn bã. Ánh mắt sắc bén của cấp trên như xuyên thấu tâm can cô.
 "Nhân danh ơn đức của Sentinel, hãy nhớ vị trí của mình."
-...Cô vẫn chưa hoàn toàn thích nghi với vai trò mới. Là một Acolyte, cô không thể có những gắn bó thân thiết với Echoes.
-Sentinel đã dẫn dắt cô đến với những con người tốt bụng, cho cô cơm ăn áo mặc và mái nhà che đầu. Với những ân huệ đó, cô phải gánh vác trách nhiệm mới. Là một Acolyte, bổn phận của cô là báo đáp lòng tốt ấy.
+...Cô vẫn chưa hoàn toàn thích nghi với vai trò mới. Là một Tín Đồ, cô không thể có những gắn bó thân thiết với Echoes.
+Sentinel đã dẫn dắt cô đến với những con người tốt bụng, cho cô cơm ăn áo mặc và mái nhà che đầu. Với những ân huệ đó, cô phải gánh vác trách nhiệm mới. Là một Tín Đồ, bổn phận của cô là báo đáp lòng tốt ấy.
 Nhưng với tư cách là Phoebe, cô vẫn có thời gian riêng để gặp gỡ bạn bè.
 Bất giác, tay cô đưa lên chiếc mề đay đeo ở eo. Đó là phép màu nhỏ bé của riêng cô. Một bảo vật mà bạn bè đã giúp cô lấy lại từ đáy biển sâu.
 "Chị Phoebe ơi, bóng của con mắc trên cây rồi, không lấy xuống được. Jimmy bảo chị biết bay mà. Chị giúp con được không..."
-"Of course!"
+"Tất nhiên rồi!"
 Đứa trẻ kéo áo cô đã kéo Phoebe ra khỏi dòng suy nghĩ miên man. Cô gác lại những suy tư rối bời và trở lại với đám đông, đắm chìm trong công việc bận rộn của buổi lễ.
 Khi mặt trời bắt đầu lặn, sắc hoàng hôn dần trải dài trên bầu trời.
 Công việc trong ngày đã xong, đám đông đã giải tán, mọi thứ trở nên yên bình. Phoebe ngồi trên chiếc ghế dài, nhắm mắt lại và để làn gió biển nhẹ nhàng vỗ về. Thời gian như chậm lại.
 Dáng vẻ nhỏ bé của cô trông thật cô đơn dưới ánh hoàng hôn. Cấp trên của cô đến tìm, nhưng khi thấy hơi thở đều đều, bà nhận ra cô đã ngủ say.
-Khi cô gái ngủ say trên ghế, những Echoes nhỏ lặng lẽ tiến đến và quây quần bên cô.
-Acolyte cấp trên thở dài, quay lưng đi để cô được yên.
+Khi cô gái ngủ say trên ghế, những Echo nhỏ lặng lẽ tiến đến và quây quần bên cô.
+Tín Đồ cấp trên thở dài, quay lưng đi để cô được yên.
 "Lần này... ta sẽ coi như không thấy gì."</t>
         </is>
       </c>
@@ -35445,7 +35374,7 @@
 Ngồi trên vai bố, cô ngước nhìn những con Wingray bay lượn trên bầu trời, trong khi những dải băng rực rỡ và cánh hoa rơi như mưa, tiếng reo hò vang dội khắp nơi. Nhưng ký ức tuổi thơ ấy giờ chỉ còn là những mảnh mờ nhạt, khó níu giữ. Mỗi khi nghĩ về Carnevale, cô chỉ còn nhớ đến ánh sáng dịu nhẹ và tiếng vọng xa xăm.
 Dù vậy, cô vẫn nhớ rõ nụ cười của bố mẹ. Tiếng cười ấy xuất phát từ tận đáy lòng. Những ký ức từng khiến cô đau đớn giờ lại lấp lánh sâu thẳm trong tâm hồn.
 Những cảnh tượng chỉ còn hiện hữu trong giấc mơ giờ đây lại hiện ra trước mắt.
-Cô đứng giữa đám đông, nhìn người anh hùng tóc đen chìm trong ánh sáng khi vòng nguyệt quế vàng từ từ hạ xuống, đặt lên đầu {Male=anh;Female=cô} ấy.
+Cô đứng giữa đám đông, nhìn người anh hùng tóc đen chìm trong ánh sáng khi vòng nguyệt quế vàng từ từ hạ xuống, đặt lên đầu {Male=he;Female=she} ấy.
 Tim cô như ngừng đập. Giữa tiếng reo hò, ánh mắt cô không thể rời khỏi luồng sáng vàng ấy.
 "Đó là &lt;te href=850103&gt;Laureate&lt;/te&gt;!"
 "Tôn vinh &lt;te href=850105&gt;Imperator&lt;/te&gt;!"
@@ -35453,9 +35382,9 @@
 Nước mắt nhòa đi trong tiếng khóc hạnh phúc.
 Ai mà không xúc động trước cảnh tượng rực rỡ như vậy? Ngay cả Thần Linh cũng ban phép màu cho khoảnh khắc này. Trong giây phút ấy, Phoebe không khỏi thắc mắc: làm sao Sentinel lại có thể tức giận khi mọi người ăn mừng Carnevale? Chắc chắn Sentinel cũng yêu Carnevale và niềm vui của mọi người.
 Bóng tối mờ nhạt ám ảnh tâm trí cô kể từ khi trở về từ Atrium of Reflections lại hiện lên, nhưng nhanh chóng bị cuốn trôi bởi tiếng hát và tiếng cười.
-Nhưng lần này, Phoebe quyết bám lấy mảnh nghi ngờ thoáng qua ấy. Những điều cô đã nhận ra, nhưng lại gạt đi. Những câu hỏi đã nảy sinh, nhưng cô Dodge.
+Nhưng lần này, Phoebe quyết bám lấy mảnh nghi ngờ thoáng qua ấy. Những điều cô đã nhận ra, nhưng lại gạt đi. Những câu hỏi đã nảy sinh, nhưng cô né tránh.
 Phoebe chớp mắt thật mạnh, lau đi những giọt nước mắt còn đọng ở khóe mắt. Cô lại hướng ánh nhìn về phía người đang bị đám đông vây quanh.
-Cô có linh cảm rằng {Male=anh;Female=cô} ấy có thể giải đáp những thắc mắc của mình.
+Cô có linh cảm rằng {Male=he;Female=she} ấy có thể giải đáp những thắc mắc của mình.
 Và một ngày nào đó, cô sẽ tìm ra sự thật đằng sau nghi ngờ ấy.</t>
         </is>
       </c>
@@ -35532,14 +35461,14 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Đã quá nửa đêm, ánh đèn trong các cửa hiệu đã tắt lịm, để lại thành phố sôi động &lt;te href=850097&gt;Ragunna&lt;/te&gt; chìm trong sự trang nghiêm và tĩnh lặng. Ngay cả Signor Octopus trên tháp chuông cũng như đã chìm vào giấc mộng. À, nếu &lt;te href=850082&gt;Echoes&lt;/te&gt; có thể mơ được thì thế.
+          <t>Đã quá nửa đêm, ánh đèn trong các cửa hiệu đã tắt lịm, để lại thành phố sôi động &lt;te href=850097&gt;Ragunna&lt;/te&gt; chìm trong sự trang nghiêm và tĩnh lặng. Ngay cả Ngài Bạch Tuộc trên tháp chuông cũng như đã chìm vào giấc mộng. À, nếu &lt;te href=850082&gt;Echoes&lt;/te&gt; có thể mơ được thì thế.
 "Có vẻ đêm nay không còn khách nào nữa," Margherita ngáp dài. "Thôi, dọn dẹp xong rồi về nhà thôi."
-"Chào Margherita. Như thường lệ nhé. Một ly Nectarwine và khoai tây chiên. Bổ Sung mứt gemberry và tiêu đen. Cảm ơn"
+"Chào Margherita. Như thường lệ nhé. Một ly Nectarwine và khoai tây chiên. Thêm mứt gemberry và tiêu đen. Cảm ơn."
 Margherita bất động khi nghe giọng nói quen thuộc đột ngột vang lên sau lưng. Giọng nói ấy mang theo sự mệt mỏi đến rã rời, như thể linh hồn của chủ nhân đã bị &lt;te href=850105&gt;Imperator&lt;/te&gt; cuốn đi, chỉ còn lại một cái xác không hồn. Với bất kỳ ai không quen thuộc với Ragunna, giọng nói vô hồn ấy có thể khiến họ phải bỏ chạy.
 "Lâu rồi không thấy chị ghé qua, chị Zani," Margherita nói, vẫn tập trung quét những mẩu vụn bánh pizza trong lò. "Vừa tan làm à? Dạo này chị bận lắm hả?"
-"À, cũng tạm," Zani đáp, ánh mắt dán chặt vào quầy như đang nhìn một đống báo cáo vừa in xong chứ không phải những chiếc bánh pizza thơm ngon. "Chị biết đấy, &lt;te href=850102&gt;Carnevale&lt;/te&gt; sắp tới rồi, &lt;te href=850135&gt;Bank&lt;/te&gt; làm việc gấp ba lần bình thường. Dù có thế nào thì khối lượng công việc cũng chẳng bao giờ giảm đâu."
+"À, cũng tạm," Zani đáp, ánh mắt dán chặt vào quầy như đang nhìn một đống báo cáo vừa in xong chứ không phải những chiếc bánh pizza thơm ngon. "Chị biết đấy, &lt;te href=850102&gt;Carnevale&lt;/sắp tới rồi, &lt;te href=850135&gt;Ngân Hàng&lt;/te&gt; làm việc gấp ba lần bình thường. Dù có thế nào thì khối lượng công việc cũng chẳng bao giờ giảm đâu."
 "Với chúng ta, những người &lt;te href=850101&gt;Montelli&lt;/te&gt;, Carnevale vừa là cơ hội vừa là thách thức," Zani nhớ lại lời Alberto khi giao nhiệm vụ cho cô. "Vì tương lai của Ragunna, tất cả chúng ta đều phải đóng vai trò của mình."
-Với Zani, những lời đó nghe thật rỗng tuếch. Cô làm việc cho Bank vì họ trả lương cho cô. Cô không phải diễn viên để "đóng vai trò" gì cả. Dù vậy, cô phải thừa nhận rằng vị khách mà cô được giao bảo vệ đã khơi dậy một chút tò mò trong lòng. Mùi thơm phức của khoai tây chiên trong chảo khiến bụng cô réo lên phản đối.
+Với Zani, những lời đó nghe thật rỗng tuếch. Cô làm việc cho Ngân Hàng vì họ trả lương cho cô. Cô không phải diễn viên để "đóng vai trò" gì cả. Dù vậy, cô phải thừa nhận rằng vị khách mà cô được giao bảo vệ đã khơi dậy một chút tò mò trong lòng. Mùi thơm phức của khoai tây chiên trong chảo khiến bụng cô réo lên phản đối.
 "Sáng mai nên ăn gì nhỉ?" cô tự hỏi. "Bánh kếp sáng nay lạnh ngắt, ăn vào còn đau bụng. Hay là cháo trứng nướng... À, và nhất định phải thêm hai thìa đường..."
 Đúng lúc đó, một tiếng nứt nhỏ xé toạc không khí đêm khuya. Margherita, đang bận rộn với chảo chiên, không hề để ý. Có lẽ cả thành phố Ragunna đang say giấc cũng không ai nghe thấy. Nhưng Zani thì có. Cô ngẩng đầu lên và thấy một bóng đen lướt qua mái nhà. Tiếng động phát ra từ một viên ngói bị giẫm vỡ bởi bước chân bất cẩn của hắn.
 Carnevale thu hút không chỉ khách du lịch tuân thủ pháp luật. Với một tiếng thở dài cam chịu, Zani rút ví ra và đặt vài &lt;te href=850104&gt;Shell Credit&lt;/te&gt; lên quầy. Vậy là bữa ăn khuya coi như tiêu rồi.
@@ -35621,7 +35550,7 @@
           <t>"Đúng rồi, nhà Figaro bảo họ đã thanh toán từ ba ngày trước. Người bảo lãnh 'đáng kính' của họ? Biến mất như chưa từng tồn tại. Giờ họ lại cố biến bằng chứng mỏng manh này thành lỗi sổ sách của chúng ta." Zani nhún vai, giọng điệu bình thản như đang trò chuyện với Thanh Kiếm Acorus trong vườn. "Ừ. Rõ ràng họ đang muốn moi tiền chúng ta. Một chiêu cũ rích từ thời Ragunnesi còn bắt cá trên Gondola. Không sao, tôi sẽ 'thương lượng' với họ. Được rồi, thế là xong. Ciao."
 Zani cúp máy, kẹp sổ cái dưới nách rồi bước ra khỏi văn phòng. Phía sau, những lời thì thầm khe khẽ lan truyền khắp nơi làm việc. Không phải đồng nghiệp nghi ngờ khả năng của cô. Họ đều biết quá rõ kết cục sẽ ra sao. Một chuyện nhỏ nhặt thế này chẳng bao giờ lên trang nhất báo đâu. Tối đa, nó chỉ được nhét vào góc cuối một cột, bên cạnh mấy tin tìm người thất lạc và quảng cáo rẻ tiền. Báo chí chắc chắn sẽ không nhắc đến Zani hay gia tộc &lt;te href=850101&gt;Montelli&lt;/te&gt;. Có chăng chỉ là một bản tin ngắn về mấy thành viên nhà Figaro bị thương do giàn giáo đổ gần tháp đồng hồ, hay việc gia trưởng Figaro hào phóng tài trợ nghệ thuật cho đối tác kinh doanh trung thành của họ – gia tộc Montelli.
 Zani có phải nhân viên xuất sắc nhất ngân hàng không? Không cần bàn cãi.
-Thành tích công việc của cô thường khiến nhân viên mới tò mò. Ngày nào cô cũng làm việc đến khuya, đến công ty với đôi mắt thâm quầng vì kiệt sức. Ngoài ra, cô còn đảm nhận những công việc nguy hiểm nhất ngoài hiện trường mà chưa bao giờ làm hỏng một nhiệm vụ nào. Các nhân viên lâu năm nhắc về cô với giọng kính cẩn, gần như coi cô như một vị thần toàn năng. Người ta đồn rằng nếu giao cho cô bắt &lt;te href=850106&gt;Cetus the Tidebreaker&lt;/te&gt; chỉ với một sợi mì ướt, sáng hôm sau cô sẽ mang con 'cá voi nhỏ' đó về đúng giờ, như thể chỉ là một phần pizza giao tận nơi.
+Thành tích công việc của cô thường khiến nhân viên mới tò mò. Ngày nào cô cũng làm việc đến khuya, đến công ty với đôi mắt thâm quầng vì kiệt sức. Ngoài ra, cô còn đảm nhận những công việc nguy hiểm nhất ngoài hiện trường mà chưa bao giờ làm hỏng một nhiệm vụ nào. Các nhân viên lâu năm nhắc về cô với giọng kính cẩn, gần như coi cô như một vị thần toàn năng. Người ta đồn rằng nếu giao cho cô bắt &lt;te href=850106&gt;Cetus Kẻ Phá Thủy Triều&lt;/te&gt; chỉ với một sợi mì ướt, sáng hôm sau cô sẽ mang con 'cá voi nhỏ' đó về đúng giờ, như thể chỉ là một phần pizza giao tận nơi.
 Cô làm thế nào? Không ai biết.
 Một số nhân viên mới háo hức bắt chước mọi hành động và thói quen của Zani, tin rằng đó là chìa khóa dẫn đến sự xuất sắc của cô. Họ để ý cô lúc nào cũng có một lon nước tăng lực bên người và cho rằng đó chính là nguồn gốc sức mạnh siêu nhiên của cô, như nấm Heliobane Fungia đối với thủy thủ Riccioli trong một bộ truyện tranh cũ. Thế là họ nốc nước tăng lực ừng ực, tin rằng nó sẽ giúp họ thức trắng đêm và hoàn thành những dự án huyền thoại như Zani. Nhưng thường thì họ chỉ thấy mình gục trên bàn làm việc, đau nhức vì ngủ gục trên ghế, rồi bị cấp trên mắng vì làm việc kém hiệu quả vào ngày hôm sau.
 Cô đang nghĩ gì? Không ai biết.
@@ -35707,17 +35636,17 @@
       <c r="M495" t="inlineStr">
         <is>
           <t>Zani có lẽ đã mơ. Hoặc có thể không. Nếu có, giấc mơ ấy đã trôi khỏi tâm trí cô nhẹ nhàng như bơ chảy. Cô mở mắt, tắt chiếc đồng hồ báo thức vẫn đang réo inh ỏi bên gối.
-Ánh sáng buổi sáng len lỏi qua khung cửa sổ, viền những đường Dodget của tấm thảm dưới sàn bằng một vệt vàng dịu dàng. Cô dành một phút để ép bản thân hoàn toàn tỉnh táo, và ngay khi đó, mảnh vỡ cuối cùng của giấc mơ tan biến vào hư vô.
+Ánh sáng buổi sáng len lỏi qua khung cửa sổ, viền những đường nét của tấm thảm dưới sàn bằng một vệt vàng dịu dàng. Cô dành một phút để ép bản thân hoàn toàn tỉnh táo, và ngay khi đó, mảnh vỡ cuối cùng của giấc mơ tan biến vào hư vô.
 Dù sao thì cũng chẳng quan trọng. Có lẽ đó cũng chẳng phải giấc mơ đẹp đẽ gì.
 Với đống công việc làm thêm gần đây, ngay cả những giấc mơ của Zani cũng trở nên vô nghĩa và rời rạc, thường chỉ là mớ hỗn độn những công việc dở dang lướt qua tâm trí. Chẳng có lối thoát nào khỏi áp lực khi tỉnh táo, vậy tại sao cô lại mong tìm thấy điều đó trong giấc mơ?
 "Thôi, đủ rồi. Tôi còn việc quan trọng phải làm." Zani vỗ nhẹ vào má để kéo mình ra khỏi dòng suy nghĩ. Cô biết mình cần xử lý nhiệm vụ này thật tốt nếu muốn nhận được kỳ nghỉ có lương mà cấp trên đã hứa.
-Đứng trước gương, cô chỉnh đốn trang phục một cách tỉ mỉ, kéo cà vạt cho thật ngay ngắn. Cô không biết nhiều về vị khách bí ẩn kia. Tất cả những gì Zani biết là {Male=anh ấy;Female=cô ấy} sở hữu một &lt;te href=850082&gt;Echo&lt;/te&gt; rất đặc biệt, và gia đình đã cung cấp cho {Male=anh ấy;Female=cô ấy} một khoản tiền kha khá.
+Đứng trước gương, cô chỉnh đốn trang phục một cách tỉ mỉ, kéo cà vạt cho thật ngay ngắn. Cô không biết nhiều về vị khách bí ẩn kia. Tất cả những gì Zani biết là {Male=sir;Female=miss} sở hữu một &lt;te href=850082&gt;Echo&lt;/te&gt; rất đặc biệt, và gia đình đã cung cấp cho {Male=anh ấy;Female=cô ấy} một khoản tiền kha khá.
 Không hiểu sao, cô cảm thấy có điều gì đó không đơn giản. Có lẽ chỉ là cảm giác bất an còn vương lại từ giấc mơ kỳ lạ đó, nhưng cô không thể phủ nhận cảm giác rằng những gì cô và vị khách này làm trong vài ngày tới sẽ quyết định số phận của nhiều người ở Ragunna.
 "Hừ, thôi nào. Tôi chỉ là một nhân viên bình thường." Bình thường đến mức nếu một tấm biển quảng cáo ở khu &lt;te href=850101&gt;Montelli&lt;/te&gt; đổ xuống, cô sẽ bị đè bẹp cùng với cả chục người khác. Zani lấy áo choàng từ giá treo và khoác lên vai, như mọi buổi sáng.
 Cô ngáp một cái. May mà không có đồng nghiệp nào nhìn thấy.
 Hôm nay cô không bị giao quá nhiều việc. Ông Alberto bảo cô có thể về ngay sau khi giúp vị khách quý mặc đồ đen hoàn tất công việc tại &lt;te href=850135&gt;Ngân hàng&lt;/te&gt;. Sau đó, trách nhiệm duy nhất của cô là bảo vệ và dẫn đường cho {Male=anh ấy;Female=cô ấy} cho đến khi &lt;te href=850102&gt;Carnevale&lt;/te&gt; kết thúc. Nghe có vẻ là nhiệm vụ dễ dàng.
 "Chỉ cần làm tốt công việc của mình là được." Zani hít một hơi sâu. Kỳ lạ thay, cô cảm thấy lo lắng, đuôi cô ve vẩy phía sau mà cô không hề hay biết.
-"Nếu {Male=anh ấy;Female=cô ấy} đến vào giờ ăn trưa, tôi sẽ gợi ý dùng bữa tại Trattoria Margherita để thưởng thức đặc sản của &lt;te href=850097&gt;Ragunna&lt;/te&gt;. Còn nếu {Male=anh ấy;Female=cô ấy} từ chối, tôi sẽ áp dụng phương án dự phòng," Zani nhanh chóng lướt qua lịch trình. "Chúng ta có thể ăn pizza ở tiệm bánh Bratta và tận hưởng buổi chiều thư giãn bên Whisperwind Haven..." Cô kiểm tra lại lịch trình hết lần này đến lần khác, chỉ cho phép mình thư giãn khi không còn lỗ hổng nào.
+"Nếu {Male=anh ấy;Female=cô ấy} đến vào giờ ăn trưa, tôi sẽ gợi ý dùng bữa tại Trattoria Margherita để thưởng thức đặc sản của Ragunna. Còn nếu {Male=anh ấy;Female=cô ấy} từ chối, tôi sẽ áp dụng phương án dự phòng," Zani nhanh chóng lướt qua lịch trình. "Chúng ta có thể ăn pizza ở tiệm bánh Bratta và tận hưởng buổi chiều thư giãn bên Whisperwind Haven..." Cô kiểm tra lại lịch trình hết lần này đến lần khác, chỉ cho phép mình thư giãn khi không còn lỗ hổng nào.
 Một nụ cười nhẹ nhàng nở trên khóe môi cô. Kia rồi, qua cánh cổng ngân hàng, cô nhìn thấy vị khách quý kia, mặc đồ đen, với đôi mắt vàng lấp lánh. Đúng như cô đã mong đợi.
 "Chúng tôi đã đợi {PlayerName} đến. Chào mừng đến với &lt;te href=850107&gt;Ngân hàng Averardo&lt;/te&gt;, {Male=thưa ngài;Female=thưa cô}."</t>
         </is>
@@ -35792,15 +35721,15 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>"Bạn có nghe chưa? Vị Giám đốc mới của &lt;te href=850085&gt;Bộ Phát triển&lt;/te&gt;, Cục Quốc phòng chẳng để lọt bất cứ thứ gì đâu!" Tin đồn này lan nhanh khắp &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, nhanh chóng trở thành đề tài nóng bỏng của thành phố.
-Bộ Phát triển đã đặt một lô vật liệu để xây dựng tuyến phòng thủ mới, nhưng một container lại chứa hàng kém chất lượng không nhãn mác. Để làm mọi chuyện thêm rắc rối, lô hàng này có tới ba nhà sản xuất khác nhau, và không bên nào chịu nhận trách nhiệm về lỗi.
-"Giám đốc Taoqi, cô phải giúp chúng tôi giải quyết chuyện này. Bộ Phát triển không thể vu khống người vô tội được!"
-Ba đại diện lên tiếng, giọng điệu ngày càng lớn hơn trong nỗ lực thu hút sự chú ý.
-Taoqi bình tĩnh vượt qua đám đông ồn ào, khéo léo từ chối những lời phàn nàn của các đại diện. "Được rồi, được rồi, tôi hiểu rồi," dù thực ra cô chẳng mấy quan tâm đến lời họ nói. Sau đó, cô cúi xuống kiểm tra container không nhãn mác. Xem xét một vài món vật liệu, Taoqi dường như đã nảy ra ý tưởng. Với giọng điệu thoải mái, cô quay sang ba đại diện và nói: "Nhưng có vẻ như một trong các anh đang nói dối. Hoặc có lẽ, cả ba anh đều vậy."
-Sau đó, Taoqi cùng trợ lý Xiaoyu bí mật đến thăm ba nhà máy sản xuất. Họ thu thập manh mối về máy móc, tuyến đường vận chuyển được sử dụng vào tối hôm đó và lịch trình giao hàng. Với những thông tin này, Taoqi đã giải được câu đố và đảm bảo những kẻ gian dối sẽ phải chịu hậu quả.
-Chỉ trong vài ngày, tin đồn lan khắp thành phố. Một trong ba đại diện đã bị Giám đốc Taoqi của Bộ Phát triển thẩm vấn. Sau đó, tin tức về việc đại diện thứ hai bị bắt tiếp tục xuất hiện, rồi đến người cuối cùng. Cuối cùng, Jinzhou News đưa tin về việc họ thông đồng cung cấp vật liệu kém chất lượng. Công chúng vô cùng sửng sốt, trong khi chỉ có Taoqi và Xiaoyu biết sự thật.
-"Tôi biết rồi! Đ-đây chính là tình huống tiến thoái lưỡng nan của tù nhân điển hình! Cô đã gọi một người vào 'nói chuyện riêng' trước, rồi đảm bảo hai người kia biết chuyện xảy ra. Tất cả chỉ để gây áp lực buộc họ phản bội và tố cáo lẫn nhau, phải không? Nhưng làm sao cô biết được họ đều đang nói dối?"
-"Con người có thể nói dối, nhưng máy móc thì không. Mỗi nhà máy có thông số máy móc riêng. Câu trả lời đã rõ ràng khi tôi kiểm tra những món vật liệu đó. Ừ thì... cũng tốn mất mấy bữa trưa của tôi đấy." Taoqi than thở khi kéo chiếc mặt nạ ngủ xuống, quyết tâm bù lại những giấc trưa đã mất.</t>
+          <t>"Cậu nghe chưa? Vị Giám đốc mới của Bộ Phát triển, Cục Quốc phòng này, không để lọt bất cứ thứ gì đâu!" Tin đồn lan nhanh khắp &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, nhanh chóng trở thành đề tài nóng hổi của thành phố.
+Bộ Phát triển đã đặt một lô vật liệu để xây dựng tuyến phòng thủ mới, nhưng một thùng hàng lại chứa toàn đồ không nhãn mác, chất lượng kém. Để làm mọi chuyện thêm rắc rối, lô hàng này lại có tới ba nhà sản xuất khác nhau, không ai chịu nhận trách nhiệm về lỗi đó.
+"Giám đốc Đào Kỳ à, cô phải giúp chúng tôi phân xử vụ này. Bộ Phát triển không thể vu cáo người vô tội được!"
+Ba đại diện lên tiếng, giọng điệu ngày càng lớn để thu hút sự chú ý.
+Đào Kỳ bình tĩnh luồn lách qua đám đông ồn ào, nhẹ nhàng gạt những lời phàn nàn của họ sang một bên. "Được rồi, được rồi, tôi hiểu rồi," dù thực ra cô chẳng mấy quan tâm đến lời họ nói. Rồi cô cúi xuống kiểm tra thùng hàng không nhãn mác. Sau khi xem xét vài món đồ một lúc, Đào Kỳ như đã nảy ra ý gì đó. Cô quay sang ba đại diện với giọng điệu thoải mái: "Nhưng có vẻ như một trong các anh đang nói dối. Hoặc có khi cả ba đều thế."
+Sau đó, Đào Kỳ cùng cấp dưới của mình, Tiểu Vũ, bí mật đến thăm ba nhà máy sản xuất. Họ thu thập manh mối về máy móc, tuyến đường vận chuyển đêm đó và lịch giao hàng. Với những thông tin này, Đào Kỳ đã giải được câu đố và đảm bảo những kẻ gian dối sẽ phải chịu hậu quả.
+Chỉ trong vài ngày, tin đồn lan khắp thành phố. Một trong ba đại diện bị Giám đốc Đào Kỳ của Bộ Phát triển thẩm vấn. Rồi tin tức về việc đại diện thứ hai bị bắt, sau đó là người cuối cùng. Cuối cùng, báo Jinzhou đăng tải bài viết vạch trần âm mưu cung cấp vật liệu kém chất lượng của họ. Công chúng sững sờ, nhưng chỉ có Đào Kỳ và Tiểu Vũ biết sự thật.
+"Tớ biết rồi! Đây... đây chính là bài toán tù nhân kinh điển! Cô gọi một người vào 'nói chuyện riêng' trước, rồi đảm bảo hai người kia biết chuyện. Tất cả chỉ để gây áp lực, khiến họ phản bội và tố cáo lẫn nhau, phải không? Nhưng làm sao cô biết được cả ba đều nói dối?"
+"Con người có thể nói dối, nhưng máy móc thì không. Mỗi nhà máy có thông số máy móc riêng. Câu trả lời đã rõ ràng khi tôi kiểm tra những món đồ đó. Thôi được... cũng mất mấy bữa trưa của tôi đấy." Đào Kỳ càu nhàu khi kéo mặt nạ ngủ xuống, quyết tâm bù lại những giấc ngủ trưa đã mất.</t>
         </is>
       </c>
     </row>
@@ -35889,11 +35818,11 @@
 Đường phố nhộn nhịp với những gánh hàng sáng, dòng người đi làm đã xếp hàng dài. Người thì để tiền rồi vội vàng lấy túi bánh bao, kẻ thì hối hả lao đi làm. Chủ hàng không cần phải rao to, ai cũng muốn nhanh chóng có bữa sáng rồi lên đường.
 Jinzhou, sau một đêm nghỉ ngơi, lại bừng tỉnh sức sống.
 Giữa dòng người tấp nập, Đào Kỳ bước ra với dáng vẻ thong dong. Miếng che mắt vẫn còn trên trán, thỉnh thoảng cô lại ngáp, trông như chưa tỉnh hẳn.
-"Hmm... xếp hàng nào nhỉ?"
+"Hừm... xếp hàng nào nhỉ?"
 Vò mắt một lúc, Đào Kỳ quan sát từng hàng rồi lẩm nhẩm đếm: "Ba, hai, một..."
 Vừa đếm xong, người đứng đầu hàng cũng vừa cầm túi bánh bao nóng hổi rời đi.
 Đào Kỳ dường như đang tính thời gian hấp bánh ở mỗi hàng. Sau khi kiểm tra giờ và số người trong hàng, cô quyết định chọn.
-"Hmm... Tốt rồi. Hôm nay chắc không muộn đâu."
+"Hừm... Tốt rồi. Hôm nay chắc không muộn đâu."
 Đào Kỳ nhịp nhàng vỗ tay theo nhịp đếm thời gian. Khi hàng tiến lên, cô nhận ra nhịp "ba, hai, một" của mình hơi nhanh hơn tốc độ xếp hàng.
 "Ơ? Xem ra vẫn muộn mất thôi."
 Đào Kỳ quyết tâm phải chấm công đúng giờ, nhưng nhịp đếm của cô không khớp với tốc độ hàng. Cô kiểm tra lại nhịp vỗ tay, vẫn chính xác. Hay là chủ hàng làm chậm? Cô quan sát kỹ, thấy tay họ thoăn thoắt. Không hiểu sao lại không khớp. Thời gian trôi qua, cô thực sự cần đến chỗ làm đúng giờ.
@@ -35986,7 +35915,7 @@
       <c r="M498" t="inlineStr">
         <is>
           <t>Dù vẻ ngoài của Taoqi có vẻ lười biếng, như thể cô có thể ngủ gật bất cứ lúc nào, nhưng cô luôn hoàn thành mọi việc một cách hoàn hảo.
-"Liệu chị Taoqi lại ngủ gật rồi không nhỉ?" Những tân binh ở Ministry of Development thường hay nghi ngờ như vậy. Trong những tình huống đó, đồng nghiệp quen biết Taoqi luôn trấn an họ rằng cô thực sự là một lãnh đạo rất đáng tin cậy.
+"Liệu chị Taoqi lại ngủ gật rồi không nhỉ?" Những tân binh ở Bộ Phát Triển thường hay nghi ngờ như vậy. Trong những tình huống đó, đồng nghiệp quen biết Taoqi luôn trấn an họ rằng cô thực sự là một lãnh đạo rất đáng tin cậy.
 "Chị Taoqi, xin lỗi đã làm phiền, nhưng em đã cố tối ưu kế hoạch xây dựng này một thời gian rồi mà vẫn chưa ra được..." Trong thời gian rảnh, Taoqi thường bị các đồng nghiệp trẻ tìm đến để xin lời khuyên.
 "Hmm... trễ rồi. Hôm nay đến đây thôi. Đi dạo một chút nhé. Nghe nói có quán ăn mới ngon lắm. Đi thử không?"
 "Ơ, ơ... xin lỗi chị?" Các đàn em thường không theo kịp những thay đổi đề tài đột ngột của cô.
@@ -36000,7 +35929,7 @@
 "Đúng vậy."
 "Phải làm việc chăm chỉ hơn để trả nợ thế chấp, nhưng nghĩ đến điều đó là em lại thấy áp lực quá... Cảm giác như bị rút hết sức lực vậy..."
 "Em cũng thế..."
-"Sigh... Thời gian trôi nhanh quá. Đến lúc phải quay lại làm việc rồi..."
+"Thở dài... Thời gian trôi nhanh quá. Đến lúc phải quay lại làm việc rồi..."
 Có lẽ sự phổ biến của phòng trò chuyện này đơn giản chỉ vì đây là nơi để những người trẻ tuổi trút bầu tâm sự và tìm thấy sự an ủi từ nhau.
 Còn với Taoqi, cô chỉ cần là một người lắng nghe kiên nhẫn, thấu hiểu những lo lắng của họ và đưa ra lời khuyên khi cần thiết để nhẹ nhàng giảm bớt gánh nặng cho họ.</t>
         </is>
@@ -36096,7 +36025,7 @@
 "Tôi tưởng chị Taoqi lúc nào cũng thong dong vậy chứ?"
 "Đúng rồi. Nhưng hồi nhỏ chị ấy khác lắm! Nhớ hồi đó chị ấy cứ bám theo tụi mình khắp nơi. Giờ thì cứ thấy thảnh thơi thế này, kỳ lạ thật. Ngày xưa còn lạc đường rồi khóc vì bị bỏ lại nữa cơ."
 "Chị ấy còn bị bắt nạt nữa..."
-"Oh really? Không thể tin chị Taoqi từng trải qua chuyện đó..."
+"Thật á? Không thể tin chị Taoqi từng trải qua chuyện đó..."
 "Haha, chắc chắn là không tin được rồi. Và đó là lúc tụi tôi, những người bạn thân của chị ấy, ra tay. Đánh cho bọn kia một trận nhớ đời!"
 "Ồ... Thế chị Taoqi làm gì?"
 "Ờm... Chị ấy hỗ trợ hậu cần? Kiểu như mách bố mẹ bọn nó, thương lượng bồi thường và mấy thứ tương tự."
@@ -36271,7 +36200,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Diệt trừ mọi cái ác quả là một nhiệm vụ nặng nề. Ngã tư sương mù kia hóa ra chỉ là một trạm trung chuyển, nhưng Danjin không hề nản lòng. Dù chỉ là tiến bộ nhỏ, nhưng vẫn là tiến bộ, hơn nữa cô còn giải cứu được mấy đứa trẻ bị bắt cóc trên đường. Sau khi đưa bọn trẻ về Patrol Station, Danjin thở phào nhẹ nhõm và quyết định trở về thành phố để nghỉ ngơi cho đỡ mệt.
+          <t>Diệt trừ mọi cái ác quả là một nhiệm vụ nặng nề. Ngã tư sương mù kia hóa ra chỉ là một trạm trung chuyển, nhưng Danjin không hề nản lòng. Dù chỉ là tiến bộ nhỏ, nhưng vẫn là tiến bộ, hơn nữa cô còn giải cứu được mấy đứa trẻ bị bắt cóc trên đường. Sau khi đưa bọn trẻ về Trạm Tuần Tra, Danjin thở phào nhẹ nhõm và quyết định trở về thành phố để nghỉ ngơi cho đỡ mệt.
 Cô thong thả bước trên con phố được trang hoàng rực rỡ bởi đèn lồng lễ hội và ánh sáng ấm áp. Trăng sáng vằng vặc trên cao, tô điểm thêm cho bầu không khí huyền ảo của đêm.
 Nhiều năm trước, vào một đêm trăng sáng như thế này, gia đình cô đã có những khoảnh khắc quý giá bên nhau. Mẹ cô đã chuẩn bị một bàn đầy những món ăn ngon miệng, còn cô em gái thì vui vẻ đưa ra hai miếng &lt;te href=850115&gt;Bánh Phồng Râu Rồng&lt;/te&gt;, một cho em, một cho chị Danjin.
 "C-chị ơi, cái này cho chị..."
